--- a/grupos/1CV - Estadisticos 20231.xlsx
+++ b/grupos/1CV - Estadisticos 20231.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="511" uniqueCount="177">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="507" uniqueCount="174">
   <si>
     <t>Materia</t>
   </si>
@@ -155,9 +155,6 @@
     <t>RAMIREZ MOLINA AIDE SCARLET</t>
   </si>
   <si>
-    <t>RODRIGUEZ GUEVARA ANIELA SAMANTA</t>
-  </si>
-  <si>
     <t>SALAZAR DE JESUS DAFNE DANAE</t>
   </si>
   <si>
@@ -332,30 +329,30 @@
     <t>RAMIREZ</t>
   </si>
   <si>
+    <t>SAN JUAN</t>
+  </si>
+  <si>
+    <t>SANCHEZ</t>
+  </si>
+  <si>
+    <t>SALAZAR</t>
+  </si>
+  <si>
+    <t>TEXCAHUA</t>
+  </si>
+  <si>
+    <t>VEGA</t>
+  </si>
+  <si>
+    <t>VELA</t>
+  </si>
+  <si>
+    <t>SANTOS</t>
+  </si>
+  <si>
     <t>RODRIGUEZ</t>
   </si>
   <si>
-    <t>SAN JUAN</t>
-  </si>
-  <si>
-    <t>SANCHEZ</t>
-  </si>
-  <si>
-    <t>SALAZAR</t>
-  </si>
-  <si>
-    <t>TEXCAHUA</t>
-  </si>
-  <si>
-    <t>VEGA</t>
-  </si>
-  <si>
-    <t>VELA</t>
-  </si>
-  <si>
-    <t>SANTOS</t>
-  </si>
-  <si>
     <t>MACUIXTLE</t>
   </si>
   <si>
@@ -422,9 +419,6 @@
     <t>MOLINA</t>
   </si>
   <si>
-    <t>GUEVARA</t>
-  </si>
-  <si>
     <t>AGUILAR</t>
   </si>
   <si>
@@ -525,9 +519,6 @@
   </si>
   <si>
     <t>AIDE SCARLET</t>
-  </si>
-  <si>
-    <t>ANIELA SAMANTA</t>
   </si>
   <si>
     <t>KARINA MONSERRATH</t>
@@ -910,7 +901,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AC43"/>
+  <dimension ref="A1:AC42"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="50.7109375" customWidth="1"/>
@@ -3905,10 +3896,10 @@
         <v>6</v>
       </c>
       <c r="C36">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D36">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E36">
         <v>5</v>
@@ -3968,10 +3959,10 @@
         <v>6</v>
       </c>
       <c r="X36">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="Y36">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Z36">
         <v>5</v>
@@ -3991,10 +3982,10 @@
         <v>46</v>
       </c>
       <c r="B37">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C37">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D37">
         <v>6</v>
@@ -4003,7 +3994,7 @@
         <v>5</v>
       </c>
       <c r="F37">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G37">
         <v>-1</v>
@@ -4054,10 +4045,10 @@
         <v>-1</v>
       </c>
       <c r="W37">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="X37">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="Y37">
         <v>6</v>
@@ -4066,7 +4057,7 @@
         <v>5</v>
       </c>
       <c r="AA37">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AB37">
         <v>-1</v>
@@ -4080,10 +4071,10 @@
         <v>47</v>
       </c>
       <c r="B38">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C38">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D38">
         <v>6</v>
@@ -4092,7 +4083,7 @@
         <v>5</v>
       </c>
       <c r="F38">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G38">
         <v>-1</v>
@@ -4143,10 +4134,10 @@
         <v>-1</v>
       </c>
       <c r="W38">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X38">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="Y38">
         <v>6</v>
@@ -4155,7 +4146,7 @@
         <v>5</v>
       </c>
       <c r="AA38">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AB38">
         <v>-1</v>
@@ -4169,25 +4160,25 @@
         <v>48</v>
       </c>
       <c r="B39">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C39">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="D39">
         <v>6</v>
       </c>
       <c r="E39">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F39">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="G39">
         <v>-1</v>
       </c>
       <c r="H39">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I39">
         <v>-1</v>
@@ -4232,25 +4223,25 @@
         <v>-1</v>
       </c>
       <c r="W39">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X39">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="Y39">
         <v>6</v>
       </c>
       <c r="Z39">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA39">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="AB39">
         <v>-1</v>
       </c>
       <c r="AC39">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="40" spans="1:29">
@@ -4258,19 +4249,19 @@
         <v>49</v>
       </c>
       <c r="B40">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C40">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D40">
         <v>6</v>
       </c>
       <c r="E40">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F40">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="G40">
         <v>-1</v>
@@ -4321,19 +4312,19 @@
         <v>-1</v>
       </c>
       <c r="W40">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="X40">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Y40">
         <v>6</v>
       </c>
       <c r="Z40">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AA40">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="AB40">
         <v>-1</v>
@@ -4347,7 +4338,7 @@
         <v>50</v>
       </c>
       <c r="B41">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C41">
         <v>7</v>
@@ -4356,10 +4347,10 @@
         <v>6</v>
       </c>
       <c r="E41">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F41">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G41">
         <v>-1</v>
@@ -4410,7 +4401,7 @@
         <v>-1</v>
       </c>
       <c r="W41">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X41">
         <v>7</v>
@@ -4419,10 +4410,10 @@
         <v>6</v>
       </c>
       <c r="Z41">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AA41">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AB41">
         <v>-1</v>
@@ -4436,19 +4427,19 @@
         <v>51</v>
       </c>
       <c r="B42">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C42">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D42">
         <v>6</v>
       </c>
       <c r="E42">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F42">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G42">
         <v>-1</v>
@@ -4499,113 +4490,24 @@
         <v>-1</v>
       </c>
       <c r="W42">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="X42">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="Y42">
         <v>6</v>
       </c>
       <c r="Z42">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AA42">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AB42">
         <v>-1</v>
       </c>
       <c r="AC42">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="43" spans="1:29">
-      <c r="A43" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="B43">
-        <v>5</v>
-      </c>
-      <c r="C43">
-        <v>5</v>
-      </c>
-      <c r="D43">
-        <v>6</v>
-      </c>
-      <c r="E43">
-        <v>5</v>
-      </c>
-      <c r="F43">
-        <v>5</v>
-      </c>
-      <c r="G43">
-        <v>-1</v>
-      </c>
-      <c r="H43">
-        <v>6</v>
-      </c>
-      <c r="I43">
-        <v>-1</v>
-      </c>
-      <c r="J43">
-        <v>-1</v>
-      </c>
-      <c r="K43">
-        <v>-1</v>
-      </c>
-      <c r="L43">
-        <v>-1</v>
-      </c>
-      <c r="M43">
-        <v>-1</v>
-      </c>
-      <c r="N43">
-        <v>-1</v>
-      </c>
-      <c r="O43">
-        <v>-1</v>
-      </c>
-      <c r="P43">
-        <v>-1</v>
-      </c>
-      <c r="Q43">
-        <v>-1</v>
-      </c>
-      <c r="R43">
-        <v>-1</v>
-      </c>
-      <c r="S43">
-        <v>-1</v>
-      </c>
-      <c r="T43">
-        <v>-1</v>
-      </c>
-      <c r="U43">
-        <v>-1</v>
-      </c>
-      <c r="V43">
-        <v>-1</v>
-      </c>
-      <c r="W43">
-        <v>5</v>
-      </c>
-      <c r="X43">
-        <v>5</v>
-      </c>
-      <c r="Y43">
-        <v>6</v>
-      </c>
-      <c r="Z43">
-        <v>5</v>
-      </c>
-      <c r="AA43">
-        <v>5</v>
-      </c>
-      <c r="AB43">
-        <v>-1</v>
-      </c>
-      <c r="AC43">
         <v>6</v>
       </c>
     </row>
@@ -4622,40 +4524,43 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:S43"/>
+  <dimension ref="A1:V42"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="50.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19">
+    <row r="1" spans="1:22">
       <c r="A1" s="1"/>
       <c r="B1" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C1" s="1"/>
       <c r="D1" s="1"/>
       <c r="E1" s="1"/>
       <c r="F1" s="1"/>
       <c r="G1" s="1"/>
-      <c r="H1" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="I1" s="1"/>
+      <c r="H1" s="1"/>
+      <c r="I1" s="1" t="s">
+        <v>53</v>
+      </c>
       <c r="J1" s="1"/>
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-      <c r="N1" s="1" t="s">
-        <v>55</v>
-      </c>
+      <c r="N1" s="1"/>
       <c r="O1" s="1"/>
-      <c r="P1" s="1"/>
+      <c r="P1" s="1" t="s">
+        <v>54</v>
+      </c>
       <c r="Q1" s="1"/>
       <c r="R1" s="1"/>
       <c r="S1" s="1"/>
-    </row>
-    <row r="2" spans="1:19">
+      <c r="T1" s="1"/>
+      <c r="U1" s="1"/>
+      <c r="V1" s="1"/>
+    </row>
+    <row r="2" spans="1:22">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
@@ -4675,51 +4580,60 @@
         <v>9</v>
       </c>
       <c r="G2" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="H2" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="H2" s="1" t="s">
-        <v>5</v>
-      </c>
       <c r="I2" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="K2" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="L2" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="L2" s="1" t="s">
+      <c r="M2" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="M2" s="1" t="s">
+      <c r="N2" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="O2" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="N2" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="O2" s="1" t="s">
-        <v>6</v>
-      </c>
       <c r="P2" s="1" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="Q2" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="S2" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="R2" s="1" t="s">
+      <c r="T2" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="S2" s="1" t="s">
+      <c r="U2" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="V2" s="1" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="3" spans="1:19">
+    <row r="3" spans="1:22">
       <c r="A3" s="1" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="4" spans="1:19">
+    <row r="4" spans="1:22">
       <c r="A4" s="1" t="s">
         <v>13</v>
       </c>
@@ -4739,11 +4653,11 @@
         <v>100</v>
       </c>
       <c r="G4">
+        <v>0</v>
+      </c>
+      <c r="H4">
         <v>80</v>
       </c>
-      <c r="H4">
-        <v>100</v>
-      </c>
       <c r="I4">
         <v>100</v>
       </c>
@@ -4757,14 +4671,14 @@
         <v>100</v>
       </c>
       <c r="M4">
+        <v>100</v>
+      </c>
+      <c r="N4">
+        <v>0</v>
+      </c>
+      <c r="O4">
         <v>80</v>
       </c>
-      <c r="N4">
-        <v>100</v>
-      </c>
-      <c r="O4">
-        <v>100</v>
-      </c>
       <c r="P4">
         <v>100</v>
       </c>
@@ -4775,10 +4689,19 @@
         <v>100</v>
       </c>
       <c r="S4">
+        <v>100</v>
+      </c>
+      <c r="T4">
+        <v>100</v>
+      </c>
+      <c r="U4">
+        <v>0</v>
+      </c>
+      <c r="V4">
         <v>80</v>
       </c>
     </row>
-    <row r="5" spans="1:19">
+    <row r="5" spans="1:22">
       <c r="A5" s="1" t="s">
         <v>14</v>
       </c>
@@ -4798,11 +4721,11 @@
         <v>100</v>
       </c>
       <c r="G5">
+        <v>0</v>
+      </c>
+      <c r="H5">
         <v>85</v>
       </c>
-      <c r="H5">
-        <v>100</v>
-      </c>
       <c r="I5">
         <v>100</v>
       </c>
@@ -4816,14 +4739,14 @@
         <v>100</v>
       </c>
       <c r="M5">
+        <v>100</v>
+      </c>
+      <c r="N5">
+        <v>0</v>
+      </c>
+      <c r="O5">
         <v>85</v>
       </c>
-      <c r="N5">
-        <v>100</v>
-      </c>
-      <c r="O5">
-        <v>100</v>
-      </c>
       <c r="P5">
         <v>100</v>
       </c>
@@ -4834,10 +4757,19 @@
         <v>100</v>
       </c>
       <c r="S5">
+        <v>100</v>
+      </c>
+      <c r="T5">
+        <v>100</v>
+      </c>
+      <c r="U5">
+        <v>0</v>
+      </c>
+      <c r="V5">
         <v>85</v>
       </c>
     </row>
-    <row r="6" spans="1:19">
+    <row r="6" spans="1:22">
       <c r="A6" s="1" t="s">
         <v>15</v>
       </c>
@@ -4857,14 +4789,14 @@
         <v>90</v>
       </c>
       <c r="G6">
+        <v>0</v>
+      </c>
+      <c r="H6">
         <v>85</v>
       </c>
-      <c r="H6">
+      <c r="I6">
         <v>80</v>
       </c>
-      <c r="I6">
-        <v>100</v>
-      </c>
       <c r="J6">
         <v>100</v>
       </c>
@@ -4872,31 +4804,40 @@
         <v>100</v>
       </c>
       <c r="L6">
+        <v>100</v>
+      </c>
+      <c r="M6">
         <v>90</v>
       </c>
-      <c r="M6">
+      <c r="N6">
+        <v>0</v>
+      </c>
+      <c r="O6">
         <v>85</v>
       </c>
-      <c r="N6">
+      <c r="P6">
         <v>80</v>
       </c>
-      <c r="O6">
-        <v>100</v>
-      </c>
-      <c r="P6">
-        <v>100</v>
-      </c>
       <c r="Q6">
         <v>100</v>
       </c>
       <c r="R6">
+        <v>100</v>
+      </c>
+      <c r="S6">
+        <v>100</v>
+      </c>
+      <c r="T6">
         <v>90</v>
       </c>
-      <c r="S6">
+      <c r="U6">
+        <v>0</v>
+      </c>
+      <c r="V6">
         <v>85</v>
       </c>
     </row>
-    <row r="7" spans="1:19">
+    <row r="7" spans="1:22">
       <c r="A7" s="1" t="s">
         <v>16</v>
       </c>
@@ -4916,14 +4857,14 @@
         <v>100</v>
       </c>
       <c r="G7">
+        <v>0</v>
+      </c>
+      <c r="H7">
         <v>85</v>
       </c>
-      <c r="H7">
+      <c r="I7">
         <v>80</v>
       </c>
-      <c r="I7">
-        <v>100</v>
-      </c>
       <c r="J7">
         <v>100</v>
       </c>
@@ -4934,17 +4875,17 @@
         <v>100</v>
       </c>
       <c r="M7">
+        <v>100</v>
+      </c>
+      <c r="N7">
+        <v>0</v>
+      </c>
+      <c r="O7">
         <v>85</v>
       </c>
-      <c r="N7">
+      <c r="P7">
         <v>80</v>
       </c>
-      <c r="O7">
-        <v>100</v>
-      </c>
-      <c r="P7">
-        <v>100</v>
-      </c>
       <c r="Q7">
         <v>100</v>
       </c>
@@ -4952,10 +4893,19 @@
         <v>100</v>
       </c>
       <c r="S7">
+        <v>100</v>
+      </c>
+      <c r="T7">
+        <v>100</v>
+      </c>
+      <c r="U7">
+        <v>0</v>
+      </c>
+      <c r="V7">
         <v>85</v>
       </c>
     </row>
-    <row r="8" spans="1:19">
+    <row r="8" spans="1:22">
       <c r="A8" s="1" t="s">
         <v>17</v>
       </c>
@@ -4975,11 +4925,11 @@
         <v>100</v>
       </c>
       <c r="G8">
+        <v>0</v>
+      </c>
+      <c r="H8">
         <v>90</v>
       </c>
-      <c r="H8">
-        <v>100</v>
-      </c>
       <c r="I8">
         <v>100</v>
       </c>
@@ -4993,14 +4943,14 @@
         <v>100</v>
       </c>
       <c r="M8">
+        <v>100</v>
+      </c>
+      <c r="N8">
+        <v>0</v>
+      </c>
+      <c r="O8">
         <v>90</v>
       </c>
-      <c r="N8">
-        <v>100</v>
-      </c>
-      <c r="O8">
-        <v>100</v>
-      </c>
       <c r="P8">
         <v>100</v>
       </c>
@@ -5011,10 +4961,19 @@
         <v>100</v>
       </c>
       <c r="S8">
+        <v>100</v>
+      </c>
+      <c r="T8">
+        <v>100</v>
+      </c>
+      <c r="U8">
+        <v>0</v>
+      </c>
+      <c r="V8">
         <v>90</v>
       </c>
     </row>
-    <row r="9" spans="1:19">
+    <row r="9" spans="1:22">
       <c r="A9" s="1" t="s">
         <v>18</v>
       </c>
@@ -5034,46 +4993,55 @@
         <v>100</v>
       </c>
       <c r="G9">
+        <v>0</v>
+      </c>
+      <c r="H9">
         <v>85</v>
       </c>
-      <c r="H9">
-        <v>100</v>
-      </c>
       <c r="I9">
         <v>100</v>
       </c>
       <c r="J9">
+        <v>100</v>
+      </c>
+      <c r="K9">
         <v>95.8</v>
       </c>
-      <c r="K9">
-        <v>100</v>
-      </c>
       <c r="L9">
         <v>100</v>
       </c>
       <c r="M9">
+        <v>100</v>
+      </c>
+      <c r="N9">
+        <v>0</v>
+      </c>
+      <c r="O9">
         <v>85</v>
       </c>
-      <c r="N9">
-        <v>100</v>
-      </c>
-      <c r="O9">
-        <v>100</v>
-      </c>
       <c r="P9">
+        <v>100</v>
+      </c>
+      <c r="Q9">
+        <v>100</v>
+      </c>
+      <c r="R9">
         <v>95.8</v>
       </c>
-      <c r="Q9">
-        <v>100</v>
-      </c>
-      <c r="R9">
-        <v>100</v>
-      </c>
       <c r="S9">
+        <v>100</v>
+      </c>
+      <c r="T9">
+        <v>100</v>
+      </c>
+      <c r="U9">
+        <v>0</v>
+      </c>
+      <c r="V9">
         <v>85</v>
       </c>
     </row>
-    <row r="10" spans="1:19">
+    <row r="10" spans="1:22">
       <c r="A10" s="1" t="s">
         <v>19</v>
       </c>
@@ -5093,46 +5061,55 @@
         <v>100</v>
       </c>
       <c r="G10">
+        <v>0</v>
+      </c>
+      <c r="H10">
         <v>95</v>
       </c>
-      <c r="H10">
-        <v>100</v>
-      </c>
       <c r="I10">
         <v>100</v>
       </c>
       <c r="J10">
+        <v>100</v>
+      </c>
+      <c r="K10">
         <v>91.7</v>
       </c>
-      <c r="K10">
-        <v>100</v>
-      </c>
       <c r="L10">
         <v>100</v>
       </c>
       <c r="M10">
+        <v>100</v>
+      </c>
+      <c r="N10">
+        <v>0</v>
+      </c>
+      <c r="O10">
         <v>95</v>
       </c>
-      <c r="N10">
-        <v>100</v>
-      </c>
-      <c r="O10">
-        <v>100</v>
-      </c>
       <c r="P10">
+        <v>100</v>
+      </c>
+      <c r="Q10">
+        <v>100</v>
+      </c>
+      <c r="R10">
         <v>91.7</v>
       </c>
-      <c r="Q10">
-        <v>100</v>
-      </c>
-      <c r="R10">
-        <v>100</v>
-      </c>
       <c r="S10">
+        <v>100</v>
+      </c>
+      <c r="T10">
+        <v>100</v>
+      </c>
+      <c r="U10">
+        <v>0</v>
+      </c>
+      <c r="V10">
         <v>95</v>
       </c>
     </row>
-    <row r="11" spans="1:19">
+    <row r="11" spans="1:22">
       <c r="A11" s="1" t="s">
         <v>20</v>
       </c>
@@ -5152,46 +5129,55 @@
         <v>100</v>
       </c>
       <c r="G11">
+        <v>0</v>
+      </c>
+      <c r="H11">
         <v>95</v>
       </c>
-      <c r="H11">
-        <v>100</v>
-      </c>
       <c r="I11">
         <v>100</v>
       </c>
       <c r="J11">
+        <v>100</v>
+      </c>
+      <c r="K11">
         <v>95.8</v>
       </c>
-      <c r="K11">
-        <v>100</v>
-      </c>
       <c r="L11">
         <v>100</v>
       </c>
       <c r="M11">
+        <v>100</v>
+      </c>
+      <c r="N11">
+        <v>0</v>
+      </c>
+      <c r="O11">
         <v>95</v>
       </c>
-      <c r="N11">
-        <v>100</v>
-      </c>
-      <c r="O11">
-        <v>100</v>
-      </c>
       <c r="P11">
+        <v>100</v>
+      </c>
+      <c r="Q11">
+        <v>100</v>
+      </c>
+      <c r="R11">
         <v>95.8</v>
       </c>
-      <c r="Q11">
-        <v>100</v>
-      </c>
-      <c r="R11">
-        <v>100</v>
-      </c>
       <c r="S11">
+        <v>100</v>
+      </c>
+      <c r="T11">
+        <v>100</v>
+      </c>
+      <c r="U11">
+        <v>0</v>
+      </c>
+      <c r="V11">
         <v>95</v>
       </c>
     </row>
-    <row r="12" spans="1:19">
+    <row r="12" spans="1:22">
       <c r="A12" s="1" t="s">
         <v>21</v>
       </c>
@@ -5211,11 +5197,11 @@
         <v>100</v>
       </c>
       <c r="G12">
+        <v>0</v>
+      </c>
+      <c r="H12">
         <v>95</v>
       </c>
-      <c r="H12">
-        <v>100</v>
-      </c>
       <c r="I12">
         <v>100</v>
       </c>
@@ -5229,14 +5215,14 @@
         <v>100</v>
       </c>
       <c r="M12">
+        <v>100</v>
+      </c>
+      <c r="N12">
+        <v>0</v>
+      </c>
+      <c r="O12">
         <v>95</v>
       </c>
-      <c r="N12">
-        <v>100</v>
-      </c>
-      <c r="O12">
-        <v>100</v>
-      </c>
       <c r="P12">
         <v>100</v>
       </c>
@@ -5247,10 +5233,19 @@
         <v>100</v>
       </c>
       <c r="S12">
+        <v>100</v>
+      </c>
+      <c r="T12">
+        <v>100</v>
+      </c>
+      <c r="U12">
+        <v>0</v>
+      </c>
+      <c r="V12">
         <v>95</v>
       </c>
     </row>
-    <row r="13" spans="1:19">
+    <row r="13" spans="1:22">
       <c r="A13" s="1" t="s">
         <v>22</v>
       </c>
@@ -5270,46 +5265,55 @@
         <v>100</v>
       </c>
       <c r="G13">
+        <v>0</v>
+      </c>
+      <c r="H13">
         <v>90</v>
       </c>
-      <c r="H13">
-        <v>100</v>
-      </c>
       <c r="I13">
         <v>100</v>
       </c>
       <c r="J13">
+        <v>100</v>
+      </c>
+      <c r="K13">
         <v>95.8</v>
       </c>
-      <c r="K13">
-        <v>100</v>
-      </c>
       <c r="L13">
         <v>100</v>
       </c>
       <c r="M13">
+        <v>100</v>
+      </c>
+      <c r="N13">
+        <v>0</v>
+      </c>
+      <c r="O13">
         <v>90</v>
       </c>
-      <c r="N13">
-        <v>100</v>
-      </c>
-      <c r="O13">
-        <v>100</v>
-      </c>
       <c r="P13">
+        <v>100</v>
+      </c>
+      <c r="Q13">
+        <v>100</v>
+      </c>
+      <c r="R13">
         <v>95.8</v>
       </c>
-      <c r="Q13">
-        <v>100</v>
-      </c>
-      <c r="R13">
-        <v>100</v>
-      </c>
       <c r="S13">
+        <v>100</v>
+      </c>
+      <c r="T13">
+        <v>100</v>
+      </c>
+      <c r="U13">
+        <v>0</v>
+      </c>
+      <c r="V13">
         <v>90</v>
       </c>
     </row>
-    <row r="14" spans="1:19">
+    <row r="14" spans="1:22">
       <c r="A14" s="1" t="s">
         <v>23</v>
       </c>
@@ -5329,46 +5333,55 @@
         <v>100</v>
       </c>
       <c r="G14">
+        <v>0</v>
+      </c>
+      <c r="H14">
         <v>85</v>
       </c>
-      <c r="H14">
+      <c r="I14">
         <v>80</v>
       </c>
-      <c r="I14">
-        <v>100</v>
-      </c>
       <c r="J14">
+        <v>100</v>
+      </c>
+      <c r="K14">
         <v>95.8</v>
       </c>
-      <c r="K14">
-        <v>100</v>
-      </c>
       <c r="L14">
         <v>100</v>
       </c>
       <c r="M14">
+        <v>100</v>
+      </c>
+      <c r="N14">
+        <v>0</v>
+      </c>
+      <c r="O14">
         <v>85</v>
       </c>
-      <c r="N14">
+      <c r="P14">
         <v>80</v>
       </c>
-      <c r="O14">
-        <v>100</v>
-      </c>
-      <c r="P14">
+      <c r="Q14">
+        <v>100</v>
+      </c>
+      <c r="R14">
         <v>95.8</v>
       </c>
-      <c r="Q14">
-        <v>100</v>
-      </c>
-      <c r="R14">
-        <v>100</v>
-      </c>
       <c r="S14">
+        <v>100</v>
+      </c>
+      <c r="T14">
+        <v>100</v>
+      </c>
+      <c r="U14">
+        <v>0</v>
+      </c>
+      <c r="V14">
         <v>85</v>
       </c>
     </row>
-    <row r="15" spans="1:19">
+    <row r="15" spans="1:22">
       <c r="A15" s="1" t="s">
         <v>24</v>
       </c>
@@ -5388,13 +5401,13 @@
         <v>100</v>
       </c>
       <c r="G15">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="H15">
         <v>80</v>
       </c>
       <c r="I15">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="J15">
         <v>100</v>
@@ -5406,17 +5419,17 @@
         <v>100</v>
       </c>
       <c r="M15">
+        <v>100</v>
+      </c>
+      <c r="N15">
+        <v>0</v>
+      </c>
+      <c r="O15">
         <v>80</v>
       </c>
-      <c r="N15">
+      <c r="P15">
         <v>80</v>
       </c>
-      <c r="O15">
-        <v>100</v>
-      </c>
-      <c r="P15">
-        <v>100</v>
-      </c>
       <c r="Q15">
         <v>100</v>
       </c>
@@ -5424,10 +5437,19 @@
         <v>100</v>
       </c>
       <c r="S15">
+        <v>100</v>
+      </c>
+      <c r="T15">
+        <v>100</v>
+      </c>
+      <c r="U15">
+        <v>0</v>
+      </c>
+      <c r="V15">
         <v>80</v>
       </c>
     </row>
-    <row r="16" spans="1:19">
+    <row r="16" spans="1:22">
       <c r="A16" s="1" t="s">
         <v>25</v>
       </c>
@@ -5447,13 +5469,13 @@
         <v>95</v>
       </c>
       <c r="G16">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="H16">
         <v>80</v>
       </c>
       <c r="I16">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="J16">
         <v>100</v>
@@ -5462,31 +5484,40 @@
         <v>100</v>
       </c>
       <c r="L16">
+        <v>100</v>
+      </c>
+      <c r="M16">
         <v>95</v>
       </c>
-      <c r="M16">
+      <c r="N16">
+        <v>0</v>
+      </c>
+      <c r="O16">
         <v>80</v>
       </c>
-      <c r="N16">
+      <c r="P16">
         <v>80</v>
       </c>
-      <c r="O16">
-        <v>100</v>
-      </c>
-      <c r="P16">
-        <v>100</v>
-      </c>
       <c r="Q16">
         <v>100</v>
       </c>
       <c r="R16">
+        <v>100</v>
+      </c>
+      <c r="S16">
+        <v>100</v>
+      </c>
+      <c r="T16">
         <v>95</v>
       </c>
-      <c r="S16">
+      <c r="U16">
+        <v>0</v>
+      </c>
+      <c r="V16">
         <v>80</v>
       </c>
     </row>
-    <row r="17" spans="1:19">
+    <row r="17" spans="1:22">
       <c r="A17" s="1" t="s">
         <v>26</v>
       </c>
@@ -5506,46 +5537,55 @@
         <v>100</v>
       </c>
       <c r="G17">
+        <v>0</v>
+      </c>
+      <c r="H17">
         <v>90</v>
       </c>
-      <c r="H17">
-        <v>100</v>
-      </c>
       <c r="I17">
         <v>100</v>
       </c>
       <c r="J17">
+        <v>100</v>
+      </c>
+      <c r="K17">
         <v>95.8</v>
       </c>
-      <c r="K17">
-        <v>100</v>
-      </c>
       <c r="L17">
         <v>100</v>
       </c>
       <c r="M17">
+        <v>100</v>
+      </c>
+      <c r="N17">
+        <v>0</v>
+      </c>
+      <c r="O17">
         <v>90</v>
       </c>
-      <c r="N17">
-        <v>100</v>
-      </c>
-      <c r="O17">
-        <v>100</v>
-      </c>
       <c r="P17">
+        <v>100</v>
+      </c>
+      <c r="Q17">
+        <v>100</v>
+      </c>
+      <c r="R17">
         <v>95.8</v>
       </c>
-      <c r="Q17">
-        <v>100</v>
-      </c>
-      <c r="R17">
-        <v>100</v>
-      </c>
       <c r="S17">
+        <v>100</v>
+      </c>
+      <c r="T17">
+        <v>100</v>
+      </c>
+      <c r="U17">
+        <v>0</v>
+      </c>
+      <c r="V17">
         <v>90</v>
       </c>
     </row>
-    <row r="18" spans="1:19">
+    <row r="18" spans="1:22">
       <c r="A18" s="1" t="s">
         <v>27</v>
       </c>
@@ -5565,46 +5605,55 @@
         <v>100</v>
       </c>
       <c r="G18">
+        <v>0</v>
+      </c>
+      <c r="H18">
         <v>90</v>
       </c>
-      <c r="H18">
+      <c r="I18">
         <v>80</v>
       </c>
-      <c r="I18">
-        <v>100</v>
-      </c>
       <c r="J18">
+        <v>100</v>
+      </c>
+      <c r="K18">
         <v>95.8</v>
       </c>
-      <c r="K18">
-        <v>100</v>
-      </c>
       <c r="L18">
         <v>100</v>
       </c>
       <c r="M18">
+        <v>100</v>
+      </c>
+      <c r="N18">
+        <v>0</v>
+      </c>
+      <c r="O18">
         <v>90</v>
       </c>
-      <c r="N18">
+      <c r="P18">
         <v>80</v>
       </c>
-      <c r="O18">
-        <v>100</v>
-      </c>
-      <c r="P18">
+      <c r="Q18">
+        <v>100</v>
+      </c>
+      <c r="R18">
         <v>95.8</v>
       </c>
-      <c r="Q18">
-        <v>100</v>
-      </c>
-      <c r="R18">
-        <v>100</v>
-      </c>
       <c r="S18">
+        <v>100</v>
+      </c>
+      <c r="T18">
+        <v>100</v>
+      </c>
+      <c r="U18">
+        <v>0</v>
+      </c>
+      <c r="V18">
         <v>90</v>
       </c>
     </row>
-    <row r="19" spans="1:19">
+    <row r="19" spans="1:22">
       <c r="A19" s="1" t="s">
         <v>28</v>
       </c>
@@ -5624,46 +5673,55 @@
         <v>75</v>
       </c>
       <c r="G19">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="H19">
         <v>80</v>
       </c>
       <c r="I19">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="J19">
+        <v>100</v>
+      </c>
+      <c r="K19">
         <v>95.8</v>
       </c>
-      <c r="K19">
-        <v>100</v>
-      </c>
       <c r="L19">
+        <v>100</v>
+      </c>
+      <c r="M19">
         <v>75</v>
       </c>
-      <c r="M19">
+      <c r="N19">
+        <v>0</v>
+      </c>
+      <c r="O19">
         <v>80</v>
       </c>
-      <c r="N19">
+      <c r="P19">
         <v>80</v>
       </c>
-      <c r="O19">
-        <v>100</v>
-      </c>
-      <c r="P19">
+      <c r="Q19">
+        <v>100</v>
+      </c>
+      <c r="R19">
         <v>95.8</v>
       </c>
-      <c r="Q19">
-        <v>100</v>
-      </c>
-      <c r="R19">
+      <c r="S19">
+        <v>100</v>
+      </c>
+      <c r="T19">
         <v>75</v>
       </c>
-      <c r="S19">
+      <c r="U19">
+        <v>0</v>
+      </c>
+      <c r="V19">
         <v>80</v>
       </c>
     </row>
-    <row r="20" spans="1:19">
+    <row r="20" spans="1:22">
       <c r="A20" s="1" t="s">
         <v>29</v>
       </c>
@@ -5683,46 +5741,55 @@
         <v>75</v>
       </c>
       <c r="G20">
+        <v>0</v>
+      </c>
+      <c r="H20">
         <v>80</v>
       </c>
-      <c r="H20">
+      <c r="I20">
         <v>50</v>
       </c>
-      <c r="I20">
-        <v>100</v>
-      </c>
       <c r="J20">
+        <v>100</v>
+      </c>
+      <c r="K20">
         <v>62.5</v>
       </c>
-      <c r="K20">
-        <v>100</v>
-      </c>
       <c r="L20">
+        <v>100</v>
+      </c>
+      <c r="M20">
         <v>75</v>
       </c>
-      <c r="M20">
+      <c r="N20">
+        <v>0</v>
+      </c>
+      <c r="O20">
         <v>80</v>
       </c>
-      <c r="N20">
+      <c r="P20">
         <v>50</v>
       </c>
-      <c r="O20">
-        <v>100</v>
-      </c>
-      <c r="P20">
+      <c r="Q20">
+        <v>100</v>
+      </c>
+      <c r="R20">
         <v>62.5</v>
       </c>
-      <c r="Q20">
-        <v>100</v>
-      </c>
-      <c r="R20">
+      <c r="S20">
+        <v>100</v>
+      </c>
+      <c r="T20">
         <v>75</v>
       </c>
-      <c r="S20">
+      <c r="U20">
+        <v>0</v>
+      </c>
+      <c r="V20">
         <v>80</v>
       </c>
     </row>
-    <row r="21" spans="1:19">
+    <row r="21" spans="1:22">
       <c r="A21" s="1" t="s">
         <v>30</v>
       </c>
@@ -5742,46 +5809,55 @@
         <v>100</v>
       </c>
       <c r="G21">
+        <v>0</v>
+      </c>
+      <c r="H21">
         <v>95</v>
       </c>
-      <c r="H21">
+      <c r="I21">
         <v>90</v>
       </c>
-      <c r="I21">
-        <v>100</v>
-      </c>
       <c r="J21">
+        <v>100</v>
+      </c>
+      <c r="K21">
         <v>95.8</v>
       </c>
-      <c r="K21">
-        <v>100</v>
-      </c>
       <c r="L21">
         <v>100</v>
       </c>
       <c r="M21">
+        <v>100</v>
+      </c>
+      <c r="N21">
+        <v>0</v>
+      </c>
+      <c r="O21">
         <v>95</v>
       </c>
-      <c r="N21">
+      <c r="P21">
         <v>90</v>
       </c>
-      <c r="O21">
-        <v>100</v>
-      </c>
-      <c r="P21">
+      <c r="Q21">
+        <v>100</v>
+      </c>
+      <c r="R21">
         <v>95.8</v>
       </c>
-      <c r="Q21">
-        <v>100</v>
-      </c>
-      <c r="R21">
-        <v>100</v>
-      </c>
       <c r="S21">
+        <v>100</v>
+      </c>
+      <c r="T21">
+        <v>100</v>
+      </c>
+      <c r="U21">
+        <v>0</v>
+      </c>
+      <c r="V21">
         <v>95</v>
       </c>
     </row>
-    <row r="22" spans="1:19">
+    <row r="22" spans="1:22">
       <c r="A22" s="1" t="s">
         <v>31</v>
       </c>
@@ -5801,46 +5877,55 @@
         <v>100</v>
       </c>
       <c r="G22">
+        <v>0</v>
+      </c>
+      <c r="H22">
         <v>90</v>
       </c>
-      <c r="H22">
+      <c r="I22">
         <v>80</v>
       </c>
-      <c r="I22">
-        <v>100</v>
-      </c>
       <c r="J22">
+        <v>100</v>
+      </c>
+      <c r="K22">
         <v>91.7</v>
       </c>
-      <c r="K22">
-        <v>100</v>
-      </c>
       <c r="L22">
         <v>100</v>
       </c>
       <c r="M22">
+        <v>100</v>
+      </c>
+      <c r="N22">
+        <v>0</v>
+      </c>
+      <c r="O22">
         <v>90</v>
       </c>
-      <c r="N22">
+      <c r="P22">
         <v>80</v>
       </c>
-      <c r="O22">
-        <v>100</v>
-      </c>
-      <c r="P22">
+      <c r="Q22">
+        <v>100</v>
+      </c>
+      <c r="R22">
         <v>91.7</v>
       </c>
-      <c r="Q22">
-        <v>100</v>
-      </c>
-      <c r="R22">
-        <v>100</v>
-      </c>
       <c r="S22">
+        <v>100</v>
+      </c>
+      <c r="T22">
+        <v>100</v>
+      </c>
+      <c r="U22">
+        <v>0</v>
+      </c>
+      <c r="V22">
         <v>90</v>
       </c>
     </row>
-    <row r="23" spans="1:19">
+    <row r="23" spans="1:22">
       <c r="A23" s="1" t="s">
         <v>32</v>
       </c>
@@ -5860,46 +5945,55 @@
         <v>100</v>
       </c>
       <c r="G23">
+        <v>0</v>
+      </c>
+      <c r="H23">
         <v>85</v>
       </c>
-      <c r="H23">
-        <v>100</v>
-      </c>
       <c r="I23">
         <v>100</v>
       </c>
       <c r="J23">
+        <v>100</v>
+      </c>
+      <c r="K23">
         <v>91.7</v>
       </c>
-      <c r="K23">
-        <v>100</v>
-      </c>
       <c r="L23">
         <v>100</v>
       </c>
       <c r="M23">
+        <v>100</v>
+      </c>
+      <c r="N23">
+        <v>0</v>
+      </c>
+      <c r="O23">
         <v>85</v>
       </c>
-      <c r="N23">
-        <v>100</v>
-      </c>
-      <c r="O23">
-        <v>100</v>
-      </c>
       <c r="P23">
+        <v>100</v>
+      </c>
+      <c r="Q23">
+        <v>100</v>
+      </c>
+      <c r="R23">
         <v>91.7</v>
       </c>
-      <c r="Q23">
-        <v>100</v>
-      </c>
-      <c r="R23">
-        <v>100</v>
-      </c>
       <c r="S23">
+        <v>100</v>
+      </c>
+      <c r="T23">
+        <v>100</v>
+      </c>
+      <c r="U23">
+        <v>0</v>
+      </c>
+      <c r="V23">
         <v>85</v>
       </c>
     </row>
-    <row r="24" spans="1:19">
+    <row r="24" spans="1:22">
       <c r="A24" s="1" t="s">
         <v>33</v>
       </c>
@@ -5919,7 +6013,7 @@
         <v>100</v>
       </c>
       <c r="G24">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="H24">
         <v>100</v>
@@ -5928,11 +6022,11 @@
         <v>100</v>
       </c>
       <c r="J24">
+        <v>100</v>
+      </c>
+      <c r="K24">
         <v>95.8</v>
       </c>
-      <c r="K24">
-        <v>100</v>
-      </c>
       <c r="L24">
         <v>100</v>
       </c>
@@ -5940,25 +6034,34 @@
         <v>100</v>
       </c>
       <c r="N24">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="O24">
         <v>100</v>
       </c>
       <c r="P24">
+        <v>100</v>
+      </c>
+      <c r="Q24">
+        <v>100</v>
+      </c>
+      <c r="R24">
         <v>95.8</v>
       </c>
-      <c r="Q24">
-        <v>100</v>
-      </c>
-      <c r="R24">
-        <v>100</v>
-      </c>
       <c r="S24">
         <v>100</v>
       </c>
-    </row>
-    <row r="25" spans="1:19">
+      <c r="T24">
+        <v>100</v>
+      </c>
+      <c r="U24">
+        <v>0</v>
+      </c>
+      <c r="V24">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="25" spans="1:22">
       <c r="A25" s="1" t="s">
         <v>34</v>
       </c>
@@ -5978,46 +6081,55 @@
         <v>100</v>
       </c>
       <c r="G25">
+        <v>0</v>
+      </c>
+      <c r="H25">
         <v>90</v>
       </c>
-      <c r="H25">
-        <v>100</v>
-      </c>
       <c r="I25">
         <v>100</v>
       </c>
       <c r="J25">
+        <v>100</v>
+      </c>
+      <c r="K25">
         <v>91.7</v>
       </c>
-      <c r="K25">
-        <v>100</v>
-      </c>
       <c r="L25">
         <v>100</v>
       </c>
       <c r="M25">
+        <v>100</v>
+      </c>
+      <c r="N25">
+        <v>0</v>
+      </c>
+      <c r="O25">
         <v>90</v>
       </c>
-      <c r="N25">
-        <v>100</v>
-      </c>
-      <c r="O25">
-        <v>100</v>
-      </c>
       <c r="P25">
+        <v>100</v>
+      </c>
+      <c r="Q25">
+        <v>100</v>
+      </c>
+      <c r="R25">
         <v>91.7</v>
       </c>
-      <c r="Q25">
-        <v>100</v>
-      </c>
-      <c r="R25">
-        <v>100</v>
-      </c>
       <c r="S25">
+        <v>100</v>
+      </c>
+      <c r="T25">
+        <v>100</v>
+      </c>
+      <c r="U25">
+        <v>0</v>
+      </c>
+      <c r="V25">
         <v>90</v>
       </c>
     </row>
-    <row r="26" spans="1:19">
+    <row r="26" spans="1:22">
       <c r="A26" s="1" t="s">
         <v>35</v>
       </c>
@@ -6037,46 +6149,55 @@
         <v>100</v>
       </c>
       <c r="G26">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="H26">
         <v>80</v>
       </c>
       <c r="I26">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="J26">
+        <v>100</v>
+      </c>
+      <c r="K26">
         <v>91.7</v>
       </c>
-      <c r="K26">
-        <v>100</v>
-      </c>
       <c r="L26">
         <v>100</v>
       </c>
       <c r="M26">
+        <v>100</v>
+      </c>
+      <c r="N26">
+        <v>0</v>
+      </c>
+      <c r="O26">
         <v>80</v>
       </c>
-      <c r="N26">
+      <c r="P26">
         <v>80</v>
       </c>
-      <c r="O26">
-        <v>100</v>
-      </c>
-      <c r="P26">
+      <c r="Q26">
+        <v>100</v>
+      </c>
+      <c r="R26">
         <v>91.7</v>
       </c>
-      <c r="Q26">
-        <v>100</v>
-      </c>
-      <c r="R26">
-        <v>100</v>
-      </c>
       <c r="S26">
+        <v>100</v>
+      </c>
+      <c r="T26">
+        <v>100</v>
+      </c>
+      <c r="U26">
+        <v>0</v>
+      </c>
+      <c r="V26">
         <v>80</v>
       </c>
     </row>
-    <row r="27" spans="1:19">
+    <row r="27" spans="1:22">
       <c r="A27" s="1" t="s">
         <v>36</v>
       </c>
@@ -6096,46 +6217,55 @@
         <v>100</v>
       </c>
       <c r="G27">
+        <v>0</v>
+      </c>
+      <c r="H27">
         <v>95</v>
       </c>
-      <c r="H27">
-        <v>100</v>
-      </c>
       <c r="I27">
         <v>100</v>
       </c>
       <c r="J27">
+        <v>100</v>
+      </c>
+      <c r="K27">
         <v>95.8</v>
       </c>
-      <c r="K27">
-        <v>100</v>
-      </c>
       <c r="L27">
         <v>100</v>
       </c>
       <c r="M27">
+        <v>100</v>
+      </c>
+      <c r="N27">
+        <v>0</v>
+      </c>
+      <c r="O27">
         <v>95</v>
       </c>
-      <c r="N27">
-        <v>100</v>
-      </c>
-      <c r="O27">
-        <v>100</v>
-      </c>
       <c r="P27">
+        <v>100</v>
+      </c>
+      <c r="Q27">
+        <v>100</v>
+      </c>
+      <c r="R27">
         <v>95.8</v>
       </c>
-      <c r="Q27">
-        <v>100</v>
-      </c>
-      <c r="R27">
-        <v>100</v>
-      </c>
       <c r="S27">
+        <v>100</v>
+      </c>
+      <c r="T27">
+        <v>100</v>
+      </c>
+      <c r="U27">
+        <v>0</v>
+      </c>
+      <c r="V27">
         <v>95</v>
       </c>
     </row>
-    <row r="28" spans="1:19">
+    <row r="28" spans="1:22">
       <c r="A28" s="1" t="s">
         <v>37</v>
       </c>
@@ -6155,11 +6285,11 @@
         <v>100</v>
       </c>
       <c r="G28">
+        <v>0</v>
+      </c>
+      <c r="H28">
         <v>95</v>
       </c>
-      <c r="H28">
-        <v>100</v>
-      </c>
       <c r="I28">
         <v>100</v>
       </c>
@@ -6173,14 +6303,14 @@
         <v>100</v>
       </c>
       <c r="M28">
+        <v>100</v>
+      </c>
+      <c r="N28">
+        <v>0</v>
+      </c>
+      <c r="O28">
         <v>95</v>
       </c>
-      <c r="N28">
-        <v>100</v>
-      </c>
-      <c r="O28">
-        <v>100</v>
-      </c>
       <c r="P28">
         <v>100</v>
       </c>
@@ -6191,10 +6321,19 @@
         <v>100</v>
       </c>
       <c r="S28">
+        <v>100</v>
+      </c>
+      <c r="T28">
+        <v>100</v>
+      </c>
+      <c r="U28">
+        <v>0</v>
+      </c>
+      <c r="V28">
         <v>95</v>
       </c>
     </row>
-    <row r="29" spans="1:19">
+    <row r="29" spans="1:22">
       <c r="A29" s="1" t="s">
         <v>38</v>
       </c>
@@ -6214,46 +6353,55 @@
         <v>100</v>
       </c>
       <c r="G29">
+        <v>0</v>
+      </c>
+      <c r="H29">
         <v>90</v>
       </c>
-      <c r="H29">
-        <v>100</v>
-      </c>
       <c r="I29">
         <v>100</v>
       </c>
       <c r="J29">
+        <v>100</v>
+      </c>
+      <c r="K29">
         <v>95.8</v>
       </c>
-      <c r="K29">
-        <v>100</v>
-      </c>
       <c r="L29">
         <v>100</v>
       </c>
       <c r="M29">
+        <v>100</v>
+      </c>
+      <c r="N29">
+        <v>0</v>
+      </c>
+      <c r="O29">
         <v>90</v>
       </c>
-      <c r="N29">
-        <v>100</v>
-      </c>
-      <c r="O29">
-        <v>100</v>
-      </c>
       <c r="P29">
+        <v>100</v>
+      </c>
+      <c r="Q29">
+        <v>100</v>
+      </c>
+      <c r="R29">
         <v>95.8</v>
       </c>
-      <c r="Q29">
-        <v>100</v>
-      </c>
-      <c r="R29">
-        <v>100</v>
-      </c>
       <c r="S29">
+        <v>100</v>
+      </c>
+      <c r="T29">
+        <v>100</v>
+      </c>
+      <c r="U29">
+        <v>0</v>
+      </c>
+      <c r="V29">
         <v>90</v>
       </c>
     </row>
-    <row r="30" spans="1:19">
+    <row r="30" spans="1:22">
       <c r="A30" s="1" t="s">
         <v>39</v>
       </c>
@@ -6273,46 +6421,55 @@
         <v>100</v>
       </c>
       <c r="G30">
+        <v>0</v>
+      </c>
+      <c r="H30">
         <v>85</v>
       </c>
-      <c r="H30">
-        <v>100</v>
-      </c>
       <c r="I30">
         <v>100</v>
       </c>
       <c r="J30">
+        <v>100</v>
+      </c>
+      <c r="K30">
         <v>95.8</v>
       </c>
-      <c r="K30">
-        <v>100</v>
-      </c>
       <c r="L30">
         <v>100</v>
       </c>
       <c r="M30">
+        <v>100</v>
+      </c>
+      <c r="N30">
+        <v>0</v>
+      </c>
+      <c r="O30">
         <v>85</v>
       </c>
-      <c r="N30">
-        <v>100</v>
-      </c>
-      <c r="O30">
-        <v>100</v>
-      </c>
       <c r="P30">
+        <v>100</v>
+      </c>
+      <c r="Q30">
+        <v>100</v>
+      </c>
+      <c r="R30">
         <v>95.8</v>
       </c>
-      <c r="Q30">
-        <v>100</v>
-      </c>
-      <c r="R30">
-        <v>100</v>
-      </c>
       <c r="S30">
+        <v>100</v>
+      </c>
+      <c r="T30">
+        <v>100</v>
+      </c>
+      <c r="U30">
+        <v>0</v>
+      </c>
+      <c r="V30">
         <v>85</v>
       </c>
     </row>
-    <row r="31" spans="1:19">
+    <row r="31" spans="1:22">
       <c r="A31" s="1" t="s">
         <v>40</v>
       </c>
@@ -6332,46 +6489,55 @@
         <v>100</v>
       </c>
       <c r="G31">
+        <v>0</v>
+      </c>
+      <c r="H31">
         <v>95</v>
       </c>
-      <c r="H31">
-        <v>100</v>
-      </c>
       <c r="I31">
         <v>100</v>
       </c>
       <c r="J31">
+        <v>100</v>
+      </c>
+      <c r="K31">
         <v>95.8</v>
       </c>
-      <c r="K31">
-        <v>100</v>
-      </c>
       <c r="L31">
         <v>100</v>
       </c>
       <c r="M31">
+        <v>100</v>
+      </c>
+      <c r="N31">
+        <v>0</v>
+      </c>
+      <c r="O31">
         <v>95</v>
       </c>
-      <c r="N31">
-        <v>100</v>
-      </c>
-      <c r="O31">
-        <v>100</v>
-      </c>
       <c r="P31">
+        <v>100</v>
+      </c>
+      <c r="Q31">
+        <v>100</v>
+      </c>
+      <c r="R31">
         <v>95.8</v>
       </c>
-      <c r="Q31">
-        <v>100</v>
-      </c>
-      <c r="R31">
-        <v>100</v>
-      </c>
       <c r="S31">
+        <v>100</v>
+      </c>
+      <c r="T31">
+        <v>100</v>
+      </c>
+      <c r="U31">
+        <v>0</v>
+      </c>
+      <c r="V31">
         <v>95</v>
       </c>
     </row>
-    <row r="32" spans="1:19">
+    <row r="32" spans="1:22">
       <c r="A32" s="1" t="s">
         <v>41</v>
       </c>
@@ -6397,16 +6563,16 @@
         <v>0</v>
       </c>
       <c r="I32">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="J32">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K32">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="L32">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M32">
         <v>0</v>
@@ -6415,7 +6581,7 @@
         <v>0</v>
       </c>
       <c r="O32">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="P32">
         <v>0</v>
@@ -6427,10 +6593,19 @@
         <v>0</v>
       </c>
       <c r="S32">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="33" spans="1:19">
+        <v>100</v>
+      </c>
+      <c r="T32">
+        <v>0</v>
+      </c>
+      <c r="U32">
+        <v>0</v>
+      </c>
+      <c r="V32">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="1:22">
       <c r="A33" s="1" t="s">
         <v>42</v>
       </c>
@@ -6450,46 +6625,55 @@
         <v>100</v>
       </c>
       <c r="G33">
+        <v>0</v>
+      </c>
+      <c r="H33">
         <v>90</v>
       </c>
-      <c r="H33">
+      <c r="I33">
         <v>80</v>
       </c>
-      <c r="I33">
-        <v>100</v>
-      </c>
       <c r="J33">
+        <v>100</v>
+      </c>
+      <c r="K33">
         <v>95.8</v>
       </c>
-      <c r="K33">
-        <v>100</v>
-      </c>
       <c r="L33">
         <v>100</v>
       </c>
       <c r="M33">
+        <v>100</v>
+      </c>
+      <c r="N33">
+        <v>0</v>
+      </c>
+      <c r="O33">
         <v>90</v>
       </c>
-      <c r="N33">
+      <c r="P33">
         <v>80</v>
       </c>
-      <c r="O33">
-        <v>100</v>
-      </c>
-      <c r="P33">
+      <c r="Q33">
+        <v>100</v>
+      </c>
+      <c r="R33">
         <v>95.8</v>
       </c>
-      <c r="Q33">
-        <v>100</v>
-      </c>
-      <c r="R33">
-        <v>100</v>
-      </c>
       <c r="S33">
+        <v>100</v>
+      </c>
+      <c r="T33">
+        <v>100</v>
+      </c>
+      <c r="U33">
+        <v>0</v>
+      </c>
+      <c r="V33">
         <v>90</v>
       </c>
     </row>
-    <row r="34" spans="1:19">
+    <row r="34" spans="1:22">
       <c r="A34" s="1" t="s">
         <v>43</v>
       </c>
@@ -6512,43 +6696,52 @@
         <v>0</v>
       </c>
       <c r="H34">
+        <v>0</v>
+      </c>
+      <c r="I34">
         <v>80</v>
       </c>
-      <c r="I34">
-        <v>100</v>
-      </c>
       <c r="J34">
+        <v>100</v>
+      </c>
+      <c r="K34">
         <v>95.8</v>
       </c>
-      <c r="K34">
-        <v>100</v>
-      </c>
       <c r="L34">
         <v>100</v>
       </c>
       <c r="M34">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N34">
+        <v>0</v>
+      </c>
+      <c r="O34">
+        <v>0</v>
+      </c>
+      <c r="P34">
         <v>80</v>
       </c>
-      <c r="O34">
-        <v>100</v>
-      </c>
-      <c r="P34">
+      <c r="Q34">
+        <v>100</v>
+      </c>
+      <c r="R34">
         <v>95.8</v>
       </c>
-      <c r="Q34">
-        <v>100</v>
-      </c>
-      <c r="R34">
-        <v>100</v>
-      </c>
       <c r="S34">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="35" spans="1:19">
+        <v>100</v>
+      </c>
+      <c r="T34">
+        <v>100</v>
+      </c>
+      <c r="U34">
+        <v>0</v>
+      </c>
+      <c r="V34">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="1:22">
       <c r="A35" s="1" t="s">
         <v>44</v>
       </c>
@@ -6568,75 +6761,84 @@
         <v>100</v>
       </c>
       <c r="G35">
+        <v>0</v>
+      </c>
+      <c r="H35">
         <v>95</v>
       </c>
-      <c r="H35">
+      <c r="I35">
         <v>90</v>
       </c>
-      <c r="I35">
-        <v>100</v>
-      </c>
       <c r="J35">
+        <v>100</v>
+      </c>
+      <c r="K35">
         <v>95.8</v>
       </c>
-      <c r="K35">
-        <v>100</v>
-      </c>
       <c r="L35">
         <v>100</v>
       </c>
       <c r="M35">
+        <v>100</v>
+      </c>
+      <c r="N35">
+        <v>0</v>
+      </c>
+      <c r="O35">
         <v>95</v>
       </c>
-      <c r="N35">
+      <c r="P35">
         <v>90</v>
       </c>
-      <c r="O35">
-        <v>100</v>
-      </c>
-      <c r="P35">
+      <c r="Q35">
+        <v>100</v>
+      </c>
+      <c r="R35">
         <v>95.8</v>
       </c>
-      <c r="Q35">
-        <v>100</v>
-      </c>
-      <c r="R35">
-        <v>100</v>
-      </c>
       <c r="S35">
+        <v>100</v>
+      </c>
+      <c r="T35">
+        <v>100</v>
+      </c>
+      <c r="U35">
+        <v>0</v>
+      </c>
+      <c r="V35">
         <v>95</v>
       </c>
     </row>
-    <row r="36" spans="1:19">
+    <row r="36" spans="1:22">
       <c r="A36" s="1" t="s">
         <v>45</v>
       </c>
       <c r="B36">
+        <v>80</v>
+      </c>
+      <c r="C36">
+        <v>100</v>
+      </c>
+      <c r="D36">
+        <v>100</v>
+      </c>
+      <c r="E36">
+        <v>100</v>
+      </c>
+      <c r="F36">
         <v>90</v>
       </c>
-      <c r="C36">
-        <v>100</v>
-      </c>
-      <c r="D36">
-        <v>95.8</v>
-      </c>
-      <c r="E36">
-        <v>100</v>
-      </c>
-      <c r="F36">
-        <v>100</v>
-      </c>
       <c r="G36">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="H36">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="I36">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="J36">
-        <v>95.8</v>
+        <v>100</v>
       </c>
       <c r="K36">
         <v>100</v>
@@ -6648,30 +6850,39 @@
         <v>90</v>
       </c>
       <c r="N36">
+        <v>0</v>
+      </c>
+      <c r="O36">
+        <v>80</v>
+      </c>
+      <c r="P36">
+        <v>80</v>
+      </c>
+      <c r="Q36">
+        <v>100</v>
+      </c>
+      <c r="R36">
+        <v>100</v>
+      </c>
+      <c r="S36">
+        <v>100</v>
+      </c>
+      <c r="T36">
         <v>90</v>
       </c>
-      <c r="O36">
-        <v>100</v>
-      </c>
-      <c r="P36">
-        <v>95.8</v>
-      </c>
-      <c r="Q36">
-        <v>100</v>
-      </c>
-      <c r="R36">
-        <v>100</v>
-      </c>
-      <c r="S36">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="37" spans="1:19">
+      <c r="U36">
+        <v>0</v>
+      </c>
+      <c r="V36">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="37" spans="1:22">
       <c r="A37" s="1" t="s">
         <v>46</v>
       </c>
       <c r="B37">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="C37">
         <v>100</v>
@@ -6683,13 +6894,13 @@
         <v>100</v>
       </c>
       <c r="F37">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="G37">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="H37">
-        <v>80</v>
+        <v>95</v>
       </c>
       <c r="I37">
         <v>100</v>
@@ -6701,16 +6912,16 @@
         <v>100</v>
       </c>
       <c r="L37">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="M37">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="N37">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="O37">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="P37">
         <v>100</v>
@@ -6719,18 +6930,27 @@
         <v>100</v>
       </c>
       <c r="R37">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="S37">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="38" spans="1:19">
+        <v>100</v>
+      </c>
+      <c r="T37">
+        <v>100</v>
+      </c>
+      <c r="U37">
+        <v>0</v>
+      </c>
+      <c r="V37">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="38" spans="1:22">
       <c r="A38" s="1" t="s">
         <v>47</v>
       </c>
       <c r="B38">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="C38">
         <v>100</v>
@@ -6745,13 +6965,13 @@
         <v>100</v>
       </c>
       <c r="G38">
-        <v>95</v>
+        <v>0</v>
       </c>
       <c r="H38">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="I38">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="J38">
         <v>100</v>
@@ -6763,16 +6983,16 @@
         <v>100</v>
       </c>
       <c r="M38">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="N38">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="O38">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="P38">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="Q38">
         <v>100</v>
@@ -6781,21 +7001,30 @@
         <v>100</v>
       </c>
       <c r="S38">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="39" spans="1:19">
+        <v>100</v>
+      </c>
+      <c r="T38">
+        <v>100</v>
+      </c>
+      <c r="U38">
+        <v>0</v>
+      </c>
+      <c r="V38">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="39" spans="1:22">
       <c r="A39" s="1" t="s">
         <v>48</v>
       </c>
       <c r="B39">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="C39">
         <v>100</v>
       </c>
       <c r="D39">
-        <v>100</v>
+        <v>95.8</v>
       </c>
       <c r="E39">
         <v>100</v>
@@ -6804,10 +7033,10 @@
         <v>100</v>
       </c>
       <c r="G39">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="H39">
-        <v>80</v>
+        <v>95</v>
       </c>
       <c r="I39">
         <v>100</v>
@@ -6816,19 +7045,19 @@
         <v>100</v>
       </c>
       <c r="K39">
-        <v>100</v>
+        <v>95.8</v>
       </c>
       <c r="L39">
         <v>100</v>
       </c>
       <c r="M39">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="N39">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="O39">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="P39">
         <v>100</v>
@@ -6837,13 +7066,22 @@
         <v>100</v>
       </c>
       <c r="R39">
-        <v>100</v>
+        <v>95.8</v>
       </c>
       <c r="S39">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="40" spans="1:19">
+        <v>100</v>
+      </c>
+      <c r="T39">
+        <v>100</v>
+      </c>
+      <c r="U39">
+        <v>0</v>
+      </c>
+      <c r="V39">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="40" spans="1:22">
       <c r="A40" s="1" t="s">
         <v>49</v>
       </c>
@@ -6863,46 +7101,55 @@
         <v>100</v>
       </c>
       <c r="G40">
-        <v>95</v>
+        <v>0</v>
       </c>
       <c r="H40">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="I40">
         <v>100</v>
       </c>
       <c r="J40">
+        <v>100</v>
+      </c>
+      <c r="K40">
         <v>95.8</v>
       </c>
-      <c r="K40">
-        <v>100</v>
-      </c>
       <c r="L40">
         <v>100</v>
       </c>
       <c r="M40">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="N40">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="O40">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="P40">
+        <v>100</v>
+      </c>
+      <c r="Q40">
+        <v>100</v>
+      </c>
+      <c r="R40">
         <v>95.8</v>
       </c>
-      <c r="Q40">
-        <v>100</v>
-      </c>
-      <c r="R40">
-        <v>100</v>
-      </c>
       <c r="S40">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="41" spans="1:19">
+        <v>100</v>
+      </c>
+      <c r="T40">
+        <v>100</v>
+      </c>
+      <c r="U40">
+        <v>0</v>
+      </c>
+      <c r="V40">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="41" spans="1:22">
       <c r="A41" s="1" t="s">
         <v>50</v>
       </c>
@@ -6913,7 +7160,7 @@
         <v>100</v>
       </c>
       <c r="D41">
-        <v>95.8</v>
+        <v>100</v>
       </c>
       <c r="E41">
         <v>100</v>
@@ -6922,16 +7169,16 @@
         <v>100</v>
       </c>
       <c r="G41">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="H41">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="I41">
         <v>100</v>
       </c>
       <c r="J41">
-        <v>95.8</v>
+        <v>100</v>
       </c>
       <c r="K41">
         <v>100</v>
@@ -6940,16 +7187,16 @@
         <v>100</v>
       </c>
       <c r="M41">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="N41">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="O41">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="P41">
-        <v>95.8</v>
+        <v>100</v>
       </c>
       <c r="Q41">
         <v>100</v>
@@ -6958,132 +7205,91 @@
         <v>100</v>
       </c>
       <c r="S41">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="42" spans="1:19">
+        <v>100</v>
+      </c>
+      <c r="T41">
+        <v>100</v>
+      </c>
+      <c r="U41">
+        <v>0</v>
+      </c>
+      <c r="V41">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="42" spans="1:22">
       <c r="A42" s="1" t="s">
         <v>51</v>
       </c>
       <c r="B42">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="C42">
         <v>100</v>
       </c>
       <c r="D42">
-        <v>100</v>
+        <v>95.8</v>
       </c>
       <c r="E42">
         <v>100</v>
       </c>
       <c r="F42">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="G42">
-        <v>95</v>
+        <v>0</v>
       </c>
       <c r="H42">
-        <v>100</v>
+        <v>85</v>
       </c>
       <c r="I42">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="J42">
         <v>100</v>
       </c>
       <c r="K42">
-        <v>100</v>
+        <v>95.8</v>
       </c>
       <c r="L42">
         <v>100</v>
       </c>
       <c r="M42">
-        <v>95</v>
+        <v>80</v>
       </c>
       <c r="N42">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="O42">
-        <v>100</v>
+        <v>85</v>
       </c>
       <c r="P42">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="Q42">
         <v>100</v>
       </c>
       <c r="R42">
-        <v>100</v>
+        <v>95.8</v>
       </c>
       <c r="S42">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="43" spans="1:19">
-      <c r="A43" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="B43">
+        <v>100</v>
+      </c>
+      <c r="T42">
         <v>80</v>
       </c>
-      <c r="C43">
-        <v>100</v>
-      </c>
-      <c r="D43">
-        <v>95.8</v>
-      </c>
-      <c r="E43">
-        <v>100</v>
-      </c>
-      <c r="F43">
-        <v>80</v>
-      </c>
-      <c r="G43">
-        <v>85</v>
-      </c>
-      <c r="H43">
-        <v>80</v>
-      </c>
-      <c r="I43">
-        <v>100</v>
-      </c>
-      <c r="J43">
-        <v>95.8</v>
-      </c>
-      <c r="K43">
-        <v>100</v>
-      </c>
-      <c r="L43">
-        <v>80</v>
-      </c>
-      <c r="M43">
-        <v>85</v>
-      </c>
-      <c r="N43">
-        <v>80</v>
-      </c>
-      <c r="O43">
-        <v>100</v>
-      </c>
-      <c r="P43">
-        <v>95.8</v>
-      </c>
-      <c r="Q43">
-        <v>100</v>
-      </c>
-      <c r="R43">
-        <v>80</v>
-      </c>
-      <c r="S43">
+      <c r="U42">
+        <v>0</v>
+      </c>
+      <c r="V42">
         <v>85</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="3">
-    <mergeCell ref="B1:G1"/>
-    <mergeCell ref="H1:M1"/>
-    <mergeCell ref="N1:S1"/>
+    <mergeCell ref="B1:H1"/>
+    <mergeCell ref="I1:O1"/>
+    <mergeCell ref="P1:V1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -7104,31 +7310,31 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>63</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>64</v>
       </c>
     </row>
     <row r="2" spans="1:10">
@@ -7136,10 +7342,10 @@
         <v>10</v>
       </c>
       <c r="B2" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C2">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D2">
         <v>0</v>
@@ -7154,7 +7360,7 @@
         <v>0</v>
       </c>
       <c r="I2">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="J2" s="2">
         <v>100</v>
@@ -7165,22 +7371,22 @@
         <v>11</v>
       </c>
       <c r="B3" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C3">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D3">
         <v>19</v>
       </c>
       <c r="E3">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F3" s="2">
-        <v>47.5</v>
+        <v>48.7</v>
       </c>
       <c r="G3" s="2">
-        <v>52.5</v>
+        <v>51.3</v>
       </c>
       <c r="H3">
         <v>5.5</v>
@@ -7197,22 +7403,22 @@
         <v>8</v>
       </c>
       <c r="B4" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C4">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D4">
         <v>21</v>
       </c>
       <c r="E4">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F4" s="2">
-        <v>52.5</v>
+        <v>53.8</v>
       </c>
       <c r="G4" s="2">
-        <v>47.5</v>
+        <v>46.2</v>
       </c>
       <c r="H4">
         <v>5.9</v>
@@ -7229,22 +7435,22 @@
         <v>5</v>
       </c>
       <c r="B5" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C5">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D5">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E5">
         <v>14</v>
       </c>
       <c r="F5" s="2">
-        <v>65</v>
+        <v>64.09999999999999</v>
       </c>
       <c r="G5" s="2">
-        <v>35</v>
+        <v>35.9</v>
       </c>
       <c r="H5">
         <v>6</v>
@@ -7261,22 +7467,22 @@
         <v>9</v>
       </c>
       <c r="B6" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C6">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D6">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E6">
         <v>14</v>
       </c>
       <c r="F6" s="2">
-        <v>65</v>
+        <v>64.09999999999999</v>
       </c>
       <c r="G6" s="2">
-        <v>35</v>
+        <v>35.9</v>
       </c>
       <c r="H6">
         <v>6.7</v>
@@ -7293,25 +7499,25 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C7">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D7">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E7">
         <v>7</v>
       </c>
       <c r="F7" s="2">
-        <v>82.5</v>
+        <v>82.09999999999999</v>
       </c>
       <c r="G7" s="2">
-        <v>17.5</v>
+        <v>17.9</v>
       </c>
       <c r="H7">
-        <v>6.8</v>
+        <v>6.7</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -7325,22 +7531,22 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C8">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D8">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E8">
         <v>7</v>
       </c>
       <c r="F8" s="2">
-        <v>82.5</v>
+        <v>82.09999999999999</v>
       </c>
       <c r="G8" s="2">
-        <v>17.5</v>
+        <v>17.9</v>
       </c>
       <c r="H8">
         <v>6.5</v>
@@ -7354,10 +7560,10 @@
     </row>
     <row r="9" spans="1:10">
       <c r="A9" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B9" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C9">
         <v>0</v>
@@ -7379,7 +7585,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F41"/>
+  <dimension ref="A1:F40"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -7388,16 +7594,16 @@
   <sheetData>
     <row r="1" spans="1:6">
       <c r="A1" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="C1" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>75</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>76</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>0</v>
@@ -7411,19 +7617,19 @@
         <v>23330051920218</v>
       </c>
       <c r="B2" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C2" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="D2" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="E2" t="s">
         <v>10</v>
       </c>
       <c r="F2" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="3" spans="1:6">
@@ -7431,19 +7637,19 @@
         <v>23330051920219</v>
       </c>
       <c r="B3" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C3" t="s">
-        <v>104</v>
+        <v>110</v>
       </c>
       <c r="D3" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="E3" t="s">
         <v>10</v>
       </c>
       <c r="F3" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -7451,19 +7657,19 @@
         <v>23330051920217</v>
       </c>
       <c r="B4" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C4" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="D4" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="E4" t="s">
         <v>10</v>
       </c>
       <c r="F4" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -7471,19 +7677,19 @@
         <v>23330051920220</v>
       </c>
       <c r="B5" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C5" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="D5" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="E5" t="s">
         <v>10</v>
       </c>
       <c r="F5" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="6" spans="1:6">
@@ -7491,19 +7697,19 @@
         <v>23330051920221</v>
       </c>
       <c r="B6" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C6" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="D6" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="E6" t="s">
         <v>10</v>
       </c>
       <c r="F6" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="7" spans="1:6">
@@ -7511,19 +7717,19 @@
         <v>23330051920223</v>
       </c>
       <c r="B7" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C7" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D7" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="E7" t="s">
         <v>10</v>
       </c>
       <c r="F7" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -7531,19 +7737,19 @@
         <v>23330051920222</v>
       </c>
       <c r="B8" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C8" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D8" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="E8" t="s">
         <v>10</v>
       </c>
       <c r="F8" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -7551,19 +7757,19 @@
         <v>23330051920224</v>
       </c>
       <c r="B9" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C9" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="D9" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="E9" t="s">
         <v>10</v>
       </c>
       <c r="F9" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -7571,19 +7777,19 @@
         <v>23330051920225</v>
       </c>
       <c r="B10" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C10" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D10" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="E10" t="s">
         <v>10</v>
       </c>
       <c r="F10" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -7591,19 +7797,19 @@
         <v>23330051920228</v>
       </c>
       <c r="B11" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C11" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D11" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="E11" t="s">
         <v>10</v>
       </c>
       <c r="F11" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -7611,19 +7817,19 @@
         <v>23330051920230</v>
       </c>
       <c r="B12" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C12" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="D12" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="E12" t="s">
         <v>10</v>
       </c>
       <c r="F12" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="13" spans="1:6">
@@ -7631,19 +7837,19 @@
         <v>23330051920229</v>
       </c>
       <c r="B13" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C13" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="D13" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="E13" t="s">
         <v>10</v>
       </c>
       <c r="F13" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="14" spans="1:6">
@@ -7651,19 +7857,19 @@
         <v>23330051920231</v>
       </c>
       <c r="B14" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C14" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="D14" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="E14" t="s">
         <v>10</v>
       </c>
       <c r="F14" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="15" spans="1:6">
@@ -7671,19 +7877,19 @@
         <v>23330051920232</v>
       </c>
       <c r="B15" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C15" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D15" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="E15" t="s">
         <v>10</v>
       </c>
       <c r="F15" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="16" spans="1:6">
@@ -7691,19 +7897,19 @@
         <v>23330051920233</v>
       </c>
       <c r="B16" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C16" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="D16" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="E16" t="s">
         <v>10</v>
       </c>
       <c r="F16" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="17" spans="1:6">
@@ -7711,19 +7917,19 @@
         <v>23330051920234</v>
       </c>
       <c r="B17" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C17" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="D17" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="E17" t="s">
         <v>10</v>
       </c>
       <c r="F17" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="18" spans="1:6">
@@ -7731,19 +7937,19 @@
         <v>23330051920235</v>
       </c>
       <c r="B18" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C18" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="D18" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="E18" t="s">
         <v>10</v>
       </c>
       <c r="F18" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="19" spans="1:6">
@@ -7751,19 +7957,19 @@
         <v>23330051920236</v>
       </c>
       <c r="B19" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C19" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="D19" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="E19" t="s">
         <v>10</v>
       </c>
       <c r="F19" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="20" spans="1:6">
@@ -7771,19 +7977,19 @@
         <v>23330051920238</v>
       </c>
       <c r="B20" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C20" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="D20" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="E20" t="s">
         <v>10</v>
       </c>
       <c r="F20" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="21" spans="1:6">
@@ -7791,19 +7997,19 @@
         <v>23330051920271</v>
       </c>
       <c r="B21" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C21" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="D21" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="E21" t="s">
         <v>10</v>
       </c>
       <c r="F21" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="22" spans="1:6">
@@ -7811,19 +8017,19 @@
         <v>23330051920241</v>
       </c>
       <c r="B22" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C22" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="D22" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="E22" t="s">
         <v>10</v>
       </c>
       <c r="F22" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="23" spans="1:6">
@@ -7831,19 +8037,19 @@
         <v>23330051920243</v>
       </c>
       <c r="B23" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C23" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="D23" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="E23" t="s">
         <v>10</v>
       </c>
       <c r="F23" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="24" spans="1:6">
@@ -7851,19 +8057,19 @@
         <v>23330051920335</v>
       </c>
       <c r="B24" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C24" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="D24" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="E24" t="s">
         <v>10</v>
       </c>
       <c r="F24" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="25" spans="1:6">
@@ -7871,19 +8077,19 @@
         <v>23330051920245</v>
       </c>
       <c r="B25" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C25" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="D25" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="E25" t="s">
         <v>10</v>
       </c>
       <c r="F25" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="26" spans="1:6">
@@ -7891,19 +8097,19 @@
         <v>23330051920247</v>
       </c>
       <c r="B26" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C26" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="D26" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="E26" t="s">
         <v>10</v>
       </c>
       <c r="F26" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="27" spans="1:6">
@@ -7911,19 +8117,19 @@
         <v>23330051920249</v>
       </c>
       <c r="B27" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C27" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="D27" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="E27" t="s">
         <v>10</v>
       </c>
       <c r="F27" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="28" spans="1:6">
@@ -7931,19 +8137,19 @@
         <v>23330051920251</v>
       </c>
       <c r="B28" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C28" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D28" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="E28" t="s">
         <v>10</v>
       </c>
       <c r="F28" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="29" spans="1:6">
@@ -7951,19 +8157,19 @@
         <v>23330051920253</v>
       </c>
       <c r="B29" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C29" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="D29" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="E29" t="s">
         <v>10</v>
       </c>
       <c r="F29" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="30" spans="1:6">
@@ -7971,19 +8177,19 @@
         <v>23330051920334</v>
       </c>
       <c r="B30" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C30" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="D30" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="E30" t="s">
         <v>10</v>
       </c>
       <c r="F30" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="31" spans="1:6">
@@ -7991,19 +8197,19 @@
         <v>23330051920318</v>
       </c>
       <c r="B31" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C31" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="D31" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="E31" t="s">
         <v>10</v>
       </c>
       <c r="F31" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="32" spans="1:6">
@@ -8011,19 +8217,19 @@
         <v>23330051920355</v>
       </c>
       <c r="B32" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C32" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="D32" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="E32" t="s">
         <v>10</v>
       </c>
       <c r="F32" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="33" spans="1:6">
@@ -8031,179 +8237,159 @@
         <v>23330051920258</v>
       </c>
       <c r="B33" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C33" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="D33" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="E33" t="s">
         <v>10</v>
       </c>
       <c r="F33" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="34" spans="1:6">
       <c r="A34">
-        <v>23330051920261</v>
+        <v>23330051920264</v>
       </c>
       <c r="B34" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C34" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="D34" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="E34" t="s">
         <v>10</v>
       </c>
       <c r="F34" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="35" spans="1:6">
       <c r="A35">
-        <v>23330051920264</v>
+        <v>23330051920361</v>
       </c>
       <c r="B35" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C35" t="s">
-        <v>135</v>
+        <v>126</v>
       </c>
       <c r="D35" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="E35" t="s">
         <v>10</v>
       </c>
       <c r="F35" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="36" spans="1:6">
       <c r="A36">
-        <v>23330051920361</v>
+        <v>23330051920359</v>
       </c>
       <c r="B36" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C36" t="s">
-        <v>127</v>
+        <v>134</v>
       </c>
       <c r="D36" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="E36" t="s">
         <v>10</v>
       </c>
       <c r="F36" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="37" spans="1:6">
       <c r="A37">
-        <v>23330051920359</v>
+        <v>23330051920265</v>
       </c>
       <c r="B37" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="C37" t="s">
-        <v>136</v>
+        <v>98</v>
       </c>
       <c r="D37" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="E37" t="s">
         <v>10</v>
       </c>
       <c r="F37" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="38" spans="1:6">
       <c r="A38">
-        <v>23330051920265</v>
+        <v>23330051920267</v>
       </c>
       <c r="B38" t="s">
         <v>106</v>
       </c>
       <c r="C38" t="s">
-        <v>99</v>
+        <v>123</v>
       </c>
       <c r="D38" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="E38" t="s">
         <v>10</v>
       </c>
       <c r="F38" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="39" spans="1:6">
       <c r="A39">
-        <v>23330051920267</v>
+        <v>23330051920273</v>
       </c>
       <c r="B39" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C39" t="s">
-        <v>124</v>
+        <v>87</v>
       </c>
       <c r="D39" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="E39" t="s">
         <v>10</v>
       </c>
       <c r="F39" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="40" spans="1:6">
       <c r="A40">
-        <v>23330051920273</v>
+        <v>23330051920268</v>
       </c>
       <c r="B40" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C40" t="s">
-        <v>88</v>
+        <v>135</v>
       </c>
       <c r="D40" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="E40" t="s">
         <v>10</v>
       </c>
       <c r="F40" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="41" spans="1:6">
-      <c r="A41">
-        <v>23330051920268</v>
-      </c>
-      <c r="B41" t="s">
-        <v>110</v>
-      </c>
-      <c r="C41" t="s">
-        <v>137</v>
-      </c>
-      <c r="D41" t="s">
-        <v>176</v>
-      </c>
-      <c r="E41" t="s">
-        <v>10</v>
-      </c>
-      <c r="F41" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
   </sheetData>
@@ -8222,22 +8408,22 @@
   <sheetData>
     <row r="1" spans="1:7">
       <c r="A1" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="C1" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="D1" s="1" t="s">
-        <v>76</v>
-      </c>
       <c r="E1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>4</v>
@@ -8248,19 +8434,19 @@
         <v>23330051920217</v>
       </c>
       <c r="B2" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C2" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="D2" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="E2" t="s">
         <v>10</v>
       </c>
       <c r="F2" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="G2">
         <v>-1</v>
@@ -8271,19 +8457,19 @@
         <v>23330051920217</v>
       </c>
       <c r="B3" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C3" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="D3" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="E3" t="s">
         <v>11</v>
       </c>
       <c r="F3" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="G3">
         <v>5</v>
@@ -8294,19 +8480,19 @@
         <v>23330051920220</v>
       </c>
       <c r="B4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C4" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="D4" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="E4" t="s">
         <v>10</v>
       </c>
       <c r="F4" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="G4">
         <v>-1</v>
@@ -8317,19 +8503,19 @@
         <v>23330051920220</v>
       </c>
       <c r="B5" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C5" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="D5" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="E5" t="s">
         <v>11</v>
       </c>
       <c r="F5" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="G5">
         <v>5</v>
@@ -8340,19 +8526,19 @@
         <v>23330051920221</v>
       </c>
       <c r="B6" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C6" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="D6" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="E6" t="s">
         <v>10</v>
       </c>
       <c r="F6" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="G6">
         <v>-1</v>
@@ -8363,19 +8549,19 @@
         <v>23330051920221</v>
       </c>
       <c r="B7" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C7" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="D7" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="E7" t="s">
         <v>11</v>
       </c>
       <c r="F7" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="G7">
         <v>5</v>
@@ -8386,19 +8572,19 @@
         <v>23330051920222</v>
       </c>
       <c r="B8" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C8" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D8" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="E8" t="s">
         <v>9</v>
       </c>
       <c r="F8" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="G8">
         <v>5</v>
@@ -8409,19 +8595,19 @@
         <v>23330051920222</v>
       </c>
       <c r="B9" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C9" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D9" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="E9" t="s">
         <v>10</v>
       </c>
       <c r="F9" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="G9">
         <v>-1</v>
@@ -8432,19 +8618,19 @@
         <v>23330051920247</v>
       </c>
       <c r="B10" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C10" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="D10" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="E10" t="s">
         <v>5</v>
       </c>
       <c r="F10" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G10">
         <v>5</v>
@@ -8455,19 +8641,19 @@
         <v>23330051920247</v>
       </c>
       <c r="B11" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C11" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="D11" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="E11" t="s">
         <v>10</v>
       </c>
       <c r="F11" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="G11">
         <v>-1</v>
@@ -8478,19 +8664,19 @@
         <v>23330051920251</v>
       </c>
       <c r="B12" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C12" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D12" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="E12" t="s">
         <v>10</v>
       </c>
       <c r="F12" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="G12">
         <v>-1</v>
@@ -8501,19 +8687,19 @@
         <v>23330051920251</v>
       </c>
       <c r="B13" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C13" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D13" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="E13" t="s">
         <v>11</v>
       </c>
       <c r="F13" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="G13">
         <v>5</v>
@@ -8524,19 +8710,19 @@
         <v>23330051920253</v>
       </c>
       <c r="B14" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C14" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="D14" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="E14" t="s">
         <v>10</v>
       </c>
       <c r="F14" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="G14">
         <v>-1</v>
@@ -8547,19 +8733,19 @@
         <v>23330051920253</v>
       </c>
       <c r="B15" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C15" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="D15" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="E15" t="s">
         <v>11</v>
       </c>
       <c r="F15" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="G15">
         <v>5</v>
@@ -8570,19 +8756,19 @@
         <v>23330051920318</v>
       </c>
       <c r="B16" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C16" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="D16" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="E16" t="s">
         <v>5</v>
       </c>
       <c r="F16" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G16">
         <v>5</v>
@@ -8593,19 +8779,19 @@
         <v>23330051920318</v>
       </c>
       <c r="B17" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C17" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="D17" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="E17" t="s">
         <v>10</v>
       </c>
       <c r="F17" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="G17">
         <v>-1</v>
@@ -8616,19 +8802,19 @@
         <v>23330051920218</v>
       </c>
       <c r="B18" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C18" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="D18" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="E18" t="s">
         <v>10</v>
       </c>
       <c r="F18" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="G18">
         <v>-1</v>
@@ -8639,19 +8825,19 @@
         <v>23330051920223</v>
       </c>
       <c r="B19" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C19" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D19" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="E19" t="s">
         <v>10</v>
       </c>
       <c r="F19" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="G19">
         <v>-1</v>
@@ -8662,19 +8848,19 @@
         <v>23330051920224</v>
       </c>
       <c r="B20" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C20" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="D20" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="E20" t="s">
         <v>10</v>
       </c>
       <c r="F20" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="G20">
         <v>-1</v>
@@ -8685,19 +8871,19 @@
         <v>23330051920225</v>
       </c>
       <c r="B21" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C21" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D21" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="E21" t="s">
         <v>10</v>
       </c>
       <c r="F21" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="G21">
         <v>-1</v>
@@ -8708,19 +8894,19 @@
         <v>23330051920231</v>
       </c>
       <c r="B22" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C22" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="D22" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="E22" t="s">
         <v>10</v>
       </c>
       <c r="F22" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="G22">
         <v>-1</v>
@@ -8731,19 +8917,19 @@
         <v>23330051920232</v>
       </c>
       <c r="B23" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C23" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D23" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="E23" t="s">
         <v>10</v>
       </c>
       <c r="F23" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="G23">
         <v>-1</v>
@@ -8754,19 +8940,19 @@
         <v>23330051920243</v>
       </c>
       <c r="B24" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C24" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="D24" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="E24" t="s">
         <v>10</v>
       </c>
       <c r="F24" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="G24">
         <v>-1</v>
@@ -8777,19 +8963,19 @@
         <v>23330051920249</v>
       </c>
       <c r="B25" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C25" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="D25" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="E25" t="s">
         <v>10</v>
       </c>
       <c r="F25" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="G25">
         <v>-1</v>
@@ -8800,19 +8986,19 @@
         <v>23330051920258</v>
       </c>
       <c r="B26" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C26" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="D26" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="E26" t="s">
         <v>10</v>
       </c>
       <c r="F26" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="G26">
         <v>-1</v>
@@ -8823,19 +9009,19 @@
         <v>23330051920265</v>
       </c>
       <c r="B27" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="C27" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D27" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="E27" t="s">
         <v>10</v>
       </c>
       <c r="F27" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="G27">
         <v>-1</v>
@@ -8846,19 +9032,19 @@
         <v>23330051920273</v>
       </c>
       <c r="B28" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="C28" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D28" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="E28" t="s">
         <v>10</v>
       </c>
       <c r="F28" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="G28">
         <v>-1</v>

--- a/grupos/1CV - Estadisticos 20231.xlsx
+++ b/grupos/1CV - Estadisticos 20231.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="507" uniqueCount="174">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="232" uniqueCount="98">
   <si>
     <t>Materia</t>
   </si>
@@ -215,27 +215,27 @@
     <t>Recursos socioemocionales I</t>
   </si>
   <si>
+    <t>Rodríguez Román Leticia</t>
+  </si>
+  <si>
+    <t>Villanueva Morales Luis Arturo</t>
+  </si>
+  <si>
+    <t>Gaspar Velazco Juan Francisco</t>
+  </si>
+  <si>
+    <t>Martínez López Miguel Ángel</t>
+  </si>
+  <si>
+    <t>Contreras Díaz Irma Ivette</t>
+  </si>
+  <si>
     <t>Vargas Olvera Francisco Eduardo</t>
   </si>
   <si>
-    <t>Rodríguez Román Leticia</t>
-  </si>
-  <si>
-    <t>Villanueva Morales Luis Arturo</t>
-  </si>
-  <si>
-    <t>Martínez López Miguel Ángel</t>
-  </si>
-  <si>
-    <t>Contreras Díaz Irma Ivette</t>
-  </si>
-  <si>
     <t>Pesce Bautista Victor Manuel</t>
   </si>
   <si>
-    <t>Gaspar Velazco Juan Francisco</t>
-  </si>
-  <si>
     <t>NC</t>
   </si>
   <si>
@@ -248,13 +248,13 @@
     <t>Nombres</t>
   </si>
   <si>
-    <t>ALMANZA</t>
-  </si>
-  <si>
-    <t>ATILANO</t>
-  </si>
-  <si>
-    <t>ALFONSO</t>
+    <t>GARCIA</t>
+  </si>
+  <si>
+    <t>LOPEZ</t>
+  </si>
+  <si>
+    <t>MARQUEZ</t>
   </si>
   <si>
     <t>BARRAGAN</t>
@@ -266,175 +266,37 @@
     <t>CUAPIO</t>
   </si>
   <si>
-    <t>DORANTES</t>
-  </si>
-  <si>
-    <t>FLORES</t>
-  </si>
-  <si>
-    <t>GARCIA</t>
-  </si>
-  <si>
-    <t>GILES</t>
-  </si>
-  <si>
-    <t>GOMEZ</t>
+    <t>MENDEZ</t>
+  </si>
+  <si>
+    <t>SANTIAGO</t>
   </si>
   <si>
     <t>GONZALEZ</t>
   </si>
   <si>
-    <t>GUERRA</t>
-  </si>
-  <si>
-    <t>HERNANDEZ</t>
+    <t>MACUIXTLE</t>
+  </si>
+  <si>
+    <t>CASTILLO</t>
   </si>
   <si>
     <t>HUERTA</t>
   </si>
   <si>
-    <t>IXMATLAHUA</t>
-  </si>
-  <si>
-    <t>JUAREZ</t>
-  </si>
-  <si>
-    <t>LAGUNA</t>
-  </si>
-  <si>
-    <t>LOBATO</t>
-  </si>
-  <si>
-    <t>LOPEZ</t>
-  </si>
-  <si>
-    <t>LUIS</t>
-  </si>
-  <si>
-    <t>MARQUEZ</t>
-  </si>
-  <si>
-    <t>MENDEZ</t>
-  </si>
-  <si>
-    <t>OLAVARRIA</t>
-  </si>
-  <si>
-    <t>PEREZ</t>
-  </si>
-  <si>
-    <t>PICHARDO</t>
-  </si>
-  <si>
-    <t>RAMIREZ</t>
-  </si>
-  <si>
-    <t>SAN JUAN</t>
-  </si>
-  <si>
-    <t>SANCHEZ</t>
-  </si>
-  <si>
-    <t>SALAZAR</t>
-  </si>
-  <si>
-    <t>TEXCAHUA</t>
-  </si>
-  <si>
-    <t>VEGA</t>
-  </si>
-  <si>
-    <t>VELA</t>
-  </si>
-  <si>
     <t>SANTOS</t>
   </si>
   <si>
-    <t>RODRIGUEZ</t>
-  </si>
-  <si>
-    <t>MACUIXTLE</t>
-  </si>
-  <si>
-    <t>CASTILLO</t>
-  </si>
-  <si>
-    <t>PORRAS</t>
-  </si>
-  <si>
-    <t>VAZQUEZ</t>
-  </si>
-  <si>
-    <t>ROSALES</t>
-  </si>
-  <si>
-    <t>SANTIAGO</t>
-  </si>
-  <si>
-    <t>FIGUEROA</t>
-  </si>
-  <si>
-    <t>TZITZIHUA</t>
-  </si>
-  <si>
-    <t>ARIAS</t>
-  </si>
-  <si>
-    <t>ROSAS</t>
-  </si>
-  <si>
-    <t>SARMIENTO</t>
-  </si>
-  <si>
-    <t>ALCANTARA</t>
-  </si>
-  <si>
-    <t>DE LA CRUZ</t>
-  </si>
-  <si>
-    <t>NATH</t>
-  </si>
-  <si>
-    <t>ANTONIO</t>
-  </si>
-  <si>
-    <t>ESPINOZA</t>
-  </si>
-  <si>
-    <t>VERA</t>
-  </si>
-  <si>
     <t>MONDRAGON</t>
   </si>
   <si>
-    <t>ARROYO</t>
-  </si>
-  <si>
-    <t>PAZ</t>
-  </si>
-  <si>
-    <t>MORENO</t>
-  </si>
-  <si>
-    <t>MOLINA</t>
-  </si>
-  <si>
-    <t>AGUILAR</t>
-  </si>
-  <si>
-    <t>DE JESUS</t>
-  </si>
-  <si>
-    <t>LUNA</t>
-  </si>
-  <si>
-    <t>VANESA BETHSABE</t>
-  </si>
-  <si>
-    <t>JAVIER DE JESUS</t>
-  </si>
-  <si>
-    <t>ROSA ICELA</t>
+    <t>MARIANA</t>
+  </si>
+  <si>
+    <t>RAYMUNDO</t>
+  </si>
+  <si>
+    <t>DIEGO GREGORIO</t>
   </si>
   <si>
     <t>MARIA FERNANDA</t>
@@ -443,103 +305,13 @@
     <t>RAMSES</t>
   </si>
   <si>
-    <t>FRANCISCO XAVIER</t>
-  </si>
-  <si>
     <t>JESSICA</t>
   </si>
   <si>
-    <t>ROBERTO</t>
-  </si>
-  <si>
-    <t>MARCO ANTONIO</t>
-  </si>
-  <si>
-    <t>REGINA DAYTRI</t>
-  </si>
-  <si>
     <t>JAIRO</t>
   </si>
   <si>
-    <t>MARIANA</t>
-  </si>
-  <si>
-    <t>ALEXA YAMILET</t>
-  </si>
-  <si>
-    <t>ANGEL GABRIEL</t>
-  </si>
-  <si>
-    <t>MIRIAM</t>
-  </si>
-  <si>
-    <t>ALEX TADEO</t>
-  </si>
-  <si>
-    <t>LIZ AIDE</t>
-  </si>
-  <si>
-    <t>EDUARDO</t>
-  </si>
-  <si>
-    <t>JHON STEVE</t>
-  </si>
-  <si>
-    <t>FERNANDA YAMILET</t>
-  </si>
-  <si>
-    <t>MARYSOL</t>
-  </si>
-  <si>
-    <t>AARON ZACHARY</t>
-  </si>
-  <si>
-    <t>DIANA LAURA</t>
-  </si>
-  <si>
-    <t>ESTEFANIA</t>
-  </si>
-  <si>
-    <t>RAYMUNDO</t>
-  </si>
-  <si>
-    <t>DIEGO GREGORIO</t>
-  </si>
-  <si>
     <t>ANGEL ADRIAN</t>
-  </si>
-  <si>
-    <t>PEDRO MIGUEL</t>
-  </si>
-  <si>
-    <t>SAMIR</t>
-  </si>
-  <si>
-    <t>ABRIL</t>
-  </si>
-  <si>
-    <t>AIDE SCARLET</t>
-  </si>
-  <si>
-    <t>KARINA MONSERRATH</t>
-  </si>
-  <si>
-    <t>RICARDO</t>
-  </si>
-  <si>
-    <t>DAFNE DANAE</t>
-  </si>
-  <si>
-    <t>KAREN</t>
-  </si>
-  <si>
-    <t>KARINA</t>
-  </si>
-  <si>
-    <t>MIREILLE</t>
-  </si>
-  <si>
-    <t>YAEL EMMANUEL</t>
   </si>
 </sst>
 </file>
@@ -1060,19 +832,19 @@
         <v>7</v>
       </c>
       <c r="G4">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="H4">
         <v>5</v>
       </c>
       <c r="I4">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="J4">
         <v>-1</v>
       </c>
       <c r="K4">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L4">
         <v>-1</v>
@@ -1081,7 +853,7 @@
         <v>-1</v>
       </c>
       <c r="N4">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O4">
         <v>-1</v>
@@ -1108,13 +880,13 @@
         <v>-1</v>
       </c>
       <c r="W4">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="X4">
         <v>7</v>
       </c>
       <c r="Y4">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Z4">
         <v>6</v>
@@ -1123,7 +895,7 @@
         <v>7</v>
       </c>
       <c r="AB4">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AC4">
         <v>5</v>
@@ -1149,19 +921,19 @@
         <v>8</v>
       </c>
       <c r="G5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="H5">
         <v>6</v>
       </c>
       <c r="I5">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J5">
         <v>-1</v>
       </c>
       <c r="K5">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L5">
         <v>-1</v>
@@ -1170,7 +942,7 @@
         <v>-1</v>
       </c>
       <c r="N5">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O5">
         <v>-1</v>
@@ -1197,7 +969,7 @@
         <v>-1</v>
       </c>
       <c r="W5">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X5">
         <v>8</v>
@@ -1212,7 +984,7 @@
         <v>8</v>
       </c>
       <c r="AB5">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AC5">
         <v>6</v>
@@ -1238,19 +1010,19 @@
         <v>5</v>
       </c>
       <c r="G6">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="H6">
         <v>5</v>
       </c>
       <c r="I6">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J6">
         <v>-1</v>
       </c>
       <c r="K6">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="L6">
         <v>-1</v>
@@ -1259,7 +1031,7 @@
         <v>-1</v>
       </c>
       <c r="N6">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O6">
         <v>-1</v>
@@ -1292,7 +1064,7 @@
         <v>8</v>
       </c>
       <c r="Y6">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="Z6">
         <v>5</v>
@@ -1301,7 +1073,7 @@
         <v>5</v>
       </c>
       <c r="AB6">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AC6">
         <v>5</v>
@@ -1327,19 +1099,19 @@
         <v>9</v>
       </c>
       <c r="G7">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="H7">
         <v>5</v>
       </c>
       <c r="I7">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J7">
         <v>-1</v>
       </c>
       <c r="K7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L7">
         <v>-1</v>
@@ -1348,7 +1120,7 @@
         <v>-1</v>
       </c>
       <c r="N7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O7">
         <v>-1</v>
@@ -1381,7 +1153,7 @@
         <v>7</v>
       </c>
       <c r="Y7">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Z7">
         <v>6</v>
@@ -1390,7 +1162,7 @@
         <v>9</v>
       </c>
       <c r="AB7">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AC7">
         <v>5</v>
@@ -1416,19 +1188,19 @@
         <v>6</v>
       </c>
       <c r="G8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="H8">
         <v>5</v>
       </c>
       <c r="I8">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J8">
         <v>-1</v>
       </c>
       <c r="K8">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L8">
         <v>-1</v>
@@ -1437,7 +1209,7 @@
         <v>-1</v>
       </c>
       <c r="N8">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O8">
         <v>-1</v>
@@ -1479,7 +1251,7 @@
         <v>6</v>
       </c>
       <c r="AB8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AC8">
         <v>5</v>
@@ -1505,19 +1277,19 @@
         <v>6</v>
       </c>
       <c r="G9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="H9">
         <v>6</v>
       </c>
       <c r="I9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J9">
         <v>-1</v>
       </c>
       <c r="K9">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L9">
         <v>-1</v>
@@ -1526,7 +1298,7 @@
         <v>-1</v>
       </c>
       <c r="N9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O9">
         <v>-1</v>
@@ -1553,13 +1325,13 @@
         <v>-1</v>
       </c>
       <c r="W9">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X9">
         <v>6</v>
       </c>
       <c r="Y9">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Z9">
         <v>7</v>
@@ -1568,7 +1340,7 @@
         <v>6</v>
       </c>
       <c r="AB9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AC9">
         <v>6</v>
@@ -1594,19 +1366,19 @@
         <v>5</v>
       </c>
       <c r="G10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="H10">
         <v>6</v>
       </c>
       <c r="I10">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J10">
         <v>-1</v>
       </c>
       <c r="K10">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L10">
         <v>-1</v>
@@ -1615,7 +1387,7 @@
         <v>-1</v>
       </c>
       <c r="N10">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O10">
         <v>-1</v>
@@ -1657,7 +1429,7 @@
         <v>5</v>
       </c>
       <c r="AB10">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AC10">
         <v>6</v>
@@ -1683,19 +1455,19 @@
         <v>7</v>
       </c>
       <c r="G11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="H11">
         <v>6</v>
       </c>
       <c r="I11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J11">
         <v>-1</v>
       </c>
       <c r="K11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L11">
         <v>-1</v>
@@ -1704,7 +1476,7 @@
         <v>-1</v>
       </c>
       <c r="N11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O11">
         <v>-1</v>
@@ -1746,7 +1518,7 @@
         <v>7</v>
       </c>
       <c r="AB11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AC11">
         <v>6</v>
@@ -1772,19 +1544,19 @@
         <v>8</v>
       </c>
       <c r="G12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="H12">
         <v>6</v>
       </c>
       <c r="I12">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J12">
         <v>-1</v>
       </c>
       <c r="K12">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L12">
         <v>-1</v>
@@ -1793,7 +1565,7 @@
         <v>-1</v>
       </c>
       <c r="N12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O12">
         <v>-1</v>
@@ -1820,7 +1592,7 @@
         <v>-1</v>
       </c>
       <c r="W12">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X12">
         <v>7</v>
@@ -1835,7 +1607,7 @@
         <v>8</v>
       </c>
       <c r="AB12">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AC12">
         <v>6</v>
@@ -1861,19 +1633,19 @@
         <v>9</v>
       </c>
       <c r="G13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="H13">
         <v>6</v>
       </c>
       <c r="I13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J13">
         <v>-1</v>
       </c>
       <c r="K13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L13">
         <v>-1</v>
@@ -1882,7 +1654,7 @@
         <v>-1</v>
       </c>
       <c r="N13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O13">
         <v>-1</v>
@@ -1924,7 +1696,7 @@
         <v>9</v>
       </c>
       <c r="AB13">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AC13">
         <v>6</v>
@@ -1950,19 +1722,19 @@
         <v>5</v>
       </c>
       <c r="G14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="H14">
         <v>5</v>
       </c>
       <c r="I14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J14">
         <v>-1</v>
       </c>
       <c r="K14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L14">
         <v>-1</v>
@@ -1971,7 +1743,7 @@
         <v>-1</v>
       </c>
       <c r="N14">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O14">
         <v>-1</v>
@@ -2013,7 +1785,7 @@
         <v>5</v>
       </c>
       <c r="AB14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AC14">
         <v>5</v>
@@ -2039,19 +1811,19 @@
         <v>8</v>
       </c>
       <c r="G15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="H15">
         <v>5</v>
       </c>
       <c r="I15">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J15">
         <v>-1</v>
       </c>
       <c r="K15">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L15">
         <v>-1</v>
@@ -2060,7 +1832,7 @@
         <v>-1</v>
       </c>
       <c r="N15">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O15">
         <v>-1</v>
@@ -2087,13 +1859,13 @@
         <v>-1</v>
       </c>
       <c r="W15">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="X15">
         <v>7</v>
       </c>
       <c r="Y15">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Z15">
         <v>6</v>
@@ -2102,7 +1874,7 @@
         <v>8</v>
       </c>
       <c r="AB15">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AC15">
         <v>5</v>
@@ -2128,19 +1900,19 @@
         <v>8</v>
       </c>
       <c r="G16">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="H16">
         <v>6</v>
       </c>
       <c r="I16">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J16">
         <v>-1</v>
       </c>
       <c r="K16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L16">
         <v>-1</v>
@@ -2149,7 +1921,7 @@
         <v>-1</v>
       </c>
       <c r="N16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O16">
         <v>-1</v>
@@ -2176,13 +1948,13 @@
         <v>-1</v>
       </c>
       <c r="W16">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X16">
         <v>7</v>
       </c>
       <c r="Y16">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Z16">
         <v>7</v>
@@ -2191,7 +1963,7 @@
         <v>8</v>
       </c>
       <c r="AB16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AC16">
         <v>6</v>
@@ -2217,19 +1989,19 @@
         <v>9</v>
       </c>
       <c r="G17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="H17">
         <v>6</v>
       </c>
       <c r="I17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J17">
         <v>-1</v>
       </c>
       <c r="K17">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L17">
         <v>-1</v>
@@ -2238,7 +2010,7 @@
         <v>-1</v>
       </c>
       <c r="N17">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O17">
         <v>-1</v>
@@ -2265,13 +2037,13 @@
         <v>-1</v>
       </c>
       <c r="W17">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X17">
         <v>7</v>
       </c>
       <c r="Y17">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Z17">
         <v>7</v>
@@ -2280,7 +2052,7 @@
         <v>9</v>
       </c>
       <c r="AB17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AC17">
         <v>6</v>
@@ -2306,19 +2078,19 @@
         <v>5</v>
       </c>
       <c r="G18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="H18">
         <v>5</v>
       </c>
       <c r="I18">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="J18">
         <v>-1</v>
       </c>
       <c r="K18">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L18">
         <v>-1</v>
@@ -2327,7 +2099,7 @@
         <v>-1</v>
       </c>
       <c r="N18">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O18">
         <v>-1</v>
@@ -2354,7 +2126,7 @@
         <v>-1</v>
       </c>
       <c r="W18">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="X18">
         <v>7</v>
@@ -2369,7 +2141,7 @@
         <v>5</v>
       </c>
       <c r="AB18">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AC18">
         <v>5</v>
@@ -2395,19 +2167,19 @@
         <v>5</v>
       </c>
       <c r="G19">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="H19">
         <v>5</v>
       </c>
       <c r="I19">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J19">
         <v>-1</v>
       </c>
       <c r="K19">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L19">
         <v>-1</v>
@@ -2416,7 +2188,7 @@
         <v>-1</v>
       </c>
       <c r="N19">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O19">
         <v>-1</v>
@@ -2458,7 +2230,7 @@
         <v>5</v>
       </c>
       <c r="AB19">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AC19">
         <v>5</v>
@@ -2484,19 +2256,19 @@
         <v>5</v>
       </c>
       <c r="G20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="H20">
         <v>5</v>
       </c>
       <c r="I20">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J20">
         <v>-1</v>
       </c>
       <c r="K20">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="L20">
         <v>-1</v>
@@ -2505,7 +2277,7 @@
         <v>-1</v>
       </c>
       <c r="N20">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O20">
         <v>-1</v>
@@ -2547,7 +2319,7 @@
         <v>5</v>
       </c>
       <c r="AB20">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AC20">
         <v>5</v>
@@ -2573,19 +2345,19 @@
         <v>5</v>
       </c>
       <c r="G21">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="H21">
         <v>6</v>
       </c>
       <c r="I21">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J21">
         <v>-1</v>
       </c>
       <c r="K21">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L21">
         <v>-1</v>
@@ -2594,7 +2366,7 @@
         <v>-1</v>
       </c>
       <c r="N21">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O21">
         <v>-1</v>
@@ -2636,7 +2408,7 @@
         <v>5</v>
       </c>
       <c r="AB21">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AC21">
         <v>6</v>
@@ -2662,19 +2434,19 @@
         <v>5</v>
       </c>
       <c r="G22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="H22">
         <v>5</v>
       </c>
       <c r="I22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J22">
         <v>-1</v>
       </c>
       <c r="K22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L22">
         <v>-1</v>
@@ -2683,7 +2455,7 @@
         <v>-1</v>
       </c>
       <c r="N22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O22">
         <v>-1</v>
@@ -2716,7 +2488,7 @@
         <v>6</v>
       </c>
       <c r="Y22">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Z22">
         <v>5</v>
@@ -2725,7 +2497,7 @@
         <v>5</v>
       </c>
       <c r="AB22">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AC22">
         <v>5</v>
@@ -2751,19 +2523,19 @@
         <v>9</v>
       </c>
       <c r="G23">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="H23">
         <v>5</v>
       </c>
       <c r="I23">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J23">
         <v>-1</v>
       </c>
       <c r="K23">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L23">
         <v>-1</v>
@@ -2772,7 +2544,7 @@
         <v>-1</v>
       </c>
       <c r="N23">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O23">
         <v>-1</v>
@@ -2805,7 +2577,7 @@
         <v>7</v>
       </c>
       <c r="Y23">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Z23">
         <v>5</v>
@@ -2814,7 +2586,7 @@
         <v>9</v>
       </c>
       <c r="AB23">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AC23">
         <v>5</v>
@@ -2840,19 +2612,19 @@
         <v>5</v>
       </c>
       <c r="G24">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="H24">
         <v>5</v>
       </c>
       <c r="I24">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J24">
         <v>-1</v>
       </c>
       <c r="K24">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L24">
         <v>-1</v>
@@ -2861,7 +2633,7 @@
         <v>-1</v>
       </c>
       <c r="N24">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O24">
         <v>-1</v>
@@ -2888,7 +2660,7 @@
         <v>-1</v>
       </c>
       <c r="W24">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X24">
         <v>6</v>
@@ -2903,7 +2675,7 @@
         <v>5</v>
       </c>
       <c r="AB24">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AC24">
         <v>5</v>
@@ -2929,19 +2701,19 @@
         <v>7</v>
       </c>
       <c r="G25">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="H25">
         <v>7</v>
       </c>
       <c r="I25">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J25">
         <v>-1</v>
       </c>
       <c r="K25">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L25">
         <v>-1</v>
@@ -2950,7 +2722,7 @@
         <v>-1</v>
       </c>
       <c r="N25">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O25">
         <v>-1</v>
@@ -2977,13 +2749,13 @@
         <v>-1</v>
       </c>
       <c r="W25">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="X25">
         <v>8</v>
       </c>
       <c r="Y25">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Z25">
         <v>6</v>
@@ -2992,7 +2764,7 @@
         <v>7</v>
       </c>
       <c r="AB25">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AC25">
         <v>7</v>
@@ -3018,19 +2790,19 @@
         <v>5</v>
       </c>
       <c r="G26">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="H26">
         <v>6</v>
       </c>
       <c r="I26">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J26">
         <v>-1</v>
       </c>
       <c r="K26">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L26">
         <v>-1</v>
@@ -3039,7 +2811,7 @@
         <v>-1</v>
       </c>
       <c r="N26">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O26">
         <v>-1</v>
@@ -3072,7 +2844,7 @@
         <v>5</v>
       </c>
       <c r="Y26">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Z26">
         <v>5</v>
@@ -3081,7 +2853,7 @@
         <v>5</v>
       </c>
       <c r="AB26">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AC26">
         <v>6</v>
@@ -3107,19 +2879,19 @@
         <v>6</v>
       </c>
       <c r="G27">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="H27">
         <v>5</v>
       </c>
       <c r="I27">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J27">
         <v>-1</v>
       </c>
       <c r="K27">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="L27">
         <v>-1</v>
@@ -3128,7 +2900,7 @@
         <v>-1</v>
       </c>
       <c r="N27">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O27">
         <v>-1</v>
@@ -3161,7 +2933,7 @@
         <v>7</v>
       </c>
       <c r="Y27">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Z27">
         <v>5</v>
@@ -3170,7 +2942,7 @@
         <v>6</v>
       </c>
       <c r="AB27">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AC27">
         <v>5</v>
@@ -3196,19 +2968,19 @@
         <v>9</v>
       </c>
       <c r="G28">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="H28">
         <v>6</v>
       </c>
       <c r="I28">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J28">
         <v>-1</v>
       </c>
       <c r="K28">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L28">
         <v>-1</v>
@@ -3217,7 +2989,7 @@
         <v>-1</v>
       </c>
       <c r="N28">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O28">
         <v>-1</v>
@@ -3250,7 +3022,7 @@
         <v>7</v>
       </c>
       <c r="Y28">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Z28">
         <v>6</v>
@@ -3259,7 +3031,7 @@
         <v>9</v>
       </c>
       <c r="AB28">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AC28">
         <v>6</v>
@@ -3285,19 +3057,19 @@
         <v>8</v>
       </c>
       <c r="G29">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="H29">
         <v>6</v>
       </c>
       <c r="I29">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J29">
         <v>-1</v>
       </c>
       <c r="K29">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L29">
         <v>-1</v>
@@ -3306,7 +3078,7 @@
         <v>-1</v>
       </c>
       <c r="N29">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O29">
         <v>-1</v>
@@ -3333,13 +3105,13 @@
         <v>-1</v>
       </c>
       <c r="W29">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X29">
         <v>7</v>
       </c>
       <c r="Y29">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Z29">
         <v>6</v>
@@ -3348,7 +3120,7 @@
         <v>8</v>
       </c>
       <c r="AB29">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AC29">
         <v>6</v>
@@ -3374,19 +3146,19 @@
         <v>8</v>
       </c>
       <c r="G30">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="H30">
         <v>5</v>
       </c>
       <c r="I30">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J30">
         <v>-1</v>
       </c>
       <c r="K30">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L30">
         <v>-1</v>
@@ -3395,7 +3167,7 @@
         <v>-1</v>
       </c>
       <c r="N30">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O30">
         <v>-1</v>
@@ -3422,7 +3194,7 @@
         <v>-1</v>
       </c>
       <c r="W30">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X30">
         <v>8</v>
@@ -3437,7 +3209,7 @@
         <v>8</v>
       </c>
       <c r="AB30">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AC30">
         <v>5</v>
@@ -3463,19 +3235,19 @@
         <v>7</v>
       </c>
       <c r="G31">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="H31">
         <v>5</v>
       </c>
       <c r="I31">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J31">
         <v>-1</v>
       </c>
       <c r="K31">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L31">
         <v>-1</v>
@@ -3484,7 +3256,7 @@
         <v>-1</v>
       </c>
       <c r="N31">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O31">
         <v>-1</v>
@@ -3511,13 +3283,13 @@
         <v>-1</v>
       </c>
       <c r="W31">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X31">
         <v>7</v>
       </c>
       <c r="Y31">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="Z31">
         <v>6</v>
@@ -3526,7 +3298,7 @@
         <v>7</v>
       </c>
       <c r="AB31">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AC31">
         <v>5</v>
@@ -3552,19 +3324,19 @@
         <v>5</v>
       </c>
       <c r="G32">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="H32">
         <v>5</v>
       </c>
       <c r="I32">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J32">
         <v>-1</v>
       </c>
       <c r="K32">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="L32">
         <v>-1</v>
@@ -3573,7 +3345,7 @@
         <v>-1</v>
       </c>
       <c r="N32">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O32">
         <v>-1</v>
@@ -3615,7 +3387,7 @@
         <v>5</v>
       </c>
       <c r="AB32">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AC32">
         <v>5</v>
@@ -3641,19 +3413,19 @@
         <v>10</v>
       </c>
       <c r="G33">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="H33">
         <v>6</v>
       </c>
       <c r="I33">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J33">
         <v>-1</v>
       </c>
       <c r="K33">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L33">
         <v>-1</v>
@@ -3662,7 +3434,7 @@
         <v>-1</v>
       </c>
       <c r="N33">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O33">
         <v>-1</v>
@@ -3689,7 +3461,7 @@
         <v>-1</v>
       </c>
       <c r="W33">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="X33">
         <v>8</v>
@@ -3704,7 +3476,7 @@
         <v>10</v>
       </c>
       <c r="AB33">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AC33">
         <v>6</v>
@@ -3730,19 +3502,19 @@
         <v>6</v>
       </c>
       <c r="G34">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="H34">
         <v>5</v>
       </c>
       <c r="I34">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J34">
         <v>-1</v>
       </c>
       <c r="K34">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L34">
         <v>-1</v>
@@ -3751,7 +3523,7 @@
         <v>-1</v>
       </c>
       <c r="N34">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O34">
         <v>-1</v>
@@ -3793,7 +3565,7 @@
         <v>6</v>
       </c>
       <c r="AB34">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AC34">
         <v>5</v>
@@ -3819,19 +3591,19 @@
         <v>8</v>
       </c>
       <c r="G35">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="H35">
         <v>6</v>
       </c>
       <c r="I35">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J35">
         <v>-1</v>
       </c>
       <c r="K35">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L35">
         <v>-1</v>
@@ -3840,7 +3612,7 @@
         <v>-1</v>
       </c>
       <c r="N35">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O35">
         <v>-1</v>
@@ -3867,13 +3639,13 @@
         <v>-1</v>
       </c>
       <c r="W35">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X35">
         <v>8</v>
       </c>
       <c r="Y35">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Z35">
         <v>9</v>
@@ -3882,7 +3654,7 @@
         <v>8</v>
       </c>
       <c r="AB35">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AC35">
         <v>6</v>
@@ -3908,19 +3680,19 @@
         <v>6</v>
       </c>
       <c r="G36">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="H36">
         <v>5</v>
       </c>
       <c r="I36">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J36">
         <v>-1</v>
       </c>
       <c r="K36">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="L36">
         <v>-1</v>
@@ -3929,7 +3701,7 @@
         <v>-1</v>
       </c>
       <c r="N36">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O36">
         <v>-1</v>
@@ -3956,13 +3728,13 @@
         <v>-1</v>
       </c>
       <c r="W36">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="X36">
         <v>5</v>
       </c>
       <c r="Y36">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Z36">
         <v>5</v>
@@ -3971,7 +3743,7 @@
         <v>6</v>
       </c>
       <c r="AB36">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AC36">
         <v>5</v>
@@ -3997,19 +3769,19 @@
         <v>5</v>
       </c>
       <c r="G37">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="H37">
         <v>5</v>
       </c>
       <c r="I37">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J37">
         <v>-1</v>
       </c>
       <c r="K37">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L37">
         <v>-1</v>
@@ -4018,7 +3790,7 @@
         <v>-1</v>
       </c>
       <c r="N37">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O37">
         <v>-1</v>
@@ -4045,13 +3817,13 @@
         <v>-1</v>
       </c>
       <c r="W37">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X37">
         <v>7</v>
       </c>
       <c r="Y37">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Z37">
         <v>5</v>
@@ -4060,7 +3832,7 @@
         <v>5</v>
       </c>
       <c r="AB37">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AC37">
         <v>5</v>
@@ -4086,19 +3858,19 @@
         <v>6</v>
       </c>
       <c r="G38">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="H38">
         <v>5</v>
       </c>
       <c r="I38">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J38">
         <v>-1</v>
       </c>
       <c r="K38">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L38">
         <v>-1</v>
@@ -4107,7 +3879,7 @@
         <v>-1</v>
       </c>
       <c r="N38">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O38">
         <v>-1</v>
@@ -4134,13 +3906,13 @@
         <v>-1</v>
       </c>
       <c r="W38">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="X38">
         <v>5</v>
       </c>
       <c r="Y38">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Z38">
         <v>5</v>
@@ -4149,7 +3921,7 @@
         <v>6</v>
       </c>
       <c r="AB38">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AC38">
         <v>5</v>
@@ -4175,19 +3947,19 @@
         <v>9</v>
       </c>
       <c r="G39">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="H39">
         <v>6</v>
       </c>
       <c r="I39">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J39">
         <v>-1</v>
       </c>
       <c r="K39">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L39">
         <v>-1</v>
@@ -4196,7 +3968,7 @@
         <v>-1</v>
       </c>
       <c r="N39">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O39">
         <v>-1</v>
@@ -4238,7 +4010,7 @@
         <v>9</v>
       </c>
       <c r="AB39">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AC39">
         <v>6</v>
@@ -4264,19 +4036,19 @@
         <v>5</v>
       </c>
       <c r="G40">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="H40">
         <v>6</v>
       </c>
       <c r="I40">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J40">
         <v>-1</v>
       </c>
       <c r="K40">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L40">
         <v>-1</v>
@@ -4285,7 +4057,7 @@
         <v>-1</v>
       </c>
       <c r="N40">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O40">
         <v>-1</v>
@@ -4312,13 +4084,13 @@
         <v>-1</v>
       </c>
       <c r="W40">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X40">
         <v>7</v>
       </c>
       <c r="Y40">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Z40">
         <v>5</v>
@@ -4327,7 +4099,7 @@
         <v>5</v>
       </c>
       <c r="AB40">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AC40">
         <v>6</v>
@@ -4353,19 +4125,19 @@
         <v>6</v>
       </c>
       <c r="G41">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="H41">
         <v>6</v>
       </c>
       <c r="I41">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J41">
         <v>-1</v>
       </c>
       <c r="K41">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L41">
         <v>-1</v>
@@ -4374,7 +4146,7 @@
         <v>-1</v>
       </c>
       <c r="N41">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O41">
         <v>-1</v>
@@ -4401,13 +4173,13 @@
         <v>-1</v>
       </c>
       <c r="W41">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="X41">
         <v>7</v>
       </c>
       <c r="Y41">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Z41">
         <v>7</v>
@@ -4416,7 +4188,7 @@
         <v>6</v>
       </c>
       <c r="AB41">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AC41">
         <v>6</v>
@@ -4442,19 +4214,19 @@
         <v>5</v>
       </c>
       <c r="G42">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="H42">
         <v>6</v>
       </c>
       <c r="I42">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="J42">
         <v>-1</v>
       </c>
       <c r="K42">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="L42">
         <v>-1</v>
@@ -4463,7 +4235,7 @@
         <v>-1</v>
       </c>
       <c r="N42">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O42">
         <v>-1</v>
@@ -4496,7 +4268,7 @@
         <v>5</v>
       </c>
       <c r="Y42">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Z42">
         <v>5</v>
@@ -4505,7 +4277,7 @@
         <v>5</v>
       </c>
       <c r="AB42">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AC42">
         <v>6</v>
@@ -4653,19 +4425,19 @@
         <v>100</v>
       </c>
       <c r="G4">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H4">
         <v>80</v>
       </c>
       <c r="I4">
-        <v>100</v>
+        <v>60</v>
       </c>
       <c r="J4">
         <v>100</v>
       </c>
       <c r="K4">
-        <v>100</v>
+        <v>95.5</v>
       </c>
       <c r="L4">
         <v>100</v>
@@ -4674,19 +4446,19 @@
         <v>100</v>
       </c>
       <c r="N4">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O4">
         <v>80</v>
       </c>
       <c r="P4">
-        <v>100</v>
+        <v>60</v>
       </c>
       <c r="Q4">
         <v>100</v>
       </c>
       <c r="R4">
-        <v>100</v>
+        <v>95.5</v>
       </c>
       <c r="S4">
         <v>100</v>
@@ -4695,7 +4467,7 @@
         <v>100</v>
       </c>
       <c r="U4">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="V4">
         <v>80</v>
@@ -4721,7 +4493,7 @@
         <v>100</v>
       </c>
       <c r="G5">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H5">
         <v>85</v>
@@ -4733,7 +4505,7 @@
         <v>100</v>
       </c>
       <c r="K5">
-        <v>100</v>
+        <v>95.5</v>
       </c>
       <c r="L5">
         <v>100</v>
@@ -4742,7 +4514,7 @@
         <v>100</v>
       </c>
       <c r="N5">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O5">
         <v>85</v>
@@ -4754,7 +4526,7 @@
         <v>100</v>
       </c>
       <c r="R5">
-        <v>100</v>
+        <v>95.5</v>
       </c>
       <c r="S5">
         <v>100</v>
@@ -4763,7 +4535,7 @@
         <v>100</v>
       </c>
       <c r="U5">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="V5">
         <v>85</v>
@@ -4789,19 +4561,19 @@
         <v>90</v>
       </c>
       <c r="G6">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H6">
         <v>85</v>
       </c>
       <c r="I6">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="J6">
         <v>100</v>
       </c>
       <c r="K6">
-        <v>100</v>
+        <v>88.59999999999999</v>
       </c>
       <c r="L6">
         <v>100</v>
@@ -4810,19 +4582,19 @@
         <v>90</v>
       </c>
       <c r="N6">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O6">
         <v>85</v>
       </c>
       <c r="P6">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="Q6">
         <v>100</v>
       </c>
       <c r="R6">
-        <v>100</v>
+        <v>88.59999999999999</v>
       </c>
       <c r="S6">
         <v>100</v>
@@ -4831,7 +4603,7 @@
         <v>90</v>
       </c>
       <c r="U6">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="V6">
         <v>85</v>
@@ -4857,7 +4629,7 @@
         <v>100</v>
       </c>
       <c r="G7">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H7">
         <v>85</v>
@@ -4869,7 +4641,7 @@
         <v>100</v>
       </c>
       <c r="K7">
-        <v>100</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="L7">
         <v>100</v>
@@ -4878,7 +4650,7 @@
         <v>100</v>
       </c>
       <c r="N7">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O7">
         <v>85</v>
@@ -4890,7 +4662,7 @@
         <v>100</v>
       </c>
       <c r="R7">
-        <v>100</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="S7">
         <v>100</v>
@@ -4899,7 +4671,7 @@
         <v>100</v>
       </c>
       <c r="U7">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="V7">
         <v>85</v>
@@ -4925,7 +4697,7 @@
         <v>100</v>
       </c>
       <c r="G8">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H8">
         <v>90</v>
@@ -4946,7 +4718,7 @@
         <v>100</v>
       </c>
       <c r="N8">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O8">
         <v>90</v>
@@ -4967,7 +4739,7 @@
         <v>100</v>
       </c>
       <c r="U8">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="V8">
         <v>90</v>
@@ -4993,7 +4765,7 @@
         <v>100</v>
       </c>
       <c r="G9">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H9">
         <v>85</v>
@@ -5005,7 +4777,7 @@
         <v>100</v>
       </c>
       <c r="K9">
-        <v>95.8</v>
+        <v>97.7</v>
       </c>
       <c r="L9">
         <v>100</v>
@@ -5014,7 +4786,7 @@
         <v>100</v>
       </c>
       <c r="N9">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O9">
         <v>85</v>
@@ -5026,7 +4798,7 @@
         <v>100</v>
       </c>
       <c r="R9">
-        <v>95.8</v>
+        <v>97.7</v>
       </c>
       <c r="S9">
         <v>100</v>
@@ -5035,7 +4807,7 @@
         <v>100</v>
       </c>
       <c r="U9">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="V9">
         <v>85</v>
@@ -5061,7 +4833,7 @@
         <v>100</v>
       </c>
       <c r="G10">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H10">
         <v>95</v>
@@ -5073,7 +4845,7 @@
         <v>100</v>
       </c>
       <c r="K10">
-        <v>91.7</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="L10">
         <v>100</v>
@@ -5082,7 +4854,7 @@
         <v>100</v>
       </c>
       <c r="N10">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O10">
         <v>95</v>
@@ -5094,7 +4866,7 @@
         <v>100</v>
       </c>
       <c r="R10">
-        <v>91.7</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="S10">
         <v>100</v>
@@ -5103,7 +4875,7 @@
         <v>100</v>
       </c>
       <c r="U10">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="V10">
         <v>95</v>
@@ -5129,7 +4901,7 @@
         <v>100</v>
       </c>
       <c r="G11">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H11">
         <v>95</v>
@@ -5141,7 +4913,7 @@
         <v>100</v>
       </c>
       <c r="K11">
-        <v>95.8</v>
+        <v>93.2</v>
       </c>
       <c r="L11">
         <v>100</v>
@@ -5150,7 +4922,7 @@
         <v>100</v>
       </c>
       <c r="N11">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O11">
         <v>95</v>
@@ -5162,7 +4934,7 @@
         <v>100</v>
       </c>
       <c r="R11">
-        <v>95.8</v>
+        <v>93.2</v>
       </c>
       <c r="S11">
         <v>100</v>
@@ -5171,7 +4943,7 @@
         <v>100</v>
       </c>
       <c r="U11">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="V11">
         <v>95</v>
@@ -5197,19 +4969,19 @@
         <v>100</v>
       </c>
       <c r="G12">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H12">
         <v>95</v>
       </c>
       <c r="I12">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="J12">
         <v>100</v>
       </c>
       <c r="K12">
-        <v>100</v>
+        <v>93.2</v>
       </c>
       <c r="L12">
         <v>100</v>
@@ -5218,19 +4990,19 @@
         <v>100</v>
       </c>
       <c r="N12">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O12">
         <v>95</v>
       </c>
       <c r="P12">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="Q12">
         <v>100</v>
       </c>
       <c r="R12">
-        <v>100</v>
+        <v>93.2</v>
       </c>
       <c r="S12">
         <v>100</v>
@@ -5239,7 +5011,7 @@
         <v>100</v>
       </c>
       <c r="U12">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="V12">
         <v>95</v>
@@ -5265,7 +5037,7 @@
         <v>100</v>
       </c>
       <c r="G13">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H13">
         <v>90</v>
@@ -5277,7 +5049,7 @@
         <v>100</v>
       </c>
       <c r="K13">
-        <v>95.8</v>
+        <v>88.59999999999999</v>
       </c>
       <c r="L13">
         <v>100</v>
@@ -5286,7 +5058,7 @@
         <v>100</v>
       </c>
       <c r="N13">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O13">
         <v>90</v>
@@ -5298,7 +5070,7 @@
         <v>100</v>
       </c>
       <c r="R13">
-        <v>95.8</v>
+        <v>88.59999999999999</v>
       </c>
       <c r="S13">
         <v>100</v>
@@ -5307,7 +5079,7 @@
         <v>100</v>
       </c>
       <c r="U13">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="V13">
         <v>90</v>
@@ -5333,19 +5105,19 @@
         <v>100</v>
       </c>
       <c r="G14">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H14">
         <v>85</v>
       </c>
       <c r="I14">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="J14">
         <v>100</v>
       </c>
       <c r="K14">
-        <v>95.8</v>
+        <v>95.5</v>
       </c>
       <c r="L14">
         <v>100</v>
@@ -5354,19 +5126,19 @@
         <v>100</v>
       </c>
       <c r="N14">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O14">
         <v>85</v>
       </c>
       <c r="P14">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="Q14">
         <v>100</v>
       </c>
       <c r="R14">
-        <v>95.8</v>
+        <v>95.5</v>
       </c>
       <c r="S14">
         <v>100</v>
@@ -5375,7 +5147,7 @@
         <v>100</v>
       </c>
       <c r="U14">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="V14">
         <v>85</v>
@@ -5401,7 +5173,7 @@
         <v>100</v>
       </c>
       <c r="G15">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H15">
         <v>80</v>
@@ -5413,7 +5185,7 @@
         <v>100</v>
       </c>
       <c r="K15">
-        <v>100</v>
+        <v>97.7</v>
       </c>
       <c r="L15">
         <v>100</v>
@@ -5422,7 +5194,7 @@
         <v>100</v>
       </c>
       <c r="N15">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O15">
         <v>80</v>
@@ -5434,7 +5206,7 @@
         <v>100</v>
       </c>
       <c r="R15">
-        <v>100</v>
+        <v>97.7</v>
       </c>
       <c r="S15">
         <v>100</v>
@@ -5443,7 +5215,7 @@
         <v>100</v>
       </c>
       <c r="U15">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="V15">
         <v>80</v>
@@ -5469,7 +5241,7 @@
         <v>95</v>
       </c>
       <c r="G16">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H16">
         <v>80</v>
@@ -5481,7 +5253,7 @@
         <v>100</v>
       </c>
       <c r="K16">
-        <v>100</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="L16">
         <v>100</v>
@@ -5490,7 +5262,7 @@
         <v>95</v>
       </c>
       <c r="N16">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O16">
         <v>80</v>
@@ -5502,7 +5274,7 @@
         <v>100</v>
       </c>
       <c r="R16">
-        <v>100</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="S16">
         <v>100</v>
@@ -5511,7 +5283,7 @@
         <v>95</v>
       </c>
       <c r="U16">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="V16">
         <v>80</v>
@@ -5537,7 +5309,7 @@
         <v>100</v>
       </c>
       <c r="G17">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H17">
         <v>90</v>
@@ -5549,7 +5321,7 @@
         <v>100</v>
       </c>
       <c r="K17">
-        <v>95.8</v>
+        <v>93.2</v>
       </c>
       <c r="L17">
         <v>100</v>
@@ -5558,7 +5330,7 @@
         <v>100</v>
       </c>
       <c r="N17">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O17">
         <v>90</v>
@@ -5570,7 +5342,7 @@
         <v>100</v>
       </c>
       <c r="R17">
-        <v>95.8</v>
+        <v>93.2</v>
       </c>
       <c r="S17">
         <v>100</v>
@@ -5579,7 +5351,7 @@
         <v>100</v>
       </c>
       <c r="U17">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="V17">
         <v>90</v>
@@ -5605,7 +5377,7 @@
         <v>100</v>
       </c>
       <c r="G18">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H18">
         <v>90</v>
@@ -5617,7 +5389,7 @@
         <v>100</v>
       </c>
       <c r="K18">
-        <v>95.8</v>
+        <v>95.5</v>
       </c>
       <c r="L18">
         <v>100</v>
@@ -5626,7 +5398,7 @@
         <v>100</v>
       </c>
       <c r="N18">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O18">
         <v>90</v>
@@ -5638,7 +5410,7 @@
         <v>100</v>
       </c>
       <c r="R18">
-        <v>95.8</v>
+        <v>95.5</v>
       </c>
       <c r="S18">
         <v>100</v>
@@ -5647,7 +5419,7 @@
         <v>100</v>
       </c>
       <c r="U18">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="V18">
         <v>90</v>
@@ -5673,7 +5445,7 @@
         <v>75</v>
       </c>
       <c r="G19">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H19">
         <v>80</v>
@@ -5685,7 +5457,7 @@
         <v>100</v>
       </c>
       <c r="K19">
-        <v>95.8</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="L19">
         <v>100</v>
@@ -5694,7 +5466,7 @@
         <v>75</v>
       </c>
       <c r="N19">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O19">
         <v>80</v>
@@ -5706,7 +5478,7 @@
         <v>100</v>
       </c>
       <c r="R19">
-        <v>95.8</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="S19">
         <v>100</v>
@@ -5715,7 +5487,7 @@
         <v>75</v>
       </c>
       <c r="U19">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="V19">
         <v>80</v>
@@ -5741,19 +5513,19 @@
         <v>75</v>
       </c>
       <c r="G20">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H20">
         <v>80</v>
       </c>
       <c r="I20">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="J20">
         <v>100</v>
       </c>
       <c r="K20">
-        <v>62.5</v>
+        <v>34.1</v>
       </c>
       <c r="L20">
         <v>100</v>
@@ -5762,19 +5534,19 @@
         <v>75</v>
       </c>
       <c r="N20">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O20">
         <v>80</v>
       </c>
       <c r="P20">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="Q20">
         <v>100</v>
       </c>
       <c r="R20">
-        <v>62.5</v>
+        <v>34.1</v>
       </c>
       <c r="S20">
         <v>100</v>
@@ -5783,7 +5555,7 @@
         <v>75</v>
       </c>
       <c r="U20">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="V20">
         <v>80</v>
@@ -5809,19 +5581,19 @@
         <v>100</v>
       </c>
       <c r="G21">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H21">
         <v>95</v>
       </c>
       <c r="I21">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="J21">
         <v>100</v>
       </c>
       <c r="K21">
-        <v>95.8</v>
+        <v>88.59999999999999</v>
       </c>
       <c r="L21">
         <v>100</v>
@@ -5830,19 +5602,19 @@
         <v>100</v>
       </c>
       <c r="N21">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O21">
         <v>95</v>
       </c>
       <c r="P21">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="Q21">
         <v>100</v>
       </c>
       <c r="R21">
-        <v>95.8</v>
+        <v>88.59999999999999</v>
       </c>
       <c r="S21">
         <v>100</v>
@@ -5851,7 +5623,7 @@
         <v>100</v>
       </c>
       <c r="U21">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="V21">
         <v>95</v>
@@ -5877,19 +5649,19 @@
         <v>100</v>
       </c>
       <c r="G22">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H22">
         <v>90</v>
       </c>
       <c r="I22">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="J22">
         <v>100</v>
       </c>
       <c r="K22">
-        <v>91.7</v>
+        <v>93.2</v>
       </c>
       <c r="L22">
         <v>100</v>
@@ -5898,19 +5670,19 @@
         <v>100</v>
       </c>
       <c r="N22">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O22">
         <v>90</v>
       </c>
       <c r="P22">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="Q22">
         <v>100</v>
       </c>
       <c r="R22">
-        <v>91.7</v>
+        <v>93.2</v>
       </c>
       <c r="S22">
         <v>100</v>
@@ -5919,7 +5691,7 @@
         <v>100</v>
       </c>
       <c r="U22">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="V22">
         <v>90</v>
@@ -5945,7 +5717,7 @@
         <v>100</v>
       </c>
       <c r="G23">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H23">
         <v>85</v>
@@ -5957,7 +5729,7 @@
         <v>100</v>
       </c>
       <c r="K23">
-        <v>91.7</v>
+        <v>88.59999999999999</v>
       </c>
       <c r="L23">
         <v>100</v>
@@ -5966,7 +5738,7 @@
         <v>100</v>
       </c>
       <c r="N23">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O23">
         <v>85</v>
@@ -5978,7 +5750,7 @@
         <v>100</v>
       </c>
       <c r="R23">
-        <v>91.7</v>
+        <v>88.59999999999999</v>
       </c>
       <c r="S23">
         <v>100</v>
@@ -5987,7 +5759,7 @@
         <v>100</v>
       </c>
       <c r="U23">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="V23">
         <v>85</v>
@@ -6013,7 +5785,7 @@
         <v>100</v>
       </c>
       <c r="G24">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H24">
         <v>100</v>
@@ -6025,7 +5797,7 @@
         <v>100</v>
       </c>
       <c r="K24">
-        <v>95.8</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="L24">
         <v>100</v>
@@ -6034,7 +5806,7 @@
         <v>100</v>
       </c>
       <c r="N24">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O24">
         <v>100</v>
@@ -6046,7 +5818,7 @@
         <v>100</v>
       </c>
       <c r="R24">
-        <v>95.8</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="S24">
         <v>100</v>
@@ -6055,7 +5827,7 @@
         <v>100</v>
       </c>
       <c r="U24">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="V24">
         <v>100</v>
@@ -6081,7 +5853,7 @@
         <v>100</v>
       </c>
       <c r="G25">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H25">
         <v>90</v>
@@ -6093,7 +5865,7 @@
         <v>100</v>
       </c>
       <c r="K25">
-        <v>91.7</v>
+        <v>95.5</v>
       </c>
       <c r="L25">
         <v>100</v>
@@ -6102,7 +5874,7 @@
         <v>100</v>
       </c>
       <c r="N25">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O25">
         <v>90</v>
@@ -6114,7 +5886,7 @@
         <v>100</v>
       </c>
       <c r="R25">
-        <v>91.7</v>
+        <v>95.5</v>
       </c>
       <c r="S25">
         <v>100</v>
@@ -6123,7 +5895,7 @@
         <v>100</v>
       </c>
       <c r="U25">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="V25">
         <v>90</v>
@@ -6149,19 +5921,19 @@
         <v>100</v>
       </c>
       <c r="G26">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H26">
         <v>80</v>
       </c>
       <c r="I26">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="J26">
         <v>100</v>
       </c>
       <c r="K26">
-        <v>91.7</v>
+        <v>84.09999999999999</v>
       </c>
       <c r="L26">
         <v>100</v>
@@ -6170,19 +5942,19 @@
         <v>100</v>
       </c>
       <c r="N26">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O26">
         <v>80</v>
       </c>
       <c r="P26">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="Q26">
         <v>100</v>
       </c>
       <c r="R26">
-        <v>91.7</v>
+        <v>84.09999999999999</v>
       </c>
       <c r="S26">
         <v>100</v>
@@ -6191,7 +5963,7 @@
         <v>100</v>
       </c>
       <c r="U26">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="V26">
         <v>80</v>
@@ -6217,7 +5989,7 @@
         <v>100</v>
       </c>
       <c r="G27">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H27">
         <v>95</v>
@@ -6229,7 +6001,7 @@
         <v>100</v>
       </c>
       <c r="K27">
-        <v>95.8</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="L27">
         <v>100</v>
@@ -6238,7 +6010,7 @@
         <v>100</v>
       </c>
       <c r="N27">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O27">
         <v>95</v>
@@ -6250,7 +6022,7 @@
         <v>100</v>
       </c>
       <c r="R27">
-        <v>95.8</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="S27">
         <v>100</v>
@@ -6259,7 +6031,7 @@
         <v>100</v>
       </c>
       <c r="U27">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="V27">
         <v>95</v>
@@ -6285,7 +6057,7 @@
         <v>100</v>
       </c>
       <c r="G28">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H28">
         <v>95</v>
@@ -6297,7 +6069,7 @@
         <v>100</v>
       </c>
       <c r="K28">
-        <v>100</v>
+        <v>95.5</v>
       </c>
       <c r="L28">
         <v>100</v>
@@ -6306,7 +6078,7 @@
         <v>100</v>
       </c>
       <c r="N28">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O28">
         <v>95</v>
@@ -6318,7 +6090,7 @@
         <v>100</v>
       </c>
       <c r="R28">
-        <v>100</v>
+        <v>95.5</v>
       </c>
       <c r="S28">
         <v>100</v>
@@ -6327,7 +6099,7 @@
         <v>100</v>
       </c>
       <c r="U28">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="V28">
         <v>95</v>
@@ -6353,7 +6125,7 @@
         <v>100</v>
       </c>
       <c r="G29">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H29">
         <v>90</v>
@@ -6365,7 +6137,7 @@
         <v>100</v>
       </c>
       <c r="K29">
-        <v>95.8</v>
+        <v>93.2</v>
       </c>
       <c r="L29">
         <v>100</v>
@@ -6374,7 +6146,7 @@
         <v>100</v>
       </c>
       <c r="N29">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O29">
         <v>90</v>
@@ -6386,7 +6158,7 @@
         <v>100</v>
       </c>
       <c r="R29">
-        <v>95.8</v>
+        <v>93.2</v>
       </c>
       <c r="S29">
         <v>100</v>
@@ -6395,7 +6167,7 @@
         <v>100</v>
       </c>
       <c r="U29">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="V29">
         <v>90</v>
@@ -6421,7 +6193,7 @@
         <v>100</v>
       </c>
       <c r="G30">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H30">
         <v>85</v>
@@ -6433,7 +6205,7 @@
         <v>100</v>
       </c>
       <c r="K30">
-        <v>95.8</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="L30">
         <v>100</v>
@@ -6442,7 +6214,7 @@
         <v>100</v>
       </c>
       <c r="N30">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O30">
         <v>85</v>
@@ -6454,7 +6226,7 @@
         <v>100</v>
       </c>
       <c r="R30">
-        <v>95.8</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="S30">
         <v>100</v>
@@ -6463,7 +6235,7 @@
         <v>100</v>
       </c>
       <c r="U30">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="V30">
         <v>85</v>
@@ -6489,7 +6261,7 @@
         <v>100</v>
       </c>
       <c r="G31">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H31">
         <v>95</v>
@@ -6501,7 +6273,7 @@
         <v>100</v>
       </c>
       <c r="K31">
-        <v>95.8</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="L31">
         <v>100</v>
@@ -6510,7 +6282,7 @@
         <v>100</v>
       </c>
       <c r="N31">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O31">
         <v>95</v>
@@ -6522,7 +6294,7 @@
         <v>100</v>
       </c>
       <c r="R31">
-        <v>95.8</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="S31">
         <v>100</v>
@@ -6531,7 +6303,7 @@
         <v>100</v>
       </c>
       <c r="U31">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="V31">
         <v>95</v>
@@ -6557,7 +6329,7 @@
         <v>0</v>
       </c>
       <c r="G32">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H32">
         <v>0</v>
@@ -6578,7 +6350,7 @@
         <v>0</v>
       </c>
       <c r="N32">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O32">
         <v>0</v>
@@ -6599,7 +6371,7 @@
         <v>0</v>
       </c>
       <c r="U32">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="V32">
         <v>0</v>
@@ -6625,19 +6397,19 @@
         <v>100</v>
       </c>
       <c r="G33">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H33">
         <v>90</v>
       </c>
       <c r="I33">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="J33">
         <v>100</v>
       </c>
       <c r="K33">
-        <v>95.8</v>
+        <v>97.7</v>
       </c>
       <c r="L33">
         <v>100</v>
@@ -6646,19 +6418,19 @@
         <v>100</v>
       </c>
       <c r="N33">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O33">
         <v>90</v>
       </c>
       <c r="P33">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="Q33">
         <v>100</v>
       </c>
       <c r="R33">
-        <v>95.8</v>
+        <v>97.7</v>
       </c>
       <c r="S33">
         <v>100</v>
@@ -6667,7 +6439,7 @@
         <v>100</v>
       </c>
       <c r="U33">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="V33">
         <v>90</v>
@@ -6693,19 +6465,19 @@
         <v>100</v>
       </c>
       <c r="G34">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H34">
         <v>0</v>
       </c>
       <c r="I34">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="J34">
         <v>100</v>
       </c>
       <c r="K34">
-        <v>95.8</v>
+        <v>84.09999999999999</v>
       </c>
       <c r="L34">
         <v>100</v>
@@ -6714,19 +6486,19 @@
         <v>100</v>
       </c>
       <c r="N34">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O34">
         <v>0</v>
       </c>
       <c r="P34">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="Q34">
         <v>100</v>
       </c>
       <c r="R34">
-        <v>95.8</v>
+        <v>84.09999999999999</v>
       </c>
       <c r="S34">
         <v>100</v>
@@ -6735,7 +6507,7 @@
         <v>100</v>
       </c>
       <c r="U34">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="V34">
         <v>0</v>
@@ -6761,19 +6533,19 @@
         <v>100</v>
       </c>
       <c r="G35">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H35">
         <v>95</v>
       </c>
       <c r="I35">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="J35">
         <v>100</v>
       </c>
       <c r="K35">
-        <v>95.8</v>
+        <v>56.8</v>
       </c>
       <c r="L35">
         <v>100</v>
@@ -6782,19 +6554,19 @@
         <v>100</v>
       </c>
       <c r="N35">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O35">
         <v>95</v>
       </c>
       <c r="P35">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="Q35">
         <v>100</v>
       </c>
       <c r="R35">
-        <v>95.8</v>
+        <v>56.8</v>
       </c>
       <c r="S35">
         <v>100</v>
@@ -6803,7 +6575,7 @@
         <v>100</v>
       </c>
       <c r="U35">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="V35">
         <v>95</v>
@@ -6829,19 +6601,19 @@
         <v>90</v>
       </c>
       <c r="G36">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H36">
         <v>80</v>
       </c>
       <c r="I36">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="J36">
         <v>100</v>
       </c>
       <c r="K36">
-        <v>100</v>
+        <v>84.09999999999999</v>
       </c>
       <c r="L36">
         <v>100</v>
@@ -6850,19 +6622,19 @@
         <v>90</v>
       </c>
       <c r="N36">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O36">
         <v>80</v>
       </c>
       <c r="P36">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="Q36">
         <v>100</v>
       </c>
       <c r="R36">
-        <v>100</v>
+        <v>84.09999999999999</v>
       </c>
       <c r="S36">
         <v>100</v>
@@ -6871,7 +6643,7 @@
         <v>90</v>
       </c>
       <c r="U36">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="V36">
         <v>80</v>
@@ -6897,7 +6669,7 @@
         <v>100</v>
       </c>
       <c r="G37">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H37">
         <v>95</v>
@@ -6909,7 +6681,7 @@
         <v>100</v>
       </c>
       <c r="K37">
-        <v>100</v>
+        <v>97.7</v>
       </c>
       <c r="L37">
         <v>100</v>
@@ -6918,7 +6690,7 @@
         <v>100</v>
       </c>
       <c r="N37">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O37">
         <v>95</v>
@@ -6930,7 +6702,7 @@
         <v>100</v>
       </c>
       <c r="R37">
-        <v>100</v>
+        <v>97.7</v>
       </c>
       <c r="S37">
         <v>100</v>
@@ -6939,7 +6711,7 @@
         <v>100</v>
       </c>
       <c r="U37">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="V37">
         <v>95</v>
@@ -6965,19 +6737,19 @@
         <v>100</v>
       </c>
       <c r="G38">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H38">
         <v>80</v>
       </c>
       <c r="I38">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="J38">
         <v>100</v>
       </c>
       <c r="K38">
-        <v>100</v>
+        <v>97.7</v>
       </c>
       <c r="L38">
         <v>100</v>
@@ -6986,19 +6758,19 @@
         <v>100</v>
       </c>
       <c r="N38">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O38">
         <v>80</v>
       </c>
       <c r="P38">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="Q38">
         <v>100</v>
       </c>
       <c r="R38">
-        <v>100</v>
+        <v>97.7</v>
       </c>
       <c r="S38">
         <v>100</v>
@@ -7007,7 +6779,7 @@
         <v>100</v>
       </c>
       <c r="U38">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="V38">
         <v>80</v>
@@ -7033,7 +6805,7 @@
         <v>100</v>
       </c>
       <c r="G39">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H39">
         <v>95</v>
@@ -7045,7 +6817,7 @@
         <v>100</v>
       </c>
       <c r="K39">
-        <v>95.8</v>
+        <v>95.5</v>
       </c>
       <c r="L39">
         <v>100</v>
@@ -7054,7 +6826,7 @@
         <v>100</v>
       </c>
       <c r="N39">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O39">
         <v>95</v>
@@ -7066,7 +6838,7 @@
         <v>100</v>
       </c>
       <c r="R39">
-        <v>95.8</v>
+        <v>95.5</v>
       </c>
       <c r="S39">
         <v>100</v>
@@ -7075,7 +6847,7 @@
         <v>100</v>
       </c>
       <c r="U39">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="V39">
         <v>95</v>
@@ -7101,7 +6873,7 @@
         <v>100</v>
       </c>
       <c r="G40">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H40">
         <v>90</v>
@@ -7113,7 +6885,7 @@
         <v>100</v>
       </c>
       <c r="K40">
-        <v>95.8</v>
+        <v>97.7</v>
       </c>
       <c r="L40">
         <v>100</v>
@@ -7122,7 +6894,7 @@
         <v>100</v>
       </c>
       <c r="N40">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O40">
         <v>90</v>
@@ -7134,7 +6906,7 @@
         <v>100</v>
       </c>
       <c r="R40">
-        <v>95.8</v>
+        <v>97.7</v>
       </c>
       <c r="S40">
         <v>100</v>
@@ -7143,7 +6915,7 @@
         <v>100</v>
       </c>
       <c r="U40">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="V40">
         <v>90</v>
@@ -7169,7 +6941,7 @@
         <v>100</v>
       </c>
       <c r="G41">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H41">
         <v>95</v>
@@ -7190,7 +6962,7 @@
         <v>100</v>
       </c>
       <c r="N41">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O41">
         <v>95</v>
@@ -7211,7 +6983,7 @@
         <v>100</v>
       </c>
       <c r="U41">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="V41">
         <v>95</v>
@@ -7237,7 +7009,7 @@
         <v>80</v>
       </c>
       <c r="G42">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H42">
         <v>85</v>
@@ -7249,7 +7021,7 @@
         <v>100</v>
       </c>
       <c r="K42">
-        <v>95.8</v>
+        <v>81.8</v>
       </c>
       <c r="L42">
         <v>100</v>
@@ -7258,7 +7030,7 @@
         <v>80</v>
       </c>
       <c r="N42">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O42">
         <v>85</v>
@@ -7270,7 +7042,7 @@
         <v>100</v>
       </c>
       <c r="R42">
-        <v>95.8</v>
+        <v>81.8</v>
       </c>
       <c r="S42">
         <v>100</v>
@@ -7279,7 +7051,7 @@
         <v>80</v>
       </c>
       <c r="U42">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="V42">
         <v>85</v>
@@ -7339,7 +7111,7 @@
     </row>
     <row r="2" spans="1:10">
       <c r="A2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B2" t="s">
         <v>65</v>
@@ -7348,27 +7120,30 @@
         <v>39</v>
       </c>
       <c r="D2">
+        <v>19</v>
+      </c>
+      <c r="E2">
+        <v>20</v>
+      </c>
+      <c r="F2" s="2">
+        <v>48.7</v>
+      </c>
+      <c r="G2" s="2">
+        <v>51.3</v>
+      </c>
+      <c r="H2">
+        <v>5.5</v>
+      </c>
+      <c r="I2">
         <v>0</v>
       </c>
-      <c r="E2">
+      <c r="J2" s="2">
         <v>0</v>
-      </c>
-      <c r="F2" s="2">
-        <v>0</v>
-      </c>
-      <c r="G2" s="2">
-        <v>0</v>
-      </c>
-      <c r="I2">
-        <v>39</v>
-      </c>
-      <c r="J2" s="2">
-        <v>100</v>
       </c>
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="B3" t="s">
         <v>66</v>
@@ -7377,19 +7152,19 @@
         <v>39</v>
       </c>
       <c r="D3">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="E3">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="F3" s="2">
-        <v>48.7</v>
+        <v>53.8</v>
       </c>
       <c r="G3" s="2">
-        <v>51.3</v>
+        <v>46.2</v>
       </c>
       <c r="H3">
-        <v>5.5</v>
+        <v>5.9</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -7400,7 +7175,7 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B4" t="s">
         <v>67</v>
@@ -7409,19 +7184,19 @@
         <v>39</v>
       </c>
       <c r="D4">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E4">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F4" s="2">
-        <v>53.8</v>
+        <v>56.4</v>
       </c>
       <c r="G4" s="2">
-        <v>46.2</v>
+        <v>43.6</v>
       </c>
       <c r="H4">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -7441,19 +7216,19 @@
         <v>39</v>
       </c>
       <c r="D5">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E5">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F5" s="2">
-        <v>64.09999999999999</v>
+        <v>61.5</v>
       </c>
       <c r="G5" s="2">
-        <v>35.9</v>
+        <v>38.5</v>
       </c>
       <c r="H5">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -7496,7 +7271,7 @@
     </row>
     <row r="7" spans="1:10">
       <c r="A7" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="B7" t="s">
         <v>70</v>
@@ -7505,19 +7280,19 @@
         <v>39</v>
       </c>
       <c r="D7">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E7">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F7" s="2">
-        <v>82.09999999999999</v>
+        <v>79.5</v>
       </c>
       <c r="G7" s="2">
-        <v>17.9</v>
+        <v>20.5</v>
       </c>
       <c r="H7">
-        <v>6.7</v>
+        <v>7.3</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -7528,7 +7303,7 @@
     </row>
     <row r="8" spans="1:10">
       <c r="A8" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B8" t="s">
         <v>71</v>
@@ -7549,7 +7324,7 @@
         <v>17.9</v>
       </c>
       <c r="H8">
-        <v>6.5</v>
+        <v>6.7</v>
       </c>
       <c r="I8">
         <v>0</v>
@@ -7563,7 +7338,7 @@
         <v>64</v>
       </c>
       <c r="B9" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C9">
         <v>0</v>
@@ -7585,7 +7360,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F40"/>
+  <dimension ref="A1:F1"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -7612,786 +7387,6 @@
         <v>12</v>
       </c>
     </row>
-    <row r="2" spans="1:6">
-      <c r="A2">
-        <v>23330051920218</v>
-      </c>
-      <c r="B2" t="s">
-        <v>76</v>
-      </c>
-      <c r="C2" t="s">
-        <v>109</v>
-      </c>
-      <c r="D2" t="s">
-        <v>136</v>
-      </c>
-      <c r="E2" t="s">
-        <v>10</v>
-      </c>
-      <c r="F2" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6">
-      <c r="A3">
-        <v>23330051920219</v>
-      </c>
-      <c r="B3" t="s">
-        <v>77</v>
-      </c>
-      <c r="C3" t="s">
-        <v>110</v>
-      </c>
-      <c r="D3" t="s">
-        <v>137</v>
-      </c>
-      <c r="E3" t="s">
-        <v>10</v>
-      </c>
-      <c r="F3" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6">
-      <c r="A4">
-        <v>23330051920217</v>
-      </c>
-      <c r="B4" t="s">
-        <v>78</v>
-      </c>
-      <c r="C4" t="s">
-        <v>104</v>
-      </c>
-      <c r="D4" t="s">
-        <v>138</v>
-      </c>
-      <c r="E4" t="s">
-        <v>10</v>
-      </c>
-      <c r="F4" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6">
-      <c r="A5">
-        <v>23330051920220</v>
-      </c>
-      <c r="B5" t="s">
-        <v>79</v>
-      </c>
-      <c r="C5" t="s">
-        <v>111</v>
-      </c>
-      <c r="D5" t="s">
-        <v>139</v>
-      </c>
-      <c r="E5" t="s">
-        <v>10</v>
-      </c>
-      <c r="F5" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6">
-      <c r="A6">
-        <v>23330051920221</v>
-      </c>
-      <c r="B6" t="s">
-        <v>80</v>
-      </c>
-      <c r="C6" t="s">
-        <v>112</v>
-      </c>
-      <c r="D6" t="s">
-        <v>140</v>
-      </c>
-      <c r="E6" t="s">
-        <v>10</v>
-      </c>
-      <c r="F6" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6">
-      <c r="A7">
-        <v>23330051920223</v>
-      </c>
-      <c r="B7" t="s">
-        <v>81</v>
-      </c>
-      <c r="C7" t="s">
-        <v>90</v>
-      </c>
-      <c r="D7" t="s">
-        <v>141</v>
-      </c>
-      <c r="E7" t="s">
-        <v>10</v>
-      </c>
-      <c r="F7" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6">
-      <c r="A8">
-        <v>23330051920222</v>
-      </c>
-      <c r="B8" t="s">
-        <v>81</v>
-      </c>
-      <c r="C8" t="s">
-        <v>90</v>
-      </c>
-      <c r="D8" t="s">
-        <v>142</v>
-      </c>
-      <c r="E8" t="s">
-        <v>10</v>
-      </c>
-      <c r="F8" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6">
-      <c r="A9">
-        <v>23330051920224</v>
-      </c>
-      <c r="B9" t="s">
-        <v>82</v>
-      </c>
-      <c r="C9" t="s">
-        <v>113</v>
-      </c>
-      <c r="D9" t="s">
-        <v>143</v>
-      </c>
-      <c r="E9" t="s">
-        <v>10</v>
-      </c>
-      <c r="F9" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6">
-      <c r="A10">
-        <v>23330051920225</v>
-      </c>
-      <c r="B10" t="s">
-        <v>83</v>
-      </c>
-      <c r="C10" t="s">
-        <v>114</v>
-      </c>
-      <c r="D10" t="s">
-        <v>144</v>
-      </c>
-      <c r="E10" t="s">
-        <v>10</v>
-      </c>
-      <c r="F10" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6">
-      <c r="A11">
-        <v>23330051920228</v>
-      </c>
-      <c r="B11" t="s">
-        <v>84</v>
-      </c>
-      <c r="C11" t="s">
-        <v>115</v>
-      </c>
-      <c r="D11" t="s">
-        <v>145</v>
-      </c>
-      <c r="E11" t="s">
-        <v>10</v>
-      </c>
-      <c r="F11" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6">
-      <c r="A12">
-        <v>23330051920230</v>
-      </c>
-      <c r="B12" t="s">
-        <v>84</v>
-      </c>
-      <c r="C12" t="s">
-        <v>109</v>
-      </c>
-      <c r="D12" t="s">
-        <v>146</v>
-      </c>
-      <c r="E12" t="s">
-        <v>10</v>
-      </c>
-      <c r="F12" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6">
-      <c r="A13">
-        <v>23330051920229</v>
-      </c>
-      <c r="B13" t="s">
-        <v>84</v>
-      </c>
-      <c r="C13" t="s">
-        <v>116</v>
-      </c>
-      <c r="D13" t="s">
-        <v>147</v>
-      </c>
-      <c r="E13" t="s">
-        <v>10</v>
-      </c>
-      <c r="F13" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6">
-      <c r="A14">
-        <v>23330051920231</v>
-      </c>
-      <c r="B14" t="s">
-        <v>85</v>
-      </c>
-      <c r="C14" t="s">
-        <v>117</v>
-      </c>
-      <c r="D14" t="s">
-        <v>148</v>
-      </c>
-      <c r="E14" t="s">
-        <v>10</v>
-      </c>
-      <c r="F14" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6">
-      <c r="A15">
-        <v>23330051920232</v>
-      </c>
-      <c r="B15" t="s">
-        <v>86</v>
-      </c>
-      <c r="C15" t="s">
-        <v>80</v>
-      </c>
-      <c r="D15" t="s">
-        <v>149</v>
-      </c>
-      <c r="E15" t="s">
-        <v>10</v>
-      </c>
-      <c r="F15" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6">
-      <c r="A16">
-        <v>23330051920233</v>
-      </c>
-      <c r="B16" t="s">
-        <v>87</v>
-      </c>
-      <c r="C16" t="s">
-        <v>118</v>
-      </c>
-      <c r="D16" t="s">
-        <v>150</v>
-      </c>
-      <c r="E16" t="s">
-        <v>10</v>
-      </c>
-      <c r="F16" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6">
-      <c r="A17">
-        <v>23330051920234</v>
-      </c>
-      <c r="B17" t="s">
-        <v>88</v>
-      </c>
-      <c r="C17" t="s">
-        <v>119</v>
-      </c>
-      <c r="D17" t="s">
-        <v>151</v>
-      </c>
-      <c r="E17" t="s">
-        <v>10</v>
-      </c>
-      <c r="F17" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6">
-      <c r="A18">
-        <v>23330051920235</v>
-      </c>
-      <c r="B18" t="s">
-        <v>89</v>
-      </c>
-      <c r="C18" t="s">
-        <v>120</v>
-      </c>
-      <c r="D18" t="s">
-        <v>152</v>
-      </c>
-      <c r="E18" t="s">
-        <v>10</v>
-      </c>
-      <c r="F18" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6">
-      <c r="A19">
-        <v>23330051920236</v>
-      </c>
-      <c r="B19" t="s">
-        <v>89</v>
-      </c>
-      <c r="C19" t="s">
-        <v>121</v>
-      </c>
-      <c r="D19" t="s">
-        <v>153</v>
-      </c>
-      <c r="E19" t="s">
-        <v>10</v>
-      </c>
-      <c r="F19" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6">
-      <c r="A20">
-        <v>23330051920238</v>
-      </c>
-      <c r="B20" t="s">
-        <v>90</v>
-      </c>
-      <c r="C20" t="s">
-        <v>122</v>
-      </c>
-      <c r="D20" t="s">
-        <v>154</v>
-      </c>
-      <c r="E20" t="s">
-        <v>10</v>
-      </c>
-      <c r="F20" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6">
-      <c r="A21">
-        <v>23330051920271</v>
-      </c>
-      <c r="B21" t="s">
-        <v>91</v>
-      </c>
-      <c r="C21" t="s">
-        <v>89</v>
-      </c>
-      <c r="D21" t="s">
-        <v>155</v>
-      </c>
-      <c r="E21" t="s">
-        <v>10</v>
-      </c>
-      <c r="F21" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6">
-      <c r="A22">
-        <v>23330051920241</v>
-      </c>
-      <c r="B22" t="s">
-        <v>92</v>
-      </c>
-      <c r="C22" t="s">
-        <v>123</v>
-      </c>
-      <c r="D22" t="s">
-        <v>156</v>
-      </c>
-      <c r="E22" t="s">
-        <v>10</v>
-      </c>
-      <c r="F22" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6">
-      <c r="A23">
-        <v>23330051920243</v>
-      </c>
-      <c r="B23" t="s">
-        <v>93</v>
-      </c>
-      <c r="C23" t="s">
-        <v>124</v>
-      </c>
-      <c r="D23" t="s">
-        <v>157</v>
-      </c>
-      <c r="E23" t="s">
-        <v>10</v>
-      </c>
-      <c r="F23" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="24" spans="1:6">
-      <c r="A24">
-        <v>23330051920335</v>
-      </c>
-      <c r="B24" t="s">
-        <v>94</v>
-      </c>
-      <c r="C24" t="s">
-        <v>125</v>
-      </c>
-      <c r="D24" t="s">
-        <v>158</v>
-      </c>
-      <c r="E24" t="s">
-        <v>10</v>
-      </c>
-      <c r="F24" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="25" spans="1:6">
-      <c r="A25">
-        <v>23330051920245</v>
-      </c>
-      <c r="B25" t="s">
-        <v>95</v>
-      </c>
-      <c r="C25" t="s">
-        <v>126</v>
-      </c>
-      <c r="D25" t="s">
-        <v>159</v>
-      </c>
-      <c r="E25" t="s">
-        <v>10</v>
-      </c>
-      <c r="F25" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="26" spans="1:6">
-      <c r="A26">
-        <v>23330051920247</v>
-      </c>
-      <c r="B26" t="s">
-        <v>95</v>
-      </c>
-      <c r="C26" t="s">
-        <v>116</v>
-      </c>
-      <c r="D26" t="s">
-        <v>160</v>
-      </c>
-      <c r="E26" t="s">
-        <v>10</v>
-      </c>
-      <c r="F26" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="27" spans="1:6">
-      <c r="A27">
-        <v>23330051920249</v>
-      </c>
-      <c r="B27" t="s">
-        <v>96</v>
-      </c>
-      <c r="C27" t="s">
-        <v>127</v>
-      </c>
-      <c r="D27" t="s">
-        <v>158</v>
-      </c>
-      <c r="E27" t="s">
-        <v>10</v>
-      </c>
-      <c r="F27" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="28" spans="1:6">
-      <c r="A28">
-        <v>23330051920251</v>
-      </c>
-      <c r="B28" t="s">
-        <v>97</v>
-      </c>
-      <c r="C28" t="s">
-        <v>87</v>
-      </c>
-      <c r="D28" t="s">
-        <v>161</v>
-      </c>
-      <c r="E28" t="s">
-        <v>10</v>
-      </c>
-      <c r="F28" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="29" spans="1:6">
-      <c r="A29">
-        <v>23330051920253</v>
-      </c>
-      <c r="B29" t="s">
-        <v>98</v>
-      </c>
-      <c r="C29" t="s">
-        <v>128</v>
-      </c>
-      <c r="D29" t="s">
-        <v>162</v>
-      </c>
-      <c r="E29" t="s">
-        <v>10</v>
-      </c>
-      <c r="F29" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="30" spans="1:6">
-      <c r="A30">
-        <v>23330051920334</v>
-      </c>
-      <c r="B30" t="s">
-        <v>99</v>
-      </c>
-      <c r="C30" t="s">
-        <v>129</v>
-      </c>
-      <c r="D30" t="s">
-        <v>163</v>
-      </c>
-      <c r="E30" t="s">
-        <v>10</v>
-      </c>
-      <c r="F30" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="31" spans="1:6">
-      <c r="A31">
-        <v>23330051920318</v>
-      </c>
-      <c r="B31" t="s">
-        <v>100</v>
-      </c>
-      <c r="C31" t="s">
-        <v>130</v>
-      </c>
-      <c r="D31" t="s">
-        <v>164</v>
-      </c>
-      <c r="E31" t="s">
-        <v>10</v>
-      </c>
-      <c r="F31" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="32" spans="1:6">
-      <c r="A32">
-        <v>23330051920355</v>
-      </c>
-      <c r="B32" t="s">
-        <v>101</v>
-      </c>
-      <c r="C32" t="s">
-        <v>131</v>
-      </c>
-      <c r="D32" t="s">
-        <v>165</v>
-      </c>
-      <c r="E32" t="s">
-        <v>10</v>
-      </c>
-      <c r="F32" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="33" spans="1:6">
-      <c r="A33">
-        <v>23330051920258</v>
-      </c>
-      <c r="B33" t="s">
-        <v>102</v>
-      </c>
-      <c r="C33" t="s">
-        <v>132</v>
-      </c>
-      <c r="D33" t="s">
-        <v>166</v>
-      </c>
-      <c r="E33" t="s">
-        <v>10</v>
-      </c>
-      <c r="F33" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="34" spans="1:6">
-      <c r="A34">
-        <v>23330051920264</v>
-      </c>
-      <c r="B34" t="s">
-        <v>103</v>
-      </c>
-      <c r="C34" t="s">
-        <v>133</v>
-      </c>
-      <c r="D34" t="s">
-        <v>167</v>
-      </c>
-      <c r="E34" t="s">
-        <v>10</v>
-      </c>
-      <c r="F34" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="35" spans="1:6">
-      <c r="A35">
-        <v>23330051920361</v>
-      </c>
-      <c r="B35" t="s">
-        <v>104</v>
-      </c>
-      <c r="C35" t="s">
-        <v>126</v>
-      </c>
-      <c r="D35" t="s">
-        <v>168</v>
-      </c>
-      <c r="E35" t="s">
-        <v>10</v>
-      </c>
-      <c r="F35" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="36" spans="1:6">
-      <c r="A36">
-        <v>23330051920359</v>
-      </c>
-      <c r="B36" t="s">
-        <v>105</v>
-      </c>
-      <c r="C36" t="s">
-        <v>134</v>
-      </c>
-      <c r="D36" t="s">
-        <v>169</v>
-      </c>
-      <c r="E36" t="s">
-        <v>10</v>
-      </c>
-      <c r="F36" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="37" spans="1:6">
-      <c r="A37">
-        <v>23330051920265</v>
-      </c>
-      <c r="B37" t="s">
-        <v>104</v>
-      </c>
-      <c r="C37" t="s">
-        <v>98</v>
-      </c>
-      <c r="D37" t="s">
-        <v>170</v>
-      </c>
-      <c r="E37" t="s">
-        <v>10</v>
-      </c>
-      <c r="F37" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="38" spans="1:6">
-      <c r="A38">
-        <v>23330051920267</v>
-      </c>
-      <c r="B38" t="s">
-        <v>106</v>
-      </c>
-      <c r="C38" t="s">
-        <v>123</v>
-      </c>
-      <c r="D38" t="s">
-        <v>171</v>
-      </c>
-      <c r="E38" t="s">
-        <v>10</v>
-      </c>
-      <c r="F38" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="39" spans="1:6">
-      <c r="A39">
-        <v>23330051920273</v>
-      </c>
-      <c r="B39" t="s">
-        <v>107</v>
-      </c>
-      <c r="C39" t="s">
-        <v>87</v>
-      </c>
-      <c r="D39" t="s">
-        <v>172</v>
-      </c>
-      <c r="E39" t="s">
-        <v>10</v>
-      </c>
-      <c r="F39" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="40" spans="1:6">
-      <c r="A40">
-        <v>23330051920268</v>
-      </c>
-      <c r="B40" t="s">
-        <v>108</v>
-      </c>
-      <c r="C40" t="s">
-        <v>135</v>
-      </c>
-      <c r="D40" t="s">
-        <v>173</v>
-      </c>
-      <c r="E40" t="s">
-        <v>10</v>
-      </c>
-      <c r="F40" t="s">
-        <v>65</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -8399,7 +7394,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G28"/>
+  <dimension ref="A1:G12"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -8431,45 +7426,45 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>23330051920217</v>
+        <v>23330051920229</v>
       </c>
       <c r="B2" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="C2" t="s">
-        <v>104</v>
+        <v>83</v>
       </c>
       <c r="D2" t="s">
-        <v>138</v>
+        <v>90</v>
       </c>
       <c r="E2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F2" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="G2">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>23330051920217</v>
+        <v>23330051920229</v>
       </c>
       <c r="B3" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="C3" t="s">
-        <v>104</v>
+        <v>83</v>
       </c>
       <c r="D3" t="s">
-        <v>138</v>
+        <v>90</v>
       </c>
       <c r="E3" t="s">
         <v>11</v>
       </c>
       <c r="F3" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="G3">
         <v>5</v>
@@ -8477,45 +7472,45 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>23330051920220</v>
+        <v>23330051920247</v>
       </c>
       <c r="B4" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="C4" t="s">
-        <v>111</v>
+        <v>83</v>
       </c>
       <c r="D4" t="s">
-        <v>139</v>
+        <v>91</v>
       </c>
       <c r="E4" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="F4" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="G4">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>23330051920220</v>
+        <v>23330051920247</v>
       </c>
       <c r="B5" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="C5" t="s">
-        <v>111</v>
+        <v>83</v>
       </c>
       <c r="D5" t="s">
-        <v>139</v>
+        <v>91</v>
       </c>
       <c r="E5" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="F5" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="G5">
         <v>5</v>
@@ -8523,45 +7518,45 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>23330051920221</v>
+        <v>23330051920251</v>
       </c>
       <c r="B6" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="C6" t="s">
-        <v>112</v>
+        <v>84</v>
       </c>
       <c r="D6" t="s">
-        <v>140</v>
+        <v>92</v>
       </c>
       <c r="E6" t="s">
         <v>10</v>
       </c>
       <c r="F6" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="G6">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>23330051920221</v>
+        <v>23330051920251</v>
       </c>
       <c r="B7" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="C7" t="s">
-        <v>112</v>
+        <v>84</v>
       </c>
       <c r="D7" t="s">
-        <v>140</v>
+        <v>92</v>
       </c>
       <c r="E7" t="s">
         <v>11</v>
       </c>
       <c r="F7" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="G7">
         <v>5</v>
@@ -8569,22 +7564,22 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>23330051920222</v>
+        <v>23330051920220</v>
       </c>
       <c r="B8" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="C8" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="D8" t="s">
-        <v>142</v>
+        <v>93</v>
       </c>
       <c r="E8" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="F8" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="G8">
         <v>5</v>
@@ -8592,45 +7587,45 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>23330051920222</v>
+        <v>23330051920221</v>
       </c>
       <c r="B9" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C9" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="D9" t="s">
-        <v>142</v>
+        <v>94</v>
       </c>
       <c r="E9" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F9" t="s">
         <v>65</v>
       </c>
       <c r="G9">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>23330051920247</v>
+        <v>23330051920222</v>
       </c>
       <c r="B10" t="s">
+        <v>81</v>
+      </c>
+      <c r="C10" t="s">
+        <v>87</v>
+      </c>
+      <c r="D10" t="s">
         <v>95</v>
       </c>
-      <c r="C10" t="s">
-        <v>116</v>
-      </c>
-      <c r="D10" t="s">
-        <v>160</v>
-      </c>
       <c r="E10" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="F10" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G10">
         <v>5</v>
@@ -8638,416 +7633,48 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>23330051920247</v>
+        <v>23330051920230</v>
       </c>
       <c r="B11" t="s">
-        <v>95</v>
+        <v>76</v>
       </c>
       <c r="C11" t="s">
-        <v>116</v>
+        <v>88</v>
       </c>
       <c r="D11" t="s">
-        <v>160</v>
+        <v>96</v>
       </c>
       <c r="E11" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F11" t="s">
         <v>65</v>
       </c>
       <c r="G11">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>23330051920251</v>
+        <v>23330051920253</v>
       </c>
       <c r="B12" t="s">
+        <v>82</v>
+      </c>
+      <c r="C12" t="s">
+        <v>89</v>
+      </c>
+      <c r="D12" t="s">
         <v>97</v>
       </c>
-      <c r="C12" t="s">
-        <v>87</v>
-      </c>
-      <c r="D12" t="s">
-        <v>161</v>
-      </c>
       <c r="E12" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F12" t="s">
         <v>65</v>
       </c>
       <c r="G12">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7">
-      <c r="A13">
-        <v>23330051920251</v>
-      </c>
-      <c r="B13" t="s">
-        <v>97</v>
-      </c>
-      <c r="C13" t="s">
-        <v>87</v>
-      </c>
-      <c r="D13" t="s">
-        <v>161</v>
-      </c>
-      <c r="E13" t="s">
-        <v>11</v>
-      </c>
-      <c r="F13" t="s">
-        <v>66</v>
-      </c>
-      <c r="G13">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7">
-      <c r="A14">
-        <v>23330051920253</v>
-      </c>
-      <c r="B14" t="s">
-        <v>98</v>
-      </c>
-      <c r="C14" t="s">
-        <v>128</v>
-      </c>
-      <c r="D14" t="s">
-        <v>162</v>
-      </c>
-      <c r="E14" t="s">
-        <v>10</v>
-      </c>
-      <c r="F14" t="s">
-        <v>65</v>
-      </c>
-      <c r="G14">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7">
-      <c r="A15">
-        <v>23330051920253</v>
-      </c>
-      <c r="B15" t="s">
-        <v>98</v>
-      </c>
-      <c r="C15" t="s">
-        <v>128</v>
-      </c>
-      <c r="D15" t="s">
-        <v>162</v>
-      </c>
-      <c r="E15" t="s">
-        <v>11</v>
-      </c>
-      <c r="F15" t="s">
-        <v>66</v>
-      </c>
-      <c r="G15">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7">
-      <c r="A16">
-        <v>23330051920318</v>
-      </c>
-      <c r="B16" t="s">
-        <v>100</v>
-      </c>
-      <c r="C16" t="s">
-        <v>130</v>
-      </c>
-      <c r="D16" t="s">
-        <v>164</v>
-      </c>
-      <c r="E16" t="s">
-        <v>5</v>
-      </c>
-      <c r="F16" t="s">
-        <v>68</v>
-      </c>
-      <c r="G16">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7">
-      <c r="A17">
-        <v>23330051920318</v>
-      </c>
-      <c r="B17" t="s">
-        <v>100</v>
-      </c>
-      <c r="C17" t="s">
-        <v>130</v>
-      </c>
-      <c r="D17" t="s">
-        <v>164</v>
-      </c>
-      <c r="E17" t="s">
-        <v>10</v>
-      </c>
-      <c r="F17" t="s">
-        <v>65</v>
-      </c>
-      <c r="G17">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7">
-      <c r="A18">
-        <v>23330051920218</v>
-      </c>
-      <c r="B18" t="s">
-        <v>76</v>
-      </c>
-      <c r="C18" t="s">
-        <v>109</v>
-      </c>
-      <c r="D18" t="s">
-        <v>136</v>
-      </c>
-      <c r="E18" t="s">
-        <v>10</v>
-      </c>
-      <c r="F18" t="s">
-        <v>65</v>
-      </c>
-      <c r="G18">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7">
-      <c r="A19">
-        <v>23330051920223</v>
-      </c>
-      <c r="B19" t="s">
-        <v>81</v>
-      </c>
-      <c r="C19" t="s">
-        <v>90</v>
-      </c>
-      <c r="D19" t="s">
-        <v>141</v>
-      </c>
-      <c r="E19" t="s">
-        <v>10</v>
-      </c>
-      <c r="F19" t="s">
-        <v>65</v>
-      </c>
-      <c r="G19">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7">
-      <c r="A20">
-        <v>23330051920224</v>
-      </c>
-      <c r="B20" t="s">
-        <v>82</v>
-      </c>
-      <c r="C20" t="s">
-        <v>113</v>
-      </c>
-      <c r="D20" t="s">
-        <v>143</v>
-      </c>
-      <c r="E20" t="s">
-        <v>10</v>
-      </c>
-      <c r="F20" t="s">
-        <v>65</v>
-      </c>
-      <c r="G20">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7">
-      <c r="A21">
-        <v>23330051920225</v>
-      </c>
-      <c r="B21" t="s">
-        <v>83</v>
-      </c>
-      <c r="C21" t="s">
-        <v>114</v>
-      </c>
-      <c r="D21" t="s">
-        <v>144</v>
-      </c>
-      <c r="E21" t="s">
-        <v>10</v>
-      </c>
-      <c r="F21" t="s">
-        <v>65</v>
-      </c>
-      <c r="G21">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7">
-      <c r="A22">
-        <v>23330051920231</v>
-      </c>
-      <c r="B22" t="s">
-        <v>85</v>
-      </c>
-      <c r="C22" t="s">
-        <v>117</v>
-      </c>
-      <c r="D22" t="s">
-        <v>148</v>
-      </c>
-      <c r="E22" t="s">
-        <v>10</v>
-      </c>
-      <c r="F22" t="s">
-        <v>65</v>
-      </c>
-      <c r="G22">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7">
-      <c r="A23">
-        <v>23330051920232</v>
-      </c>
-      <c r="B23" t="s">
-        <v>86</v>
-      </c>
-      <c r="C23" t="s">
-        <v>80</v>
-      </c>
-      <c r="D23" t="s">
-        <v>149</v>
-      </c>
-      <c r="E23" t="s">
-        <v>10</v>
-      </c>
-      <c r="F23" t="s">
-        <v>65</v>
-      </c>
-      <c r="G23">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7">
-      <c r="A24">
-        <v>23330051920243</v>
-      </c>
-      <c r="B24" t="s">
-        <v>93</v>
-      </c>
-      <c r="C24" t="s">
-        <v>124</v>
-      </c>
-      <c r="D24" t="s">
-        <v>157</v>
-      </c>
-      <c r="E24" t="s">
-        <v>10</v>
-      </c>
-      <c r="F24" t="s">
-        <v>65</v>
-      </c>
-      <c r="G24">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="25" spans="1:7">
-      <c r="A25">
-        <v>23330051920249</v>
-      </c>
-      <c r="B25" t="s">
-        <v>96</v>
-      </c>
-      <c r="C25" t="s">
-        <v>127</v>
-      </c>
-      <c r="D25" t="s">
-        <v>158</v>
-      </c>
-      <c r="E25" t="s">
-        <v>10</v>
-      </c>
-      <c r="F25" t="s">
-        <v>65</v>
-      </c>
-      <c r="G25">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="26" spans="1:7">
-      <c r="A26">
-        <v>23330051920258</v>
-      </c>
-      <c r="B26" t="s">
-        <v>102</v>
-      </c>
-      <c r="C26" t="s">
-        <v>132</v>
-      </c>
-      <c r="D26" t="s">
-        <v>166</v>
-      </c>
-      <c r="E26" t="s">
-        <v>10</v>
-      </c>
-      <c r="F26" t="s">
-        <v>65</v>
-      </c>
-      <c r="G26">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="27" spans="1:7">
-      <c r="A27">
-        <v>23330051920265</v>
-      </c>
-      <c r="B27" t="s">
-        <v>104</v>
-      </c>
-      <c r="C27" t="s">
-        <v>98</v>
-      </c>
-      <c r="D27" t="s">
-        <v>170</v>
-      </c>
-      <c r="E27" t="s">
-        <v>10</v>
-      </c>
-      <c r="F27" t="s">
-        <v>65</v>
-      </c>
-      <c r="G27">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="28" spans="1:7">
-      <c r="A28">
-        <v>23330051920273</v>
-      </c>
-      <c r="B28" t="s">
-        <v>107</v>
-      </c>
-      <c r="C28" t="s">
-        <v>87</v>
-      </c>
-      <c r="D28" t="s">
-        <v>172</v>
-      </c>
-      <c r="E28" t="s">
-        <v>10</v>
-      </c>
-      <c r="F28" t="s">
-        <v>65</v>
-      </c>
-      <c r="G28">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>

--- a/grupos/1CV - Estadisticos 20231.xlsx
+++ b/grupos/1CV - Estadisticos 20231.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="232" uniqueCount="98">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="257" uniqueCount="109">
   <si>
     <t>Materia</t>
   </si>
@@ -230,12 +230,12 @@
     <t>Contreras Díaz Irma Ivette</t>
   </si>
   <si>
+    <t>Pesce Bautista Victor Manuel</t>
+  </si>
+  <si>
     <t>Vargas Olvera Francisco Eduardo</t>
   </si>
   <si>
-    <t>Pesce Bautista Victor Manuel</t>
-  </si>
-  <si>
     <t>NC</t>
   </si>
   <si>
@@ -248,70 +248,103 @@
     <t>Nombres</t>
   </si>
   <si>
+    <t>BARRAGAN</t>
+  </si>
+  <si>
+    <t>CUAPIO</t>
+  </si>
+  <si>
     <t>GARCIA</t>
   </si>
   <si>
-    <t>LOPEZ</t>
-  </si>
-  <si>
     <t>MARQUEZ</t>
   </si>
   <si>
-    <t>BARRAGAN</t>
+    <t>ALMANZA</t>
   </si>
   <si>
     <t>CRUZ</t>
   </si>
   <si>
-    <t>CUAPIO</t>
+    <t>DORANTES</t>
+  </si>
+  <si>
+    <t>GILES</t>
+  </si>
+  <si>
+    <t>LAGUNA</t>
   </si>
   <si>
     <t>MENDEZ</t>
   </si>
   <si>
+    <t>SANCHEZ</t>
+  </si>
+  <si>
+    <t>MACUIXTLE</t>
+  </si>
+  <si>
+    <t>HUERTA</t>
+  </si>
+  <si>
     <t>SANTIAGO</t>
   </si>
   <si>
     <t>GONZALEZ</t>
   </si>
   <si>
-    <t>MACUIXTLE</t>
+    <t>SANTOS</t>
   </si>
   <si>
     <t>CASTILLO</t>
   </si>
   <si>
-    <t>HUERTA</t>
-  </si>
-  <si>
-    <t>SANTOS</t>
+    <t>PORRAS</t>
+  </si>
+  <si>
+    <t>FIGUEROA</t>
+  </si>
+  <si>
+    <t>NATH</t>
   </si>
   <si>
     <t>MONDRAGON</t>
   </si>
   <si>
+    <t>MARIA FERNANDA</t>
+  </si>
+  <si>
+    <t>JESSICA</t>
+  </si>
+  <si>
     <t>MARIANA</t>
   </si>
   <si>
-    <t>RAYMUNDO</t>
-  </si>
-  <si>
     <t>DIEGO GREGORIO</t>
   </si>
   <si>
-    <t>MARIA FERNANDA</t>
+    <t>VANESA BETHSABE</t>
   </si>
   <si>
     <t>RAMSES</t>
   </si>
   <si>
-    <t>JESSICA</t>
+    <t>ROBERTO</t>
   </si>
   <si>
     <t>JAIRO</t>
   </si>
   <si>
+    <t>ALEXA YAMILET</t>
+  </si>
+  <si>
+    <t>AARON ZACHARY</t>
+  </si>
+  <si>
     <t>ANGEL ADRIAN</t>
+  </si>
+  <si>
+    <t>KAREN</t>
   </si>
 </sst>
 </file>
@@ -841,22 +874,22 @@
         <v>3</v>
       </c>
       <c r="J4">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K4">
         <v>5</v>
       </c>
       <c r="L4">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="M4">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N4">
         <v>5</v>
       </c>
       <c r="O4">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P4">
         <v>-1</v>
@@ -889,10 +922,10 @@
         <v>6</v>
       </c>
       <c r="Z4">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AA4">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AB4">
         <v>5</v>
@@ -930,22 +963,22 @@
         <v>6</v>
       </c>
       <c r="J5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K5">
         <v>6</v>
       </c>
       <c r="L5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M5">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N5">
         <v>8</v>
       </c>
       <c r="O5">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P5">
         <v>-1</v>
@@ -972,13 +1005,13 @@
         <v>7</v>
       </c>
       <c r="X5">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Y5">
         <v>7</v>
       </c>
       <c r="Z5">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AA5">
         <v>8</v>
@@ -1019,22 +1052,22 @@
         <v>5</v>
       </c>
       <c r="J6">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K6">
         <v>4</v>
       </c>
       <c r="L6">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M6">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N6">
         <v>6</v>
       </c>
       <c r="O6">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P6">
         <v>-1</v>
@@ -1108,22 +1141,22 @@
         <v>6</v>
       </c>
       <c r="J7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K7">
         <v>5</v>
       </c>
       <c r="L7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N7">
         <v>5</v>
       </c>
       <c r="O7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P7">
         <v>-1</v>
@@ -1150,16 +1183,16 @@
         <v>6</v>
       </c>
       <c r="X7">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Y7">
         <v>7</v>
       </c>
       <c r="Z7">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AA7">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AB7">
         <v>7</v>
@@ -1197,22 +1230,22 @@
         <v>6</v>
       </c>
       <c r="J8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K8">
         <v>7</v>
       </c>
       <c r="L8">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M8">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N8">
         <v>7</v>
       </c>
       <c r="O8">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P8">
         <v>-1</v>
@@ -1239,13 +1272,13 @@
         <v>7</v>
       </c>
       <c r="X8">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Y8">
         <v>7</v>
       </c>
       <c r="Z8">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AA8">
         <v>6</v>
@@ -1286,22 +1319,22 @@
         <v>8</v>
       </c>
       <c r="J9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K9">
         <v>7</v>
       </c>
       <c r="L9">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M9">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N9">
         <v>8</v>
       </c>
       <c r="O9">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P9">
         <v>-1</v>
@@ -1328,7 +1361,7 @@
         <v>7</v>
       </c>
       <c r="X9">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y9">
         <v>7</v>
@@ -1337,7 +1370,7 @@
         <v>7</v>
       </c>
       <c r="AA9">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AB9">
         <v>8</v>
@@ -1375,22 +1408,22 @@
         <v>7</v>
       </c>
       <c r="J10">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K10">
         <v>6</v>
       </c>
       <c r="L10">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M10">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N10">
         <v>9</v>
       </c>
       <c r="O10">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P10">
         <v>-1</v>
@@ -1417,7 +1450,7 @@
         <v>7</v>
       </c>
       <c r="X10">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Y10">
         <v>6</v>
@@ -1432,7 +1465,7 @@
         <v>9</v>
       </c>
       <c r="AC10">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="11" spans="1:29">
@@ -1464,22 +1497,22 @@
         <v>7</v>
       </c>
       <c r="J11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K11">
         <v>7</v>
       </c>
       <c r="L11">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M11">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N11">
         <v>8</v>
       </c>
       <c r="O11">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P11">
         <v>-1</v>
@@ -1512,7 +1545,7 @@
         <v>7</v>
       </c>
       <c r="Z11">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AA11">
         <v>7</v>
@@ -1553,22 +1586,22 @@
         <v>9</v>
       </c>
       <c r="J12">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K12">
         <v>7</v>
       </c>
       <c r="L12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N12">
         <v>6</v>
       </c>
       <c r="O12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P12">
         <v>-1</v>
@@ -1595,13 +1628,13 @@
         <v>8</v>
       </c>
       <c r="X12">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Y12">
         <v>7</v>
       </c>
       <c r="Z12">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AA12">
         <v>8</v>
@@ -1642,22 +1675,22 @@
         <v>6</v>
       </c>
       <c r="J13">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K13">
         <v>6</v>
       </c>
       <c r="L13">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N13">
         <v>6</v>
       </c>
       <c r="O13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P13">
         <v>-1</v>
@@ -1693,7 +1726,7 @@
         <v>5</v>
       </c>
       <c r="AA13">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AB13">
         <v>7</v>
@@ -1731,22 +1764,22 @@
         <v>6</v>
       </c>
       <c r="J14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K14">
         <v>6</v>
       </c>
       <c r="L14">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M14">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N14">
         <v>7</v>
       </c>
       <c r="O14">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P14">
         <v>-1</v>
@@ -1779,7 +1812,7 @@
         <v>7</v>
       </c>
       <c r="Z14">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA14">
         <v>5</v>
@@ -1820,22 +1853,22 @@
         <v>9</v>
       </c>
       <c r="J15">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K15">
         <v>6</v>
       </c>
       <c r="L15">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M15">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N15">
         <v>6</v>
       </c>
       <c r="O15">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P15">
         <v>-1</v>
@@ -1868,10 +1901,10 @@
         <v>7</v>
       </c>
       <c r="Z15">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA15">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AB15">
         <v>7</v>
@@ -1909,22 +1942,22 @@
         <v>7</v>
       </c>
       <c r="J16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K16">
         <v>5</v>
       </c>
       <c r="L16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N16">
         <v>6</v>
       </c>
       <c r="O16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P16">
         <v>-1</v>
@@ -1951,22 +1984,22 @@
         <v>7</v>
       </c>
       <c r="X16">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Y16">
         <v>6</v>
       </c>
       <c r="Z16">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AA16">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AB16">
         <v>8</v>
       </c>
       <c r="AC16">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="17" spans="1:29">
@@ -1998,22 +2031,22 @@
         <v>8</v>
       </c>
       <c r="J17">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K17">
         <v>7</v>
       </c>
       <c r="L17">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M17">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N17">
         <v>9</v>
       </c>
       <c r="O17">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P17">
         <v>-1</v>
@@ -2040,7 +2073,7 @@
         <v>7</v>
       </c>
       <c r="X17">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Y17">
         <v>8</v>
@@ -2087,22 +2120,22 @@
         <v>4</v>
       </c>
       <c r="J18">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K18">
         <v>6</v>
       </c>
       <c r="L18">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M18">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N18">
         <v>6</v>
       </c>
       <c r="O18">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P18">
         <v>-1</v>
@@ -2129,7 +2162,7 @@
         <v>5</v>
       </c>
       <c r="X18">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Y18">
         <v>6</v>
@@ -2176,22 +2209,22 @@
         <v>6</v>
       </c>
       <c r="J19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K19">
         <v>6</v>
       </c>
       <c r="L19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M19">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N19">
         <v>7</v>
       </c>
       <c r="O19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P19">
         <v>-1</v>
@@ -2218,7 +2251,7 @@
         <v>5</v>
       </c>
       <c r="X19">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Y19">
         <v>5</v>
@@ -2227,7 +2260,7 @@
         <v>5</v>
       </c>
       <c r="AA19">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AB19">
         <v>7</v>
@@ -2265,22 +2298,22 @@
         <v>5</v>
       </c>
       <c r="J20">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K20">
         <v>4</v>
       </c>
       <c r="L20">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M20">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N20">
         <v>5</v>
       </c>
       <c r="O20">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P20">
         <v>-1</v>
@@ -2354,22 +2387,22 @@
         <v>7</v>
       </c>
       <c r="J21">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K21">
         <v>6</v>
       </c>
       <c r="L21">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N21">
         <v>5</v>
       </c>
       <c r="O21">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P21">
         <v>-1</v>
@@ -2405,13 +2438,13 @@
         <v>5</v>
       </c>
       <c r="AA21">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AB21">
         <v>6</v>
       </c>
       <c r="AC21">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="22" spans="1:29">
@@ -2443,22 +2476,22 @@
         <v>8</v>
       </c>
       <c r="J22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K22">
         <v>5</v>
       </c>
       <c r="L22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N22">
         <v>6</v>
       </c>
       <c r="O22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P22">
         <v>-1</v>
@@ -2485,7 +2518,7 @@
         <v>8</v>
       </c>
       <c r="X22">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Y22">
         <v>5</v>
@@ -2532,22 +2565,22 @@
         <v>6</v>
       </c>
       <c r="J23">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K23">
         <v>5</v>
       </c>
       <c r="L23">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M23">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N23">
         <v>6</v>
       </c>
       <c r="O23">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P23">
         <v>-1</v>
@@ -2583,7 +2616,7 @@
         <v>5</v>
       </c>
       <c r="AA23">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AB23">
         <v>8</v>
@@ -2621,22 +2654,22 @@
         <v>8</v>
       </c>
       <c r="J24">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K24">
         <v>5</v>
       </c>
       <c r="L24">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M24">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N24">
         <v>7</v>
       </c>
       <c r="O24">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P24">
         <v>-1</v>
@@ -2663,7 +2696,7 @@
         <v>8</v>
       </c>
       <c r="X24">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Y24">
         <v>5</v>
@@ -2710,22 +2743,22 @@
         <v>9</v>
       </c>
       <c r="J25">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K25">
         <v>6</v>
       </c>
       <c r="L25">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M25">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N25">
         <v>6</v>
       </c>
       <c r="O25">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P25">
         <v>-1</v>
@@ -2752,16 +2785,16 @@
         <v>8</v>
       </c>
       <c r="X25">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y25">
         <v>7</v>
       </c>
       <c r="Z25">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AA25">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AB25">
         <v>8</v>
@@ -2799,22 +2832,22 @@
         <v>5</v>
       </c>
       <c r="J26">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K26">
         <v>5</v>
       </c>
       <c r="L26">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M26">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N26">
         <v>5</v>
       </c>
       <c r="O26">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P26">
         <v>-1</v>
@@ -2856,7 +2889,7 @@
         <v>5</v>
       </c>
       <c r="AC26">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="27" spans="1:29">
@@ -2888,22 +2921,22 @@
         <v>7</v>
       </c>
       <c r="J27">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K27">
         <v>4</v>
       </c>
       <c r="L27">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M27">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N27">
         <v>7</v>
       </c>
       <c r="O27">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P27">
         <v>-1</v>
@@ -2977,22 +3010,22 @@
         <v>6</v>
       </c>
       <c r="J28">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K28">
         <v>5</v>
       </c>
       <c r="L28">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M28">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N28">
         <v>7</v>
       </c>
       <c r="O28">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P28">
         <v>-1</v>
@@ -3025,7 +3058,7 @@
         <v>5</v>
       </c>
       <c r="Z28">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AA28">
         <v>9</v>
@@ -3066,22 +3099,22 @@
         <v>8</v>
       </c>
       <c r="J29">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K29">
         <v>5</v>
       </c>
       <c r="L29">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M29">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N29">
         <v>8</v>
       </c>
       <c r="O29">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P29">
         <v>-1</v>
@@ -3117,7 +3150,7 @@
         <v>6</v>
       </c>
       <c r="AA29">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AB29">
         <v>8</v>
@@ -3155,22 +3188,22 @@
         <v>8</v>
       </c>
       <c r="J30">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K30">
         <v>6</v>
       </c>
       <c r="L30">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M30">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N30">
         <v>5</v>
       </c>
       <c r="O30">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P30">
         <v>-1</v>
@@ -3197,7 +3230,7 @@
         <v>7</v>
       </c>
       <c r="X30">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y30">
         <v>7</v>
@@ -3244,22 +3277,22 @@
         <v>7</v>
       </c>
       <c r="J31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K31">
         <v>6</v>
       </c>
       <c r="L31">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M31">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N31">
         <v>7</v>
       </c>
       <c r="O31">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P31">
         <v>-1</v>
@@ -3286,13 +3319,13 @@
         <v>7</v>
       </c>
       <c r="X31">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="Y31">
         <v>8</v>
       </c>
       <c r="Z31">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA31">
         <v>7</v>
@@ -3333,22 +3366,22 @@
         <v>5</v>
       </c>
       <c r="J32">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K32">
         <v>0</v>
       </c>
       <c r="L32">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M32">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N32">
         <v>5</v>
       </c>
       <c r="O32">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P32">
         <v>-1</v>
@@ -3422,22 +3455,22 @@
         <v>8</v>
       </c>
       <c r="J33">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K33">
         <v>7</v>
       </c>
       <c r="L33">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M33">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N33">
         <v>8</v>
       </c>
       <c r="O33">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P33">
         <v>-1</v>
@@ -3473,7 +3506,7 @@
         <v>8</v>
       </c>
       <c r="AA33">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AB33">
         <v>8</v>
@@ -3511,22 +3544,22 @@
         <v>5</v>
       </c>
       <c r="J34">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K34">
         <v>5</v>
       </c>
       <c r="L34">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M34">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N34">
         <v>5</v>
       </c>
       <c r="O34">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P34">
         <v>-1</v>
@@ -3562,7 +3595,7 @@
         <v>5</v>
       </c>
       <c r="AA34">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AB34">
         <v>5</v>
@@ -3600,22 +3633,22 @@
         <v>10</v>
       </c>
       <c r="J35">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K35">
         <v>6</v>
       </c>
       <c r="L35">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M35">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N35">
         <v>8</v>
       </c>
       <c r="O35">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P35">
         <v>-1</v>
@@ -3648,7 +3681,7 @@
         <v>7</v>
       </c>
       <c r="Z35">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AA35">
         <v>8</v>
@@ -3689,22 +3722,22 @@
         <v>5</v>
       </c>
       <c r="J36">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K36">
         <v>4</v>
       </c>
       <c r="L36">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="M36">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N36">
         <v>5</v>
       </c>
       <c r="O36">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P36">
         <v>-1</v>
@@ -3740,7 +3773,7 @@
         <v>5</v>
       </c>
       <c r="AA36">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AB36">
         <v>5</v>
@@ -3778,22 +3811,22 @@
         <v>7</v>
       </c>
       <c r="J37">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K37">
         <v>5</v>
       </c>
       <c r="L37">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M37">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N37">
         <v>8</v>
       </c>
       <c r="O37">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P37">
         <v>-1</v>
@@ -3820,7 +3853,7 @@
         <v>6</v>
       </c>
       <c r="X37">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Y37">
         <v>5</v>
@@ -3867,22 +3900,22 @@
         <v>5</v>
       </c>
       <c r="J38">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K38">
         <v>5</v>
       </c>
       <c r="L38">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M38">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N38">
         <v>5</v>
       </c>
       <c r="O38">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P38">
         <v>-1</v>
@@ -3918,7 +3951,7 @@
         <v>5</v>
       </c>
       <c r="AA38">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AB38">
         <v>5</v>
@@ -3956,22 +3989,22 @@
         <v>7</v>
       </c>
       <c r="J39">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K39">
         <v>6</v>
       </c>
       <c r="L39">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M39">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N39">
         <v>7</v>
       </c>
       <c r="O39">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P39">
         <v>-1</v>
@@ -4004,10 +4037,10 @@
         <v>6</v>
       </c>
       <c r="Z39">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AA39">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AB39">
         <v>8</v>
@@ -4045,22 +4078,22 @@
         <v>7</v>
       </c>
       <c r="J40">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K40">
         <v>5</v>
       </c>
       <c r="L40">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M40">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N40">
         <v>7</v>
       </c>
       <c r="O40">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P40">
         <v>-1</v>
@@ -4102,7 +4135,7 @@
         <v>8</v>
       </c>
       <c r="AC40">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="41" spans="1:29">
@@ -4134,22 +4167,22 @@
         <v>10</v>
       </c>
       <c r="J41">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K41">
         <v>8</v>
       </c>
       <c r="L41">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M41">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N41">
         <v>9</v>
       </c>
       <c r="O41">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P41">
         <v>-1</v>
@@ -4176,16 +4209,16 @@
         <v>9</v>
       </c>
       <c r="X41">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Y41">
         <v>7</v>
       </c>
       <c r="Z41">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AA41">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AB41">
         <v>9</v>
@@ -4223,22 +4256,22 @@
         <v>3</v>
       </c>
       <c r="J42">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K42">
         <v>4</v>
       </c>
       <c r="L42">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="M42">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N42">
         <v>6</v>
       </c>
       <c r="O42">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P42">
         <v>-1</v>
@@ -4280,7 +4313,7 @@
         <v>7</v>
       </c>
       <c r="AC42">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -4440,7 +4473,7 @@
         <v>95.5</v>
       </c>
       <c r="L4">
-        <v>100</v>
+        <v>93.8</v>
       </c>
       <c r="M4">
         <v>100</v>
@@ -4449,7 +4482,7 @@
         <v>100</v>
       </c>
       <c r="O4">
-        <v>80</v>
+        <v>79.5</v>
       </c>
       <c r="P4">
         <v>60</v>
@@ -4461,7 +4494,7 @@
         <v>95.5</v>
       </c>
       <c r="S4">
-        <v>100</v>
+        <v>93.8</v>
       </c>
       <c r="T4">
         <v>100</v>
@@ -4470,7 +4503,7 @@
         <v>100</v>
       </c>
       <c r="V4">
-        <v>80</v>
+        <v>79.5</v>
       </c>
     </row>
     <row r="5" spans="1:22">
@@ -4517,7 +4550,7 @@
         <v>100</v>
       </c>
       <c r="O5">
-        <v>85</v>
+        <v>87.2</v>
       </c>
       <c r="P5">
         <v>100</v>
@@ -4538,7 +4571,7 @@
         <v>100</v>
       </c>
       <c r="V5">
-        <v>85</v>
+        <v>87.2</v>
       </c>
     </row>
     <row r="6" spans="1:22">
@@ -4576,16 +4609,16 @@
         <v>88.59999999999999</v>
       </c>
       <c r="L6">
-        <v>100</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="M6">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="N6">
         <v>100</v>
       </c>
       <c r="O6">
-        <v>85</v>
+        <v>84.59999999999999</v>
       </c>
       <c r="P6">
         <v>90</v>
@@ -4597,16 +4630,16 @@
         <v>88.59999999999999</v>
       </c>
       <c r="S6">
-        <v>100</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="T6">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="U6">
         <v>100</v>
       </c>
       <c r="V6">
-        <v>85</v>
+        <v>84.59999999999999</v>
       </c>
     </row>
     <row r="7" spans="1:22">
@@ -4653,7 +4686,7 @@
         <v>100</v>
       </c>
       <c r="O7">
-        <v>85</v>
+        <v>89.7</v>
       </c>
       <c r="P7">
         <v>80</v>
@@ -4674,7 +4707,7 @@
         <v>100</v>
       </c>
       <c r="V7">
-        <v>85</v>
+        <v>89.7</v>
       </c>
     </row>
     <row r="8" spans="1:22">
@@ -4721,7 +4754,7 @@
         <v>100</v>
       </c>
       <c r="O8">
-        <v>90</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="P8">
         <v>100</v>
@@ -4742,7 +4775,7 @@
         <v>100</v>
       </c>
       <c r="V8">
-        <v>90</v>
+        <v>94.90000000000001</v>
       </c>
     </row>
     <row r="9" spans="1:22">
@@ -4789,7 +4822,7 @@
         <v>100</v>
       </c>
       <c r="O9">
-        <v>85</v>
+        <v>87.2</v>
       </c>
       <c r="P9">
         <v>100</v>
@@ -4810,7 +4843,7 @@
         <v>100</v>
       </c>
       <c r="V9">
-        <v>85</v>
+        <v>87.2</v>
       </c>
     </row>
     <row r="10" spans="1:22">
@@ -4857,7 +4890,7 @@
         <v>100</v>
       </c>
       <c r="O10">
-        <v>95</v>
+        <v>97.40000000000001</v>
       </c>
       <c r="P10">
         <v>100</v>
@@ -4878,7 +4911,7 @@
         <v>100</v>
       </c>
       <c r="V10">
-        <v>95</v>
+        <v>97.40000000000001</v>
       </c>
     </row>
     <row r="11" spans="1:22">
@@ -4925,7 +4958,7 @@
         <v>100</v>
       </c>
       <c r="O11">
-        <v>95</v>
+        <v>97.40000000000001</v>
       </c>
       <c r="P11">
         <v>100</v>
@@ -4946,7 +4979,7 @@
         <v>100</v>
       </c>
       <c r="V11">
-        <v>95</v>
+        <v>97.40000000000001</v>
       </c>
     </row>
     <row r="12" spans="1:22">
@@ -4984,7 +5017,7 @@
         <v>93.2</v>
       </c>
       <c r="L12">
-        <v>100</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="M12">
         <v>100</v>
@@ -4993,7 +5026,7 @@
         <v>100</v>
       </c>
       <c r="O12">
-        <v>95</v>
+        <v>92.3</v>
       </c>
       <c r="P12">
         <v>90</v>
@@ -5005,7 +5038,7 @@
         <v>93.2</v>
       </c>
       <c r="S12">
-        <v>100</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="T12">
         <v>100</v>
@@ -5014,7 +5047,7 @@
         <v>100</v>
       </c>
       <c r="V12">
-        <v>95</v>
+        <v>92.3</v>
       </c>
     </row>
     <row r="13" spans="1:22">
@@ -5052,7 +5085,7 @@
         <v>88.59999999999999</v>
       </c>
       <c r="L13">
-        <v>100</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="M13">
         <v>100</v>
@@ -5061,7 +5094,7 @@
         <v>100</v>
       </c>
       <c r="O13">
-        <v>90</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="P13">
         <v>100</v>
@@ -5073,7 +5106,7 @@
         <v>88.59999999999999</v>
       </c>
       <c r="S13">
-        <v>100</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="T13">
         <v>100</v>
@@ -5082,7 +5115,7 @@
         <v>100</v>
       </c>
       <c r="V13">
-        <v>90</v>
+        <v>94.90000000000001</v>
       </c>
     </row>
     <row r="14" spans="1:22">
@@ -5129,7 +5162,7 @@
         <v>100</v>
       </c>
       <c r="O14">
-        <v>85</v>
+        <v>92.3</v>
       </c>
       <c r="P14">
         <v>90</v>
@@ -5150,7 +5183,7 @@
         <v>100</v>
       </c>
       <c r="V14">
-        <v>85</v>
+        <v>92.3</v>
       </c>
     </row>
     <row r="15" spans="1:22">
@@ -5188,7 +5221,7 @@
         <v>97.7</v>
       </c>
       <c r="L15">
-        <v>100</v>
+        <v>93.8</v>
       </c>
       <c r="M15">
         <v>100</v>
@@ -5197,7 +5230,7 @@
         <v>100</v>
       </c>
       <c r="O15">
-        <v>80</v>
+        <v>87.2</v>
       </c>
       <c r="P15">
         <v>80</v>
@@ -5209,7 +5242,7 @@
         <v>97.7</v>
       </c>
       <c r="S15">
-        <v>100</v>
+        <v>93.8</v>
       </c>
       <c r="T15">
         <v>100</v>
@@ -5218,7 +5251,7 @@
         <v>100</v>
       </c>
       <c r="V15">
-        <v>80</v>
+        <v>87.2</v>
       </c>
     </row>
     <row r="16" spans="1:22">
@@ -5256,7 +5289,7 @@
         <v>86.40000000000001</v>
       </c>
       <c r="L16">
-        <v>100</v>
+        <v>93.8</v>
       </c>
       <c r="M16">
         <v>95</v>
@@ -5265,7 +5298,7 @@
         <v>100</v>
       </c>
       <c r="O16">
-        <v>80</v>
+        <v>76.90000000000001</v>
       </c>
       <c r="P16">
         <v>80</v>
@@ -5277,7 +5310,7 @@
         <v>86.40000000000001</v>
       </c>
       <c r="S16">
-        <v>100</v>
+        <v>93.8</v>
       </c>
       <c r="T16">
         <v>95</v>
@@ -5286,7 +5319,7 @@
         <v>100</v>
       </c>
       <c r="V16">
-        <v>80</v>
+        <v>76.90000000000001</v>
       </c>
     </row>
     <row r="17" spans="1:22">
@@ -5333,7 +5366,7 @@
         <v>100</v>
       </c>
       <c r="O17">
-        <v>90</v>
+        <v>92.3</v>
       </c>
       <c r="P17">
         <v>100</v>
@@ -5354,7 +5387,7 @@
         <v>100</v>
       </c>
       <c r="V17">
-        <v>90</v>
+        <v>92.3</v>
       </c>
     </row>
     <row r="18" spans="1:22">
@@ -5392,7 +5425,7 @@
         <v>95.5</v>
       </c>
       <c r="L18">
-        <v>100</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="M18">
         <v>100</v>
@@ -5401,7 +5434,7 @@
         <v>100</v>
       </c>
       <c r="O18">
-        <v>90</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="P18">
         <v>80</v>
@@ -5413,7 +5446,7 @@
         <v>95.5</v>
       </c>
       <c r="S18">
-        <v>100</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="T18">
         <v>100</v>
@@ -5422,7 +5455,7 @@
         <v>100</v>
       </c>
       <c r="V18">
-        <v>90</v>
+        <v>94.90000000000001</v>
       </c>
     </row>
     <row r="19" spans="1:22">
@@ -5460,16 +5493,16 @@
         <v>86.40000000000001</v>
       </c>
       <c r="L19">
-        <v>100</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="M19">
-        <v>75</v>
+        <v>87.5</v>
       </c>
       <c r="N19">
         <v>100</v>
       </c>
       <c r="O19">
-        <v>80</v>
+        <v>76.90000000000001</v>
       </c>
       <c r="P19">
         <v>80</v>
@@ -5481,16 +5514,16 @@
         <v>86.40000000000001</v>
       </c>
       <c r="S19">
-        <v>100</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="T19">
-        <v>75</v>
+        <v>87.5</v>
       </c>
       <c r="U19">
         <v>100</v>
       </c>
       <c r="V19">
-        <v>80</v>
+        <v>76.90000000000001</v>
       </c>
     </row>
     <row r="20" spans="1:22">
@@ -5522,43 +5555,43 @@
         <v>25</v>
       </c>
       <c r="J20">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="K20">
         <v>34.1</v>
       </c>
       <c r="L20">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="M20">
-        <v>75</v>
+        <v>37.5</v>
       </c>
       <c r="N20">
         <v>100</v>
       </c>
       <c r="O20">
-        <v>80</v>
+        <v>41</v>
       </c>
       <c r="P20">
         <v>25</v>
       </c>
       <c r="Q20">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="R20">
         <v>34.1</v>
       </c>
       <c r="S20">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="T20">
-        <v>75</v>
+        <v>37.5</v>
       </c>
       <c r="U20">
         <v>100</v>
       </c>
       <c r="V20">
-        <v>80</v>
+        <v>41</v>
       </c>
     </row>
     <row r="21" spans="1:22">
@@ -5605,7 +5638,7 @@
         <v>100</v>
       </c>
       <c r="O21">
-        <v>95</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="P21">
         <v>95</v>
@@ -5626,7 +5659,7 @@
         <v>100</v>
       </c>
       <c r="V21">
-        <v>95</v>
+        <v>94.90000000000001</v>
       </c>
     </row>
     <row r="22" spans="1:22">
@@ -5673,7 +5706,7 @@
         <v>100</v>
       </c>
       <c r="O22">
-        <v>90</v>
+        <v>87.2</v>
       </c>
       <c r="P22">
         <v>90</v>
@@ -5694,7 +5727,7 @@
         <v>100</v>
       </c>
       <c r="V22">
-        <v>90</v>
+        <v>87.2</v>
       </c>
     </row>
     <row r="23" spans="1:22">
@@ -5732,7 +5765,7 @@
         <v>88.59999999999999</v>
       </c>
       <c r="L23">
-        <v>100</v>
+        <v>93.8</v>
       </c>
       <c r="M23">
         <v>100</v>
@@ -5741,7 +5774,7 @@
         <v>100</v>
       </c>
       <c r="O23">
-        <v>85</v>
+        <v>89.7</v>
       </c>
       <c r="P23">
         <v>100</v>
@@ -5753,7 +5786,7 @@
         <v>88.59999999999999</v>
       </c>
       <c r="S23">
-        <v>100</v>
+        <v>93.8</v>
       </c>
       <c r="T23">
         <v>100</v>
@@ -5762,7 +5795,7 @@
         <v>100</v>
       </c>
       <c r="V23">
-        <v>85</v>
+        <v>89.7</v>
       </c>
     </row>
     <row r="24" spans="1:22">
@@ -5800,7 +5833,7 @@
         <v>86.40000000000001</v>
       </c>
       <c r="L24">
-        <v>100</v>
+        <v>93.8</v>
       </c>
       <c r="M24">
         <v>100</v>
@@ -5809,7 +5842,7 @@
         <v>100</v>
       </c>
       <c r="O24">
-        <v>100</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="P24">
         <v>100</v>
@@ -5821,7 +5854,7 @@
         <v>86.40000000000001</v>
       </c>
       <c r="S24">
-        <v>100</v>
+        <v>93.8</v>
       </c>
       <c r="T24">
         <v>100</v>
@@ -5830,7 +5863,7 @@
         <v>100</v>
       </c>
       <c r="V24">
-        <v>100</v>
+        <v>94.90000000000001</v>
       </c>
     </row>
     <row r="25" spans="1:22">
@@ -5877,7 +5910,7 @@
         <v>100</v>
       </c>
       <c r="O25">
-        <v>90</v>
+        <v>97.40000000000001</v>
       </c>
       <c r="P25">
         <v>100</v>
@@ -5898,7 +5931,7 @@
         <v>100</v>
       </c>
       <c r="V25">
-        <v>90</v>
+        <v>97.40000000000001</v>
       </c>
     </row>
     <row r="26" spans="1:22">
@@ -5936,7 +5969,7 @@
         <v>84.09999999999999</v>
       </c>
       <c r="L26">
-        <v>100</v>
+        <v>93.8</v>
       </c>
       <c r="M26">
         <v>100</v>
@@ -5945,7 +5978,7 @@
         <v>100</v>
       </c>
       <c r="O26">
-        <v>80</v>
+        <v>84.59999999999999</v>
       </c>
       <c r="P26">
         <v>90</v>
@@ -5957,7 +5990,7 @@
         <v>84.09999999999999</v>
       </c>
       <c r="S26">
-        <v>100</v>
+        <v>93.8</v>
       </c>
       <c r="T26">
         <v>100</v>
@@ -5966,7 +5999,7 @@
         <v>100</v>
       </c>
       <c r="V26">
-        <v>80</v>
+        <v>84.59999999999999</v>
       </c>
     </row>
     <row r="27" spans="1:22">
@@ -6013,7 +6046,7 @@
         <v>100</v>
       </c>
       <c r="O27">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="P27">
         <v>100</v>
@@ -6034,7 +6067,7 @@
         <v>100</v>
       </c>
       <c r="V27">
-        <v>95</v>
+        <v>100</v>
       </c>
     </row>
     <row r="28" spans="1:22">
@@ -6072,7 +6105,7 @@
         <v>95.5</v>
       </c>
       <c r="L28">
-        <v>100</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="M28">
         <v>100</v>
@@ -6081,7 +6114,7 @@
         <v>100</v>
       </c>
       <c r="O28">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="P28">
         <v>100</v>
@@ -6093,7 +6126,7 @@
         <v>95.5</v>
       </c>
       <c r="S28">
-        <v>100</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="T28">
         <v>100</v>
@@ -6102,7 +6135,7 @@
         <v>100</v>
       </c>
       <c r="V28">
-        <v>95</v>
+        <v>100</v>
       </c>
     </row>
     <row r="29" spans="1:22">
@@ -6140,7 +6173,7 @@
         <v>93.2</v>
       </c>
       <c r="L29">
-        <v>100</v>
+        <v>93.8</v>
       </c>
       <c r="M29">
         <v>100</v>
@@ -6149,7 +6182,7 @@
         <v>100</v>
       </c>
       <c r="O29">
-        <v>90</v>
+        <v>92.3</v>
       </c>
       <c r="P29">
         <v>100</v>
@@ -6161,7 +6194,7 @@
         <v>93.2</v>
       </c>
       <c r="S29">
-        <v>100</v>
+        <v>93.8</v>
       </c>
       <c r="T29">
         <v>100</v>
@@ -6170,7 +6203,7 @@
         <v>100</v>
       </c>
       <c r="V29">
-        <v>90</v>
+        <v>92.3</v>
       </c>
     </row>
     <row r="30" spans="1:22">
@@ -6208,7 +6241,7 @@
         <v>86.40000000000001</v>
       </c>
       <c r="L30">
-        <v>100</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="M30">
         <v>100</v>
@@ -6217,7 +6250,7 @@
         <v>100</v>
       </c>
       <c r="O30">
-        <v>85</v>
+        <v>84.59999999999999</v>
       </c>
       <c r="P30">
         <v>100</v>
@@ -6229,7 +6262,7 @@
         <v>86.40000000000001</v>
       </c>
       <c r="S30">
-        <v>100</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="T30">
         <v>100</v>
@@ -6238,7 +6271,7 @@
         <v>100</v>
       </c>
       <c r="V30">
-        <v>85</v>
+        <v>84.59999999999999</v>
       </c>
     </row>
     <row r="31" spans="1:22">
@@ -6276,7 +6309,7 @@
         <v>90.90000000000001</v>
       </c>
       <c r="L31">
-        <v>100</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="M31">
         <v>100</v>
@@ -6285,7 +6318,7 @@
         <v>100</v>
       </c>
       <c r="O31">
-        <v>95</v>
+        <v>92.3</v>
       </c>
       <c r="P31">
         <v>100</v>
@@ -6297,7 +6330,7 @@
         <v>90.90000000000001</v>
       </c>
       <c r="S31">
-        <v>100</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="T31">
         <v>100</v>
@@ -6306,7 +6339,7 @@
         <v>100</v>
       </c>
       <c r="V31">
-        <v>95</v>
+        <v>92.3</v>
       </c>
     </row>
     <row r="32" spans="1:22">
@@ -6338,13 +6371,13 @@
         <v>0</v>
       </c>
       <c r="J32">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="K32">
         <v>0</v>
       </c>
       <c r="L32">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="M32">
         <v>0</v>
@@ -6359,13 +6392,13 @@
         <v>0</v>
       </c>
       <c r="Q32">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="R32">
         <v>0</v>
       </c>
       <c r="S32">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="T32">
         <v>0</v>
@@ -6421,7 +6454,7 @@
         <v>100</v>
       </c>
       <c r="O33">
-        <v>90</v>
+        <v>97.40000000000001</v>
       </c>
       <c r="P33">
         <v>90</v>
@@ -6442,7 +6475,7 @@
         <v>100</v>
       </c>
       <c r="V33">
-        <v>90</v>
+        <v>97.40000000000001</v>
       </c>
     </row>
     <row r="34" spans="1:22">
@@ -6480,7 +6513,7 @@
         <v>84.09999999999999</v>
       </c>
       <c r="L34">
-        <v>100</v>
+        <v>84.40000000000001</v>
       </c>
       <c r="M34">
         <v>100</v>
@@ -6489,7 +6522,7 @@
         <v>100</v>
       </c>
       <c r="O34">
-        <v>0</v>
+        <v>25.6</v>
       </c>
       <c r="P34">
         <v>70</v>
@@ -6501,7 +6534,7 @@
         <v>84.09999999999999</v>
       </c>
       <c r="S34">
-        <v>100</v>
+        <v>84.40000000000001</v>
       </c>
       <c r="T34">
         <v>100</v>
@@ -6510,7 +6543,7 @@
         <v>100</v>
       </c>
       <c r="V34">
-        <v>0</v>
+        <v>25.6</v>
       </c>
     </row>
     <row r="35" spans="1:22">
@@ -6548,7 +6581,7 @@
         <v>56.8</v>
       </c>
       <c r="L35">
-        <v>100</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="M35">
         <v>100</v>
@@ -6557,7 +6590,7 @@
         <v>100</v>
       </c>
       <c r="O35">
-        <v>95</v>
+        <v>97.40000000000001</v>
       </c>
       <c r="P35">
         <v>95</v>
@@ -6569,7 +6602,7 @@
         <v>56.8</v>
       </c>
       <c r="S35">
-        <v>100</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="T35">
         <v>100</v>
@@ -6578,7 +6611,7 @@
         <v>100</v>
       </c>
       <c r="V35">
-        <v>95</v>
+        <v>97.40000000000001</v>
       </c>
     </row>
     <row r="36" spans="1:22">
@@ -6610,13 +6643,13 @@
         <v>70</v>
       </c>
       <c r="J36">
-        <v>100</v>
+        <v>76.7</v>
       </c>
       <c r="K36">
         <v>84.09999999999999</v>
       </c>
       <c r="L36">
-        <v>100</v>
+        <v>81.3</v>
       </c>
       <c r="M36">
         <v>90</v>
@@ -6625,19 +6658,19 @@
         <v>100</v>
       </c>
       <c r="O36">
-        <v>80</v>
+        <v>74.40000000000001</v>
       </c>
       <c r="P36">
         <v>70</v>
       </c>
       <c r="Q36">
-        <v>100</v>
+        <v>76.7</v>
       </c>
       <c r="R36">
         <v>84.09999999999999</v>
       </c>
       <c r="S36">
-        <v>100</v>
+        <v>81.3</v>
       </c>
       <c r="T36">
         <v>90</v>
@@ -6646,7 +6679,7 @@
         <v>100</v>
       </c>
       <c r="V36">
-        <v>80</v>
+        <v>74.40000000000001</v>
       </c>
     </row>
     <row r="37" spans="1:22">
@@ -6684,7 +6717,7 @@
         <v>97.7</v>
       </c>
       <c r="L37">
-        <v>100</v>
+        <v>93.8</v>
       </c>
       <c r="M37">
         <v>100</v>
@@ -6693,7 +6726,7 @@
         <v>100</v>
       </c>
       <c r="O37">
-        <v>95</v>
+        <v>92.3</v>
       </c>
       <c r="P37">
         <v>100</v>
@@ -6705,7 +6738,7 @@
         <v>97.7</v>
       </c>
       <c r="S37">
-        <v>100</v>
+        <v>93.8</v>
       </c>
       <c r="T37">
         <v>100</v>
@@ -6714,7 +6747,7 @@
         <v>100</v>
       </c>
       <c r="V37">
-        <v>95</v>
+        <v>92.3</v>
       </c>
     </row>
     <row r="38" spans="1:22">
@@ -6761,7 +6794,7 @@
         <v>100</v>
       </c>
       <c r="O38">
-        <v>80</v>
+        <v>89.7</v>
       </c>
       <c r="P38">
         <v>90</v>
@@ -6782,7 +6815,7 @@
         <v>100</v>
       </c>
       <c r="V38">
-        <v>80</v>
+        <v>89.7</v>
       </c>
     </row>
     <row r="39" spans="1:22">
@@ -6820,7 +6853,7 @@
         <v>95.5</v>
       </c>
       <c r="L39">
-        <v>100</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="M39">
         <v>100</v>
@@ -6829,7 +6862,7 @@
         <v>100</v>
       </c>
       <c r="O39">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="P39">
         <v>100</v>
@@ -6841,7 +6874,7 @@
         <v>95.5</v>
       </c>
       <c r="S39">
-        <v>100</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="T39">
         <v>100</v>
@@ -6850,7 +6883,7 @@
         <v>100</v>
       </c>
       <c r="V39">
-        <v>95</v>
+        <v>100</v>
       </c>
     </row>
     <row r="40" spans="1:22">
@@ -6888,7 +6921,7 @@
         <v>97.7</v>
       </c>
       <c r="L40">
-        <v>100</v>
+        <v>93.8</v>
       </c>
       <c r="M40">
         <v>100</v>
@@ -6897,7 +6930,7 @@
         <v>100</v>
       </c>
       <c r="O40">
-        <v>90</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="P40">
         <v>100</v>
@@ -6909,7 +6942,7 @@
         <v>97.7</v>
       </c>
       <c r="S40">
-        <v>100</v>
+        <v>93.8</v>
       </c>
       <c r="T40">
         <v>100</v>
@@ -6918,7 +6951,7 @@
         <v>100</v>
       </c>
       <c r="V40">
-        <v>90</v>
+        <v>94.90000000000001</v>
       </c>
     </row>
     <row r="41" spans="1:22">
@@ -6965,7 +6998,7 @@
         <v>100</v>
       </c>
       <c r="O41">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="P41">
         <v>100</v>
@@ -6986,7 +7019,7 @@
         <v>100</v>
       </c>
       <c r="V41">
-        <v>95</v>
+        <v>100</v>
       </c>
     </row>
     <row r="42" spans="1:22">
@@ -7024,16 +7057,16 @@
         <v>81.8</v>
       </c>
       <c r="L42">
-        <v>100</v>
+        <v>84.40000000000001</v>
       </c>
       <c r="M42">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="N42">
         <v>100</v>
       </c>
       <c r="O42">
-        <v>85</v>
+        <v>74.40000000000001</v>
       </c>
       <c r="P42">
         <v>80</v>
@@ -7045,16 +7078,16 @@
         <v>81.8</v>
       </c>
       <c r="S42">
-        <v>100</v>
+        <v>84.40000000000001</v>
       </c>
       <c r="T42">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="U42">
         <v>100</v>
       </c>
       <c r="V42">
-        <v>85</v>
+        <v>74.40000000000001</v>
       </c>
     </row>
   </sheetData>
@@ -7120,19 +7153,19 @@
         <v>39</v>
       </c>
       <c r="D2">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="E2">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="F2" s="2">
-        <v>48.7</v>
+        <v>33.3</v>
       </c>
       <c r="G2" s="2">
-        <v>51.3</v>
+        <v>66.7</v>
       </c>
       <c r="H2">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="I2">
         <v>0</v>
@@ -7152,19 +7185,19 @@
         <v>39</v>
       </c>
       <c r="D3">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="E3">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="F3" s="2">
-        <v>53.8</v>
+        <v>35.9</v>
       </c>
       <c r="G3" s="2">
-        <v>46.2</v>
+        <v>64.09999999999999</v>
       </c>
       <c r="H3">
-        <v>5.9</v>
+        <v>5.7</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -7248,19 +7281,19 @@
         <v>39</v>
       </c>
       <c r="D6">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E6">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F6" s="2">
-        <v>64.09999999999999</v>
+        <v>61.5</v>
       </c>
       <c r="G6" s="2">
-        <v>35.9</v>
+        <v>38.5</v>
       </c>
       <c r="H6">
-        <v>6.7</v>
+        <v>6.5</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -7271,7 +7304,7 @@
     </row>
     <row r="7" spans="1:10">
       <c r="A7" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="B7" t="s">
         <v>70</v>
@@ -7280,19 +7313,19 @@
         <v>39</v>
       </c>
       <c r="D7">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="E7">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F7" s="2">
-        <v>79.5</v>
+        <v>74.40000000000001</v>
       </c>
       <c r="G7" s="2">
-        <v>20.5</v>
+        <v>25.6</v>
       </c>
       <c r="H7">
-        <v>7.3</v>
+        <v>6.7</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -7303,7 +7336,7 @@
     </row>
     <row r="8" spans="1:10">
       <c r="A8" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="B8" t="s">
         <v>71</v>
@@ -7312,19 +7345,19 @@
         <v>39</v>
       </c>
       <c r="D8">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E8">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F8" s="2">
-        <v>82.09999999999999</v>
+        <v>79.5</v>
       </c>
       <c r="G8" s="2">
-        <v>17.9</v>
+        <v>20.5</v>
       </c>
       <c r="H8">
-        <v>6.7</v>
+        <v>7.3</v>
       </c>
       <c r="I8">
         <v>0</v>
@@ -7338,7 +7371,7 @@
         <v>64</v>
       </c>
       <c r="B9" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C9">
         <v>0</v>
@@ -7394,7 +7427,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G12"/>
+  <dimension ref="A1:G17"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -7426,22 +7459,22 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>23330051920229</v>
+        <v>23330051920220</v>
       </c>
       <c r="B2" t="s">
         <v>76</v>
       </c>
       <c r="C2" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="D2" t="s">
-        <v>90</v>
+        <v>97</v>
       </c>
       <c r="E2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F2" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="G2">
         <v>5</v>
@@ -7449,16 +7482,16 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>23330051920229</v>
+        <v>23330051920220</v>
       </c>
       <c r="B3" t="s">
         <v>76</v>
       </c>
       <c r="C3" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="D3" t="s">
-        <v>90</v>
+        <v>97</v>
       </c>
       <c r="E3" t="s">
         <v>11</v>
@@ -7472,22 +7505,22 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>23330051920247</v>
+        <v>23330051920222</v>
       </c>
       <c r="B4" t="s">
         <v>77</v>
       </c>
       <c r="C4" t="s">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="D4" t="s">
-        <v>91</v>
+        <v>98</v>
       </c>
       <c r="E4" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="F4" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G4">
         <v>5</v>
@@ -7495,22 +7528,22 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>23330051920247</v>
+        <v>23330051920222</v>
       </c>
       <c r="B5" t="s">
         <v>77</v>
       </c>
       <c r="C5" t="s">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="D5" t="s">
-        <v>91</v>
+        <v>98</v>
       </c>
       <c r="E5" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="F5" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="G5">
         <v>5</v>
@@ -7518,22 +7551,22 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>23330051920251</v>
+        <v>23330051920229</v>
       </c>
       <c r="B6" t="s">
         <v>78</v>
       </c>
       <c r="C6" t="s">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="D6" t="s">
-        <v>92</v>
+        <v>99</v>
       </c>
       <c r="E6" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F6" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="G6">
         <v>5</v>
@@ -7541,16 +7574,16 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>23330051920251</v>
+        <v>23330051920229</v>
       </c>
       <c r="B7" t="s">
         <v>78</v>
       </c>
       <c r="C7" t="s">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="D7" t="s">
-        <v>92</v>
+        <v>99</v>
       </c>
       <c r="E7" t="s">
         <v>11</v>
@@ -7564,22 +7597,22 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>23330051920220</v>
+        <v>23330051920251</v>
       </c>
       <c r="B8" t="s">
         <v>79</v>
       </c>
       <c r="C8" t="s">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="D8" t="s">
-        <v>93</v>
+        <v>100</v>
       </c>
       <c r="E8" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F8" t="s">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="G8">
         <v>5</v>
@@ -7587,16 +7620,16 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>23330051920221</v>
+        <v>23330051920251</v>
       </c>
       <c r="B9" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C9" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="D9" t="s">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="E9" t="s">
         <v>11</v>
@@ -7610,22 +7643,22 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>23330051920222</v>
+        <v>23330051920218</v>
       </c>
       <c r="B10" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C10" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="D10" t="s">
-        <v>95</v>
+        <v>101</v>
       </c>
       <c r="E10" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F10" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="G10">
         <v>5</v>
@@ -7633,16 +7666,16 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>23330051920230</v>
+        <v>23330051920221</v>
       </c>
       <c r="B11" t="s">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="C11" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="D11" t="s">
-        <v>96</v>
+        <v>102</v>
       </c>
       <c r="E11" t="s">
         <v>11</v>
@@ -7656,24 +7689,139 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>23330051920253</v>
+        <v>23330051920224</v>
       </c>
       <c r="B12" t="s">
         <v>82</v>
       </c>
       <c r="C12" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="D12" t="s">
-        <v>97</v>
+        <v>103</v>
       </c>
       <c r="E12" t="s">
+        <v>8</v>
+      </c>
+      <c r="F12" t="s">
+        <v>66</v>
+      </c>
+      <c r="G12">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7">
+      <c r="A13">
+        <v>23330051920230</v>
+      </c>
+      <c r="B13" t="s">
+        <v>78</v>
+      </c>
+      <c r="C13" t="s">
+        <v>91</v>
+      </c>
+      <c r="D13" t="s">
+        <v>104</v>
+      </c>
+      <c r="E13" t="s">
         <v>11</v>
       </c>
-      <c r="F12" t="s">
+      <c r="F13" t="s">
         <v>65</v>
       </c>
-      <c r="G12">
+      <c r="G13">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7">
+      <c r="A14">
+        <v>23330051920231</v>
+      </c>
+      <c r="B14" t="s">
+        <v>83</v>
+      </c>
+      <c r="C14" t="s">
+        <v>94</v>
+      </c>
+      <c r="D14" t="s">
+        <v>105</v>
+      </c>
+      <c r="E14" t="s">
+        <v>11</v>
+      </c>
+      <c r="F14" t="s">
+        <v>65</v>
+      </c>
+      <c r="G14">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7">
+      <c r="A15">
+        <v>23330051920243</v>
+      </c>
+      <c r="B15" t="s">
+        <v>84</v>
+      </c>
+      <c r="C15" t="s">
+        <v>95</v>
+      </c>
+      <c r="D15" t="s">
+        <v>106</v>
+      </c>
+      <c r="E15" t="s">
+        <v>8</v>
+      </c>
+      <c r="F15" t="s">
+        <v>66</v>
+      </c>
+      <c r="G15">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7">
+      <c r="A16">
+        <v>23330051920253</v>
+      </c>
+      <c r="B16" t="s">
+        <v>85</v>
+      </c>
+      <c r="C16" t="s">
+        <v>96</v>
+      </c>
+      <c r="D16" t="s">
+        <v>107</v>
+      </c>
+      <c r="E16" t="s">
+        <v>11</v>
+      </c>
+      <c r="F16" t="s">
+        <v>65</v>
+      </c>
+      <c r="G16">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7">
+      <c r="A17">
+        <v>23330051920265</v>
+      </c>
+      <c r="B17" t="s">
+        <v>86</v>
+      </c>
+      <c r="C17" t="s">
+        <v>85</v>
+      </c>
+      <c r="D17" t="s">
+        <v>108</v>
+      </c>
+      <c r="E17" t="s">
+        <v>8</v>
+      </c>
+      <c r="F17" t="s">
+        <v>66</v>
+      </c>
+      <c r="G17">
         <v>5</v>
       </c>
     </row>

--- a/grupos/1CV - Estadisticos 20231.xlsx
+++ b/grupos/1CV - Estadisticos 20231.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="257" uniqueCount="109">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="317" uniqueCount="129">
   <si>
     <t>Materia</t>
   </si>
@@ -224,18 +224,18 @@
     <t>Gaspar Velazco Juan Francisco</t>
   </si>
   <si>
+    <t>Contreras Díaz Irma Ivette</t>
+  </si>
+  <si>
     <t>Martínez López Miguel Ángel</t>
   </si>
   <si>
-    <t>Contreras Díaz Irma Ivette</t>
+    <t>Vargas Olvera Francisco Eduardo</t>
   </si>
   <si>
     <t>Pesce Bautista Victor Manuel</t>
   </si>
   <si>
-    <t>Vargas Olvera Francisco Eduardo</t>
-  </si>
-  <si>
     <t>NC</t>
   </si>
   <si>
@@ -251,97 +251,157 @@
     <t>BARRAGAN</t>
   </si>
   <si>
+    <t>GARCIA</t>
+  </si>
+  <si>
+    <t>GONZALEZ</t>
+  </si>
+  <si>
+    <t>GUERRA</t>
+  </si>
+  <si>
+    <t>HERNANDEZ</t>
+  </si>
+  <si>
+    <t>IXMATLAHUA</t>
+  </si>
+  <si>
+    <t>LOBATO</t>
+  </si>
+  <si>
+    <t>SAN JUAN</t>
+  </si>
+  <si>
+    <t>ALMANZA</t>
+  </si>
+  <si>
+    <t>CRUZ</t>
+  </si>
+  <si>
     <t>CUAPIO</t>
   </si>
   <si>
-    <t>GARCIA</t>
+    <t>DORANTES</t>
+  </si>
+  <si>
+    <t>LAGUNA</t>
+  </si>
+  <si>
+    <t>LUIS</t>
   </si>
   <si>
     <t>MARQUEZ</t>
   </si>
   <si>
-    <t>ALMANZA</t>
-  </si>
-  <si>
-    <t>CRUZ</t>
-  </si>
-  <si>
-    <t>DORANTES</t>
-  </si>
-  <si>
-    <t>GILES</t>
-  </si>
-  <si>
-    <t>LAGUNA</t>
-  </si>
-  <si>
     <t>MENDEZ</t>
   </si>
   <si>
+    <t>RAMIREZ</t>
+  </si>
+  <si>
     <t>SANCHEZ</t>
   </si>
   <si>
     <t>MACUIXTLE</t>
   </si>
   <si>
+    <t>ROSALES</t>
+  </si>
+  <si>
+    <t>TZITZIHUA</t>
+  </si>
+  <si>
+    <t>ARIAS</t>
+  </si>
+  <si>
+    <t>SARMIENTO</t>
+  </si>
+  <si>
+    <t>ANTONIO</t>
+  </si>
+  <si>
+    <t>AGUILAR</t>
+  </si>
+  <si>
+    <t>SANTOS</t>
+  </si>
+  <si>
+    <t>CASTILLO</t>
+  </si>
+  <si>
     <t>HUERTA</t>
   </si>
   <si>
+    <t>PORRAS</t>
+  </si>
+  <si>
     <t>SANTIAGO</t>
   </si>
   <si>
-    <t>GONZALEZ</t>
-  </si>
-  <si>
-    <t>SANTOS</t>
-  </si>
-  <si>
-    <t>CASTILLO</t>
-  </si>
-  <si>
-    <t>PORRAS</t>
-  </si>
-  <si>
-    <t>FIGUEROA</t>
-  </si>
-  <si>
     <t>NATH</t>
   </si>
   <si>
+    <t>VERA</t>
+  </si>
+  <si>
     <t>MONDRAGON</t>
   </si>
   <si>
+    <t>MOLINA</t>
+  </si>
+  <si>
     <t>MARIA FERNANDA</t>
   </si>
   <si>
+    <t>REGINA DAYTRI</t>
+  </si>
+  <si>
+    <t>MIRIAM</t>
+  </si>
+  <si>
+    <t>ALEX TADEO</t>
+  </si>
+  <si>
+    <t>EDUARDO</t>
+  </si>
+  <si>
+    <t>FERNANDA YAMILET</t>
+  </si>
+  <si>
+    <t>DIANA LAURA</t>
+  </si>
+  <si>
+    <t>KARINA MONSERRATH</t>
+  </si>
+  <si>
+    <t>VANESA BETHSABE</t>
+  </si>
+  <si>
+    <t>RAMSES</t>
+  </si>
+  <si>
     <t>JESSICA</t>
   </si>
   <si>
+    <t>ROBERTO</t>
+  </si>
+  <si>
+    <t>JAIRO</t>
+  </si>
+  <si>
     <t>MARIANA</t>
   </si>
   <si>
+    <t>AARON ZACHARY</t>
+  </si>
+  <si>
     <t>DIEGO GREGORIO</t>
   </si>
   <si>
-    <t>VANESA BETHSABE</t>
-  </si>
-  <si>
-    <t>RAMSES</t>
-  </si>
-  <si>
-    <t>ROBERTO</t>
-  </si>
-  <si>
-    <t>JAIRO</t>
-  </si>
-  <si>
-    <t>ALEXA YAMILET</t>
-  </si>
-  <si>
-    <t>AARON ZACHARY</t>
-  </si>
-  <si>
     <t>ANGEL ADRIAN</t>
+  </si>
+  <si>
+    <t>AIDE SCARLET</t>
   </si>
   <si>
     <t>KAREN</t>
@@ -895,19 +955,19 @@
         <v>-1</v>
       </c>
       <c r="Q4">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R4">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="S4">
         <v>-1</v>
       </c>
       <c r="T4">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="U4">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="V4">
         <v>-1</v>
@@ -916,16 +976,16 @@
         <v>5</v>
       </c>
       <c r="X4">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Y4">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Z4">
         <v>5</v>
       </c>
       <c r="AA4">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AB4">
         <v>5</v>
@@ -981,22 +1041,22 @@
         <v>6</v>
       </c>
       <c r="P5">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q5">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R5">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S5">
         <v>-1</v>
       </c>
       <c r="T5">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="U5">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V5">
         <v>-1</v>
@@ -1073,19 +1133,19 @@
         <v>-1</v>
       </c>
       <c r="Q6">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R6">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S6">
         <v>-1</v>
       </c>
       <c r="T6">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="U6">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V6">
         <v>-1</v>
@@ -1097,7 +1157,7 @@
         <v>8</v>
       </c>
       <c r="Y6">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Z6">
         <v>5</v>
@@ -1106,7 +1166,7 @@
         <v>5</v>
       </c>
       <c r="AB6">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AC6">
         <v>5</v>
@@ -1159,22 +1219,22 @@
         <v>5</v>
       </c>
       <c r="P7">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S7">
         <v>-1</v>
       </c>
       <c r="T7">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="U7">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="V7">
         <v>-1</v>
@@ -1192,7 +1252,7 @@
         <v>5</v>
       </c>
       <c r="AA7">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AB7">
         <v>7</v>
@@ -1248,22 +1308,22 @@
         <v>5</v>
       </c>
       <c r="P8">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q8">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R8">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S8">
         <v>-1</v>
       </c>
       <c r="T8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="U8">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="V8">
         <v>-1</v>
@@ -1272,7 +1332,7 @@
         <v>7</v>
       </c>
       <c r="X8">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Y8">
         <v>7</v>
@@ -1281,10 +1341,10 @@
         <v>7</v>
       </c>
       <c r="AA8">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AB8">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AC8">
         <v>5</v>
@@ -1337,22 +1397,22 @@
         <v>6</v>
       </c>
       <c r="P9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R9">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S9">
         <v>-1</v>
       </c>
       <c r="T9">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="U9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V9">
         <v>-1</v>
@@ -1426,22 +1486,22 @@
         <v>5</v>
       </c>
       <c r="P10">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S10">
         <v>-1</v>
       </c>
       <c r="T10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="U10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V10">
         <v>-1</v>
@@ -1450,19 +1510,19 @@
         <v>7</v>
       </c>
       <c r="X10">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y10">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Z10">
         <v>6</v>
       </c>
       <c r="AA10">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AB10">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AC10">
         <v>5</v>
@@ -1518,19 +1578,19 @@
         <v>-1</v>
       </c>
       <c r="Q11">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R11">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S11">
         <v>-1</v>
       </c>
       <c r="T11">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="U11">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V11">
         <v>-1</v>
@@ -1539,7 +1599,7 @@
         <v>7</v>
       </c>
       <c r="X11">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Y11">
         <v>7</v>
@@ -1548,10 +1608,10 @@
         <v>5</v>
       </c>
       <c r="AA11">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AB11">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AC11">
         <v>6</v>
@@ -1604,22 +1664,22 @@
         <v>6</v>
       </c>
       <c r="P12">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q12">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R12">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S12">
         <v>-1</v>
       </c>
       <c r="T12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="U12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="V12">
         <v>-1</v>
@@ -1637,7 +1697,7 @@
         <v>7</v>
       </c>
       <c r="AA12">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AB12">
         <v>7</v>
@@ -1693,28 +1753,28 @@
         <v>6</v>
       </c>
       <c r="P13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q13">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R13">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="S13">
         <v>-1</v>
       </c>
       <c r="T13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="V13">
         <v>-1</v>
       </c>
       <c r="W13">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X13">
         <v>7</v>
@@ -1782,22 +1842,22 @@
         <v>5</v>
       </c>
       <c r="P14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R14">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S14">
         <v>-1</v>
       </c>
       <c r="T14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="U14">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="V14">
         <v>-1</v>
@@ -1809,16 +1869,16 @@
         <v>8</v>
       </c>
       <c r="Y14">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Z14">
         <v>7</v>
       </c>
       <c r="AA14">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AB14">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AC14">
         <v>5</v>
@@ -1871,28 +1931,28 @@
         <v>6</v>
       </c>
       <c r="P15">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R15">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S15">
         <v>-1</v>
       </c>
       <c r="T15">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="U15">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="V15">
         <v>-1</v>
       </c>
       <c r="W15">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X15">
         <v>7</v>
@@ -1904,10 +1964,10 @@
         <v>7</v>
       </c>
       <c r="AA15">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AB15">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AC15">
         <v>5</v>
@@ -1960,22 +2020,22 @@
         <v>5</v>
       </c>
       <c r="P16">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R16">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="S16">
         <v>-1</v>
       </c>
       <c r="T16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="U16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V16">
         <v>-1</v>
@@ -1984,19 +2044,19 @@
         <v>7</v>
       </c>
       <c r="X16">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Y16">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Z16">
         <v>6</v>
       </c>
       <c r="AA16">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AB16">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="AC16">
         <v>5</v>
@@ -2049,34 +2109,34 @@
         <v>6</v>
       </c>
       <c r="P17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S17">
         <v>-1</v>
       </c>
       <c r="T17">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="U17">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="V17">
         <v>-1</v>
       </c>
       <c r="W17">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X17">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y17">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Z17">
         <v>7</v>
@@ -2085,7 +2145,7 @@
         <v>9</v>
       </c>
       <c r="AB17">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AC17">
         <v>6</v>
@@ -2138,28 +2198,28 @@
         <v>5</v>
       </c>
       <c r="P18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q18">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R18">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S18">
         <v>-1</v>
       </c>
       <c r="T18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="U18">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="V18">
         <v>-1</v>
       </c>
       <c r="W18">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X18">
         <v>6</v>
@@ -2171,7 +2231,7 @@
         <v>5</v>
       </c>
       <c r="AA18">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AB18">
         <v>7</v>
@@ -2227,34 +2287,34 @@
         <v>5</v>
       </c>
       <c r="P19">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q19">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R19">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S19">
         <v>-1</v>
       </c>
       <c r="T19">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="U19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V19">
         <v>-1</v>
       </c>
       <c r="W19">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X19">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y19">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Z19">
         <v>5</v>
@@ -2316,22 +2376,22 @@
         <v>5</v>
       </c>
       <c r="P20">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q20">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R20">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="S20">
         <v>-1</v>
       </c>
       <c r="T20">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="U20">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V20">
         <v>-1</v>
@@ -2405,34 +2465,34 @@
         <v>5</v>
       </c>
       <c r="P21">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R21">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S21">
         <v>-1</v>
       </c>
       <c r="T21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="U21">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="V21">
         <v>-1</v>
       </c>
       <c r="W21">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X21">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y21">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Z21">
         <v>5</v>
@@ -2497,19 +2557,19 @@
         <v>-1</v>
       </c>
       <c r="Q22">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R22">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="S22">
         <v>-1</v>
       </c>
       <c r="T22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="U22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V22">
         <v>-1</v>
@@ -2518,7 +2578,7 @@
         <v>8</v>
       </c>
       <c r="X22">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y22">
         <v>5</v>
@@ -2530,7 +2590,7 @@
         <v>5</v>
       </c>
       <c r="AB22">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AC22">
         <v>5</v>
@@ -2586,19 +2646,19 @@
         <v>-1</v>
       </c>
       <c r="Q23">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R23">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S23">
         <v>-1</v>
       </c>
       <c r="T23">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="U23">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="V23">
         <v>-1</v>
@@ -2610,7 +2670,7 @@
         <v>7</v>
       </c>
       <c r="Y23">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Z23">
         <v>5</v>
@@ -2619,7 +2679,7 @@
         <v>7</v>
       </c>
       <c r="AB23">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AC23">
         <v>5</v>
@@ -2672,22 +2732,22 @@
         <v>5</v>
       </c>
       <c r="P24">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q24">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R24">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S24">
         <v>-1</v>
       </c>
       <c r="T24">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="U24">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V24">
         <v>-1</v>
@@ -2696,7 +2756,7 @@
         <v>8</v>
       </c>
       <c r="X24">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y24">
         <v>5</v>
@@ -2705,7 +2765,7 @@
         <v>5</v>
       </c>
       <c r="AA24">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AB24">
         <v>8</v>
@@ -2761,22 +2821,22 @@
         <v>6</v>
       </c>
       <c r="P25">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q25">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R25">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S25">
         <v>-1</v>
       </c>
       <c r="T25">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="U25">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="V25">
         <v>-1</v>
@@ -2797,7 +2857,7 @@
         <v>8</v>
       </c>
       <c r="AB25">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AC25">
         <v>7</v>
@@ -2850,31 +2910,31 @@
         <v>5</v>
       </c>
       <c r="P26">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q26">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R26">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S26">
         <v>-1</v>
       </c>
       <c r="T26">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="U26">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="V26">
         <v>-1</v>
       </c>
       <c r="W26">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X26">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y26">
         <v>6</v>
@@ -2883,10 +2943,10 @@
         <v>5</v>
       </c>
       <c r="AA26">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AB26">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AC26">
         <v>5</v>
@@ -2939,28 +2999,28 @@
         <v>6</v>
       </c>
       <c r="P27">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q27">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R27">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="S27">
         <v>-1</v>
       </c>
       <c r="T27">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="U27">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="V27">
         <v>-1</v>
       </c>
       <c r="W27">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X27">
         <v>7</v>
@@ -2972,10 +3032,10 @@
         <v>5</v>
       </c>
       <c r="AA27">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AB27">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AC27">
         <v>5</v>
@@ -3031,19 +3091,19 @@
         <v>-1</v>
       </c>
       <c r="Q28">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R28">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="S28">
         <v>-1</v>
       </c>
       <c r="T28">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="U28">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="V28">
         <v>-1</v>
@@ -3117,22 +3177,22 @@
         <v>6</v>
       </c>
       <c r="P29">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q29">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R29">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S29">
         <v>-1</v>
       </c>
       <c r="T29">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="U29">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="V29">
         <v>-1</v>
@@ -3141,10 +3201,10 @@
         <v>7</v>
       </c>
       <c r="X29">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Y29">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Z29">
         <v>6</v>
@@ -3153,7 +3213,7 @@
         <v>7</v>
       </c>
       <c r="AB29">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AC29">
         <v>6</v>
@@ -3206,22 +3266,22 @@
         <v>6</v>
       </c>
       <c r="P30">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q30">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R30">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S30">
         <v>-1</v>
       </c>
       <c r="T30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U30">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V30">
         <v>-1</v>
@@ -3230,19 +3290,19 @@
         <v>7</v>
       </c>
       <c r="X30">
+        <v>8</v>
+      </c>
+      <c r="Y30">
+        <v>7</v>
+      </c>
+      <c r="Z30">
+        <v>8</v>
+      </c>
+      <c r="AA30">
         <v>9</v>
       </c>
-      <c r="Y30">
-        <v>7</v>
-      </c>
-      <c r="Z30">
-        <v>8</v>
-      </c>
-      <c r="AA30">
-        <v>8</v>
-      </c>
       <c r="AB30">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AC30">
         <v>5</v>
@@ -3295,22 +3355,22 @@
         <v>6</v>
       </c>
       <c r="P31">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q31">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R31">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S31">
         <v>-1</v>
       </c>
       <c r="T31">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="U31">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="V31">
         <v>-1</v>
@@ -3328,10 +3388,10 @@
         <v>7</v>
       </c>
       <c r="AA31">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AB31">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AC31">
         <v>5</v>
@@ -3384,22 +3444,22 @@
         <v>5</v>
       </c>
       <c r="P32">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q32">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R32">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="S32">
         <v>-1</v>
       </c>
       <c r="T32">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="U32">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V32">
         <v>-1</v>
@@ -3473,22 +3533,22 @@
         <v>6</v>
       </c>
       <c r="P33">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q33">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R33">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S33">
         <v>-1</v>
       </c>
       <c r="T33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U33">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V33">
         <v>-1</v>
@@ -3562,28 +3622,28 @@
         <v>5</v>
       </c>
       <c r="P34">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q34">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R34">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S34">
         <v>-1</v>
       </c>
       <c r="T34">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="U34">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V34">
         <v>-1</v>
       </c>
       <c r="W34">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X34">
         <v>5</v>
@@ -3618,7 +3678,7 @@
         <v>8</v>
       </c>
       <c r="E35">
-        <v>8</v>
+        <v>8.5</v>
       </c>
       <c r="F35">
         <v>8</v>
@@ -3651,22 +3711,22 @@
         <v>6</v>
       </c>
       <c r="P35">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q35">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R35">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S35">
         <v>-1</v>
       </c>
       <c r="T35">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="U35">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="V35">
         <v>-1</v>
@@ -3678,7 +3738,7 @@
         <v>8</v>
       </c>
       <c r="Y35">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="Z35">
         <v>7</v>
@@ -3743,19 +3803,19 @@
         <v>-1</v>
       </c>
       <c r="Q36">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R36">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S36">
         <v>-1</v>
       </c>
       <c r="T36">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="U36">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V36">
         <v>-1</v>
@@ -3829,43 +3889,43 @@
         <v>5</v>
       </c>
       <c r="P37">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q37">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R37">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S37">
         <v>-1</v>
       </c>
       <c r="T37">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="U37">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="V37">
         <v>-1</v>
       </c>
       <c r="W37">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X37">
         <v>6</v>
       </c>
       <c r="Y37">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Z37">
         <v>5</v>
       </c>
       <c r="AA37">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AB37">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AC37">
         <v>5</v>
@@ -3921,19 +3981,19 @@
         <v>-1</v>
       </c>
       <c r="Q38">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R38">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S38">
         <v>-1</v>
       </c>
       <c r="T38">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="U38">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V38">
         <v>-1</v>
@@ -3942,10 +4002,10 @@
         <v>5</v>
       </c>
       <c r="X38">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y38">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Z38">
         <v>5</v>
@@ -4007,22 +4067,22 @@
         <v>6</v>
       </c>
       <c r="P39">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q39">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R39">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S39">
         <v>-1</v>
       </c>
       <c r="T39">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="U39">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="V39">
         <v>-1</v>
@@ -4034,7 +4094,7 @@
         <v>8</v>
       </c>
       <c r="Y39">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Z39">
         <v>5</v>
@@ -4096,22 +4156,22 @@
         <v>5</v>
       </c>
       <c r="P40">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q40">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R40">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="S40">
         <v>-1</v>
       </c>
       <c r="T40">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="U40">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="V40">
         <v>-1</v>
@@ -4120,7 +4180,7 @@
         <v>7</v>
       </c>
       <c r="X40">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Y40">
         <v>5</v>
@@ -4129,7 +4189,7 @@
         <v>5</v>
       </c>
       <c r="AA40">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AB40">
         <v>8</v>
@@ -4185,22 +4245,22 @@
         <v>6</v>
       </c>
       <c r="P41">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q41">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R41">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S41">
         <v>-1</v>
       </c>
       <c r="T41">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="U41">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="V41">
         <v>-1</v>
@@ -4212,7 +4272,7 @@
         <v>8</v>
       </c>
       <c r="Y41">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Z41">
         <v>6</v>
@@ -4274,22 +4334,22 @@
         <v>5</v>
       </c>
       <c r="P42">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q42">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R42">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="S42">
         <v>-1</v>
       </c>
       <c r="T42">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="U42">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V42">
         <v>-1</v>
@@ -4310,7 +4370,7 @@
         <v>5</v>
       </c>
       <c r="AB42">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AC42">
         <v>5</v>
@@ -4485,19 +4545,19 @@
         <v>79.5</v>
       </c>
       <c r="P4">
-        <v>60</v>
+        <v>37.5</v>
       </c>
       <c r="Q4">
         <v>100</v>
       </c>
       <c r="R4">
-        <v>95.5</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="S4">
         <v>93.8</v>
       </c>
       <c r="T4">
-        <v>100</v>
+        <v>98.3</v>
       </c>
       <c r="U4">
         <v>100</v>
@@ -4559,7 +4619,7 @@
         <v>100</v>
       </c>
       <c r="R5">
-        <v>95.5</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="S5">
         <v>100</v>
@@ -4621,13 +4681,13 @@
         <v>84.59999999999999</v>
       </c>
       <c r="P6">
-        <v>90</v>
+        <v>56.3</v>
       </c>
       <c r="Q6">
         <v>100</v>
       </c>
       <c r="R6">
-        <v>88.59999999999999</v>
+        <v>85.90000000000001</v>
       </c>
       <c r="S6">
         <v>96.90000000000001</v>
@@ -4636,7 +4696,7 @@
         <v>95</v>
       </c>
       <c r="U6">
-        <v>100</v>
+        <v>88.90000000000001</v>
       </c>
       <c r="V6">
         <v>84.59999999999999</v>
@@ -4689,13 +4749,13 @@
         <v>89.7</v>
       </c>
       <c r="P7">
-        <v>80</v>
+        <v>87.5</v>
       </c>
       <c r="Q7">
         <v>100</v>
       </c>
       <c r="R7">
-        <v>90.90000000000001</v>
+        <v>89.09999999999999</v>
       </c>
       <c r="S7">
         <v>100</v>
@@ -4831,7 +4891,7 @@
         <v>100</v>
       </c>
       <c r="R9">
-        <v>97.7</v>
+        <v>95.3</v>
       </c>
       <c r="S9">
         <v>100</v>
@@ -4899,7 +4959,7 @@
         <v>100</v>
       </c>
       <c r="R10">
-        <v>90.90000000000001</v>
+        <v>93.8</v>
       </c>
       <c r="S10">
         <v>100</v>
@@ -4961,13 +5021,13 @@
         <v>97.40000000000001</v>
       </c>
       <c r="P11">
-        <v>100</v>
+        <v>62.5</v>
       </c>
       <c r="Q11">
         <v>100</v>
       </c>
       <c r="R11">
-        <v>93.2</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="S11">
         <v>100</v>
@@ -5029,19 +5089,19 @@
         <v>92.3</v>
       </c>
       <c r="P12">
-        <v>90</v>
+        <v>93.8</v>
       </c>
       <c r="Q12">
         <v>100</v>
       </c>
       <c r="R12">
-        <v>93.2</v>
+        <v>93.8</v>
       </c>
       <c r="S12">
         <v>96.90000000000001</v>
       </c>
       <c r="T12">
-        <v>100</v>
+        <v>98.3</v>
       </c>
       <c r="U12">
         <v>100</v>
@@ -5103,7 +5163,7 @@
         <v>100</v>
       </c>
       <c r="R13">
-        <v>88.59999999999999</v>
+        <v>85.90000000000001</v>
       </c>
       <c r="S13">
         <v>96.90000000000001</v>
@@ -5165,19 +5225,19 @@
         <v>92.3</v>
       </c>
       <c r="P14">
-        <v>90</v>
+        <v>93.8</v>
       </c>
       <c r="Q14">
         <v>100</v>
       </c>
       <c r="R14">
-        <v>95.5</v>
+        <v>93.8</v>
       </c>
       <c r="S14">
         <v>100</v>
       </c>
       <c r="T14">
-        <v>100</v>
+        <v>98.3</v>
       </c>
       <c r="U14">
         <v>100</v>
@@ -5233,13 +5293,13 @@
         <v>87.2</v>
       </c>
       <c r="P15">
-        <v>80</v>
+        <v>87.5</v>
       </c>
       <c r="Q15">
         <v>100</v>
       </c>
       <c r="R15">
-        <v>97.7</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="S15">
         <v>93.8</v>
@@ -5301,13 +5361,13 @@
         <v>76.90000000000001</v>
       </c>
       <c r="P16">
-        <v>80</v>
+        <v>87.5</v>
       </c>
       <c r="Q16">
         <v>100</v>
       </c>
       <c r="R16">
-        <v>86.40000000000001</v>
+        <v>84.40000000000001</v>
       </c>
       <c r="S16">
         <v>93.8</v>
@@ -5316,7 +5376,7 @@
         <v>95</v>
       </c>
       <c r="U16">
-        <v>100</v>
+        <v>77.8</v>
       </c>
       <c r="V16">
         <v>76.90000000000001</v>
@@ -5375,7 +5435,7 @@
         <v>100</v>
       </c>
       <c r="R17">
-        <v>93.2</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="S17">
         <v>100</v>
@@ -5437,13 +5497,13 @@
         <v>94.90000000000001</v>
       </c>
       <c r="P18">
-        <v>80</v>
+        <v>87.5</v>
       </c>
       <c r="Q18">
         <v>100</v>
       </c>
       <c r="R18">
-        <v>95.5</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="S18">
         <v>96.90000000000001</v>
@@ -5505,19 +5565,19 @@
         <v>76.90000000000001</v>
       </c>
       <c r="P19">
-        <v>80</v>
+        <v>87.5</v>
       </c>
       <c r="Q19">
         <v>100</v>
       </c>
       <c r="R19">
-        <v>86.40000000000001</v>
+        <v>87.5</v>
       </c>
       <c r="S19">
         <v>96.90000000000001</v>
       </c>
       <c r="T19">
-        <v>87.5</v>
+        <v>90</v>
       </c>
       <c r="U19">
         <v>100</v>
@@ -5573,19 +5633,19 @@
         <v>41</v>
       </c>
       <c r="P20">
-        <v>25</v>
+        <v>15.6</v>
       </c>
       <c r="Q20">
-        <v>80</v>
+        <v>86.7</v>
       </c>
       <c r="R20">
-        <v>34.1</v>
+        <v>23.4</v>
       </c>
       <c r="S20">
         <v>50</v>
       </c>
       <c r="T20">
-        <v>37.5</v>
+        <v>25</v>
       </c>
       <c r="U20">
         <v>100</v>
@@ -5641,13 +5701,13 @@
         <v>94.90000000000001</v>
       </c>
       <c r="P21">
-        <v>95</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="Q21">
         <v>100</v>
       </c>
       <c r="R21">
-        <v>88.59999999999999</v>
+        <v>89.09999999999999</v>
       </c>
       <c r="S21">
         <v>100</v>
@@ -5709,19 +5769,19 @@
         <v>87.2</v>
       </c>
       <c r="P22">
-        <v>90</v>
+        <v>56.3</v>
       </c>
       <c r="Q22">
         <v>100</v>
       </c>
       <c r="R22">
-        <v>93.2</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="S22">
         <v>100</v>
       </c>
       <c r="T22">
-        <v>100</v>
+        <v>98.3</v>
       </c>
       <c r="U22">
         <v>100</v>
@@ -5777,19 +5837,19 @@
         <v>89.7</v>
       </c>
       <c r="P23">
-        <v>100</v>
+        <v>62.5</v>
       </c>
       <c r="Q23">
         <v>100</v>
       </c>
       <c r="R23">
-        <v>88.59999999999999</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="S23">
         <v>93.8</v>
       </c>
       <c r="T23">
-        <v>100</v>
+        <v>98.3</v>
       </c>
       <c r="U23">
         <v>100</v>
@@ -5851,13 +5911,13 @@
         <v>100</v>
       </c>
       <c r="R24">
-        <v>86.40000000000001</v>
+        <v>85.90000000000001</v>
       </c>
       <c r="S24">
         <v>93.8</v>
       </c>
       <c r="T24">
-        <v>100</v>
+        <v>98.3</v>
       </c>
       <c r="U24">
         <v>100</v>
@@ -5919,13 +5979,13 @@
         <v>100</v>
       </c>
       <c r="R25">
-        <v>95.5</v>
+        <v>89.09999999999999</v>
       </c>
       <c r="S25">
         <v>100</v>
       </c>
       <c r="T25">
-        <v>100</v>
+        <v>98.3</v>
       </c>
       <c r="U25">
         <v>100</v>
@@ -5981,13 +6041,13 @@
         <v>84.59999999999999</v>
       </c>
       <c r="P26">
-        <v>90</v>
+        <v>93.8</v>
       </c>
       <c r="Q26">
         <v>100</v>
       </c>
       <c r="R26">
-        <v>84.09999999999999</v>
+        <v>82.8</v>
       </c>
       <c r="S26">
         <v>93.8</v>
@@ -6055,7 +6115,7 @@
         <v>100</v>
       </c>
       <c r="R27">
-        <v>90.90000000000001</v>
+        <v>93.8</v>
       </c>
       <c r="S27">
         <v>100</v>
@@ -6117,13 +6177,13 @@
         <v>100</v>
       </c>
       <c r="P28">
-        <v>100</v>
+        <v>62.5</v>
       </c>
       <c r="Q28">
         <v>100</v>
       </c>
       <c r="R28">
-        <v>95.5</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="S28">
         <v>96.90000000000001</v>
@@ -6191,7 +6251,7 @@
         <v>100</v>
       </c>
       <c r="R29">
-        <v>93.2</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="S29">
         <v>93.8</v>
@@ -6259,7 +6319,7 @@
         <v>100</v>
       </c>
       <c r="R30">
-        <v>86.40000000000001</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="S30">
         <v>96.90000000000001</v>
@@ -6327,7 +6387,7 @@
         <v>100</v>
       </c>
       <c r="R31">
-        <v>90.90000000000001</v>
+        <v>87.5</v>
       </c>
       <c r="S31">
         <v>96.90000000000001</v>
@@ -6392,7 +6452,7 @@
         <v>0</v>
       </c>
       <c r="Q32">
-        <v>80</v>
+        <v>86.7</v>
       </c>
       <c r="R32">
         <v>0</v>
@@ -6457,13 +6517,13 @@
         <v>97.40000000000001</v>
       </c>
       <c r="P33">
-        <v>90</v>
+        <v>93.8</v>
       </c>
       <c r="Q33">
         <v>100</v>
       </c>
       <c r="R33">
-        <v>97.7</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="S33">
         <v>100</v>
@@ -6525,19 +6585,19 @@
         <v>25.6</v>
       </c>
       <c r="P34">
-        <v>70</v>
+        <v>81.3</v>
       </c>
       <c r="Q34">
         <v>100</v>
       </c>
       <c r="R34">
-        <v>84.09999999999999</v>
+        <v>76.59999999999999</v>
       </c>
       <c r="S34">
         <v>84.40000000000001</v>
       </c>
       <c r="T34">
-        <v>100</v>
+        <v>98.3</v>
       </c>
       <c r="U34">
         <v>100</v>
@@ -6593,13 +6653,13 @@
         <v>97.40000000000001</v>
       </c>
       <c r="P35">
-        <v>95</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="Q35">
         <v>100</v>
       </c>
       <c r="R35">
-        <v>56.8</v>
+        <v>70.3</v>
       </c>
       <c r="S35">
         <v>96.90000000000001</v>
@@ -6661,19 +6721,19 @@
         <v>74.40000000000001</v>
       </c>
       <c r="P36">
-        <v>70</v>
+        <v>43.8</v>
       </c>
       <c r="Q36">
-        <v>76.7</v>
+        <v>84.40000000000001</v>
       </c>
       <c r="R36">
-        <v>84.09999999999999</v>
+        <v>78.09999999999999</v>
       </c>
       <c r="S36">
         <v>81.3</v>
       </c>
       <c r="T36">
-        <v>90</v>
+        <v>91.7</v>
       </c>
       <c r="U36">
         <v>100</v>
@@ -6735,13 +6795,13 @@
         <v>100</v>
       </c>
       <c r="R37">
-        <v>97.7</v>
+        <v>92.2</v>
       </c>
       <c r="S37">
         <v>93.8</v>
       </c>
       <c r="T37">
-        <v>100</v>
+        <v>98.3</v>
       </c>
       <c r="U37">
         <v>100</v>
@@ -6797,19 +6857,19 @@
         <v>89.7</v>
       </c>
       <c r="P38">
-        <v>90</v>
+        <v>56.3</v>
       </c>
       <c r="Q38">
         <v>100</v>
       </c>
       <c r="R38">
-        <v>97.7</v>
+        <v>92.2</v>
       </c>
       <c r="S38">
         <v>100</v>
       </c>
       <c r="T38">
-        <v>100</v>
+        <v>98.3</v>
       </c>
       <c r="U38">
         <v>100</v>
@@ -6871,7 +6931,7 @@
         <v>100</v>
       </c>
       <c r="R39">
-        <v>95.5</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="S39">
         <v>96.90000000000001</v>
@@ -6939,7 +6999,7 @@
         <v>100</v>
       </c>
       <c r="R40">
-        <v>97.7</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="S40">
         <v>93.8</v>
@@ -7069,13 +7129,13 @@
         <v>74.40000000000001</v>
       </c>
       <c r="P42">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="Q42">
-        <v>100</v>
+        <v>77.8</v>
       </c>
       <c r="R42">
-        <v>81.8</v>
+        <v>56.3</v>
       </c>
       <c r="S42">
         <v>84.40000000000001</v>
@@ -7217,19 +7277,19 @@
         <v>39</v>
       </c>
       <c r="D4">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="E4">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F4" s="2">
-        <v>56.4</v>
+        <v>61.5</v>
       </c>
       <c r="G4" s="2">
-        <v>43.6</v>
+        <v>38.5</v>
       </c>
       <c r="H4">
-        <v>6</v>
+        <v>6.1</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -7240,7 +7300,7 @@
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="B5" t="s">
         <v>68</v>
@@ -7249,19 +7309,19 @@
         <v>39</v>
       </c>
       <c r="D5">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="E5">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="F5" s="2">
-        <v>61.5</v>
+        <v>76.90000000000001</v>
       </c>
       <c r="G5" s="2">
-        <v>38.5</v>
+        <v>23.1</v>
       </c>
       <c r="H5">
-        <v>6.4</v>
+        <v>6.7</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -7272,7 +7332,7 @@
     </row>
     <row r="6" spans="1:10">
       <c r="A6" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="B6" t="s">
         <v>69</v>
@@ -7281,19 +7341,19 @@
         <v>39</v>
       </c>
       <c r="D6">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="E6">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="F6" s="2">
-        <v>61.5</v>
+        <v>79.5</v>
       </c>
       <c r="G6" s="2">
-        <v>38.5</v>
+        <v>20.5</v>
       </c>
       <c r="H6">
-        <v>6.5</v>
+        <v>6.6</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -7304,7 +7364,7 @@
     </row>
     <row r="7" spans="1:10">
       <c r="A7" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="B7" t="s">
         <v>70</v>
@@ -7313,19 +7373,19 @@
         <v>39</v>
       </c>
       <c r="D7">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="E7">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F7" s="2">
-        <v>74.40000000000001</v>
+        <v>82.09999999999999</v>
       </c>
       <c r="G7" s="2">
-        <v>25.6</v>
+        <v>17.9</v>
       </c>
       <c r="H7">
-        <v>6.7</v>
+        <v>6.9</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -7336,7 +7396,7 @@
     </row>
     <row r="8" spans="1:10">
       <c r="A8" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="B8" t="s">
         <v>71</v>
@@ -7345,19 +7405,19 @@
         <v>39</v>
       </c>
       <c r="D8">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="E8">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F8" s="2">
-        <v>79.5</v>
+        <v>84.59999999999999</v>
       </c>
       <c r="G8" s="2">
-        <v>20.5</v>
+        <v>15.4</v>
       </c>
       <c r="H8">
-        <v>7.3</v>
+        <v>6.7</v>
       </c>
       <c r="I8">
         <v>0</v>
@@ -7371,7 +7431,7 @@
         <v>64</v>
       </c>
       <c r="B9" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C9">
         <v>0</v>
@@ -7427,7 +7487,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G17"/>
+  <dimension ref="A1:G29"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -7465,10 +7525,10 @@
         <v>76</v>
       </c>
       <c r="C2" t="s">
-        <v>87</v>
+        <v>94</v>
       </c>
       <c r="D2" t="s">
-        <v>97</v>
+        <v>110</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -7488,10 +7548,10 @@
         <v>76</v>
       </c>
       <c r="C3" t="s">
-        <v>87</v>
+        <v>94</v>
       </c>
       <c r="D3" t="s">
-        <v>97</v>
+        <v>110</v>
       </c>
       <c r="E3" t="s">
         <v>11</v>
@@ -7505,22 +7565,22 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>23330051920222</v>
+        <v>23330051920228</v>
       </c>
       <c r="B4" t="s">
         <v>77</v>
       </c>
       <c r="C4" t="s">
-        <v>88</v>
+        <v>95</v>
       </c>
       <c r="D4" t="s">
-        <v>98</v>
+        <v>111</v>
       </c>
       <c r="E4" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F4" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="G4">
         <v>5</v>
@@ -7528,22 +7588,22 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>23330051920222</v>
+        <v>23330051920228</v>
       </c>
       <c r="B5" t="s">
         <v>77</v>
       </c>
       <c r="C5" t="s">
-        <v>88</v>
+        <v>95</v>
       </c>
       <c r="D5" t="s">
-        <v>98</v>
+        <v>111</v>
       </c>
       <c r="E5" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F5" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="G5">
         <v>5</v>
@@ -7551,22 +7611,22 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>23330051920229</v>
+        <v>23330051920233</v>
       </c>
       <c r="B6" t="s">
         <v>78</v>
       </c>
       <c r="C6" t="s">
-        <v>89</v>
+        <v>96</v>
       </c>
       <c r="D6" t="s">
-        <v>99</v>
+        <v>112</v>
       </c>
       <c r="E6" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F6" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="G6">
         <v>5</v>
@@ -7574,16 +7634,16 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>23330051920229</v>
+        <v>23330051920233</v>
       </c>
       <c r="B7" t="s">
         <v>78</v>
       </c>
       <c r="C7" t="s">
-        <v>89</v>
+        <v>96</v>
       </c>
       <c r="D7" t="s">
-        <v>99</v>
+        <v>112</v>
       </c>
       <c r="E7" t="s">
         <v>11</v>
@@ -7597,22 +7657,22 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>23330051920251</v>
+        <v>23330051920234</v>
       </c>
       <c r="B8" t="s">
         <v>79</v>
       </c>
       <c r="C8" t="s">
-        <v>90</v>
+        <v>97</v>
       </c>
       <c r="D8" t="s">
-        <v>100</v>
+        <v>113</v>
       </c>
       <c r="E8" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F8" t="s">
-        <v>71</v>
+        <v>66</v>
       </c>
       <c r="G8">
         <v>5</v>
@@ -7620,16 +7680,16 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>23330051920251</v>
+        <v>23330051920234</v>
       </c>
       <c r="B9" t="s">
         <v>79</v>
       </c>
       <c r="C9" t="s">
-        <v>90</v>
+        <v>97</v>
       </c>
       <c r="D9" t="s">
-        <v>100</v>
+        <v>113</v>
       </c>
       <c r="E9" t="s">
         <v>11</v>
@@ -7643,16 +7703,16 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>23330051920218</v>
+        <v>23330051920236</v>
       </c>
       <c r="B10" t="s">
         <v>80</v>
       </c>
       <c r="C10" t="s">
-        <v>91</v>
+        <v>98</v>
       </c>
       <c r="D10" t="s">
-        <v>101</v>
+        <v>114</v>
       </c>
       <c r="E10" t="s">
         <v>8</v>
@@ -7666,16 +7726,16 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>23330051920221</v>
+        <v>23330051920236</v>
       </c>
       <c r="B11" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C11" t="s">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="D11" t="s">
-        <v>102</v>
+        <v>114</v>
       </c>
       <c r="E11" t="s">
         <v>11</v>
@@ -7689,16 +7749,16 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>23330051920224</v>
+        <v>23330051920271</v>
       </c>
       <c r="B12" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C12" t="s">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="D12" t="s">
-        <v>103</v>
+        <v>115</v>
       </c>
       <c r="E12" t="s">
         <v>8</v>
@@ -7712,16 +7772,16 @@
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>23330051920230</v>
+        <v>23330051920271</v>
       </c>
       <c r="B13" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="C13" t="s">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="D13" t="s">
-        <v>104</v>
+        <v>115</v>
       </c>
       <c r="E13" t="s">
         <v>11</v>
@@ -7735,22 +7795,22 @@
     </row>
     <row r="14" spans="1:7">
       <c r="A14">
-        <v>23330051920231</v>
+        <v>23330051920335</v>
       </c>
       <c r="B14" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C14" t="s">
-        <v>94</v>
+        <v>99</v>
       </c>
       <c r="D14" t="s">
-        <v>105</v>
+        <v>116</v>
       </c>
       <c r="E14" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F14" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="G14">
         <v>5</v>
@@ -7758,22 +7818,22 @@
     </row>
     <row r="15" spans="1:7">
       <c r="A15">
-        <v>23330051920243</v>
+        <v>23330051920335</v>
       </c>
       <c r="B15" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="C15" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="D15" t="s">
-        <v>106</v>
+        <v>116</v>
       </c>
       <c r="E15" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F15" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="G15">
         <v>5</v>
@@ -7781,22 +7841,22 @@
     </row>
     <row r="16" spans="1:7">
       <c r="A16">
-        <v>23330051920253</v>
+        <v>23330051920264</v>
       </c>
       <c r="B16" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="C16" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="D16" t="s">
-        <v>107</v>
+        <v>117</v>
       </c>
       <c r="E16" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F16" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="G16">
         <v>5</v>
@@ -7804,24 +7864,300 @@
     </row>
     <row r="17" spans="1:7">
       <c r="A17">
+        <v>23330051920264</v>
+      </c>
+      <c r="B17" t="s">
+        <v>83</v>
+      </c>
+      <c r="C17" t="s">
+        <v>100</v>
+      </c>
+      <c r="D17" t="s">
+        <v>117</v>
+      </c>
+      <c r="E17" t="s">
+        <v>11</v>
+      </c>
+      <c r="F17" t="s">
+        <v>65</v>
+      </c>
+      <c r="G17">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7">
+      <c r="A18">
+        <v>23330051920218</v>
+      </c>
+      <c r="B18" t="s">
+        <v>84</v>
+      </c>
+      <c r="C18" t="s">
+        <v>101</v>
+      </c>
+      <c r="D18" t="s">
+        <v>118</v>
+      </c>
+      <c r="E18" t="s">
+        <v>8</v>
+      </c>
+      <c r="F18" t="s">
+        <v>66</v>
+      </c>
+      <c r="G18">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7">
+      <c r="A19">
+        <v>23330051920221</v>
+      </c>
+      <c r="B19" t="s">
+        <v>85</v>
+      </c>
+      <c r="C19" t="s">
+        <v>102</v>
+      </c>
+      <c r="D19" t="s">
+        <v>119</v>
+      </c>
+      <c r="E19" t="s">
+        <v>11</v>
+      </c>
+      <c r="F19" t="s">
+        <v>65</v>
+      </c>
+      <c r="G19">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7">
+      <c r="A20">
+        <v>23330051920222</v>
+      </c>
+      <c r="B20" t="s">
+        <v>86</v>
+      </c>
+      <c r="C20" t="s">
+        <v>103</v>
+      </c>
+      <c r="D20" t="s">
+        <v>120</v>
+      </c>
+      <c r="E20" t="s">
+        <v>11</v>
+      </c>
+      <c r="F20" t="s">
+        <v>65</v>
+      </c>
+      <c r="G20">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7">
+      <c r="A21">
+        <v>23330051920224</v>
+      </c>
+      <c r="B21" t="s">
+        <v>87</v>
+      </c>
+      <c r="C21" t="s">
+        <v>104</v>
+      </c>
+      <c r="D21" t="s">
+        <v>121</v>
+      </c>
+      <c r="E21" t="s">
+        <v>8</v>
+      </c>
+      <c r="F21" t="s">
+        <v>66</v>
+      </c>
+      <c r="G21">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7">
+      <c r="A22">
+        <v>23330051920230</v>
+      </c>
+      <c r="B22" t="s">
+        <v>77</v>
+      </c>
+      <c r="C22" t="s">
+        <v>101</v>
+      </c>
+      <c r="D22" t="s">
+        <v>122</v>
+      </c>
+      <c r="E22" t="s">
+        <v>11</v>
+      </c>
+      <c r="F22" t="s">
+        <v>65</v>
+      </c>
+      <c r="G22">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7">
+      <c r="A23">
+        <v>23330051920229</v>
+      </c>
+      <c r="B23" t="s">
+        <v>77</v>
+      </c>
+      <c r="C23" t="s">
+        <v>105</v>
+      </c>
+      <c r="D23" t="s">
+        <v>123</v>
+      </c>
+      <c r="E23" t="s">
+        <v>11</v>
+      </c>
+      <c r="F23" t="s">
+        <v>65</v>
+      </c>
+      <c r="G23">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7">
+      <c r="A24">
+        <v>23330051920243</v>
+      </c>
+      <c r="B24" t="s">
+        <v>88</v>
+      </c>
+      <c r="C24" t="s">
+        <v>106</v>
+      </c>
+      <c r="D24" t="s">
+        <v>124</v>
+      </c>
+      <c r="E24" t="s">
+        <v>8</v>
+      </c>
+      <c r="F24" t="s">
+        <v>66</v>
+      </c>
+      <c r="G24">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7">
+      <c r="A25">
+        <v>23330051920249</v>
+      </c>
+      <c r="B25" t="s">
+        <v>89</v>
+      </c>
+      <c r="C25" t="s">
+        <v>107</v>
+      </c>
+      <c r="D25" t="s">
+        <v>116</v>
+      </c>
+      <c r="E25" t="s">
+        <v>7</v>
+      </c>
+      <c r="F25" t="s">
+        <v>67</v>
+      </c>
+      <c r="G25">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7">
+      <c r="A26">
+        <v>23330051920251</v>
+      </c>
+      <c r="B26" t="s">
+        <v>90</v>
+      </c>
+      <c r="C26" t="s">
+        <v>78</v>
+      </c>
+      <c r="D26" t="s">
+        <v>125</v>
+      </c>
+      <c r="E26" t="s">
+        <v>11</v>
+      </c>
+      <c r="F26" t="s">
+        <v>65</v>
+      </c>
+      <c r="G26">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7">
+      <c r="A27">
+        <v>23330051920253</v>
+      </c>
+      <c r="B27" t="s">
+        <v>91</v>
+      </c>
+      <c r="C27" t="s">
+        <v>108</v>
+      </c>
+      <c r="D27" t="s">
+        <v>126</v>
+      </c>
+      <c r="E27" t="s">
+        <v>11</v>
+      </c>
+      <c r="F27" t="s">
+        <v>65</v>
+      </c>
+      <c r="G27">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7">
+      <c r="A28">
+        <v>23330051920258</v>
+      </c>
+      <c r="B28" t="s">
+        <v>92</v>
+      </c>
+      <c r="C28" t="s">
+        <v>109</v>
+      </c>
+      <c r="D28" t="s">
+        <v>127</v>
+      </c>
+      <c r="E28" t="s">
+        <v>7</v>
+      </c>
+      <c r="F28" t="s">
+        <v>67</v>
+      </c>
+      <c r="G28">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7">
+      <c r="A29">
         <v>23330051920265</v>
       </c>
-      <c r="B17" t="s">
-        <v>86</v>
-      </c>
-      <c r="C17" t="s">
-        <v>85</v>
-      </c>
-      <c r="D17" t="s">
-        <v>108</v>
-      </c>
-      <c r="E17" t="s">
-        <v>8</v>
-      </c>
-      <c r="F17" t="s">
+      <c r="B29" t="s">
+        <v>93</v>
+      </c>
+      <c r="C29" t="s">
+        <v>91</v>
+      </c>
+      <c r="D29" t="s">
+        <v>128</v>
+      </c>
+      <c r="E29" t="s">
+        <v>8</v>
+      </c>
+      <c r="F29" t="s">
         <v>66</v>
       </c>
-      <c r="G17">
+      <c r="G29">
         <v>5</v>
       </c>
     </row>

--- a/grupos/1CV - Estadisticos 20231.xlsx
+++ b/grupos/1CV - Estadisticos 20231.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="317" uniqueCount="129">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="287" uniqueCount="120">
   <si>
     <t>Materia</t>
   </si>
@@ -215,27 +215,27 @@
     <t>Recursos socioemocionales I</t>
   </si>
   <si>
+    <t>Villanueva Morales Luis Arturo</t>
+  </si>
+  <si>
     <t>Rodríguez Román Leticia</t>
   </si>
   <si>
-    <t>Villanueva Morales Luis Arturo</t>
-  </si>
-  <si>
     <t>Gaspar Velazco Juan Francisco</t>
   </si>
   <si>
     <t>Contreras Díaz Irma Ivette</t>
   </si>
   <si>
+    <t>Vargas Olvera Francisco Eduardo</t>
+  </si>
+  <si>
+    <t>Pesce Bautista Victor Manuel</t>
+  </si>
+  <si>
     <t>Martínez López Miguel Ángel</t>
   </si>
   <si>
-    <t>Vargas Olvera Francisco Eduardo</t>
-  </si>
-  <si>
-    <t>Pesce Bautista Victor Manuel</t>
-  </si>
-  <si>
     <t>NC</t>
   </si>
   <si>
@@ -257,99 +257,84 @@
     <t>GONZALEZ</t>
   </si>
   <si>
+    <t>IXMATLAHUA</t>
+  </si>
+  <si>
+    <t>LOPEZ</t>
+  </si>
+  <si>
+    <t>SAN JUAN</t>
+  </si>
+  <si>
+    <t>ALMANZA</t>
+  </si>
+  <si>
+    <t>DORANTES</t>
+  </si>
+  <si>
     <t>GUERRA</t>
   </si>
   <si>
     <t>HERNANDEZ</t>
   </si>
   <si>
-    <t>IXMATLAHUA</t>
+    <t>LAGUNA</t>
   </si>
   <si>
     <t>LOBATO</t>
   </si>
   <si>
-    <t>SAN JUAN</t>
-  </si>
-  <si>
-    <t>ALMANZA</t>
-  </si>
-  <si>
-    <t>CRUZ</t>
-  </si>
-  <si>
-    <t>CUAPIO</t>
-  </si>
-  <si>
-    <t>DORANTES</t>
-  </si>
-  <si>
-    <t>LAGUNA</t>
-  </si>
-  <si>
     <t>LUIS</t>
   </si>
   <si>
-    <t>MARQUEZ</t>
+    <t>RAMIREZ</t>
+  </si>
+  <si>
+    <t>SANCHEZ</t>
+  </si>
+  <si>
+    <t>MACUIXTLE</t>
+  </si>
+  <si>
+    <t>ROSALES</t>
+  </si>
+  <si>
+    <t>TZITZIHUA</t>
+  </si>
+  <si>
+    <t>SANTIAGO</t>
+  </si>
+  <si>
+    <t>AGUILAR</t>
+  </si>
+  <si>
+    <t>SANTOS</t>
+  </si>
+  <si>
+    <t>PORRAS</t>
+  </si>
+  <si>
+    <t>ARIAS</t>
+  </si>
+  <si>
+    <t>SARMIENTO</t>
+  </si>
+  <si>
+    <t>NATH</t>
+  </si>
+  <si>
+    <t>ANTONIO</t>
+  </si>
+  <si>
+    <t>VERA</t>
+  </si>
+  <si>
+    <t>MOLINA</t>
   </si>
   <si>
     <t>MENDEZ</t>
   </si>
   <si>
-    <t>RAMIREZ</t>
-  </si>
-  <si>
-    <t>SANCHEZ</t>
-  </si>
-  <si>
-    <t>MACUIXTLE</t>
-  </si>
-  <si>
-    <t>ROSALES</t>
-  </si>
-  <si>
-    <t>TZITZIHUA</t>
-  </si>
-  <si>
-    <t>ARIAS</t>
-  </si>
-  <si>
-    <t>SARMIENTO</t>
-  </si>
-  <si>
-    <t>ANTONIO</t>
-  </si>
-  <si>
-    <t>AGUILAR</t>
-  </si>
-  <si>
-    <t>SANTOS</t>
-  </si>
-  <si>
-    <t>CASTILLO</t>
-  </si>
-  <si>
-    <t>HUERTA</t>
-  </si>
-  <si>
-    <t>PORRAS</t>
-  </si>
-  <si>
-    <t>SANTIAGO</t>
-  </si>
-  <si>
-    <t>NATH</t>
-  </si>
-  <si>
-    <t>VERA</t>
-  </si>
-  <si>
-    <t>MONDRAGON</t>
-  </si>
-  <si>
-    <t>MOLINA</t>
-  </si>
-  <si>
     <t>MARIA FERNANDA</t>
   </si>
   <si>
@@ -359,46 +344,34 @@
     <t>MIRIAM</t>
   </si>
   <si>
+    <t>FERNANDA YAMILET</t>
+  </si>
+  <si>
+    <t>RAYMUNDO</t>
+  </si>
+  <si>
+    <t>KARINA MONSERRATH</t>
+  </si>
+  <si>
+    <t>VANESA BETHSABE</t>
+  </si>
+  <si>
+    <t>ROBERTO</t>
+  </si>
+  <si>
+    <t>MARIANA</t>
+  </si>
+  <si>
     <t>ALEX TADEO</t>
   </si>
   <si>
     <t>EDUARDO</t>
   </si>
   <si>
-    <t>FERNANDA YAMILET</t>
+    <t>AARON ZACHARY</t>
   </si>
   <si>
     <t>DIANA LAURA</t>
-  </si>
-  <si>
-    <t>KARINA MONSERRATH</t>
-  </si>
-  <si>
-    <t>VANESA BETHSABE</t>
-  </si>
-  <si>
-    <t>RAMSES</t>
-  </si>
-  <si>
-    <t>JESSICA</t>
-  </si>
-  <si>
-    <t>ROBERTO</t>
-  </si>
-  <si>
-    <t>JAIRO</t>
-  </si>
-  <si>
-    <t>MARIANA</t>
-  </si>
-  <si>
-    <t>AARON ZACHARY</t>
-  </si>
-  <si>
-    <t>DIEGO GREGORIO</t>
-  </si>
-  <si>
-    <t>ANGEL ADRIAN</t>
   </si>
   <si>
     <t>AIDE SCARLET</t>
@@ -952,7 +925,7 @@
         <v>5</v>
       </c>
       <c r="P4">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q4">
         <v>5</v>
@@ -970,7 +943,7 @@
         <v>6</v>
       </c>
       <c r="V4">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W4">
         <v>5</v>
@@ -1059,7 +1032,7 @@
         <v>8</v>
       </c>
       <c r="V5">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="W5">
         <v>7</v>
@@ -1148,7 +1121,7 @@
         <v>5</v>
       </c>
       <c r="V6">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W6">
         <v>5</v>
@@ -1237,7 +1210,7 @@
         <v>6</v>
       </c>
       <c r="V7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W7">
         <v>6</v>
@@ -1326,7 +1299,7 @@
         <v>6</v>
       </c>
       <c r="V8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W8">
         <v>7</v>
@@ -1347,7 +1320,7 @@
         <v>7</v>
       </c>
       <c r="AC8">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="9" spans="1:29">
@@ -1415,7 +1388,7 @@
         <v>8</v>
       </c>
       <c r="V9">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="W9">
         <v>7</v>
@@ -1504,7 +1477,7 @@
         <v>8</v>
       </c>
       <c r="V10">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W10">
         <v>7</v>
@@ -1525,7 +1498,7 @@
         <v>8</v>
       </c>
       <c r="AC10">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="11" spans="1:29">
@@ -1593,7 +1566,7 @@
         <v>5</v>
       </c>
       <c r="V11">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="W11">
         <v>7</v>
@@ -1682,7 +1655,7 @@
         <v>6</v>
       </c>
       <c r="V12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="W12">
         <v>8</v>
@@ -1771,7 +1744,7 @@
         <v>6</v>
       </c>
       <c r="V13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="W13">
         <v>6</v>
@@ -1860,7 +1833,7 @@
         <v>7</v>
       </c>
       <c r="V14">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W14">
         <v>6</v>
@@ -1949,7 +1922,7 @@
         <v>9</v>
       </c>
       <c r="V15">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W15">
         <v>8</v>
@@ -1970,7 +1943,7 @@
         <v>8</v>
       </c>
       <c r="AC15">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="16" spans="1:29">
@@ -2038,7 +2011,7 @@
         <v>5</v>
       </c>
       <c r="V16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W16">
         <v>7</v>
@@ -2127,7 +2100,7 @@
         <v>9</v>
       </c>
       <c r="V17">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W17">
         <v>8</v>
@@ -2216,7 +2189,7 @@
         <v>6</v>
       </c>
       <c r="V18">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W18">
         <v>6</v>
@@ -2305,7 +2278,7 @@
         <v>8</v>
       </c>
       <c r="V19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W19">
         <v>6</v>
@@ -2326,7 +2299,7 @@
         <v>7</v>
       </c>
       <c r="AC19">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="20" spans="1:29">
@@ -2394,7 +2367,7 @@
         <v>5</v>
       </c>
       <c r="V20">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W20">
         <v>5</v>
@@ -2483,7 +2456,7 @@
         <v>6</v>
       </c>
       <c r="V21">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W21">
         <v>6</v>
@@ -2504,7 +2477,7 @@
         <v>6</v>
       </c>
       <c r="AC21">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="22" spans="1:29">
@@ -2554,7 +2527,7 @@
         <v>5</v>
       </c>
       <c r="P22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q22">
         <v>7</v>
@@ -2572,10 +2545,10 @@
         <v>5</v>
       </c>
       <c r="V22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W22">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X22">
         <v>6</v>
@@ -2661,7 +2634,7 @@
         <v>6</v>
       </c>
       <c r="V23">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W23">
         <v>6</v>
@@ -2750,7 +2723,7 @@
         <v>8</v>
       </c>
       <c r="V24">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W24">
         <v>8</v>
@@ -2839,7 +2812,7 @@
         <v>6</v>
       </c>
       <c r="V25">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W25">
         <v>8</v>
@@ -2928,7 +2901,7 @@
         <v>7</v>
       </c>
       <c r="V26">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W26">
         <v>6</v>
@@ -2949,7 +2922,7 @@
         <v>6</v>
       </c>
       <c r="AC26">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="27" spans="1:29">
@@ -3017,7 +2990,7 @@
         <v>6</v>
       </c>
       <c r="V27">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W27">
         <v>6</v>
@@ -3088,7 +3061,7 @@
         <v>6</v>
       </c>
       <c r="P28">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q28">
         <v>8</v>
@@ -3106,10 +3079,10 @@
         <v>7</v>
       </c>
       <c r="V28">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="W28">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="X28">
         <v>7</v>
@@ -3195,7 +3168,7 @@
         <v>6</v>
       </c>
       <c r="V29">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="W29">
         <v>7</v>
@@ -3284,7 +3257,7 @@
         <v>8</v>
       </c>
       <c r="V30">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W30">
         <v>7</v>
@@ -3305,7 +3278,7 @@
         <v>6</v>
       </c>
       <c r="AC30">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="31" spans="1:29">
@@ -3373,7 +3346,7 @@
         <v>7</v>
       </c>
       <c r="V31">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W31">
         <v>7</v>
@@ -3394,7 +3367,7 @@
         <v>7</v>
       </c>
       <c r="AC31">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="32" spans="1:29">
@@ -3462,7 +3435,7 @@
         <v>5</v>
       </c>
       <c r="V32">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W32">
         <v>5</v>
@@ -3551,7 +3524,7 @@
         <v>8</v>
       </c>
       <c r="V33">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W33">
         <v>7</v>
@@ -3640,7 +3613,7 @@
         <v>5</v>
       </c>
       <c r="V34">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W34">
         <v>6</v>
@@ -3729,7 +3702,7 @@
         <v>9</v>
       </c>
       <c r="V35">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="W35">
         <v>10</v>
@@ -3818,7 +3791,7 @@
         <v>5</v>
       </c>
       <c r="V36">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W36">
         <v>5</v>
@@ -3907,7 +3880,7 @@
         <v>7</v>
       </c>
       <c r="V37">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W37">
         <v>7</v>
@@ -3978,7 +3951,7 @@
         <v>5</v>
       </c>
       <c r="P38">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q38">
         <v>8</v>
@@ -3996,10 +3969,10 @@
         <v>5</v>
       </c>
       <c r="V38">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W38">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X38">
         <v>6</v>
@@ -4085,7 +4058,7 @@
         <v>7</v>
       </c>
       <c r="V39">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="W39">
         <v>7</v>
@@ -4174,7 +4147,7 @@
         <v>7</v>
       </c>
       <c r="V40">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W40">
         <v>7</v>
@@ -4263,7 +4236,7 @@
         <v>9</v>
       </c>
       <c r="V41">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W41">
         <v>9</v>
@@ -4352,7 +4325,7 @@
         <v>5</v>
       </c>
       <c r="V42">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W42">
         <v>5</v>
@@ -4563,7 +4536,7 @@
         <v>100</v>
       </c>
       <c r="V4">
-        <v>79.5</v>
+        <v>55.6</v>
       </c>
     </row>
     <row r="5" spans="1:22">
@@ -4631,7 +4604,7 @@
         <v>100</v>
       </c>
       <c r="V5">
-        <v>87.2</v>
+        <v>90.5</v>
       </c>
     </row>
     <row r="6" spans="1:22">
@@ -4699,7 +4672,7 @@
         <v>88.90000000000001</v>
       </c>
       <c r="V6">
-        <v>84.59999999999999</v>
+        <v>88.90000000000001</v>
       </c>
     </row>
     <row r="7" spans="1:22">
@@ -4767,7 +4740,7 @@
         <v>100</v>
       </c>
       <c r="V7">
-        <v>89.7</v>
+        <v>90.5</v>
       </c>
     </row>
     <row r="8" spans="1:22">
@@ -4835,7 +4808,7 @@
         <v>100</v>
       </c>
       <c r="V8">
-        <v>94.90000000000001</v>
+        <v>96.8</v>
       </c>
     </row>
     <row r="9" spans="1:22">
@@ -4903,7 +4876,7 @@
         <v>100</v>
       </c>
       <c r="V9">
-        <v>87.2</v>
+        <v>92.09999999999999</v>
       </c>
     </row>
     <row r="10" spans="1:22">
@@ -4971,7 +4944,7 @@
         <v>100</v>
       </c>
       <c r="V10">
-        <v>97.40000000000001</v>
+        <v>98.40000000000001</v>
       </c>
     </row>
     <row r="11" spans="1:22">
@@ -5039,7 +5012,7 @@
         <v>100</v>
       </c>
       <c r="V11">
-        <v>97.40000000000001</v>
+        <v>92.09999999999999</v>
       </c>
     </row>
     <row r="12" spans="1:22">
@@ -5107,7 +5080,7 @@
         <v>100</v>
       </c>
       <c r="V12">
-        <v>92.3</v>
+        <v>92.09999999999999</v>
       </c>
     </row>
     <row r="13" spans="1:22">
@@ -5175,7 +5148,7 @@
         <v>100</v>
       </c>
       <c r="V13">
-        <v>94.90000000000001</v>
+        <v>90.5</v>
       </c>
     </row>
     <row r="14" spans="1:22">
@@ -5243,7 +5216,7 @@
         <v>100</v>
       </c>
       <c r="V14">
-        <v>92.3</v>
+        <v>88.90000000000001</v>
       </c>
     </row>
     <row r="15" spans="1:22">
@@ -5311,7 +5284,7 @@
         <v>100</v>
       </c>
       <c r="V15">
-        <v>87.2</v>
+        <v>88.90000000000001</v>
       </c>
     </row>
     <row r="16" spans="1:22">
@@ -5379,7 +5352,7 @@
         <v>77.8</v>
       </c>
       <c r="V16">
-        <v>76.90000000000001</v>
+        <v>79.40000000000001</v>
       </c>
     </row>
     <row r="17" spans="1:22">
@@ -5447,7 +5420,7 @@
         <v>100</v>
       </c>
       <c r="V17">
-        <v>92.3</v>
+        <v>95.2</v>
       </c>
     </row>
     <row r="18" spans="1:22">
@@ -5515,7 +5488,7 @@
         <v>100</v>
       </c>
       <c r="V18">
-        <v>94.90000000000001</v>
+        <v>93.7</v>
       </c>
     </row>
     <row r="19" spans="1:22">
@@ -5583,7 +5556,7 @@
         <v>100</v>
       </c>
       <c r="V19">
-        <v>76.90000000000001</v>
+        <v>85.7</v>
       </c>
     </row>
     <row r="20" spans="1:22">
@@ -5651,7 +5624,7 @@
         <v>100</v>
       </c>
       <c r="V20">
-        <v>41</v>
+        <v>25.4</v>
       </c>
     </row>
     <row r="21" spans="1:22">
@@ -5719,7 +5692,7 @@
         <v>100</v>
       </c>
       <c r="V21">
-        <v>94.90000000000001</v>
+        <v>96.8</v>
       </c>
     </row>
     <row r="22" spans="1:22">
@@ -5769,7 +5742,7 @@
         <v>87.2</v>
       </c>
       <c r="P22">
-        <v>56.3</v>
+        <v>93.8</v>
       </c>
       <c r="Q22">
         <v>100</v>
@@ -5787,7 +5760,7 @@
         <v>100</v>
       </c>
       <c r="V22">
-        <v>87.2</v>
+        <v>90.5</v>
       </c>
     </row>
     <row r="23" spans="1:22">
@@ -5855,7 +5828,7 @@
         <v>100</v>
       </c>
       <c r="V23">
-        <v>89.7</v>
+        <v>90.5</v>
       </c>
     </row>
     <row r="24" spans="1:22">
@@ -5923,7 +5896,7 @@
         <v>100</v>
       </c>
       <c r="V24">
-        <v>94.90000000000001</v>
+        <v>96.8</v>
       </c>
     </row>
     <row r="25" spans="1:22">
@@ -5991,7 +5964,7 @@
         <v>100</v>
       </c>
       <c r="V25">
-        <v>97.40000000000001</v>
+        <v>98.40000000000001</v>
       </c>
     </row>
     <row r="26" spans="1:22">
@@ -6059,7 +6032,7 @@
         <v>100</v>
       </c>
       <c r="V26">
-        <v>84.59999999999999</v>
+        <v>84.09999999999999</v>
       </c>
     </row>
     <row r="27" spans="1:22">
@@ -6127,7 +6100,7 @@
         <v>100</v>
       </c>
       <c r="V27">
-        <v>100</v>
+        <v>96.8</v>
       </c>
     </row>
     <row r="28" spans="1:22">
@@ -6177,7 +6150,7 @@
         <v>100</v>
       </c>
       <c r="P28">
-        <v>62.5</v>
+        <v>100</v>
       </c>
       <c r="Q28">
         <v>100</v>
@@ -6195,7 +6168,7 @@
         <v>100</v>
       </c>
       <c r="V28">
-        <v>100</v>
+        <v>98.40000000000001</v>
       </c>
     </row>
     <row r="29" spans="1:22">
@@ -6263,7 +6236,7 @@
         <v>100</v>
       </c>
       <c r="V29">
-        <v>92.3</v>
+        <v>92.09999999999999</v>
       </c>
     </row>
     <row r="30" spans="1:22">
@@ -6331,7 +6304,7 @@
         <v>100</v>
       </c>
       <c r="V30">
-        <v>84.59999999999999</v>
+        <v>87.3</v>
       </c>
     </row>
     <row r="31" spans="1:22">
@@ -6399,7 +6372,7 @@
         <v>100</v>
       </c>
       <c r="V31">
-        <v>92.3</v>
+        <v>95.2</v>
       </c>
     </row>
     <row r="32" spans="1:22">
@@ -6535,7 +6508,7 @@
         <v>100</v>
       </c>
       <c r="V33">
-        <v>97.40000000000001</v>
+        <v>98.40000000000001</v>
       </c>
     </row>
     <row r="34" spans="1:22">
@@ -6603,7 +6576,7 @@
         <v>100</v>
       </c>
       <c r="V34">
-        <v>25.6</v>
+        <v>41.3</v>
       </c>
     </row>
     <row r="35" spans="1:22">
@@ -6671,7 +6644,7 @@
         <v>100</v>
       </c>
       <c r="V35">
-        <v>97.40000000000001</v>
+        <v>95.2</v>
       </c>
     </row>
     <row r="36" spans="1:22">
@@ -6739,7 +6712,7 @@
         <v>100</v>
       </c>
       <c r="V36">
-        <v>74.40000000000001</v>
+        <v>73</v>
       </c>
     </row>
     <row r="37" spans="1:22">
@@ -6807,7 +6780,7 @@
         <v>100</v>
       </c>
       <c r="V37">
-        <v>92.3</v>
+        <v>92.09999999999999</v>
       </c>
     </row>
     <row r="38" spans="1:22">
@@ -6857,7 +6830,7 @@
         <v>89.7</v>
       </c>
       <c r="P38">
-        <v>56.3</v>
+        <v>93.8</v>
       </c>
       <c r="Q38">
         <v>100</v>
@@ -6875,7 +6848,7 @@
         <v>100</v>
       </c>
       <c r="V38">
-        <v>89.7</v>
+        <v>90.5</v>
       </c>
     </row>
     <row r="39" spans="1:22">
@@ -6943,7 +6916,7 @@
         <v>100</v>
       </c>
       <c r="V39">
-        <v>100</v>
+        <v>96.8</v>
       </c>
     </row>
     <row r="40" spans="1:22">
@@ -7011,7 +6984,7 @@
         <v>100</v>
       </c>
       <c r="V40">
-        <v>94.90000000000001</v>
+        <v>96.8</v>
       </c>
     </row>
     <row r="41" spans="1:22">
@@ -7147,7 +7120,7 @@
         <v>100</v>
       </c>
       <c r="V42">
-        <v>74.40000000000001</v>
+        <v>46</v>
       </c>
     </row>
   </sheetData>
@@ -7204,7 +7177,7 @@
     </row>
     <row r="2" spans="1:10">
       <c r="A2" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="B2" t="s">
         <v>65</v>
@@ -7213,19 +7186,19 @@
         <v>39</v>
       </c>
       <c r="D2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E2">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F2" s="2">
-        <v>33.3</v>
+        <v>35.9</v>
       </c>
       <c r="G2" s="2">
-        <v>66.7</v>
+        <v>64.09999999999999</v>
       </c>
       <c r="H2">
-        <v>5.4</v>
+        <v>5.7</v>
       </c>
       <c r="I2">
         <v>0</v>
@@ -7236,7 +7209,7 @@
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="B3" t="s">
         <v>66</v>
@@ -7245,19 +7218,19 @@
         <v>39</v>
       </c>
       <c r="D3">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="E3">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="F3" s="2">
-        <v>35.9</v>
+        <v>53.8</v>
       </c>
       <c r="G3" s="2">
-        <v>64.09999999999999</v>
+        <v>46.2</v>
       </c>
       <c r="H3">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -7332,7 +7305,7 @@
     </row>
     <row r="6" spans="1:10">
       <c r="A6" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="B6" t="s">
         <v>69</v>
@@ -7341,19 +7314,19 @@
         <v>39</v>
       </c>
       <c r="D6">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E6">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F6" s="2">
-        <v>79.5</v>
+        <v>82.09999999999999</v>
       </c>
       <c r="G6" s="2">
-        <v>20.5</v>
+        <v>17.9</v>
       </c>
       <c r="H6">
-        <v>6.6</v>
+        <v>6.9</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -7364,7 +7337,7 @@
     </row>
     <row r="7" spans="1:10">
       <c r="A7" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="B7" t="s">
         <v>70</v>
@@ -7373,19 +7346,19 @@
         <v>39</v>
       </c>
       <c r="D7">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E7">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F7" s="2">
-        <v>82.09999999999999</v>
+        <v>84.59999999999999</v>
       </c>
       <c r="G7" s="2">
-        <v>17.9</v>
+        <v>15.4</v>
       </c>
       <c r="H7">
-        <v>6.9</v>
+        <v>6.7</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -7396,7 +7369,7 @@
     </row>
     <row r="8" spans="1:10">
       <c r="A8" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B8" t="s">
         <v>71</v>
@@ -7431,7 +7404,7 @@
         <v>64</v>
       </c>
       <c r="B9" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C9">
         <v>0</v>
@@ -7487,7 +7460,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G29"/>
+  <dimension ref="A1:G23"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -7525,16 +7498,16 @@
         <v>76</v>
       </c>
       <c r="C2" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="D2" t="s">
-        <v>110</v>
+        <v>105</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
       </c>
       <c r="F2" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="G2">
         <v>5</v>
@@ -7548,16 +7521,16 @@
         <v>76</v>
       </c>
       <c r="C3" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="D3" t="s">
-        <v>110</v>
+        <v>105</v>
       </c>
       <c r="E3" t="s">
         <v>11</v>
       </c>
       <c r="F3" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="G3">
         <v>5</v>
@@ -7571,10 +7544,10 @@
         <v>77</v>
       </c>
       <c r="C4" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="D4" t="s">
-        <v>111</v>
+        <v>106</v>
       </c>
       <c r="E4" t="s">
         <v>7</v>
@@ -7594,16 +7567,16 @@
         <v>77</v>
       </c>
       <c r="C5" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="D5" t="s">
-        <v>111</v>
+        <v>106</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
       </c>
       <c r="F5" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="G5">
         <v>5</v>
@@ -7617,16 +7590,16 @@
         <v>78</v>
       </c>
       <c r="C6" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="D6" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
       <c r="E6" t="s">
         <v>8</v>
       </c>
       <c r="F6" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="G6">
         <v>5</v>
@@ -7640,16 +7613,16 @@
         <v>78</v>
       </c>
       <c r="C7" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="D7" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
       <c r="E7" t="s">
         <v>11</v>
       </c>
       <c r="F7" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="G7">
         <v>5</v>
@@ -7657,22 +7630,22 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>23330051920234</v>
+        <v>23330051920271</v>
       </c>
       <c r="B8" t="s">
         <v>79</v>
       </c>
       <c r="C8" t="s">
-        <v>97</v>
+        <v>85</v>
       </c>
       <c r="D8" t="s">
-        <v>113</v>
+        <v>108</v>
       </c>
       <c r="E8" t="s">
         <v>8</v>
       </c>
       <c r="F8" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="G8">
         <v>5</v>
@@ -7680,22 +7653,22 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>23330051920234</v>
+        <v>23330051920271</v>
       </c>
       <c r="B9" t="s">
         <v>79</v>
       </c>
       <c r="C9" t="s">
-        <v>97</v>
+        <v>85</v>
       </c>
       <c r="D9" t="s">
-        <v>113</v>
+        <v>108</v>
       </c>
       <c r="E9" t="s">
         <v>11</v>
       </c>
       <c r="F9" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="G9">
         <v>5</v>
@@ -7703,22 +7676,22 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>23330051920236</v>
+        <v>23330051920247</v>
       </c>
       <c r="B10" t="s">
         <v>80</v>
       </c>
       <c r="C10" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="D10" t="s">
-        <v>114</v>
+        <v>109</v>
       </c>
       <c r="E10" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F10" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="G10">
         <v>5</v>
@@ -7726,19 +7699,19 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>23330051920236</v>
+        <v>23330051920247</v>
       </c>
       <c r="B11" t="s">
         <v>80</v>
       </c>
       <c r="C11" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="D11" t="s">
-        <v>114</v>
+        <v>109</v>
       </c>
       <c r="E11" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F11" t="s">
         <v>65</v>
@@ -7749,22 +7722,22 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>23330051920271</v>
+        <v>23330051920264</v>
       </c>
       <c r="B12" t="s">
         <v>81</v>
       </c>
       <c r="C12" t="s">
-        <v>80</v>
+        <v>95</v>
       </c>
       <c r="D12" t="s">
-        <v>115</v>
+        <v>110</v>
       </c>
       <c r="E12" t="s">
         <v>8</v>
       </c>
       <c r="F12" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="G12">
         <v>5</v>
@@ -7772,22 +7745,22 @@
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>23330051920271</v>
+        <v>23330051920264</v>
       </c>
       <c r="B13" t="s">
         <v>81</v>
       </c>
       <c r="C13" t="s">
-        <v>80</v>
+        <v>95</v>
       </c>
       <c r="D13" t="s">
-        <v>115</v>
+        <v>110</v>
       </c>
       <c r="E13" t="s">
         <v>11</v>
       </c>
       <c r="F13" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="G13">
         <v>5</v>
@@ -7795,22 +7768,22 @@
     </row>
     <row r="14" spans="1:7">
       <c r="A14">
-        <v>23330051920335</v>
+        <v>23330051920218</v>
       </c>
       <c r="B14" t="s">
         <v>82</v>
       </c>
       <c r="C14" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="D14" t="s">
-        <v>116</v>
+        <v>111</v>
       </c>
       <c r="E14" t="s">
         <v>8</v>
       </c>
       <c r="F14" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="G14">
         <v>5</v>
@@ -7818,19 +7791,19 @@
     </row>
     <row r="15" spans="1:7">
       <c r="A15">
-        <v>23330051920335</v>
+        <v>23330051920224</v>
       </c>
       <c r="B15" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C15" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="D15" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="E15" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F15" t="s">
         <v>65</v>
@@ -7841,19 +7814,19 @@
     </row>
     <row r="16" spans="1:7">
       <c r="A16">
-        <v>23330051920264</v>
+        <v>23330051920229</v>
       </c>
       <c r="B16" t="s">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="C16" t="s">
-        <v>100</v>
+        <v>94</v>
       </c>
       <c r="D16" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="E16" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F16" t="s">
         <v>66</v>
@@ -7864,19 +7837,19 @@
     </row>
     <row r="17" spans="1:7">
       <c r="A17">
-        <v>23330051920264</v>
+        <v>23330051920234</v>
       </c>
       <c r="B17" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C17" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="D17" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="E17" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F17" t="s">
         <v>65</v>
@@ -7887,22 +7860,22 @@
     </row>
     <row r="18" spans="1:7">
       <c r="A18">
-        <v>23330051920218</v>
+        <v>23330051920236</v>
       </c>
       <c r="B18" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C18" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="D18" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="E18" t="s">
         <v>8</v>
       </c>
       <c r="F18" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="G18">
         <v>5</v>
@@ -7910,19 +7883,19 @@
     </row>
     <row r="19" spans="1:7">
       <c r="A19">
-        <v>23330051920221</v>
+        <v>23330051920243</v>
       </c>
       <c r="B19" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C19" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="D19" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="E19" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F19" t="s">
         <v>65</v>
@@ -7933,19 +7906,19 @@
     </row>
     <row r="20" spans="1:7">
       <c r="A20">
-        <v>23330051920222</v>
+        <v>23330051920335</v>
       </c>
       <c r="B20" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C20" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="D20" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="E20" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F20" t="s">
         <v>65</v>
@@ -7956,22 +7929,22 @@
     </row>
     <row r="21" spans="1:7">
       <c r="A21">
-        <v>23330051920224</v>
+        <v>23330051920249</v>
       </c>
       <c r="B21" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C21" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="D21" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="E21" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F21" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="G21">
         <v>5</v>
@@ -7979,22 +7952,22 @@
     </row>
     <row r="22" spans="1:7">
       <c r="A22">
-        <v>23330051920230</v>
+        <v>23330051920258</v>
       </c>
       <c r="B22" t="s">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="C22" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="D22" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="E22" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="F22" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="G22">
         <v>5</v>
@@ -8002,162 +7975,24 @@
     </row>
     <row r="23" spans="1:7">
       <c r="A23">
-        <v>23330051920229</v>
+        <v>23330051920265</v>
       </c>
       <c r="B23" t="s">
-        <v>77</v>
+        <v>90</v>
       </c>
       <c r="C23" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="D23" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="E23" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F23" t="s">
         <v>65</v>
       </c>
       <c r="G23">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7">
-      <c r="A24">
-        <v>23330051920243</v>
-      </c>
-      <c r="B24" t="s">
-        <v>88</v>
-      </c>
-      <c r="C24" t="s">
-        <v>106</v>
-      </c>
-      <c r="D24" t="s">
-        <v>124</v>
-      </c>
-      <c r="E24" t="s">
-        <v>8</v>
-      </c>
-      <c r="F24" t="s">
-        <v>66</v>
-      </c>
-      <c r="G24">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="25" spans="1:7">
-      <c r="A25">
-        <v>23330051920249</v>
-      </c>
-      <c r="B25" t="s">
-        <v>89</v>
-      </c>
-      <c r="C25" t="s">
-        <v>107</v>
-      </c>
-      <c r="D25" t="s">
-        <v>116</v>
-      </c>
-      <c r="E25" t="s">
-        <v>7</v>
-      </c>
-      <c r="F25" t="s">
-        <v>67</v>
-      </c>
-      <c r="G25">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="26" spans="1:7">
-      <c r="A26">
-        <v>23330051920251</v>
-      </c>
-      <c r="B26" t="s">
-        <v>90</v>
-      </c>
-      <c r="C26" t="s">
-        <v>78</v>
-      </c>
-      <c r="D26" t="s">
-        <v>125</v>
-      </c>
-      <c r="E26" t="s">
-        <v>11</v>
-      </c>
-      <c r="F26" t="s">
-        <v>65</v>
-      </c>
-      <c r="G26">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="27" spans="1:7">
-      <c r="A27">
-        <v>23330051920253</v>
-      </c>
-      <c r="B27" t="s">
-        <v>91</v>
-      </c>
-      <c r="C27" t="s">
-        <v>108</v>
-      </c>
-      <c r="D27" t="s">
-        <v>126</v>
-      </c>
-      <c r="E27" t="s">
-        <v>11</v>
-      </c>
-      <c r="F27" t="s">
-        <v>65</v>
-      </c>
-      <c r="G27">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="28" spans="1:7">
-      <c r="A28">
-        <v>23330051920258</v>
-      </c>
-      <c r="B28" t="s">
-        <v>92</v>
-      </c>
-      <c r="C28" t="s">
-        <v>109</v>
-      </c>
-      <c r="D28" t="s">
-        <v>127</v>
-      </c>
-      <c r="E28" t="s">
-        <v>7</v>
-      </c>
-      <c r="F28" t="s">
-        <v>67</v>
-      </c>
-      <c r="G28">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="29" spans="1:7">
-      <c r="A29">
-        <v>23330051920265</v>
-      </c>
-      <c r="B29" t="s">
-        <v>93</v>
-      </c>
-      <c r="C29" t="s">
-        <v>91</v>
-      </c>
-      <c r="D29" t="s">
-        <v>128</v>
-      </c>
-      <c r="E29" t="s">
-        <v>8</v>
-      </c>
-      <c r="F29" t="s">
-        <v>66</v>
-      </c>
-      <c r="G29">
         <v>5</v>
       </c>
     </row>

--- a/grupos/1CV - Estadisticos 20231.xlsx
+++ b/grupos/1CV - Estadisticos 20231.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="287" uniqueCount="120">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="252" uniqueCount="108">
   <si>
     <t>Materia</t>
   </si>
@@ -215,18 +215,18 @@
     <t>Recursos socioemocionales I</t>
   </si>
   <si>
+    <t>Rodríguez Román Leticia</t>
+  </si>
+  <si>
+    <t>Gaspar Velazco Juan Francisco</t>
+  </si>
+  <si>
+    <t>Contreras Díaz Irma Ivette</t>
+  </si>
+  <si>
     <t>Villanueva Morales Luis Arturo</t>
   </si>
   <si>
-    <t>Rodríguez Román Leticia</t>
-  </si>
-  <si>
-    <t>Gaspar Velazco Juan Francisco</t>
-  </si>
-  <si>
-    <t>Contreras Díaz Irma Ivette</t>
-  </si>
-  <si>
     <t>Vargas Olvera Francisco Eduardo</t>
   </si>
   <si>
@@ -248,6 +248,15 @@
     <t>Nombres</t>
   </si>
   <si>
+    <t>JUAREZ</t>
+  </si>
+  <si>
+    <t>LOPEZ</t>
+  </si>
+  <si>
+    <t>TEXCAHUA</t>
+  </si>
+  <si>
     <t>BARRAGAN</t>
   </si>
   <si>
@@ -260,79 +269,52 @@
     <t>IXMATLAHUA</t>
   </si>
   <si>
-    <t>LOPEZ</t>
+    <t>LUIS</t>
+  </si>
+  <si>
+    <t>RAMIREZ</t>
   </si>
   <si>
     <t>SAN JUAN</t>
   </si>
   <si>
-    <t>ALMANZA</t>
-  </si>
-  <si>
-    <t>DORANTES</t>
-  </si>
-  <si>
-    <t>GUERRA</t>
+    <t>DE LA CRUZ</t>
+  </si>
+  <si>
+    <t>ESPINOZA</t>
+  </si>
+  <si>
+    <t>MACUIXTLE</t>
+  </si>
+  <si>
+    <t>ROSALES</t>
+  </si>
+  <si>
+    <t>SANTIAGO</t>
+  </si>
+  <si>
+    <t>TZITZIHUA</t>
   </si>
   <si>
     <t>HERNANDEZ</t>
   </si>
   <si>
-    <t>LAGUNA</t>
-  </si>
-  <si>
-    <t>LOBATO</t>
-  </si>
-  <si>
-    <t>LUIS</t>
-  </si>
-  <si>
-    <t>RAMIREZ</t>
-  </si>
-  <si>
-    <t>SANCHEZ</t>
-  </si>
-  <si>
-    <t>MACUIXTLE</t>
-  </si>
-  <si>
-    <t>ROSALES</t>
-  </si>
-  <si>
-    <t>TZITZIHUA</t>
-  </si>
-  <si>
-    <t>SANTIAGO</t>
+    <t>VERA</t>
+  </si>
+  <si>
+    <t>MOLINA</t>
   </si>
   <si>
     <t>AGUILAR</t>
   </si>
   <si>
-    <t>SANTOS</t>
-  </si>
-  <si>
-    <t>PORRAS</t>
-  </si>
-  <si>
-    <t>ARIAS</t>
-  </si>
-  <si>
-    <t>SARMIENTO</t>
-  </si>
-  <si>
-    <t>NATH</t>
-  </si>
-  <si>
-    <t>ANTONIO</t>
-  </si>
-  <si>
-    <t>VERA</t>
-  </si>
-  <si>
-    <t>MOLINA</t>
-  </si>
-  <si>
-    <t>MENDEZ</t>
+    <t>MARYSOL</t>
+  </si>
+  <si>
+    <t>ESTEFANIA</t>
+  </si>
+  <si>
+    <t>KARINA</t>
   </si>
   <si>
     <t>MARIA FERNANDA</t>
@@ -341,6 +323,9 @@
     <t>REGINA DAYTRI</t>
   </si>
   <si>
+    <t>MARIANA</t>
+  </si>
+  <si>
     <t>MIRIAM</t>
   </si>
   <si>
@@ -350,34 +335,13 @@
     <t>RAYMUNDO</t>
   </si>
   <si>
+    <t>DIANA LAURA</t>
+  </si>
+  <si>
+    <t>AIDE SCARLET</t>
+  </si>
+  <si>
     <t>KARINA MONSERRATH</t>
-  </si>
-  <si>
-    <t>VANESA BETHSABE</t>
-  </si>
-  <si>
-    <t>ROBERTO</t>
-  </si>
-  <si>
-    <t>MARIANA</t>
-  </si>
-  <si>
-    <t>ALEX TADEO</t>
-  </si>
-  <si>
-    <t>EDUARDO</t>
-  </si>
-  <si>
-    <t>AARON ZACHARY</t>
-  </si>
-  <si>
-    <t>DIANA LAURA</t>
-  </si>
-  <si>
-    <t>AIDE SCARLET</t>
-  </si>
-  <si>
-    <t>KAREN</t>
   </si>
 </sst>
 </file>
@@ -934,7 +898,7 @@
         <v>0</v>
       </c>
       <c r="S4">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T4">
         <v>5</v>
@@ -1023,7 +987,7 @@
         <v>9</v>
       </c>
       <c r="S5">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T5">
         <v>8</v>
@@ -1044,7 +1008,7 @@
         <v>7</v>
       </c>
       <c r="Z5">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA5">
         <v>8</v>
@@ -1103,7 +1067,7 @@
         <v>5</v>
       </c>
       <c r="P6">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q6">
         <v>8</v>
@@ -1112,7 +1076,7 @@
         <v>8</v>
       </c>
       <c r="S6">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T6">
         <v>5</v>
@@ -1124,7 +1088,7 @@
         <v>5</v>
       </c>
       <c r="W6">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X6">
         <v>8</v>
@@ -1201,7 +1165,7 @@
         <v>8</v>
       </c>
       <c r="S7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T7">
         <v>9</v>
@@ -1222,7 +1186,7 @@
         <v>7</v>
       </c>
       <c r="Z7">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA7">
         <v>8</v>
@@ -1290,7 +1254,7 @@
         <v>7</v>
       </c>
       <c r="S8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T8">
         <v>8</v>
@@ -1379,7 +1343,7 @@
         <v>9</v>
       </c>
       <c r="S9">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T9">
         <v>9</v>
@@ -1468,7 +1432,7 @@
         <v>8</v>
       </c>
       <c r="S10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T10">
         <v>8</v>
@@ -1489,7 +1453,7 @@
         <v>7</v>
       </c>
       <c r="Z10">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA10">
         <v>6</v>
@@ -1548,7 +1512,7 @@
         <v>6</v>
       </c>
       <c r="P11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q11">
         <v>5</v>
@@ -1557,7 +1521,7 @@
         <v>6</v>
       </c>
       <c r="S11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T11">
         <v>5</v>
@@ -1578,7 +1542,7 @@
         <v>7</v>
       </c>
       <c r="Z11">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA11">
         <v>6</v>
@@ -1646,7 +1610,7 @@
         <v>7</v>
       </c>
       <c r="S12">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T12">
         <v>6</v>
@@ -1667,7 +1631,7 @@
         <v>7</v>
       </c>
       <c r="Z12">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA12">
         <v>7</v>
@@ -1735,7 +1699,7 @@
         <v>4</v>
       </c>
       <c r="S13">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T13">
         <v>10</v>
@@ -1756,7 +1720,7 @@
         <v>5</v>
       </c>
       <c r="Z13">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA13">
         <v>8</v>
@@ -1824,7 +1788,7 @@
         <v>5</v>
       </c>
       <c r="S14">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T14">
         <v>8</v>
@@ -1913,7 +1877,7 @@
         <v>6</v>
       </c>
       <c r="S15">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T15">
         <v>7</v>
@@ -2002,7 +1966,7 @@
         <v>4</v>
       </c>
       <c r="S16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T16">
         <v>6</v>
@@ -2091,7 +2055,7 @@
         <v>10</v>
       </c>
       <c r="S17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T17">
         <v>9</v>
@@ -2180,7 +2144,7 @@
         <v>6</v>
       </c>
       <c r="S18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T18">
         <v>8</v>
@@ -2201,7 +2165,7 @@
         <v>6</v>
       </c>
       <c r="Z18">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA18">
         <v>6</v>
@@ -2269,7 +2233,7 @@
         <v>7</v>
       </c>
       <c r="S19">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T19">
         <v>7</v>
@@ -2290,7 +2254,7 @@
         <v>6</v>
       </c>
       <c r="Z19">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA19">
         <v>6</v>
@@ -2358,7 +2322,7 @@
         <v>0</v>
       </c>
       <c r="S20">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T20">
         <v>5</v>
@@ -2447,7 +2411,7 @@
         <v>7</v>
       </c>
       <c r="S21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T21">
         <v>8</v>
@@ -2468,7 +2432,7 @@
         <v>6</v>
       </c>
       <c r="Z21">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA21">
         <v>7</v>
@@ -2536,7 +2500,7 @@
         <v>4</v>
       </c>
       <c r="S22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T22">
         <v>5</v>
@@ -2557,7 +2521,7 @@
         <v>5</v>
       </c>
       <c r="Z22">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA22">
         <v>5</v>
@@ -2616,7 +2580,7 @@
         <v>5</v>
       </c>
       <c r="P23">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q23">
         <v>8</v>
@@ -2625,7 +2589,7 @@
         <v>7</v>
       </c>
       <c r="S23">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T23">
         <v>8</v>
@@ -2646,7 +2610,7 @@
         <v>6</v>
       </c>
       <c r="Z23">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA23">
         <v>7</v>
@@ -2714,7 +2678,7 @@
         <v>5</v>
       </c>
       <c r="S24">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T24">
         <v>8</v>
@@ -2735,7 +2699,7 @@
         <v>5</v>
       </c>
       <c r="Z24">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA24">
         <v>6</v>
@@ -2803,7 +2767,7 @@
         <v>6</v>
       </c>
       <c r="S25">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T25">
         <v>8</v>
@@ -2824,7 +2788,7 @@
         <v>7</v>
       </c>
       <c r="Z25">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA25">
         <v>8</v>
@@ -2892,7 +2856,7 @@
         <v>6</v>
       </c>
       <c r="S26">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T26">
         <v>8</v>
@@ -2913,7 +2877,7 @@
         <v>6</v>
       </c>
       <c r="Z26">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA26">
         <v>6</v>
@@ -2981,7 +2945,7 @@
         <v>4</v>
       </c>
       <c r="S27">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T27">
         <v>8</v>
@@ -3002,7 +2966,7 @@
         <v>5</v>
       </c>
       <c r="Z27">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA27">
         <v>7</v>
@@ -3070,7 +3034,7 @@
         <v>4</v>
       </c>
       <c r="S28">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T28">
         <v>9</v>
@@ -3091,7 +3055,7 @@
         <v>5</v>
       </c>
       <c r="Z28">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA28">
         <v>9</v>
@@ -3159,7 +3123,7 @@
         <v>5</v>
       </c>
       <c r="S29">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T29">
         <v>7</v>
@@ -3180,7 +3144,7 @@
         <v>5</v>
       </c>
       <c r="Z29">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA29">
         <v>7</v>
@@ -3248,7 +3212,7 @@
         <v>7</v>
       </c>
       <c r="S30">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T30">
         <v>10</v>
@@ -3269,7 +3233,7 @@
         <v>7</v>
       </c>
       <c r="Z30">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AA30">
         <v>9</v>
@@ -3337,7 +3301,7 @@
         <v>7</v>
       </c>
       <c r="S31">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T31">
         <v>9</v>
@@ -3426,7 +3390,7 @@
         <v>0</v>
       </c>
       <c r="S32">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T32">
         <v>5</v>
@@ -3515,7 +3479,7 @@
         <v>8</v>
       </c>
       <c r="S33">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T33">
         <v>10</v>
@@ -3604,7 +3568,7 @@
         <v>6</v>
       </c>
       <c r="S34">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T34">
         <v>6</v>
@@ -3693,7 +3657,7 @@
         <v>10</v>
       </c>
       <c r="S35">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T35">
         <v>8</v>
@@ -3714,7 +3678,7 @@
         <v>5</v>
       </c>
       <c r="Z35">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA35">
         <v>8</v>
@@ -3773,7 +3737,7 @@
         <v>5</v>
       </c>
       <c r="P36">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q36">
         <v>5</v>
@@ -3782,7 +3746,7 @@
         <v>5</v>
       </c>
       <c r="S36">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T36">
         <v>5</v>
@@ -3871,7 +3835,7 @@
         <v>7</v>
       </c>
       <c r="S37">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T37">
         <v>8</v>
@@ -3892,7 +3856,7 @@
         <v>6</v>
       </c>
       <c r="Z37">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA37">
         <v>6</v>
@@ -3960,7 +3924,7 @@
         <v>7</v>
       </c>
       <c r="S38">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T38">
         <v>5</v>
@@ -4049,7 +4013,7 @@
         <v>9</v>
       </c>
       <c r="S39">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T39">
         <v>8</v>
@@ -4070,7 +4034,7 @@
         <v>7</v>
       </c>
       <c r="Z39">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA39">
         <v>7</v>
@@ -4138,7 +4102,7 @@
         <v>4</v>
       </c>
       <c r="S40">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T40">
         <v>8</v>
@@ -4159,7 +4123,7 @@
         <v>5</v>
       </c>
       <c r="Z40">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA40">
         <v>6</v>
@@ -4227,7 +4191,7 @@
         <v>10</v>
       </c>
       <c r="S41">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T41">
         <v>8</v>
@@ -4248,7 +4212,7 @@
         <v>8</v>
       </c>
       <c r="Z41">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA41">
         <v>7</v>
@@ -4316,7 +4280,7 @@
         <v>0</v>
       </c>
       <c r="S42">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T42">
         <v>5</v>
@@ -4527,7 +4491,7 @@
         <v>65.59999999999999</v>
       </c>
       <c r="S4">
-        <v>93.8</v>
+        <v>62.5</v>
       </c>
       <c r="T4">
         <v>98.3</v>
@@ -4654,7 +4618,7 @@
         <v>84.59999999999999</v>
       </c>
       <c r="P6">
-        <v>56.3</v>
+        <v>93.8</v>
       </c>
       <c r="Q6">
         <v>100</v>
@@ -4663,7 +4627,7 @@
         <v>85.90000000000001</v>
       </c>
       <c r="S6">
-        <v>96.90000000000001</v>
+        <v>91.7</v>
       </c>
       <c r="T6">
         <v>95</v>
@@ -4994,7 +4958,7 @@
         <v>97.40000000000001</v>
       </c>
       <c r="P11">
-        <v>62.5</v>
+        <v>100</v>
       </c>
       <c r="Q11">
         <v>100</v>
@@ -5071,7 +5035,7 @@
         <v>93.8</v>
       </c>
       <c r="S12">
-        <v>96.90000000000001</v>
+        <v>93.8</v>
       </c>
       <c r="T12">
         <v>98.3</v>
@@ -5139,7 +5103,7 @@
         <v>85.90000000000001</v>
       </c>
       <c r="S13">
-        <v>96.90000000000001</v>
+        <v>89.59999999999999</v>
       </c>
       <c r="T13">
         <v>100</v>
@@ -5275,7 +5239,7 @@
         <v>96.90000000000001</v>
       </c>
       <c r="S15">
-        <v>93.8</v>
+        <v>91.7</v>
       </c>
       <c r="T15">
         <v>100</v>
@@ -5343,7 +5307,7 @@
         <v>84.40000000000001</v>
       </c>
       <c r="S16">
-        <v>93.8</v>
+        <v>89.59999999999999</v>
       </c>
       <c r="T16">
         <v>95</v>
@@ -5479,7 +5443,7 @@
         <v>96.90000000000001</v>
       </c>
       <c r="S18">
-        <v>96.90000000000001</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="T18">
         <v>100</v>
@@ -5547,7 +5511,7 @@
         <v>87.5</v>
       </c>
       <c r="S19">
-        <v>96.90000000000001</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="T19">
         <v>90</v>
@@ -5615,7 +5579,7 @@
         <v>23.4</v>
       </c>
       <c r="S20">
-        <v>50</v>
+        <v>33.3</v>
       </c>
       <c r="T20">
         <v>25</v>
@@ -5683,7 +5647,7 @@
         <v>89.09999999999999</v>
       </c>
       <c r="S21">
-        <v>100</v>
+        <v>93.8</v>
       </c>
       <c r="T21">
         <v>100</v>
@@ -5810,7 +5774,7 @@
         <v>89.7</v>
       </c>
       <c r="P23">
-        <v>62.5</v>
+        <v>100</v>
       </c>
       <c r="Q23">
         <v>100</v>
@@ -5819,7 +5783,7 @@
         <v>90.59999999999999</v>
       </c>
       <c r="S23">
-        <v>93.8</v>
+        <v>95.8</v>
       </c>
       <c r="T23">
         <v>98.3</v>
@@ -5887,7 +5851,7 @@
         <v>85.90000000000001</v>
       </c>
       <c r="S24">
-        <v>93.8</v>
+        <v>95.8</v>
       </c>
       <c r="T24">
         <v>98.3</v>
@@ -5955,7 +5919,7 @@
         <v>89.09999999999999</v>
       </c>
       <c r="S25">
-        <v>100</v>
+        <v>95.8</v>
       </c>
       <c r="T25">
         <v>98.3</v>
@@ -6023,7 +5987,7 @@
         <v>82.8</v>
       </c>
       <c r="S26">
-        <v>93.8</v>
+        <v>89.59999999999999</v>
       </c>
       <c r="T26">
         <v>100</v>
@@ -6159,7 +6123,7 @@
         <v>96.90000000000001</v>
       </c>
       <c r="S28">
-        <v>96.90000000000001</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="T28">
         <v>100</v>
@@ -6227,7 +6191,7 @@
         <v>90.59999999999999</v>
       </c>
       <c r="S29">
-        <v>93.8</v>
+        <v>95.8</v>
       </c>
       <c r="T29">
         <v>100</v>
@@ -6295,7 +6259,7 @@
         <v>90.59999999999999</v>
       </c>
       <c r="S30">
-        <v>96.90000000000001</v>
+        <v>93.8</v>
       </c>
       <c r="T30">
         <v>100</v>
@@ -6363,7 +6327,7 @@
         <v>87.5</v>
       </c>
       <c r="S31">
-        <v>96.90000000000001</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="T31">
         <v>100</v>
@@ -6431,7 +6395,7 @@
         <v>0</v>
       </c>
       <c r="S32">
-        <v>50</v>
+        <v>33.3</v>
       </c>
       <c r="T32">
         <v>0</v>
@@ -6567,7 +6531,7 @@
         <v>76.59999999999999</v>
       </c>
       <c r="S34">
-        <v>84.40000000000001</v>
+        <v>70.8</v>
       </c>
       <c r="T34">
         <v>98.3</v>
@@ -6635,7 +6599,7 @@
         <v>70.3</v>
       </c>
       <c r="S35">
-        <v>96.90000000000001</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="T35">
         <v>100</v>
@@ -6694,7 +6658,7 @@
         <v>74.40000000000001</v>
       </c>
       <c r="P36">
-        <v>43.8</v>
+        <v>81.3</v>
       </c>
       <c r="Q36">
         <v>84.40000000000001</v>
@@ -6703,7 +6667,7 @@
         <v>78.09999999999999</v>
       </c>
       <c r="S36">
-        <v>81.3</v>
+        <v>58.3</v>
       </c>
       <c r="T36">
         <v>91.7</v>
@@ -6771,7 +6735,7 @@
         <v>92.2</v>
       </c>
       <c r="S37">
-        <v>93.8</v>
+        <v>91.7</v>
       </c>
       <c r="T37">
         <v>98.3</v>
@@ -6839,7 +6803,7 @@
         <v>92.2</v>
       </c>
       <c r="S38">
-        <v>100</v>
+        <v>93.8</v>
       </c>
       <c r="T38">
         <v>98.3</v>
@@ -6907,7 +6871,7 @@
         <v>90.59999999999999</v>
       </c>
       <c r="S39">
-        <v>96.90000000000001</v>
+        <v>93.8</v>
       </c>
       <c r="T39">
         <v>100</v>
@@ -6975,7 +6939,7 @@
         <v>90.59999999999999</v>
       </c>
       <c r="S40">
-        <v>93.8</v>
+        <v>95.8</v>
       </c>
       <c r="T40">
         <v>100</v>
@@ -7111,7 +7075,7 @@
         <v>56.3</v>
       </c>
       <c r="S42">
-        <v>84.40000000000001</v>
+        <v>56.3</v>
       </c>
       <c r="T42">
         <v>90</v>
@@ -7177,7 +7141,7 @@
     </row>
     <row r="2" spans="1:10">
       <c r="A2" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="B2" t="s">
         <v>65</v>
@@ -7186,19 +7150,19 @@
         <v>39</v>
       </c>
       <c r="D2">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="E2">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="F2" s="2">
-        <v>35.9</v>
+        <v>53.8</v>
       </c>
       <c r="G2" s="2">
-        <v>64.09999999999999</v>
+        <v>46.2</v>
       </c>
       <c r="H2">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="I2">
         <v>0</v>
@@ -7209,7 +7173,7 @@
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="B3" t="s">
         <v>66</v>
@@ -7218,19 +7182,19 @@
         <v>39</v>
       </c>
       <c r="D3">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="E3">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="F3" s="2">
-        <v>53.8</v>
+        <v>61.5</v>
       </c>
       <c r="G3" s="2">
-        <v>46.2</v>
+        <v>38.5</v>
       </c>
       <c r="H3">
-        <v>5.6</v>
+        <v>6.1</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -7241,7 +7205,7 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="B4" t="s">
         <v>67</v>
@@ -7250,19 +7214,19 @@
         <v>39</v>
       </c>
       <c r="D4">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="E4">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="F4" s="2">
-        <v>61.5</v>
+        <v>76.90000000000001</v>
       </c>
       <c r="G4" s="2">
-        <v>38.5</v>
+        <v>23.1</v>
       </c>
       <c r="H4">
-        <v>6.1</v>
+        <v>6.7</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -7273,7 +7237,7 @@
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B5" t="s">
         <v>68</v>
@@ -7282,19 +7246,19 @@
         <v>39</v>
       </c>
       <c r="D5">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E5">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F5" s="2">
-        <v>76.90000000000001</v>
+        <v>79.5</v>
       </c>
       <c r="G5" s="2">
-        <v>23.1</v>
+        <v>20.5</v>
       </c>
       <c r="H5">
-        <v>6.7</v>
+        <v>6.2</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -7378,16 +7342,16 @@
         <v>39</v>
       </c>
       <c r="D8">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E8">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F8" s="2">
-        <v>84.59999999999999</v>
+        <v>87.2</v>
       </c>
       <c r="G8" s="2">
-        <v>15.4</v>
+        <v>12.8</v>
       </c>
       <c r="H8">
         <v>6.7</v>
@@ -7460,7 +7424,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G23"/>
+  <dimension ref="A1:G16"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -7492,22 +7456,22 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>23330051920220</v>
+        <v>23330051920241</v>
       </c>
       <c r="B2" t="s">
         <v>76</v>
       </c>
       <c r="C2" t="s">
-        <v>91</v>
+        <v>86</v>
       </c>
       <c r="D2" t="s">
-        <v>105</v>
+        <v>96</v>
       </c>
       <c r="E2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F2" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="G2">
         <v>5</v>
@@ -7515,22 +7479,22 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>23330051920220</v>
+        <v>23330051920241</v>
       </c>
       <c r="B3" t="s">
         <v>76</v>
       </c>
       <c r="C3" t="s">
-        <v>91</v>
+        <v>86</v>
       </c>
       <c r="D3" t="s">
-        <v>105</v>
+        <v>96</v>
       </c>
       <c r="E3" t="s">
         <v>11</v>
       </c>
       <c r="F3" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="G3">
         <v>5</v>
@@ -7538,22 +7502,22 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>23330051920228</v>
+        <v>23330051920245</v>
       </c>
       <c r="B4" t="s">
         <v>77</v>
       </c>
       <c r="C4" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="D4" t="s">
-        <v>106</v>
+        <v>97</v>
       </c>
       <c r="E4" t="s">
         <v>7</v>
       </c>
       <c r="F4" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="G4">
         <v>5</v>
@@ -7561,19 +7525,19 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>23330051920228</v>
+        <v>23330051920245</v>
       </c>
       <c r="B5" t="s">
         <v>77</v>
       </c>
       <c r="C5" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="D5" t="s">
-        <v>106</v>
+        <v>97</v>
       </c>
       <c r="E5" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F5" t="s">
         <v>65</v>
@@ -7584,22 +7548,22 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>23330051920233</v>
+        <v>23330051920267</v>
       </c>
       <c r="B6" t="s">
         <v>78</v>
       </c>
       <c r="C6" t="s">
-        <v>93</v>
+        <v>86</v>
       </c>
       <c r="D6" t="s">
-        <v>107</v>
+        <v>98</v>
       </c>
       <c r="E6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F6" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="G6">
         <v>5</v>
@@ -7607,22 +7571,22 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>23330051920233</v>
+        <v>23330051920267</v>
       </c>
       <c r="B7" t="s">
         <v>78</v>
       </c>
       <c r="C7" t="s">
-        <v>93</v>
+        <v>86</v>
       </c>
       <c r="D7" t="s">
-        <v>107</v>
+        <v>98</v>
       </c>
       <c r="E7" t="s">
         <v>11</v>
       </c>
       <c r="F7" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="G7">
         <v>5</v>
@@ -7630,19 +7594,19 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>23330051920271</v>
+        <v>23330051920220</v>
       </c>
       <c r="B8" t="s">
         <v>79</v>
       </c>
       <c r="C8" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="D8" t="s">
-        <v>108</v>
+        <v>99</v>
       </c>
       <c r="E8" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F8" t="s">
         <v>65</v>
@@ -7653,19 +7617,19 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>23330051920271</v>
+        <v>23330051920228</v>
       </c>
       <c r="B9" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C9" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="D9" t="s">
-        <v>108</v>
+        <v>100</v>
       </c>
       <c r="E9" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="F9" t="s">
         <v>66</v>
@@ -7676,22 +7640,22 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>23330051920247</v>
+        <v>23330051920229</v>
       </c>
       <c r="B10" t="s">
         <v>80</v>
       </c>
       <c r="C10" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="D10" t="s">
-        <v>109</v>
+        <v>101</v>
       </c>
       <c r="E10" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="F10" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="G10">
         <v>5</v>
@@ -7699,19 +7663,19 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>23330051920247</v>
+        <v>23330051920233</v>
       </c>
       <c r="B11" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C11" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="D11" t="s">
-        <v>109</v>
+        <v>102</v>
       </c>
       <c r="E11" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F11" t="s">
         <v>65</v>
@@ -7722,19 +7686,19 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>23330051920264</v>
+        <v>23330051920271</v>
       </c>
       <c r="B12" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C12" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="D12" t="s">
-        <v>110</v>
+        <v>103</v>
       </c>
       <c r="E12" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F12" t="s">
         <v>65</v>
@@ -7745,19 +7709,19 @@
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>23330051920264</v>
+        <v>23330051920247</v>
       </c>
       <c r="B13" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="C13" t="s">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="D13" t="s">
-        <v>110</v>
+        <v>104</v>
       </c>
       <c r="E13" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="F13" t="s">
         <v>66</v>
@@ -7768,22 +7732,22 @@
     </row>
     <row r="14" spans="1:7">
       <c r="A14">
-        <v>23330051920218</v>
+        <v>23330051920249</v>
       </c>
       <c r="B14" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C14" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="D14" t="s">
-        <v>111</v>
+        <v>105</v>
       </c>
       <c r="E14" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F14" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="G14">
         <v>5</v>
@@ -7791,22 +7755,22 @@
     </row>
     <row r="15" spans="1:7">
       <c r="A15">
-        <v>23330051920224</v>
+        <v>23330051920258</v>
       </c>
       <c r="B15" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C15" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="D15" t="s">
-        <v>112</v>
+        <v>106</v>
       </c>
       <c r="E15" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F15" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="G15">
         <v>5</v>
@@ -7814,185 +7778,24 @@
     </row>
     <row r="16" spans="1:7">
       <c r="A16">
-        <v>23330051920229</v>
+        <v>23330051920264</v>
       </c>
       <c r="B16" t="s">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="C16" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D16" t="s">
-        <v>113</v>
+        <v>107</v>
       </c>
       <c r="E16" t="s">
         <v>11</v>
       </c>
       <c r="F16" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="G16">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7">
-      <c r="A17">
-        <v>23330051920234</v>
-      </c>
-      <c r="B17" t="s">
-        <v>84</v>
-      </c>
-      <c r="C17" t="s">
-        <v>98</v>
-      </c>
-      <c r="D17" t="s">
-        <v>114</v>
-      </c>
-      <c r="E17" t="s">
-        <v>8</v>
-      </c>
-      <c r="F17" t="s">
-        <v>65</v>
-      </c>
-      <c r="G17">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7">
-      <c r="A18">
-        <v>23330051920236</v>
-      </c>
-      <c r="B18" t="s">
-        <v>85</v>
-      </c>
-      <c r="C18" t="s">
-        <v>99</v>
-      </c>
-      <c r="D18" t="s">
-        <v>115</v>
-      </c>
-      <c r="E18" t="s">
-        <v>8</v>
-      </c>
-      <c r="F18" t="s">
-        <v>65</v>
-      </c>
-      <c r="G18">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7">
-      <c r="A19">
-        <v>23330051920243</v>
-      </c>
-      <c r="B19" t="s">
-        <v>86</v>
-      </c>
-      <c r="C19" t="s">
-        <v>100</v>
-      </c>
-      <c r="D19" t="s">
-        <v>116</v>
-      </c>
-      <c r="E19" t="s">
-        <v>8</v>
-      </c>
-      <c r="F19" t="s">
-        <v>65</v>
-      </c>
-      <c r="G19">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7">
-      <c r="A20">
-        <v>23330051920335</v>
-      </c>
-      <c r="B20" t="s">
-        <v>87</v>
-      </c>
-      <c r="C20" t="s">
-        <v>101</v>
-      </c>
-      <c r="D20" t="s">
-        <v>117</v>
-      </c>
-      <c r="E20" t="s">
-        <v>8</v>
-      </c>
-      <c r="F20" t="s">
-        <v>65</v>
-      </c>
-      <c r="G20">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7">
-      <c r="A21">
-        <v>23330051920249</v>
-      </c>
-      <c r="B21" t="s">
-        <v>88</v>
-      </c>
-      <c r="C21" t="s">
-        <v>102</v>
-      </c>
-      <c r="D21" t="s">
-        <v>117</v>
-      </c>
-      <c r="E21" t="s">
-        <v>7</v>
-      </c>
-      <c r="F21" t="s">
-        <v>67</v>
-      </c>
-      <c r="G21">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7">
-      <c r="A22">
-        <v>23330051920258</v>
-      </c>
-      <c r="B22" t="s">
-        <v>89</v>
-      </c>
-      <c r="C22" t="s">
-        <v>103</v>
-      </c>
-      <c r="D22" t="s">
-        <v>118</v>
-      </c>
-      <c r="E22" t="s">
-        <v>7</v>
-      </c>
-      <c r="F22" t="s">
-        <v>67</v>
-      </c>
-      <c r="G22">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7">
-      <c r="A23">
-        <v>23330051920265</v>
-      </c>
-      <c r="B23" t="s">
-        <v>90</v>
-      </c>
-      <c r="C23" t="s">
-        <v>104</v>
-      </c>
-      <c r="D23" t="s">
-        <v>119</v>
-      </c>
-      <c r="E23" t="s">
-        <v>8</v>
-      </c>
-      <c r="F23" t="s">
-        <v>65</v>
-      </c>
-      <c r="G23">
         <v>5</v>
       </c>
     </row>

--- a/grupos/1CV - Estadisticos 20231.xlsx
+++ b/grupos/1CV - Estadisticos 20231.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="252" uniqueCount="108">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="259" uniqueCount="108">
   <si>
     <t>Materia</t>
   </si>
@@ -56,6 +56,9 @@
     <t>Pensamiento matemático I</t>
   </si>
   <si>
+    <t>Recursos socioemocionales I</t>
+  </si>
+  <si>
     <t>Nombre</t>
   </si>
   <si>
@@ -210,9 +213,6 @@
   </si>
   <si>
     <t>Por_Blancos</t>
-  </si>
-  <si>
-    <t>Recursos socioemocionales I</t>
   </si>
   <si>
     <t>Rodríguez Román Leticia</t>
@@ -703,13 +703,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AC42"/>
+  <dimension ref="A1:AG42"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="50.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:29">
+    <row r="1" spans="1:33">
       <c r="A1" s="1"/>
       <c r="B1" s="1" t="s">
         <v>1</v>
@@ -720,35 +720,39 @@
       <c r="F1" s="1"/>
       <c r="G1" s="1"/>
       <c r="H1" s="1"/>
-      <c r="I1" s="1" t="s">
+      <c r="I1" s="1"/>
+      <c r="J1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="J1" s="1"/>
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
       <c r="N1" s="1"/>
       <c r="O1" s="1"/>
-      <c r="P1" s="1" t="s">
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="Q1" s="1"/>
-      <c r="R1" s="1"/>
       <c r="S1" s="1"/>
       <c r="T1" s="1"/>
       <c r="U1" s="1"/>
       <c r="V1" s="1"/>
-      <c r="W1" s="1" t="s">
-        <v>4</v>
-      </c>
+      <c r="W1" s="1"/>
       <c r="X1" s="1"/>
       <c r="Y1" s="1"/>
-      <c r="Z1" s="1"/>
+      <c r="Z1" s="1" t="s">
+        <v>4</v>
+      </c>
       <c r="AA1" s="1"/>
       <c r="AB1" s="1"/>
       <c r="AC1" s="1"/>
-    </row>
-    <row r="2" spans="1:29">
+      <c r="AD1" s="1"/>
+      <c r="AE1" s="1"/>
+      <c r="AF1" s="1"/>
+      <c r="AG1" s="1"/>
+    </row>
+    <row r="2" spans="1:33">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
@@ -774,77 +778,89 @@
         <v>11</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="L2" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="M2" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="N2" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="N2" s="1" t="s">
-        <v>10</v>
-      </c>
       <c r="O2" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="P2" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="P2" s="1" t="s">
-        <v>5</v>
-      </c>
       <c r="Q2" s="1" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="R2" s="1" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="S2" s="1" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="T2" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="U2" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="V2" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="U2" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="V2" s="1" t="s">
+      <c r="W2" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="X2" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="W2" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="X2" s="1" t="s">
-        <v>6</v>
-      </c>
       <c r="Y2" s="1" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="Z2" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="AA2" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="AB2" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="AC2" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="AD2" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="AB2" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="AC2" s="1" t="s">
+      <c r="AE2" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="AF2" s="1" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="3" spans="1:29">
+      <c r="AG2" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="3" spans="1:33">
       <c r="A3" s="1" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="4" spans="1:29">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="4" spans="1:33">
       <c r="A4" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B4">
         <v>6</v>
@@ -868,20 +884,20 @@
         <v>5</v>
       </c>
       <c r="I4">
+        <v>10</v>
+      </c>
+      <c r="J4">
         <v>3</v>
       </c>
-      <c r="J4">
-        <v>6</v>
-      </c>
       <c r="K4">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L4">
+        <v>5</v>
+      </c>
+      <c r="M4">
         <v>3</v>
       </c>
-      <c r="M4">
-        <v>5</v>
-      </c>
       <c r="N4">
         <v>5</v>
       </c>
@@ -892,37 +908,37 @@
         <v>5</v>
       </c>
       <c r="Q4">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="R4">
+        <v>5</v>
+      </c>
+      <c r="S4">
+        <v>5</v>
+      </c>
+      <c r="T4">
         <v>0</v>
       </c>
-      <c r="S4">
-        <v>5</v>
-      </c>
-      <c r="T4">
-        <v>5</v>
-      </c>
       <c r="U4">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="V4">
         <v>5</v>
       </c>
       <c r="W4">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X4">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Y4">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="Z4">
         <v>5</v>
       </c>
       <c r="AA4">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AB4">
         <v>5</v>
@@ -930,10 +946,22 @@
       <c r="AC4">
         <v>5</v>
       </c>
-    </row>
-    <row r="5" spans="1:29">
+      <c r="AD4">
+        <v>5</v>
+      </c>
+      <c r="AE4">
+        <v>5</v>
+      </c>
+      <c r="AF4">
+        <v>5</v>
+      </c>
+      <c r="AG4">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="5" spans="1:33">
       <c r="A5" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B5">
         <v>8</v>
@@ -957,72 +985,84 @@
         <v>6</v>
       </c>
       <c r="I5">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="J5">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K5">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="L5">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M5">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="N5">
         <v>8</v>
       </c>
       <c r="O5">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="P5">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="Q5">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="R5">
+        <v>8</v>
+      </c>
+      <c r="S5">
+        <v>8</v>
+      </c>
+      <c r="T5">
         <v>9</v>
       </c>
-      <c r="S5">
-        <v>8</v>
-      </c>
-      <c r="T5">
-        <v>8</v>
-      </c>
       <c r="U5">
         <v>8</v>
       </c>
       <c r="V5">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="W5">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X5">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Y5">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="Z5">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA5">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AB5">
+        <v>7</v>
+      </c>
+      <c r="AC5">
+        <v>6</v>
+      </c>
+      <c r="AD5">
+        <v>8</v>
+      </c>
+      <c r="AE5">
         <v>9</v>
       </c>
-      <c r="AC5">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="6" spans="1:29">
+      <c r="AF5">
+        <v>6</v>
+      </c>
+      <c r="AG5">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="6" spans="1:33">
       <c r="A6" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B6">
         <v>5</v>
@@ -1046,40 +1086,40 @@
         <v>5</v>
       </c>
       <c r="I6">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="J6">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="K6">
+        <v>8</v>
+      </c>
+      <c r="L6">
         <v>4</v>
       </c>
-      <c r="L6">
-        <v>5</v>
-      </c>
       <c r="M6">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="N6">
         <v>6</v>
       </c>
       <c r="O6">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="P6">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="Q6">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="R6">
         <v>8</v>
       </c>
       <c r="S6">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="T6">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="U6">
         <v>5</v>
@@ -1088,19 +1128,19 @@
         <v>5</v>
       </c>
       <c r="W6">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="X6">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="Y6">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="Z6">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA6">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="AB6">
         <v>6</v>
@@ -1108,10 +1148,22 @@
       <c r="AC6">
         <v>5</v>
       </c>
-    </row>
-    <row r="7" spans="1:29">
+      <c r="AD6">
+        <v>5</v>
+      </c>
+      <c r="AE6">
+        <v>6</v>
+      </c>
+      <c r="AF6">
+        <v>5</v>
+      </c>
+      <c r="AG6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="7" spans="1:33">
       <c r="A7" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B7">
         <v>6</v>
@@ -1135,13 +1187,13 @@
         <v>5</v>
       </c>
       <c r="I7">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="J7">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="K7">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="L7">
         <v>5</v>
@@ -1156,34 +1208,34 @@
         <v>5</v>
       </c>
       <c r="P7">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Q7">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="R7">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="S7">
         <v>8</v>
       </c>
       <c r="T7">
+        <v>8</v>
+      </c>
+      <c r="U7">
+        <v>8</v>
+      </c>
+      <c r="V7">
         <v>9</v>
       </c>
-      <c r="U7">
-        <v>6</v>
-      </c>
-      <c r="V7">
-        <v>5</v>
-      </c>
       <c r="W7">
         <v>6</v>
       </c>
       <c r="X7">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="Y7">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="Z7">
         <v>6</v>
@@ -1195,12 +1247,24 @@
         <v>7</v>
       </c>
       <c r="AC7">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="8" spans="1:29">
+        <v>6</v>
+      </c>
+      <c r="AD7">
+        <v>8</v>
+      </c>
+      <c r="AE7">
+        <v>7</v>
+      </c>
+      <c r="AF7">
+        <v>5</v>
+      </c>
+      <c r="AG7">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="8" spans="1:33">
       <c r="A8" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B8">
         <v>7</v>
@@ -1224,55 +1288,55 @@
         <v>5</v>
       </c>
       <c r="I8">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="J8">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="K8">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="L8">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="M8">
         <v>6</v>
       </c>
       <c r="N8">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="O8">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="P8">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="Q8">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="R8">
         <v>7</v>
       </c>
       <c r="S8">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="T8">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="U8">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="V8">
         <v>8</v>
       </c>
       <c r="W8">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="X8">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Y8">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="Z8">
         <v>7</v>
@@ -1284,12 +1348,24 @@
         <v>7</v>
       </c>
       <c r="AC8">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="9" spans="1:29">
+        <v>7</v>
+      </c>
+      <c r="AD8">
+        <v>7</v>
+      </c>
+      <c r="AE8">
+        <v>7</v>
+      </c>
+      <c r="AF8">
+        <v>6</v>
+      </c>
+      <c r="AG8">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="9" spans="1:33">
       <c r="A9" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B9">
         <v>6</v>
@@ -1313,72 +1389,84 @@
         <v>6</v>
       </c>
       <c r="I9">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="J9">
         <v>8</v>
       </c>
       <c r="K9">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="L9">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="M9">
+        <v>6</v>
+      </c>
+      <c r="N9">
         <v>9</v>
       </c>
-      <c r="N9">
-        <v>8</v>
-      </c>
       <c r="O9">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="P9">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="Q9">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="R9">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="S9">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T9">
         <v>9</v>
       </c>
       <c r="U9">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="V9">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="W9">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X9">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Y9">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="Z9">
         <v>7</v>
       </c>
       <c r="AA9">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AB9">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AC9">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="10" spans="1:29">
+        <v>7</v>
+      </c>
+      <c r="AD9">
+        <v>8</v>
+      </c>
+      <c r="AE9">
+        <v>8</v>
+      </c>
+      <c r="AF9">
+        <v>6</v>
+      </c>
+      <c r="AG9">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="10" spans="1:33">
       <c r="A10" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B10">
         <v>7</v>
@@ -1402,13 +1490,13 @@
         <v>6</v>
       </c>
       <c r="I10">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="J10">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="K10">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="L10">
         <v>6</v>
@@ -1417,19 +1505,19 @@
         <v>6</v>
       </c>
       <c r="N10">
+        <v>6</v>
+      </c>
+      <c r="O10">
         <v>9</v>
       </c>
-      <c r="O10">
-        <v>5</v>
-      </c>
       <c r="P10">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Q10">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="R10">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="S10">
         <v>8</v>
@@ -1441,33 +1529,45 @@
         <v>8</v>
       </c>
       <c r="V10">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="W10">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X10">
         <v>7</v>
       </c>
       <c r="Y10">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="Z10">
         <v>7</v>
       </c>
       <c r="AA10">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AB10">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AC10">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="11" spans="1:29">
+        <v>7</v>
+      </c>
+      <c r="AD10">
+        <v>6</v>
+      </c>
+      <c r="AE10">
+        <v>8</v>
+      </c>
+      <c r="AF10">
+        <v>6</v>
+      </c>
+      <c r="AG10">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="11" spans="1:33">
       <c r="A11" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B11">
         <v>7</v>
@@ -1491,7 +1591,7 @@
         <v>6</v>
       </c>
       <c r="I11">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="J11">
         <v>7</v>
@@ -1500,52 +1600,52 @@
         <v>7</v>
       </c>
       <c r="L11">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="M11">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="N11">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="O11">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="P11">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Q11">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="R11">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="S11">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T11">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U11">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="V11">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="W11">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="X11">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Y11">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="Z11">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA11">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AB11">
         <v>7</v>
@@ -1553,10 +1653,22 @@
       <c r="AC11">
         <v>6</v>
       </c>
-    </row>
-    <row r="12" spans="1:29">
+      <c r="AD11">
+        <v>6</v>
+      </c>
+      <c r="AE11">
+        <v>7</v>
+      </c>
+      <c r="AF11">
+        <v>6</v>
+      </c>
+      <c r="AG11">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="12" spans="1:33">
       <c r="A12" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B12">
         <v>7</v>
@@ -1580,72 +1692,84 @@
         <v>6</v>
       </c>
       <c r="I12">
+        <v>10</v>
+      </c>
+      <c r="J12">
         <v>9</v>
       </c>
-      <c r="J12">
-        <v>5</v>
-      </c>
       <c r="K12">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="L12">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="M12">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="N12">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="O12">
         <v>6</v>
       </c>
       <c r="P12">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Q12">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="R12">
         <v>7</v>
       </c>
       <c r="S12">
+        <v>7</v>
+      </c>
+      <c r="T12">
+        <v>7</v>
+      </c>
+      <c r="U12">
         <v>9</v>
       </c>
-      <c r="T12">
-        <v>6</v>
-      </c>
-      <c r="U12">
-        <v>6</v>
-      </c>
       <c r="V12">
         <v>6</v>
       </c>
       <c r="W12">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="X12">
         <v>6</v>
       </c>
       <c r="Y12">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="Z12">
         <v>8</v>
       </c>
       <c r="AA12">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AB12">
         <v>7</v>
       </c>
       <c r="AC12">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="13" spans="1:29">
+        <v>8</v>
+      </c>
+      <c r="AD12">
+        <v>7</v>
+      </c>
+      <c r="AE12">
+        <v>7</v>
+      </c>
+      <c r="AF12">
+        <v>6</v>
+      </c>
+      <c r="AG12">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="13" spans="1:33">
       <c r="A13" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B13">
         <v>5</v>
@@ -1669,19 +1793,19 @@
         <v>6</v>
       </c>
       <c r="I13">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="J13">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="K13">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="L13">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M13">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="N13">
         <v>6</v>
@@ -1690,51 +1814,63 @@
         <v>6</v>
       </c>
       <c r="P13">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="Q13">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="R13">
+        <v>8</v>
+      </c>
+      <c r="S13">
+        <v>7</v>
+      </c>
+      <c r="T13">
         <v>4</v>
       </c>
-      <c r="S13">
+      <c r="U13">
         <v>9</v>
       </c>
-      <c r="T13">
-        <v>10</v>
-      </c>
-      <c r="U13">
-        <v>6</v>
-      </c>
       <c r="V13">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="W13">
         <v>6</v>
       </c>
       <c r="X13">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Y13">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="Z13">
         <v>6</v>
       </c>
       <c r="AA13">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AB13">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AC13">
         <v>6</v>
       </c>
-    </row>
-    <row r="14" spans="1:29">
+      <c r="AD13">
+        <v>8</v>
+      </c>
+      <c r="AE13">
+        <v>7</v>
+      </c>
+      <c r="AF13">
+        <v>6</v>
+      </c>
+      <c r="AG13">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="14" spans="1:33">
       <c r="A14" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B14">
         <v>6</v>
@@ -1758,72 +1894,84 @@
         <v>5</v>
       </c>
       <c r="I14">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="J14">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="K14">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="L14">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="M14">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="N14">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="O14">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="P14">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Q14">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="R14">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="S14">
+        <v>8</v>
+      </c>
+      <c r="T14">
+        <v>5</v>
+      </c>
+      <c r="U14">
         <v>9</v>
       </c>
-      <c r="T14">
-        <v>8</v>
-      </c>
-      <c r="U14">
-        <v>7</v>
-      </c>
       <c r="V14">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="W14">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X14">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="Y14">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="Z14">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AA14">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AB14">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AC14">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="15" spans="1:29">
+        <v>7</v>
+      </c>
+      <c r="AD14">
+        <v>6</v>
+      </c>
+      <c r="AE14">
+        <v>7</v>
+      </c>
+      <c r="AF14">
+        <v>5</v>
+      </c>
+      <c r="AG14">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="15" spans="1:33">
       <c r="A15" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B15">
         <v>5</v>
@@ -1847,72 +1995,84 @@
         <v>5</v>
       </c>
       <c r="I15">
+        <v>10</v>
+      </c>
+      <c r="J15">
         <v>9</v>
       </c>
-      <c r="J15">
-        <v>7</v>
-      </c>
       <c r="K15">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="L15">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="M15">
+        <v>7</v>
+      </c>
+      <c r="N15">
         <v>9</v>
       </c>
-      <c r="N15">
-        <v>6</v>
-      </c>
       <c r="O15">
         <v>6</v>
       </c>
       <c r="P15">
+        <v>6</v>
+      </c>
+      <c r="Q15">
+        <v>10</v>
+      </c>
+      <c r="R15">
         <v>9</v>
       </c>
-      <c r="Q15">
-        <v>8</v>
-      </c>
-      <c r="R15">
-        <v>6</v>
-      </c>
       <c r="S15">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T15">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="U15">
+        <v>7</v>
+      </c>
+      <c r="V15">
+        <v>7</v>
+      </c>
+      <c r="W15">
         <v>9</v>
       </c>
-      <c r="V15">
-        <v>7</v>
-      </c>
-      <c r="W15">
-        <v>8</v>
-      </c>
       <c r="X15">
         <v>7</v>
       </c>
       <c r="Y15">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="Z15">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA15">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AB15">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AC15">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="16" spans="1:29">
+        <v>7</v>
+      </c>
+      <c r="AD15">
+        <v>8</v>
+      </c>
+      <c r="AE15">
+        <v>8</v>
+      </c>
+      <c r="AF15">
+        <v>6</v>
+      </c>
+      <c r="AG15">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="16" spans="1:33">
       <c r="A16" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B16">
         <v>6</v>
@@ -1936,10 +2096,10 @@
         <v>6</v>
       </c>
       <c r="I16">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="J16">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="K16">
         <v>5</v>
@@ -1951,57 +2111,69 @@
         <v>5</v>
       </c>
       <c r="N16">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="O16">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="P16">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="Q16">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="R16">
+        <v>7</v>
+      </c>
+      <c r="S16">
+        <v>5</v>
+      </c>
+      <c r="T16">
         <v>4</v>
       </c>
-      <c r="S16">
-        <v>6</v>
-      </c>
-      <c r="T16">
-        <v>6</v>
-      </c>
       <c r="U16">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="V16">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="W16">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="X16">
         <v>5</v>
       </c>
       <c r="Y16">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="Z16">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA16">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AB16">
         <v>5</v>
       </c>
       <c r="AC16">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="17" spans="1:29">
+        <v>6</v>
+      </c>
+      <c r="AD16">
+        <v>6</v>
+      </c>
+      <c r="AE16">
+        <v>5</v>
+      </c>
+      <c r="AF16">
+        <v>5</v>
+      </c>
+      <c r="AG16">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="17" spans="1:33">
       <c r="A17" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B17">
         <v>6</v>
@@ -2025,31 +2197,31 @@
         <v>6</v>
       </c>
       <c r="I17">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="J17">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="K17">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="L17">
         <v>7</v>
       </c>
       <c r="M17">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="N17">
         <v>9</v>
       </c>
       <c r="O17">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="P17">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="Q17">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="R17">
         <v>10</v>
@@ -2058,39 +2230,51 @@
         <v>8</v>
       </c>
       <c r="T17">
+        <v>10</v>
+      </c>
+      <c r="U17">
+        <v>8</v>
+      </c>
+      <c r="V17">
         <v>9</v>
       </c>
-      <c r="U17">
+      <c r="W17">
         <v>9</v>
       </c>
-      <c r="V17">
-        <v>7</v>
-      </c>
-      <c r="W17">
-        <v>8</v>
-      </c>
       <c r="X17">
         <v>7</v>
       </c>
       <c r="Y17">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Z17">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA17">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AB17">
         <v>9</v>
       </c>
       <c r="AC17">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="18" spans="1:29">
+        <v>7</v>
+      </c>
+      <c r="AD17">
+        <v>9</v>
+      </c>
+      <c r="AE17">
+        <v>9</v>
+      </c>
+      <c r="AF17">
+        <v>6</v>
+      </c>
+      <c r="AG17">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="18" spans="1:33">
       <c r="A18" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B18">
         <v>6</v>
@@ -2114,55 +2298,55 @@
         <v>5</v>
       </c>
       <c r="I18">
+        <v>10</v>
+      </c>
+      <c r="J18">
         <v>4</v>
       </c>
-      <c r="J18">
-        <v>5</v>
-      </c>
       <c r="K18">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="L18">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M18">
         <v>5</v>
       </c>
       <c r="N18">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="O18">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="P18">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="Q18">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="R18">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="S18">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="T18">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="U18">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="V18">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="W18">
         <v>6</v>
       </c>
       <c r="X18">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Y18">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="Z18">
         <v>6</v>
@@ -2171,15 +2355,27 @@
         <v>6</v>
       </c>
       <c r="AB18">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AC18">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="19" spans="1:29">
+        <v>6</v>
+      </c>
+      <c r="AD18">
+        <v>6</v>
+      </c>
+      <c r="AE18">
+        <v>7</v>
+      </c>
+      <c r="AF18">
+        <v>5</v>
+      </c>
+      <c r="AG18">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="19" spans="1:33">
       <c r="A19" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B19">
         <v>5</v>
@@ -2203,55 +2399,55 @@
         <v>5</v>
       </c>
       <c r="I19">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="J19">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K19">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="L19">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M19">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="N19">
         <v>7</v>
       </c>
       <c r="O19">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="P19">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="Q19">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="R19">
         <v>7</v>
       </c>
       <c r="S19">
+        <v>7</v>
+      </c>
+      <c r="T19">
+        <v>7</v>
+      </c>
+      <c r="U19">
         <v>9</v>
       </c>
-      <c r="T19">
-        <v>7</v>
-      </c>
-      <c r="U19">
-        <v>8</v>
-      </c>
       <c r="V19">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="W19">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="X19">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="Y19">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="Z19">
         <v>6</v>
@@ -2260,15 +2456,27 @@
         <v>6</v>
       </c>
       <c r="AB19">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AC19">
         <v>6</v>
       </c>
-    </row>
-    <row r="20" spans="1:29">
+      <c r="AD19">
+        <v>6</v>
+      </c>
+      <c r="AE19">
+        <v>7</v>
+      </c>
+      <c r="AF19">
+        <v>6</v>
+      </c>
+      <c r="AG19">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="20" spans="1:33">
       <c r="A20" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B20">
         <v>5</v>
@@ -2292,17 +2500,17 @@
         <v>5</v>
       </c>
       <c r="I20">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="J20">
         <v>5</v>
       </c>
       <c r="K20">
+        <v>5</v>
+      </c>
+      <c r="L20">
         <v>4</v>
       </c>
-      <c r="L20">
-        <v>5</v>
-      </c>
       <c r="M20">
         <v>5</v>
       </c>
@@ -2316,17 +2524,17 @@
         <v>5</v>
       </c>
       <c r="Q20">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="R20">
+        <v>5</v>
+      </c>
+      <c r="S20">
+        <v>5</v>
+      </c>
+      <c r="T20">
         <v>0</v>
       </c>
-      <c r="S20">
-        <v>5</v>
-      </c>
-      <c r="T20">
-        <v>5</v>
-      </c>
       <c r="U20">
         <v>5</v>
       </c>
@@ -2340,7 +2548,7 @@
         <v>5</v>
       </c>
       <c r="Y20">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="Z20">
         <v>5</v>
@@ -2354,10 +2562,22 @@
       <c r="AC20">
         <v>5</v>
       </c>
-    </row>
-    <row r="21" spans="1:29">
+      <c r="AD20">
+        <v>5</v>
+      </c>
+      <c r="AE20">
+        <v>5</v>
+      </c>
+      <c r="AF20">
+        <v>5</v>
+      </c>
+      <c r="AG20">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="21" spans="1:33">
       <c r="A21" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B21">
         <v>4</v>
@@ -2381,31 +2601,31 @@
         <v>6</v>
       </c>
       <c r="I21">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="J21">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K21">
         <v>6</v>
       </c>
       <c r="L21">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M21">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="N21">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="O21">
         <v>5</v>
       </c>
       <c r="P21">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="Q21">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="R21">
         <v>7</v>
@@ -2414,13 +2634,13 @@
         <v>8</v>
       </c>
       <c r="T21">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="U21">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="V21">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="W21">
         <v>6</v>
@@ -2429,7 +2649,7 @@
         <v>7</v>
       </c>
       <c r="Y21">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="Z21">
         <v>6</v>
@@ -2443,10 +2663,22 @@
       <c r="AC21">
         <v>6</v>
       </c>
-    </row>
-    <row r="22" spans="1:29">
+      <c r="AD21">
+        <v>7</v>
+      </c>
+      <c r="AE21">
+        <v>6</v>
+      </c>
+      <c r="AF21">
+        <v>6</v>
+      </c>
+      <c r="AG21">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="22" spans="1:33">
       <c r="A22" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B22">
         <v>8</v>
@@ -2470,10 +2702,10 @@
         <v>5</v>
       </c>
       <c r="I22">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="J22">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="K22">
         <v>5</v>
@@ -2485,57 +2717,69 @@
         <v>5</v>
       </c>
       <c r="N22">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="O22">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="P22">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Q22">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="R22">
+        <v>6</v>
+      </c>
+      <c r="S22">
+        <v>7</v>
+      </c>
+      <c r="T22">
         <v>4</v>
       </c>
-      <c r="S22">
-        <v>8</v>
-      </c>
-      <c r="T22">
-        <v>5</v>
-      </c>
       <c r="U22">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="V22">
         <v>5</v>
       </c>
       <c r="W22">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="X22">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Y22">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="Z22">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA22">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AB22">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AC22">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="23" spans="1:29">
+        <v>6</v>
+      </c>
+      <c r="AD22">
+        <v>5</v>
+      </c>
+      <c r="AE22">
+        <v>6</v>
+      </c>
+      <c r="AF22">
+        <v>5</v>
+      </c>
+      <c r="AG22">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="23" spans="1:33">
       <c r="A23" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B23">
         <v>6</v>
@@ -2559,13 +2803,13 @@
         <v>5</v>
       </c>
       <c r="I23">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="J23">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="K23">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="L23">
         <v>5</v>
@@ -2574,40 +2818,40 @@
         <v>5</v>
       </c>
       <c r="N23">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="O23">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="P23">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Q23">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="R23">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="S23">
         <v>8</v>
       </c>
       <c r="T23">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="U23">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="V23">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="W23">
         <v>6</v>
       </c>
       <c r="X23">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="Y23">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="Z23">
         <v>6</v>
@@ -2616,15 +2860,27 @@
         <v>7</v>
       </c>
       <c r="AB23">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AC23">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="24" spans="1:29">
+        <v>6</v>
+      </c>
+      <c r="AD23">
+        <v>7</v>
+      </c>
+      <c r="AE23">
+        <v>7</v>
+      </c>
+      <c r="AF23">
+        <v>5</v>
+      </c>
+      <c r="AG23">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="24" spans="1:33">
       <c r="A24" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B24">
         <v>7</v>
@@ -2648,10 +2904,10 @@
         <v>5</v>
       </c>
       <c r="I24">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="J24">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="K24">
         <v>5</v>
@@ -2663,57 +2919,69 @@
         <v>5</v>
       </c>
       <c r="N24">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="O24">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="P24">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="Q24">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="R24">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="S24">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="T24">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="U24">
         <v>8</v>
       </c>
       <c r="V24">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="W24">
         <v>8</v>
       </c>
       <c r="X24">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Y24">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="Z24">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AA24">
         <v>6</v>
       </c>
       <c r="AB24">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="AC24">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="25" spans="1:29">
+        <v>6</v>
+      </c>
+      <c r="AD24">
+        <v>6</v>
+      </c>
+      <c r="AE24">
+        <v>8</v>
+      </c>
+      <c r="AF24">
+        <v>5</v>
+      </c>
+      <c r="AG24">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="25" spans="1:33">
       <c r="A25" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B25">
         <v>6</v>
@@ -2737,72 +3005,84 @@
         <v>7</v>
       </c>
       <c r="I25">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J25">
         <v>9</v>
       </c>
       <c r="K25">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="L25">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M25">
+        <v>5</v>
+      </c>
+      <c r="N25">
         <v>9</v>
       </c>
-      <c r="N25">
-        <v>6</v>
-      </c>
       <c r="O25">
         <v>6</v>
       </c>
       <c r="P25">
+        <v>6</v>
+      </c>
+      <c r="Q25">
+        <v>10</v>
+      </c>
+      <c r="R25">
         <v>9</v>
       </c>
-      <c r="Q25">
+      <c r="S25">
         <v>9</v>
       </c>
-      <c r="R25">
-        <v>6</v>
-      </c>
-      <c r="S25">
-        <v>7</v>
-      </c>
       <c r="T25">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="U25">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="V25">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="W25">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="X25">
+        <v>7</v>
+      </c>
+      <c r="Y25">
+        <v>10</v>
+      </c>
+      <c r="Z25">
+        <v>8</v>
+      </c>
+      <c r="AA25">
         <v>9</v>
       </c>
-      <c r="Y25">
-        <v>7</v>
-      </c>
-      <c r="Z25">
-        <v>6</v>
-      </c>
-      <c r="AA25">
-        <v>8</v>
-      </c>
       <c r="AB25">
         <v>7</v>
       </c>
       <c r="AC25">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="26" spans="1:29">
+        <v>6</v>
+      </c>
+      <c r="AD25">
+        <v>8</v>
+      </c>
+      <c r="AE25">
+        <v>7</v>
+      </c>
+      <c r="AF25">
+        <v>7</v>
+      </c>
+      <c r="AG25">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="26" spans="1:33">
       <c r="A26" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B26">
         <v>5</v>
@@ -2826,13 +3106,13 @@
         <v>6</v>
       </c>
       <c r="I26">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="J26">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K26">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L26">
         <v>5</v>
@@ -2847,34 +3127,34 @@
         <v>5</v>
       </c>
       <c r="P26">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="Q26">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="R26">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="S26">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="T26">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="U26">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="V26">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="W26">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X26">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y26">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="Z26">
         <v>6</v>
@@ -2888,10 +3168,22 @@
       <c r="AC26">
         <v>6</v>
       </c>
-    </row>
-    <row r="27" spans="1:29">
+      <c r="AD26">
+        <v>6</v>
+      </c>
+      <c r="AE26">
+        <v>6</v>
+      </c>
+      <c r="AF26">
+        <v>6</v>
+      </c>
+      <c r="AG26">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="27" spans="1:33">
       <c r="A27" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B27">
         <v>4</v>
@@ -2915,55 +3207,55 @@
         <v>5</v>
       </c>
       <c r="I27">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="J27">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K27">
+        <v>6</v>
+      </c>
+      <c r="L27">
         <v>4</v>
       </c>
-      <c r="L27">
-        <v>6</v>
-      </c>
       <c r="M27">
         <v>6</v>
       </c>
       <c r="N27">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="O27">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="P27">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Q27">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="R27">
+        <v>7</v>
+      </c>
+      <c r="S27">
+        <v>7</v>
+      </c>
+      <c r="T27">
         <v>4</v>
       </c>
-      <c r="S27">
-        <v>8</v>
-      </c>
-      <c r="T27">
-        <v>8</v>
-      </c>
       <c r="U27">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="V27">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="W27">
         <v>6</v>
       </c>
       <c r="X27">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="Y27">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="Z27">
         <v>6</v>
@@ -2972,15 +3264,27 @@
         <v>7</v>
       </c>
       <c r="AB27">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AC27">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="28" spans="1:29">
+        <v>6</v>
+      </c>
+      <c r="AD27">
+        <v>7</v>
+      </c>
+      <c r="AE27">
+        <v>7</v>
+      </c>
+      <c r="AF27">
+        <v>5</v>
+      </c>
+      <c r="AG27">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="28" spans="1:33">
       <c r="A28" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B28">
         <v>5</v>
@@ -3004,72 +3308,84 @@
         <v>6</v>
       </c>
       <c r="I28">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="J28">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="K28">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="L28">
         <v>5</v>
       </c>
       <c r="M28">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="N28">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="O28">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="P28">
+        <v>6</v>
+      </c>
+      <c r="Q28">
+        <v>10</v>
+      </c>
+      <c r="R28">
         <v>9</v>
       </c>
-      <c r="Q28">
-        <v>8</v>
-      </c>
-      <c r="R28">
+      <c r="S28">
+        <v>8</v>
+      </c>
+      <c r="T28">
         <v>4</v>
       </c>
-      <c r="S28">
-        <v>8</v>
-      </c>
-      <c r="T28">
+      <c r="U28">
+        <v>8</v>
+      </c>
+      <c r="V28">
         <v>9</v>
       </c>
-      <c r="U28">
-        <v>7</v>
-      </c>
-      <c r="V28">
-        <v>6</v>
-      </c>
       <c r="W28">
         <v>7</v>
       </c>
       <c r="X28">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Y28">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="Z28">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA28">
+        <v>7</v>
+      </c>
+      <c r="AB28">
+        <v>5</v>
+      </c>
+      <c r="AC28">
+        <v>6</v>
+      </c>
+      <c r="AD28">
         <v>9</v>
       </c>
-      <c r="AB28">
-        <v>7</v>
-      </c>
-      <c r="AC28">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="29" spans="1:29">
+      <c r="AE28">
+        <v>7</v>
+      </c>
+      <c r="AF28">
+        <v>6</v>
+      </c>
+      <c r="AG28">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="29" spans="1:33">
       <c r="A29" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B29">
         <v>6</v>
@@ -3093,72 +3409,84 @@
         <v>6</v>
       </c>
       <c r="I29">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="J29">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="K29">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L29">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="M29">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="N29">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="O29">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="P29">
         <v>6</v>
       </c>
       <c r="Q29">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="R29">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="S29">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="T29">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="U29">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="V29">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="W29">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="X29">
         <v>6</v>
       </c>
       <c r="Y29">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="Z29">
         <v>7</v>
       </c>
       <c r="AA29">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AB29">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AC29">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="30" spans="1:29">
+        <v>7</v>
+      </c>
+      <c r="AD29">
+        <v>7</v>
+      </c>
+      <c r="AE29">
+        <v>7</v>
+      </c>
+      <c r="AF29">
+        <v>6</v>
+      </c>
+      <c r="AG29">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="30" spans="1:33">
       <c r="A30" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B30">
         <v>6</v>
@@ -3182,72 +3510,84 @@
         <v>5</v>
       </c>
       <c r="I30">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="J30">
+        <v>8</v>
+      </c>
+      <c r="K30">
         <v>9</v>
       </c>
-      <c r="K30">
-        <v>6</v>
-      </c>
       <c r="L30">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="M30">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="N30">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="O30">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="P30">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="Q30">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="R30">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="S30">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T30">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="U30">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="V30">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="W30">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X30">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Y30">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="Z30">
         <v>7</v>
       </c>
       <c r="AA30">
+        <v>8</v>
+      </c>
+      <c r="AB30">
+        <v>7</v>
+      </c>
+      <c r="AC30">
+        <v>7</v>
+      </c>
+      <c r="AD30">
         <v>9</v>
       </c>
-      <c r="AB30">
-        <v>6</v>
-      </c>
-      <c r="AC30">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="31" spans="1:29">
+      <c r="AE30">
+        <v>6</v>
+      </c>
+      <c r="AF30">
+        <v>6</v>
+      </c>
+      <c r="AG30">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="31" spans="1:33">
       <c r="A31" s="1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B31">
         <v>6</v>
@@ -3271,16 +3611,16 @@
         <v>5</v>
       </c>
       <c r="I31">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="J31">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="K31">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="L31">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="M31">
         <v>7</v>
@@ -3289,13 +3629,13 @@
         <v>7</v>
       </c>
       <c r="O31">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="P31">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Q31">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="R31">
         <v>7</v>
@@ -3304,39 +3644,51 @@
         <v>9</v>
       </c>
       <c r="T31">
+        <v>7</v>
+      </c>
+      <c r="U31">
         <v>9</v>
       </c>
-      <c r="U31">
-        <v>7</v>
-      </c>
       <c r="V31">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="W31">
         <v>7</v>
       </c>
       <c r="X31">
+        <v>7</v>
+      </c>
+      <c r="Y31">
+        <v>10</v>
+      </c>
+      <c r="Z31">
+        <v>7</v>
+      </c>
+      <c r="AA31">
         <v>9</v>
       </c>
-      <c r="Y31">
-        <v>8</v>
-      </c>
-      <c r="Z31">
-        <v>7</v>
-      </c>
-      <c r="AA31">
-        <v>8</v>
-      </c>
       <c r="AB31">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AC31">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="32" spans="1:29">
+        <v>7</v>
+      </c>
+      <c r="AD31">
+        <v>8</v>
+      </c>
+      <c r="AE31">
+        <v>7</v>
+      </c>
+      <c r="AF31">
+        <v>6</v>
+      </c>
+      <c r="AG31">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="32" spans="1:33">
       <c r="A32" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B32">
         <v>5</v>
@@ -3366,11 +3718,11 @@
         <v>5</v>
       </c>
       <c r="K32">
+        <v>5</v>
+      </c>
+      <c r="L32">
         <v>0</v>
       </c>
-      <c r="L32">
-        <v>5</v>
-      </c>
       <c r="M32">
         <v>5</v>
       </c>
@@ -3387,14 +3739,14 @@
         <v>5</v>
       </c>
       <c r="R32">
+        <v>5</v>
+      </c>
+      <c r="S32">
+        <v>5</v>
+      </c>
+      <c r="T32">
         <v>0</v>
       </c>
-      <c r="S32">
-        <v>5</v>
-      </c>
-      <c r="T32">
-        <v>5</v>
-      </c>
       <c r="U32">
         <v>5</v>
       </c>
@@ -3422,10 +3774,22 @@
       <c r="AC32">
         <v>5</v>
       </c>
-    </row>
-    <row r="33" spans="1:29">
+      <c r="AD32">
+        <v>5</v>
+      </c>
+      <c r="AE32">
+        <v>5</v>
+      </c>
+      <c r="AF32">
+        <v>5</v>
+      </c>
+      <c r="AG32">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="33" spans="1:33">
       <c r="A33" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B33">
         <v>5</v>
@@ -3449,13 +3813,13 @@
         <v>6</v>
       </c>
       <c r="I33">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="J33">
         <v>8</v>
       </c>
       <c r="K33">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="L33">
         <v>7</v>
@@ -3464,57 +3828,69 @@
         <v>7</v>
       </c>
       <c r="N33">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="O33">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="P33">
+        <v>6</v>
+      </c>
+      <c r="Q33">
+        <v>10</v>
+      </c>
+      <c r="R33">
         <v>9</v>
       </c>
-      <c r="Q33">
-        <v>8</v>
-      </c>
-      <c r="R33">
-        <v>8</v>
-      </c>
       <c r="S33">
+        <v>8</v>
+      </c>
+      <c r="T33">
+        <v>8</v>
+      </c>
+      <c r="U33">
         <v>9</v>
       </c>
-      <c r="T33">
-        <v>10</v>
-      </c>
-      <c r="U33">
-        <v>8</v>
-      </c>
       <c r="V33">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="W33">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X33">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Y33">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="Z33">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AA33">
+        <v>8</v>
+      </c>
+      <c r="AB33">
+        <v>8</v>
+      </c>
+      <c r="AC33">
+        <v>8</v>
+      </c>
+      <c r="AD33">
         <v>9</v>
       </c>
-      <c r="AB33">
-        <v>8</v>
-      </c>
-      <c r="AC33">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="34" spans="1:29">
+      <c r="AE33">
+        <v>8</v>
+      </c>
+      <c r="AF33">
+        <v>6</v>
+      </c>
+      <c r="AG33">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="34" spans="1:33">
       <c r="A34" s="1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B34">
         <v>4</v>
@@ -3538,13 +3914,13 @@
         <v>5</v>
       </c>
       <c r="I34">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="J34">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K34">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L34">
         <v>5</v>
@@ -3559,13 +3935,13 @@
         <v>5</v>
       </c>
       <c r="P34">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="Q34">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="R34">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="S34">
         <v>5</v>
@@ -3577,19 +3953,19 @@
         <v>5</v>
       </c>
       <c r="V34">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="W34">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="X34">
         <v>5</v>
       </c>
       <c r="Y34">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="Z34">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA34">
         <v>5</v>
@@ -3600,10 +3976,22 @@
       <c r="AC34">
         <v>5</v>
       </c>
-    </row>
-    <row r="35" spans="1:29">
+      <c r="AD34">
+        <v>5</v>
+      </c>
+      <c r="AE34">
+        <v>5</v>
+      </c>
+      <c r="AF34">
+        <v>5</v>
+      </c>
+      <c r="AG34">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="35" spans="1:33">
       <c r="A35" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B35">
         <v>9</v>
@@ -3630,69 +4018,81 @@
         <v>10</v>
       </c>
       <c r="J35">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="K35">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="L35">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M35">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="N35">
         <v>8</v>
       </c>
       <c r="O35">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="P35">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="Q35">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="R35">
         <v>10</v>
       </c>
       <c r="S35">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T35">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="U35">
         <v>9</v>
       </c>
       <c r="V35">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="W35">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X35">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="Y35">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="Z35">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AA35">
         <v>8</v>
       </c>
       <c r="AB35">
+        <v>5</v>
+      </c>
+      <c r="AC35">
+        <v>8</v>
+      </c>
+      <c r="AD35">
+        <v>8</v>
+      </c>
+      <c r="AE35">
         <v>9</v>
       </c>
-      <c r="AC35">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="36" spans="1:29">
+      <c r="AF35">
+        <v>6</v>
+      </c>
+      <c r="AG35">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="36" spans="1:33">
       <c r="A36" s="1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B36">
         <v>6</v>
@@ -3716,19 +4116,19 @@
         <v>5</v>
       </c>
       <c r="I36">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="J36">
         <v>5</v>
       </c>
       <c r="K36">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L36">
         <v>4</v>
       </c>
       <c r="M36">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N36">
         <v>5</v>
@@ -3740,19 +4140,19 @@
         <v>5</v>
       </c>
       <c r="Q36">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="R36">
         <v>5</v>
       </c>
       <c r="S36">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T36">
         <v>5</v>
       </c>
       <c r="U36">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="V36">
         <v>5</v>
@@ -3764,7 +4164,7 @@
         <v>5</v>
       </c>
       <c r="Y36">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="Z36">
         <v>5</v>
@@ -3778,10 +4178,22 @@
       <c r="AC36">
         <v>5</v>
       </c>
-    </row>
-    <row r="37" spans="1:29">
+      <c r="AD36">
+        <v>5</v>
+      </c>
+      <c r="AE36">
+        <v>5</v>
+      </c>
+      <c r="AF36">
+        <v>5</v>
+      </c>
+      <c r="AG36">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="37" spans="1:33">
       <c r="A37" s="1" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B37">
         <v>5</v>
@@ -3805,10 +4217,10 @@
         <v>5</v>
       </c>
       <c r="I37">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="J37">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="K37">
         <v>5</v>
@@ -3820,57 +4232,69 @@
         <v>5</v>
       </c>
       <c r="N37">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="O37">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="P37">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="Q37">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="R37">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="S37">
+        <v>6</v>
+      </c>
+      <c r="T37">
+        <v>7</v>
+      </c>
+      <c r="U37">
         <v>9</v>
       </c>
-      <c r="T37">
-        <v>8</v>
-      </c>
-      <c r="U37">
-        <v>7</v>
-      </c>
       <c r="V37">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="W37">
         <v>7</v>
       </c>
       <c r="X37">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Y37">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="Z37">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA37">
         <v>6</v>
       </c>
       <c r="AB37">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AC37">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="38" spans="1:29">
+        <v>6</v>
+      </c>
+      <c r="AD37">
+        <v>6</v>
+      </c>
+      <c r="AE37">
+        <v>8</v>
+      </c>
+      <c r="AF37">
+        <v>5</v>
+      </c>
+      <c r="AG37">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="38" spans="1:33">
       <c r="A38" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B38">
         <v>6</v>
@@ -3894,7 +4318,7 @@
         <v>5</v>
       </c>
       <c r="I38">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="J38">
         <v>5</v>
@@ -3915,19 +4339,19 @@
         <v>5</v>
       </c>
       <c r="P38">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="Q38">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="R38">
         <v>7</v>
       </c>
       <c r="S38">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="T38">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="U38">
         <v>5</v>
@@ -3936,30 +4360,42 @@
         <v>5</v>
       </c>
       <c r="W38">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="X38">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Y38">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="Z38">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA38">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AB38">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AC38">
         <v>5</v>
       </c>
-    </row>
-    <row r="39" spans="1:29">
+      <c r="AD38">
+        <v>5</v>
+      </c>
+      <c r="AE38">
+        <v>5</v>
+      </c>
+      <c r="AF38">
+        <v>5</v>
+      </c>
+      <c r="AG38">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="39" spans="1:33">
       <c r="A39" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B39">
         <v>7</v>
@@ -3983,72 +4419,84 @@
         <v>6</v>
       </c>
       <c r="I39">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="J39">
         <v>7</v>
       </c>
       <c r="K39">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="L39">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M39">
         <v>5</v>
       </c>
       <c r="N39">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="O39">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="P39">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="Q39">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="R39">
+        <v>8</v>
+      </c>
+      <c r="S39">
+        <v>8</v>
+      </c>
+      <c r="T39">
         <v>9</v>
       </c>
-      <c r="S39">
-        <v>8</v>
-      </c>
-      <c r="T39">
-        <v>8</v>
-      </c>
       <c r="U39">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="V39">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="W39">
         <v>7</v>
       </c>
       <c r="X39">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="Y39">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="Z39">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA39">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AB39">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AC39">
         <v>6</v>
       </c>
-    </row>
-    <row r="40" spans="1:29">
+      <c r="AD39">
+        <v>7</v>
+      </c>
+      <c r="AE39">
+        <v>8</v>
+      </c>
+      <c r="AF39">
+        <v>6</v>
+      </c>
+      <c r="AG39">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="40" spans="1:33">
       <c r="A40" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B40">
         <v>6</v>
@@ -4072,72 +4520,84 @@
         <v>6</v>
       </c>
       <c r="I40">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="J40">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K40">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L40">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="M40">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="N40">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="O40">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="P40">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="Q40">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="R40">
+        <v>7</v>
+      </c>
+      <c r="S40">
+        <v>6</v>
+      </c>
+      <c r="T40">
         <v>4</v>
       </c>
-      <c r="S40">
-        <v>8</v>
-      </c>
-      <c r="T40">
-        <v>8</v>
-      </c>
       <c r="U40">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="V40">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="W40">
         <v>7</v>
       </c>
       <c r="X40">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Y40">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="Z40">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA40">
         <v>6</v>
       </c>
       <c r="AB40">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="AC40">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="41" spans="1:29">
+        <v>6</v>
+      </c>
+      <c r="AD40">
+        <v>6</v>
+      </c>
+      <c r="AE40">
+        <v>8</v>
+      </c>
+      <c r="AF40">
+        <v>5</v>
+      </c>
+      <c r="AG40">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="41" spans="1:33">
       <c r="A41" s="1" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B41">
         <v>7</v>
@@ -4164,28 +4624,28 @@
         <v>10</v>
       </c>
       <c r="J41">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="K41">
         <v>8</v>
       </c>
       <c r="L41">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="M41">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="N41">
+        <v>8</v>
+      </c>
+      <c r="O41">
         <v>9</v>
       </c>
-      <c r="O41">
-        <v>6</v>
-      </c>
       <c r="P41">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="Q41">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="R41">
         <v>10</v>
@@ -4194,39 +4654,51 @@
         <v>8</v>
       </c>
       <c r="T41">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="U41">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="V41">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="W41">
         <v>9</v>
       </c>
       <c r="X41">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Y41">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="Z41">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AA41">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AB41">
+        <v>8</v>
+      </c>
+      <c r="AC41">
+        <v>7</v>
+      </c>
+      <c r="AD41">
+        <v>7</v>
+      </c>
+      <c r="AE41">
         <v>9</v>
       </c>
-      <c r="AC41">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="42" spans="1:29">
+      <c r="AF41">
+        <v>6</v>
+      </c>
+      <c r="AG41">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="42" spans="1:33">
       <c r="A42" s="1" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B42">
         <v>5</v>
@@ -4250,25 +4722,25 @@
         <v>6</v>
       </c>
       <c r="I42">
+        <v>5</v>
+      </c>
+      <c r="J42">
         <v>3</v>
       </c>
-      <c r="J42">
-        <v>6</v>
-      </c>
       <c r="K42">
+        <v>6</v>
+      </c>
+      <c r="L42">
         <v>4</v>
       </c>
-      <c r="L42">
+      <c r="M42">
         <v>3</v>
       </c>
-      <c r="M42">
-        <v>5</v>
-      </c>
       <c r="N42">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="O42">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="P42">
         <v>5</v>
@@ -4277,14 +4749,14 @@
         <v>5</v>
       </c>
       <c r="R42">
+        <v>5</v>
+      </c>
+      <c r="S42">
+        <v>5</v>
+      </c>
+      <c r="T42">
         <v>0</v>
       </c>
-      <c r="S42">
-        <v>5</v>
-      </c>
-      <c r="T42">
-        <v>5</v>
-      </c>
       <c r="U42">
         <v>5</v>
       </c>
@@ -4307,18 +4779,30 @@
         <v>5</v>
       </c>
       <c r="AB42">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AC42">
+        <v>5</v>
+      </c>
+      <c r="AD42">
+        <v>5</v>
+      </c>
+      <c r="AE42">
+        <v>6</v>
+      </c>
+      <c r="AF42">
+        <v>5</v>
+      </c>
+      <c r="AG42">
         <v>5</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="4">
-    <mergeCell ref="B1:H1"/>
-    <mergeCell ref="I1:O1"/>
-    <mergeCell ref="P1:V1"/>
-    <mergeCell ref="W1:AC1"/>
+    <mergeCell ref="B1:I1"/>
+    <mergeCell ref="J1:Q1"/>
+    <mergeCell ref="R1:Y1"/>
+    <mergeCell ref="Z1:AG1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -4326,16 +4810,16 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:V42"/>
+  <dimension ref="A1:Y42"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="50.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:22">
+    <row r="1" spans="1:25">
       <c r="A1" s="1"/>
       <c r="B1" s="1" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C1" s="1"/>
       <c r="D1" s="1"/>
@@ -4343,26 +4827,29 @@
       <c r="F1" s="1"/>
       <c r="G1" s="1"/>
       <c r="H1" s="1"/>
-      <c r="I1" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="J1" s="1"/>
+      <c r="I1" s="1"/>
+      <c r="J1" s="1" t="s">
+        <v>54</v>
+      </c>
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
       <c r="N1" s="1"/>
       <c r="O1" s="1"/>
-      <c r="P1" s="1" t="s">
-        <v>54</v>
-      </c>
+      <c r="P1" s="1"/>
       <c r="Q1" s="1"/>
-      <c r="R1" s="1"/>
+      <c r="R1" s="1" t="s">
+        <v>55</v>
+      </c>
       <c r="S1" s="1"/>
       <c r="T1" s="1"/>
       <c r="U1" s="1"/>
       <c r="V1" s="1"/>
-    </row>
-    <row r="2" spans="1:22">
+      <c r="W1" s="1"/>
+      <c r="X1" s="1"/>
+      <c r="Y1" s="1"/>
+    </row>
+    <row r="2" spans="1:25">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
@@ -4388,56 +4875,65 @@
         <v>11</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="L2" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="M2" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="N2" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="N2" s="1" t="s">
-        <v>10</v>
-      </c>
       <c r="O2" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="P2" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="P2" s="1" t="s">
-        <v>5</v>
-      </c>
       <c r="Q2" s="1" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="R2" s="1" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="S2" s="1" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="T2" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="U2" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="V2" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="U2" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="V2" s="1" t="s">
+      <c r="W2" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="X2" s="1" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="3" spans="1:22">
+      <c r="Y2" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="3" spans="1:25">
       <c r="A3" s="1" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="4" spans="1:22">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="4" spans="1:25">
       <c r="A4" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B4">
         <v>100</v>
@@ -4461,51 +4957,60 @@
         <v>80</v>
       </c>
       <c r="I4">
+        <v>100</v>
+      </c>
+      <c r="J4">
         <v>60</v>
       </c>
-      <c r="J4">
-        <v>100</v>
-      </c>
       <c r="K4">
+        <v>100</v>
+      </c>
+      <c r="L4">
         <v>95.5</v>
       </c>
-      <c r="L4">
+      <c r="M4">
         <v>93.8</v>
       </c>
-      <c r="M4">
-        <v>100</v>
-      </c>
       <c r="N4">
         <v>100</v>
       </c>
       <c r="O4">
+        <v>100</v>
+      </c>
+      <c r="P4">
         <v>79.5</v>
       </c>
-      <c r="P4">
+      <c r="Q4">
+        <v>100</v>
+      </c>
+      <c r="R4">
         <v>37.5</v>
       </c>
-      <c r="Q4">
-        <v>100</v>
-      </c>
-      <c r="R4">
+      <c r="S4">
+        <v>100</v>
+      </c>
+      <c r="T4">
         <v>65.59999999999999</v>
       </c>
-      <c r="S4">
+      <c r="U4">
         <v>62.5</v>
       </c>
-      <c r="T4">
+      <c r="V4">
         <v>98.3</v>
       </c>
-      <c r="U4">
-        <v>100</v>
-      </c>
-      <c r="V4">
+      <c r="W4">
+        <v>100</v>
+      </c>
+      <c r="X4">
         <v>55.6</v>
       </c>
-    </row>
-    <row r="5" spans="1:22">
+      <c r="Y4">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="5" spans="1:25">
       <c r="A5" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B5">
         <v>100</v>
@@ -4535,11 +5040,11 @@
         <v>100</v>
       </c>
       <c r="K5">
+        <v>100</v>
+      </c>
+      <c r="L5">
         <v>95.5</v>
       </c>
-      <c r="L5">
-        <v>100</v>
-      </c>
       <c r="M5">
         <v>100</v>
       </c>
@@ -4547,33 +5052,42 @@
         <v>100</v>
       </c>
       <c r="O5">
+        <v>100</v>
+      </c>
+      <c r="P5">
         <v>87.2</v>
       </c>
-      <c r="P5">
-        <v>100</v>
-      </c>
       <c r="Q5">
         <v>100</v>
       </c>
       <c r="R5">
+        <v>100</v>
+      </c>
+      <c r="S5">
+        <v>100</v>
+      </c>
+      <c r="T5">
         <v>96.90000000000001</v>
       </c>
-      <c r="S5">
-        <v>100</v>
-      </c>
-      <c r="T5">
-        <v>100</v>
-      </c>
       <c r="U5">
         <v>100</v>
       </c>
       <c r="V5">
+        <v>100</v>
+      </c>
+      <c r="W5">
+        <v>100</v>
+      </c>
+      <c r="X5">
         <v>90.5</v>
       </c>
-    </row>
-    <row r="6" spans="1:22">
+      <c r="Y5">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="6" spans="1:25">
       <c r="A6" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B6">
         <v>80</v>
@@ -4597,51 +5111,60 @@
         <v>85</v>
       </c>
       <c r="I6">
+        <v>100</v>
+      </c>
+      <c r="J6">
         <v>90</v>
       </c>
-      <c r="J6">
-        <v>100</v>
-      </c>
       <c r="K6">
+        <v>100</v>
+      </c>
+      <c r="L6">
         <v>88.59999999999999</v>
       </c>
-      <c r="L6">
+      <c r="M6">
         <v>96.90000000000001</v>
       </c>
-      <c r="M6">
+      <c r="N6">
         <v>95</v>
       </c>
-      <c r="N6">
-        <v>100</v>
-      </c>
       <c r="O6">
+        <v>100</v>
+      </c>
+      <c r="P6">
         <v>84.59999999999999</v>
       </c>
-      <c r="P6">
+      <c r="Q6">
+        <v>100</v>
+      </c>
+      <c r="R6">
         <v>93.8</v>
       </c>
-      <c r="Q6">
-        <v>100</v>
-      </c>
-      <c r="R6">
+      <c r="S6">
+        <v>100</v>
+      </c>
+      <c r="T6">
         <v>85.90000000000001</v>
       </c>
-      <c r="S6">
+      <c r="U6">
         <v>91.7</v>
       </c>
-      <c r="T6">
+      <c r="V6">
         <v>95</v>
       </c>
-      <c r="U6">
+      <c r="W6">
         <v>88.90000000000001</v>
       </c>
-      <c r="V6">
+      <c r="X6">
         <v>88.90000000000001</v>
       </c>
-    </row>
-    <row r="7" spans="1:22">
+      <c r="Y6">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="7" spans="1:25">
       <c r="A7" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B7">
         <v>80</v>
@@ -4665,17 +5188,17 @@
         <v>85</v>
       </c>
       <c r="I7">
+        <v>100</v>
+      </c>
+      <c r="J7">
         <v>80</v>
       </c>
-      <c r="J7">
-        <v>100</v>
-      </c>
       <c r="K7">
+        <v>100</v>
+      </c>
+      <c r="L7">
         <v>90.90000000000001</v>
       </c>
-      <c r="L7">
-        <v>100</v>
-      </c>
       <c r="M7">
         <v>100</v>
       </c>
@@ -4683,33 +5206,42 @@
         <v>100</v>
       </c>
       <c r="O7">
+        <v>100</v>
+      </c>
+      <c r="P7">
         <v>89.7</v>
       </c>
-      <c r="P7">
+      <c r="Q7">
+        <v>100</v>
+      </c>
+      <c r="R7">
         <v>87.5</v>
       </c>
-      <c r="Q7">
-        <v>100</v>
-      </c>
-      <c r="R7">
+      <c r="S7">
+        <v>100</v>
+      </c>
+      <c r="T7">
         <v>89.09999999999999</v>
       </c>
-      <c r="S7">
-        <v>100</v>
-      </c>
-      <c r="T7">
-        <v>100</v>
-      </c>
       <c r="U7">
         <v>100</v>
       </c>
       <c r="V7">
+        <v>100</v>
+      </c>
+      <c r="W7">
+        <v>100</v>
+      </c>
+      <c r="X7">
         <v>90.5</v>
       </c>
-    </row>
-    <row r="8" spans="1:22">
+      <c r="Y7">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="8" spans="1:25">
       <c r="A8" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B8">
         <v>100</v>
@@ -4751,11 +5283,11 @@
         <v>100</v>
       </c>
       <c r="O8">
+        <v>100</v>
+      </c>
+      <c r="P8">
         <v>94.90000000000001</v>
       </c>
-      <c r="P8">
-        <v>100</v>
-      </c>
       <c r="Q8">
         <v>100</v>
       </c>
@@ -4772,12 +5304,21 @@
         <v>100</v>
       </c>
       <c r="V8">
+        <v>100</v>
+      </c>
+      <c r="W8">
+        <v>100</v>
+      </c>
+      <c r="X8">
         <v>96.8</v>
       </c>
-    </row>
-    <row r="9" spans="1:22">
+      <c r="Y8">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="9" spans="1:25">
       <c r="A9" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B9">
         <v>100</v>
@@ -4807,11 +5348,11 @@
         <v>100</v>
       </c>
       <c r="K9">
+        <v>100</v>
+      </c>
+      <c r="L9">
         <v>97.7</v>
       </c>
-      <c r="L9">
-        <v>100</v>
-      </c>
       <c r="M9">
         <v>100</v>
       </c>
@@ -4819,33 +5360,42 @@
         <v>100</v>
       </c>
       <c r="O9">
+        <v>100</v>
+      </c>
+      <c r="P9">
         <v>87.2</v>
       </c>
-      <c r="P9">
-        <v>100</v>
-      </c>
       <c r="Q9">
         <v>100</v>
       </c>
       <c r="R9">
+        <v>100</v>
+      </c>
+      <c r="S9">
+        <v>100</v>
+      </c>
+      <c r="T9">
         <v>95.3</v>
       </c>
-      <c r="S9">
-        <v>100</v>
-      </c>
-      <c r="T9">
-        <v>100</v>
-      </c>
       <c r="U9">
         <v>100</v>
       </c>
       <c r="V9">
+        <v>100</v>
+      </c>
+      <c r="W9">
+        <v>100</v>
+      </c>
+      <c r="X9">
         <v>92.09999999999999</v>
       </c>
-    </row>
-    <row r="10" spans="1:22">
+      <c r="Y9">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="10" spans="1:25">
       <c r="A10" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B10">
         <v>100</v>
@@ -4875,11 +5425,11 @@
         <v>100</v>
       </c>
       <c r="K10">
+        <v>100</v>
+      </c>
+      <c r="L10">
         <v>90.90000000000001</v>
       </c>
-      <c r="L10">
-        <v>100</v>
-      </c>
       <c r="M10">
         <v>100</v>
       </c>
@@ -4887,33 +5437,42 @@
         <v>100</v>
       </c>
       <c r="O10">
+        <v>100</v>
+      </c>
+      <c r="P10">
         <v>97.40000000000001</v>
       </c>
-      <c r="P10">
-        <v>100</v>
-      </c>
       <c r="Q10">
         <v>100</v>
       </c>
       <c r="R10">
+        <v>100</v>
+      </c>
+      <c r="S10">
+        <v>100</v>
+      </c>
+      <c r="T10">
         <v>93.8</v>
       </c>
-      <c r="S10">
-        <v>100</v>
-      </c>
-      <c r="T10">
-        <v>100</v>
-      </c>
       <c r="U10">
         <v>100</v>
       </c>
       <c r="V10">
+        <v>100</v>
+      </c>
+      <c r="W10">
+        <v>100</v>
+      </c>
+      <c r="X10">
         <v>98.40000000000001</v>
       </c>
-    </row>
-    <row r="11" spans="1:22">
+      <c r="Y10">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="11" spans="1:25">
       <c r="A11" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B11">
         <v>100</v>
@@ -4943,11 +5502,11 @@
         <v>100</v>
       </c>
       <c r="K11">
+        <v>100</v>
+      </c>
+      <c r="L11">
         <v>93.2</v>
       </c>
-      <c r="L11">
-        <v>100</v>
-      </c>
       <c r="M11">
         <v>100</v>
       </c>
@@ -4955,33 +5514,42 @@
         <v>100</v>
       </c>
       <c r="O11">
+        <v>100</v>
+      </c>
+      <c r="P11">
         <v>97.40000000000001</v>
       </c>
-      <c r="P11">
-        <v>100</v>
-      </c>
       <c r="Q11">
         <v>100</v>
       </c>
       <c r="R11">
+        <v>100</v>
+      </c>
+      <c r="S11">
+        <v>100</v>
+      </c>
+      <c r="T11">
         <v>90.59999999999999</v>
       </c>
-      <c r="S11">
-        <v>100</v>
-      </c>
-      <c r="T11">
-        <v>100</v>
-      </c>
       <c r="U11">
         <v>100</v>
       </c>
       <c r="V11">
+        <v>100</v>
+      </c>
+      <c r="W11">
+        <v>100</v>
+      </c>
+      <c r="X11">
         <v>92.09999999999999</v>
       </c>
-    </row>
-    <row r="12" spans="1:22">
+      <c r="Y11">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="12" spans="1:25">
       <c r="A12" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B12">
         <v>100</v>
@@ -5005,28 +5573,28 @@
         <v>95</v>
       </c>
       <c r="I12">
+        <v>100</v>
+      </c>
+      <c r="J12">
         <v>90</v>
       </c>
-      <c r="J12">
-        <v>100</v>
-      </c>
       <c r="K12">
+        <v>100</v>
+      </c>
+      <c r="L12">
         <v>93.2</v>
       </c>
-      <c r="L12">
+      <c r="M12">
         <v>96.90000000000001</v>
       </c>
-      <c r="M12">
-        <v>100</v>
-      </c>
       <c r="N12">
         <v>100</v>
       </c>
       <c r="O12">
+        <v>100</v>
+      </c>
+      <c r="P12">
         <v>92.3</v>
-      </c>
-      <c r="P12">
-        <v>93.8</v>
       </c>
       <c r="Q12">
         <v>100</v>
@@ -5035,21 +5603,30 @@
         <v>93.8</v>
       </c>
       <c r="S12">
+        <v>100</v>
+      </c>
+      <c r="T12">
         <v>93.8</v>
       </c>
-      <c r="T12">
+      <c r="U12">
+        <v>93.8</v>
+      </c>
+      <c r="V12">
         <v>98.3</v>
       </c>
-      <c r="U12">
-        <v>100</v>
-      </c>
-      <c r="V12">
+      <c r="W12">
+        <v>100</v>
+      </c>
+      <c r="X12">
         <v>92.09999999999999</v>
       </c>
-    </row>
-    <row r="13" spans="1:22">
+      <c r="Y12">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="13" spans="1:25">
       <c r="A13" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B13">
         <v>100</v>
@@ -5079,45 +5656,54 @@
         <v>100</v>
       </c>
       <c r="K13">
+        <v>100</v>
+      </c>
+      <c r="L13">
         <v>88.59999999999999</v>
       </c>
-      <c r="L13">
+      <c r="M13">
         <v>96.90000000000001</v>
       </c>
-      <c r="M13">
-        <v>100</v>
-      </c>
       <c r="N13">
         <v>100</v>
       </c>
       <c r="O13">
+        <v>100</v>
+      </c>
+      <c r="P13">
         <v>94.90000000000001</v>
       </c>
-      <c r="P13">
-        <v>100</v>
-      </c>
       <c r="Q13">
         <v>100</v>
       </c>
       <c r="R13">
+        <v>100</v>
+      </c>
+      <c r="S13">
+        <v>100</v>
+      </c>
+      <c r="T13">
         <v>85.90000000000001</v>
       </c>
-      <c r="S13">
+      <c r="U13">
         <v>89.59999999999999</v>
       </c>
-      <c r="T13">
-        <v>100</v>
-      </c>
-      <c r="U13">
-        <v>100</v>
-      </c>
       <c r="V13">
+        <v>100</v>
+      </c>
+      <c r="W13">
+        <v>100</v>
+      </c>
+      <c r="X13">
         <v>90.5</v>
       </c>
-    </row>
-    <row r="14" spans="1:22">
+      <c r="Y13">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="14" spans="1:25">
       <c r="A14" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B14">
         <v>80</v>
@@ -5141,17 +5727,17 @@
         <v>85</v>
       </c>
       <c r="I14">
+        <v>100</v>
+      </c>
+      <c r="J14">
         <v>90</v>
       </c>
-      <c r="J14">
-        <v>100</v>
-      </c>
       <c r="K14">
+        <v>100</v>
+      </c>
+      <c r="L14">
         <v>95.5</v>
       </c>
-      <c r="L14">
-        <v>100</v>
-      </c>
       <c r="M14">
         <v>100</v>
       </c>
@@ -5159,10 +5745,10 @@
         <v>100</v>
       </c>
       <c r="O14">
+        <v>100</v>
+      </c>
+      <c r="P14">
         <v>92.3</v>
-      </c>
-      <c r="P14">
-        <v>93.8</v>
       </c>
       <c r="Q14">
         <v>100</v>
@@ -5174,18 +5760,27 @@
         <v>100</v>
       </c>
       <c r="T14">
+        <v>93.8</v>
+      </c>
+      <c r="U14">
+        <v>100</v>
+      </c>
+      <c r="V14">
         <v>98.3</v>
       </c>
-      <c r="U14">
-        <v>100</v>
-      </c>
-      <c r="V14">
+      <c r="W14">
+        <v>100</v>
+      </c>
+      <c r="X14">
         <v>88.90000000000001</v>
       </c>
-    </row>
-    <row r="15" spans="1:22">
+      <c r="Y14">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="15" spans="1:25">
       <c r="A15" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B15">
         <v>80</v>
@@ -5209,51 +5804,60 @@
         <v>80</v>
       </c>
       <c r="I15">
+        <v>100</v>
+      </c>
+      <c r="J15">
         <v>80</v>
       </c>
-      <c r="J15">
-        <v>100</v>
-      </c>
       <c r="K15">
+        <v>100</v>
+      </c>
+      <c r="L15">
         <v>97.7</v>
       </c>
-      <c r="L15">
+      <c r="M15">
         <v>93.8</v>
       </c>
-      <c r="M15">
-        <v>100</v>
-      </c>
       <c r="N15">
         <v>100</v>
       </c>
       <c r="O15">
+        <v>100</v>
+      </c>
+      <c r="P15">
         <v>87.2</v>
       </c>
-      <c r="P15">
+      <c r="Q15">
+        <v>100</v>
+      </c>
+      <c r="R15">
         <v>87.5</v>
       </c>
-      <c r="Q15">
-        <v>100</v>
-      </c>
-      <c r="R15">
+      <c r="S15">
+        <v>100</v>
+      </c>
+      <c r="T15">
         <v>96.90000000000001</v>
       </c>
-      <c r="S15">
+      <c r="U15">
         <v>91.7</v>
       </c>
-      <c r="T15">
-        <v>100</v>
-      </c>
-      <c r="U15">
-        <v>100</v>
-      </c>
       <c r="V15">
+        <v>100</v>
+      </c>
+      <c r="W15">
+        <v>100</v>
+      </c>
+      <c r="X15">
         <v>88.90000000000001</v>
       </c>
-    </row>
-    <row r="16" spans="1:22">
+      <c r="Y15">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="16" spans="1:25">
       <c r="A16" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B16">
         <v>80</v>
@@ -5277,51 +5881,60 @@
         <v>80</v>
       </c>
       <c r="I16">
+        <v>100</v>
+      </c>
+      <c r="J16">
         <v>80</v>
       </c>
-      <c r="J16">
-        <v>100</v>
-      </c>
       <c r="K16">
+        <v>100</v>
+      </c>
+      <c r="L16">
         <v>86.40000000000001</v>
       </c>
-      <c r="L16">
+      <c r="M16">
         <v>93.8</v>
       </c>
-      <c r="M16">
+      <c r="N16">
         <v>95</v>
       </c>
-      <c r="N16">
-        <v>100</v>
-      </c>
       <c r="O16">
+        <v>100</v>
+      </c>
+      <c r="P16">
         <v>76.90000000000001</v>
       </c>
-      <c r="P16">
+      <c r="Q16">
+        <v>100</v>
+      </c>
+      <c r="R16">
         <v>87.5</v>
       </c>
-      <c r="Q16">
-        <v>100</v>
-      </c>
-      <c r="R16">
+      <c r="S16">
+        <v>100</v>
+      </c>
+      <c r="T16">
         <v>84.40000000000001</v>
       </c>
-      <c r="S16">
+      <c r="U16">
         <v>89.59999999999999</v>
       </c>
-      <c r="T16">
+      <c r="V16">
         <v>95</v>
       </c>
-      <c r="U16">
+      <c r="W16">
         <v>77.8</v>
       </c>
-      <c r="V16">
+      <c r="X16">
         <v>79.40000000000001</v>
       </c>
-    </row>
-    <row r="17" spans="1:22">
+      <c r="Y16">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="17" spans="1:25">
       <c r="A17" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B17">
         <v>100</v>
@@ -5351,11 +5964,11 @@
         <v>100</v>
       </c>
       <c r="K17">
+        <v>100</v>
+      </c>
+      <c r="L17">
         <v>93.2</v>
       </c>
-      <c r="L17">
-        <v>100</v>
-      </c>
       <c r="M17">
         <v>100</v>
       </c>
@@ -5363,33 +5976,42 @@
         <v>100</v>
       </c>
       <c r="O17">
+        <v>100</v>
+      </c>
+      <c r="P17">
         <v>92.3</v>
       </c>
-      <c r="P17">
-        <v>100</v>
-      </c>
       <c r="Q17">
         <v>100</v>
       </c>
       <c r="R17">
+        <v>100</v>
+      </c>
+      <c r="S17">
+        <v>100</v>
+      </c>
+      <c r="T17">
         <v>90.59999999999999</v>
       </c>
-      <c r="S17">
-        <v>100</v>
-      </c>
-      <c r="T17">
-        <v>100</v>
-      </c>
       <c r="U17">
         <v>100</v>
       </c>
       <c r="V17">
+        <v>100</v>
+      </c>
+      <c r="W17">
+        <v>100</v>
+      </c>
+      <c r="X17">
         <v>95.2</v>
       </c>
-    </row>
-    <row r="18" spans="1:22">
+      <c r="Y17">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="18" spans="1:25">
       <c r="A18" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B18">
         <v>80</v>
@@ -5413,51 +6035,60 @@
         <v>90</v>
       </c>
       <c r="I18">
+        <v>100</v>
+      </c>
+      <c r="J18">
         <v>80</v>
       </c>
-      <c r="J18">
-        <v>100</v>
-      </c>
       <c r="K18">
+        <v>100</v>
+      </c>
+      <c r="L18">
         <v>95.5</v>
       </c>
-      <c r="L18">
+      <c r="M18">
         <v>96.90000000000001</v>
       </c>
-      <c r="M18">
-        <v>100</v>
-      </c>
       <c r="N18">
         <v>100</v>
       </c>
       <c r="O18">
+        <v>100</v>
+      </c>
+      <c r="P18">
         <v>94.90000000000001</v>
       </c>
-      <c r="P18">
+      <c r="Q18">
+        <v>100</v>
+      </c>
+      <c r="R18">
         <v>87.5</v>
       </c>
-      <c r="Q18">
-        <v>100</v>
-      </c>
-      <c r="R18">
+      <c r="S18">
+        <v>100</v>
+      </c>
+      <c r="T18">
         <v>96.90000000000001</v>
       </c>
-      <c r="S18">
+      <c r="U18">
         <v>97.90000000000001</v>
       </c>
-      <c r="T18">
-        <v>100</v>
-      </c>
-      <c r="U18">
-        <v>100</v>
-      </c>
       <c r="V18">
+        <v>100</v>
+      </c>
+      <c r="W18">
+        <v>100</v>
+      </c>
+      <c r="X18">
         <v>93.7</v>
       </c>
-    </row>
-    <row r="19" spans="1:22">
+      <c r="Y18">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="19" spans="1:25">
       <c r="A19" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B19">
         <v>80</v>
@@ -5481,28 +6112,28 @@
         <v>80</v>
       </c>
       <c r="I19">
+        <v>100</v>
+      </c>
+      <c r="J19">
         <v>80</v>
       </c>
-      <c r="J19">
-        <v>100</v>
-      </c>
       <c r="K19">
+        <v>100</v>
+      </c>
+      <c r="L19">
         <v>86.40000000000001</v>
       </c>
-      <c r="L19">
+      <c r="M19">
         <v>96.90000000000001</v>
       </c>
-      <c r="M19">
+      <c r="N19">
         <v>87.5</v>
       </c>
-      <c r="N19">
-        <v>100</v>
-      </c>
       <c r="O19">
+        <v>100</v>
+      </c>
+      <c r="P19">
         <v>76.90000000000001</v>
-      </c>
-      <c r="P19">
-        <v>87.5</v>
       </c>
       <c r="Q19">
         <v>100</v>
@@ -5511,21 +6142,30 @@
         <v>87.5</v>
       </c>
       <c r="S19">
+        <v>100</v>
+      </c>
+      <c r="T19">
+        <v>87.5</v>
+      </c>
+      <c r="U19">
         <v>97.90000000000001</v>
       </c>
-      <c r="T19">
+      <c r="V19">
         <v>90</v>
       </c>
-      <c r="U19">
-        <v>100</v>
-      </c>
-      <c r="V19">
+      <c r="W19">
+        <v>100</v>
+      </c>
+      <c r="X19">
         <v>85.7</v>
       </c>
-    </row>
-    <row r="20" spans="1:22">
+      <c r="Y19">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="20" spans="1:25">
       <c r="A20" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B20">
         <v>50</v>
@@ -5549,51 +6189,60 @@
         <v>80</v>
       </c>
       <c r="I20">
+        <v>100</v>
+      </c>
+      <c r="J20">
         <v>25</v>
       </c>
-      <c r="J20">
+      <c r="K20">
         <v>80</v>
       </c>
-      <c r="K20">
+      <c r="L20">
         <v>34.1</v>
       </c>
-      <c r="L20">
+      <c r="M20">
         <v>50</v>
       </c>
-      <c r="M20">
+      <c r="N20">
         <v>37.5</v>
       </c>
-      <c r="N20">
-        <v>100</v>
-      </c>
       <c r="O20">
+        <v>100</v>
+      </c>
+      <c r="P20">
         <v>41</v>
       </c>
-      <c r="P20">
+      <c r="Q20">
+        <v>100</v>
+      </c>
+      <c r="R20">
         <v>15.6</v>
       </c>
-      <c r="Q20">
+      <c r="S20">
         <v>86.7</v>
       </c>
-      <c r="R20">
+      <c r="T20">
         <v>23.4</v>
       </c>
-      <c r="S20">
+      <c r="U20">
         <v>33.3</v>
       </c>
-      <c r="T20">
+      <c r="V20">
         <v>25</v>
       </c>
-      <c r="U20">
-        <v>100</v>
-      </c>
-      <c r="V20">
+      <c r="W20">
+        <v>100</v>
+      </c>
+      <c r="X20">
         <v>25.4</v>
       </c>
-    </row>
-    <row r="21" spans="1:22">
+      <c r="Y20">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="21" spans="1:25">
       <c r="A21" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B21">
         <v>90</v>
@@ -5617,17 +6266,17 @@
         <v>95</v>
       </c>
       <c r="I21">
+        <v>100</v>
+      </c>
+      <c r="J21">
         <v>95</v>
       </c>
-      <c r="J21">
-        <v>100</v>
-      </c>
       <c r="K21">
+        <v>100</v>
+      </c>
+      <c r="L21">
         <v>88.59999999999999</v>
       </c>
-      <c r="L21">
-        <v>100</v>
-      </c>
       <c r="M21">
         <v>100</v>
       </c>
@@ -5635,33 +6284,42 @@
         <v>100</v>
       </c>
       <c r="O21">
+        <v>100</v>
+      </c>
+      <c r="P21">
         <v>94.90000000000001</v>
       </c>
-      <c r="P21">
+      <c r="Q21">
+        <v>100</v>
+      </c>
+      <c r="R21">
         <v>96.90000000000001</v>
       </c>
-      <c r="Q21">
-        <v>100</v>
-      </c>
-      <c r="R21">
+      <c r="S21">
+        <v>100</v>
+      </c>
+      <c r="T21">
         <v>89.09999999999999</v>
       </c>
-      <c r="S21">
+      <c r="U21">
         <v>93.8</v>
       </c>
-      <c r="T21">
-        <v>100</v>
-      </c>
-      <c r="U21">
-        <v>100</v>
-      </c>
       <c r="V21">
+        <v>100</v>
+      </c>
+      <c r="W21">
+        <v>100</v>
+      </c>
+      <c r="X21">
         <v>96.8</v>
       </c>
-    </row>
-    <row r="22" spans="1:22">
+      <c r="Y21">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="22" spans="1:25">
       <c r="A22" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B22">
         <v>80</v>
@@ -5685,17 +6343,17 @@
         <v>90</v>
       </c>
       <c r="I22">
+        <v>100</v>
+      </c>
+      <c r="J22">
         <v>90</v>
       </c>
-      <c r="J22">
-        <v>100</v>
-      </c>
       <c r="K22">
+        <v>100</v>
+      </c>
+      <c r="L22">
         <v>93.2</v>
       </c>
-      <c r="L22">
-        <v>100</v>
-      </c>
       <c r="M22">
         <v>100</v>
       </c>
@@ -5703,33 +6361,42 @@
         <v>100</v>
       </c>
       <c r="O22">
+        <v>100</v>
+      </c>
+      <c r="P22">
         <v>87.2</v>
       </c>
-      <c r="P22">
+      <c r="Q22">
+        <v>100</v>
+      </c>
+      <c r="R22">
         <v>93.8</v>
       </c>
-      <c r="Q22">
-        <v>100</v>
-      </c>
-      <c r="R22">
+      <c r="S22">
+        <v>100</v>
+      </c>
+      <c r="T22">
         <v>90.59999999999999</v>
       </c>
-      <c r="S22">
-        <v>100</v>
-      </c>
-      <c r="T22">
+      <c r="U22">
+        <v>100</v>
+      </c>
+      <c r="V22">
         <v>98.3</v>
       </c>
-      <c r="U22">
-        <v>100</v>
-      </c>
-      <c r="V22">
+      <c r="W22">
+        <v>100</v>
+      </c>
+      <c r="X22">
         <v>90.5</v>
       </c>
-    </row>
-    <row r="23" spans="1:22">
+      <c r="Y22">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="23" spans="1:25">
       <c r="A23" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B23">
         <v>100</v>
@@ -5759,45 +6426,54 @@
         <v>100</v>
       </c>
       <c r="K23">
+        <v>100</v>
+      </c>
+      <c r="L23">
         <v>88.59999999999999</v>
       </c>
-      <c r="L23">
+      <c r="M23">
         <v>93.8</v>
       </c>
-      <c r="M23">
-        <v>100</v>
-      </c>
       <c r="N23">
         <v>100</v>
       </c>
       <c r="O23">
+        <v>100</v>
+      </c>
+      <c r="P23">
         <v>89.7</v>
       </c>
-      <c r="P23">
-        <v>100</v>
-      </c>
       <c r="Q23">
         <v>100</v>
       </c>
       <c r="R23">
+        <v>100</v>
+      </c>
+      <c r="S23">
+        <v>100</v>
+      </c>
+      <c r="T23">
         <v>90.59999999999999</v>
       </c>
-      <c r="S23">
+      <c r="U23">
         <v>95.8</v>
       </c>
-      <c r="T23">
+      <c r="V23">
         <v>98.3</v>
       </c>
-      <c r="U23">
-        <v>100</v>
-      </c>
-      <c r="V23">
+      <c r="W23">
+        <v>100</v>
+      </c>
+      <c r="X23">
         <v>90.5</v>
       </c>
-    </row>
-    <row r="24" spans="1:22">
+      <c r="Y23">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="24" spans="1:25">
       <c r="A24" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B24">
         <v>100</v>
@@ -5827,45 +6503,54 @@
         <v>100</v>
       </c>
       <c r="K24">
+        <v>100</v>
+      </c>
+      <c r="L24">
         <v>86.40000000000001</v>
       </c>
-      <c r="L24">
+      <c r="M24">
         <v>93.8</v>
       </c>
-      <c r="M24">
-        <v>100</v>
-      </c>
       <c r="N24">
         <v>100</v>
       </c>
       <c r="O24">
+        <v>100</v>
+      </c>
+      <c r="P24">
         <v>94.90000000000001</v>
       </c>
-      <c r="P24">
-        <v>100</v>
-      </c>
       <c r="Q24">
         <v>100</v>
       </c>
       <c r="R24">
+        <v>100</v>
+      </c>
+      <c r="S24">
+        <v>100</v>
+      </c>
+      <c r="T24">
         <v>85.90000000000001</v>
       </c>
-      <c r="S24">
+      <c r="U24">
         <v>95.8</v>
       </c>
-      <c r="T24">
+      <c r="V24">
         <v>98.3</v>
       </c>
-      <c r="U24">
-        <v>100</v>
-      </c>
-      <c r="V24">
+      <c r="W24">
+        <v>100</v>
+      </c>
+      <c r="X24">
         <v>96.8</v>
       </c>
-    </row>
-    <row r="25" spans="1:22">
+      <c r="Y24">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="25" spans="1:25">
       <c r="A25" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B25">
         <v>100</v>
@@ -5895,11 +6580,11 @@
         <v>100</v>
       </c>
       <c r="K25">
+        <v>100</v>
+      </c>
+      <c r="L25">
         <v>95.5</v>
       </c>
-      <c r="L25">
-        <v>100</v>
-      </c>
       <c r="M25">
         <v>100</v>
       </c>
@@ -5907,33 +6592,42 @@
         <v>100</v>
       </c>
       <c r="O25">
+        <v>100</v>
+      </c>
+      <c r="P25">
         <v>97.40000000000001</v>
       </c>
-      <c r="P25">
-        <v>100</v>
-      </c>
       <c r="Q25">
         <v>100</v>
       </c>
       <c r="R25">
+        <v>100</v>
+      </c>
+      <c r="S25">
+        <v>100</v>
+      </c>
+      <c r="T25">
         <v>89.09999999999999</v>
       </c>
-      <c r="S25">
+      <c r="U25">
         <v>95.8</v>
       </c>
-      <c r="T25">
+      <c r="V25">
         <v>98.3</v>
       </c>
-      <c r="U25">
-        <v>100</v>
-      </c>
-      <c r="V25">
+      <c r="W25">
+        <v>100</v>
+      </c>
+      <c r="X25">
         <v>98.40000000000001</v>
       </c>
-    </row>
-    <row r="26" spans="1:22">
+      <c r="Y25">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="26" spans="1:25">
       <c r="A26" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B26">
         <v>80</v>
@@ -5957,51 +6651,60 @@
         <v>80</v>
       </c>
       <c r="I26">
+        <v>100</v>
+      </c>
+      <c r="J26">
         <v>90</v>
       </c>
-      <c r="J26">
-        <v>100</v>
-      </c>
       <c r="K26">
+        <v>100</v>
+      </c>
+      <c r="L26">
         <v>84.09999999999999</v>
       </c>
-      <c r="L26">
+      <c r="M26">
         <v>93.8</v>
       </c>
-      <c r="M26">
-        <v>100</v>
-      </c>
       <c r="N26">
         <v>100</v>
       </c>
       <c r="O26">
+        <v>100</v>
+      </c>
+      <c r="P26">
         <v>84.59999999999999</v>
       </c>
-      <c r="P26">
+      <c r="Q26">
+        <v>100</v>
+      </c>
+      <c r="R26">
         <v>93.8</v>
       </c>
-      <c r="Q26">
-        <v>100</v>
-      </c>
-      <c r="R26">
+      <c r="S26">
+        <v>100</v>
+      </c>
+      <c r="T26">
         <v>82.8</v>
       </c>
-      <c r="S26">
+      <c r="U26">
         <v>89.59999999999999</v>
       </c>
-      <c r="T26">
-        <v>100</v>
-      </c>
-      <c r="U26">
-        <v>100</v>
-      </c>
       <c r="V26">
+        <v>100</v>
+      </c>
+      <c r="W26">
+        <v>100</v>
+      </c>
+      <c r="X26">
         <v>84.09999999999999</v>
       </c>
-    </row>
-    <row r="27" spans="1:22">
+      <c r="Y26">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="27" spans="1:25">
       <c r="A27" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B27">
         <v>100</v>
@@ -6031,11 +6734,11 @@
         <v>100</v>
       </c>
       <c r="K27">
+        <v>100</v>
+      </c>
+      <c r="L27">
         <v>90.90000000000001</v>
       </c>
-      <c r="L27">
-        <v>100</v>
-      </c>
       <c r="M27">
         <v>100</v>
       </c>
@@ -6052,24 +6755,33 @@
         <v>100</v>
       </c>
       <c r="R27">
+        <v>100</v>
+      </c>
+      <c r="S27">
+        <v>100</v>
+      </c>
+      <c r="T27">
         <v>93.8</v>
       </c>
-      <c r="S27">
-        <v>100</v>
-      </c>
-      <c r="T27">
-        <v>100</v>
-      </c>
       <c r="U27">
         <v>100</v>
       </c>
       <c r="V27">
+        <v>100</v>
+      </c>
+      <c r="W27">
+        <v>100</v>
+      </c>
+      <c r="X27">
         <v>96.8</v>
       </c>
-    </row>
-    <row r="28" spans="1:22">
+      <c r="Y27">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="28" spans="1:25">
       <c r="A28" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B28">
         <v>100</v>
@@ -6099,14 +6811,14 @@
         <v>100</v>
       </c>
       <c r="K28">
+        <v>100</v>
+      </c>
+      <c r="L28">
         <v>95.5</v>
       </c>
-      <c r="L28">
+      <c r="M28">
         <v>96.90000000000001</v>
       </c>
-      <c r="M28">
-        <v>100</v>
-      </c>
       <c r="N28">
         <v>100</v>
       </c>
@@ -6120,24 +6832,33 @@
         <v>100</v>
       </c>
       <c r="R28">
+        <v>100</v>
+      </c>
+      <c r="S28">
+        <v>100</v>
+      </c>
+      <c r="T28">
         <v>96.90000000000001</v>
       </c>
-      <c r="S28">
+      <c r="U28">
         <v>97.90000000000001</v>
       </c>
-      <c r="T28">
-        <v>100</v>
-      </c>
-      <c r="U28">
-        <v>100</v>
-      </c>
       <c r="V28">
+        <v>100</v>
+      </c>
+      <c r="W28">
+        <v>100</v>
+      </c>
+      <c r="X28">
         <v>98.40000000000001</v>
       </c>
-    </row>
-    <row r="29" spans="1:22">
+      <c r="Y28">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="29" spans="1:25">
       <c r="A29" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B29">
         <v>100</v>
@@ -6167,45 +6888,54 @@
         <v>100</v>
       </c>
       <c r="K29">
+        <v>100</v>
+      </c>
+      <c r="L29">
         <v>93.2</v>
       </c>
-      <c r="L29">
+      <c r="M29">
         <v>93.8</v>
       </c>
-      <c r="M29">
-        <v>100</v>
-      </c>
       <c r="N29">
         <v>100</v>
       </c>
       <c r="O29">
+        <v>100</v>
+      </c>
+      <c r="P29">
         <v>92.3</v>
       </c>
-      <c r="P29">
-        <v>100</v>
-      </c>
       <c r="Q29">
         <v>100</v>
       </c>
       <c r="R29">
+        <v>100</v>
+      </c>
+      <c r="S29">
+        <v>100</v>
+      </c>
+      <c r="T29">
         <v>90.59999999999999</v>
       </c>
-      <c r="S29">
+      <c r="U29">
         <v>95.8</v>
       </c>
-      <c r="T29">
-        <v>100</v>
-      </c>
-      <c r="U29">
-        <v>100</v>
-      </c>
       <c r="V29">
+        <v>100</v>
+      </c>
+      <c r="W29">
+        <v>100</v>
+      </c>
+      <c r="X29">
         <v>92.09999999999999</v>
       </c>
-    </row>
-    <row r="30" spans="1:22">
+      <c r="Y29">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="30" spans="1:25">
       <c r="A30" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B30">
         <v>100</v>
@@ -6235,45 +6965,54 @@
         <v>100</v>
       </c>
       <c r="K30">
+        <v>100</v>
+      </c>
+      <c r="L30">
         <v>86.40000000000001</v>
       </c>
-      <c r="L30">
+      <c r="M30">
         <v>96.90000000000001</v>
       </c>
-      <c r="M30">
-        <v>100</v>
-      </c>
       <c r="N30">
         <v>100</v>
       </c>
       <c r="O30">
+        <v>100</v>
+      </c>
+      <c r="P30">
         <v>84.59999999999999</v>
       </c>
-      <c r="P30">
-        <v>100</v>
-      </c>
       <c r="Q30">
         <v>100</v>
       </c>
       <c r="R30">
+        <v>100</v>
+      </c>
+      <c r="S30">
+        <v>100</v>
+      </c>
+      <c r="T30">
         <v>90.59999999999999</v>
       </c>
-      <c r="S30">
+      <c r="U30">
         <v>93.8</v>
       </c>
-      <c r="T30">
-        <v>100</v>
-      </c>
-      <c r="U30">
-        <v>100</v>
-      </c>
       <c r="V30">
+        <v>100</v>
+      </c>
+      <c r="W30">
+        <v>100</v>
+      </c>
+      <c r="X30">
         <v>87.3</v>
       </c>
-    </row>
-    <row r="31" spans="1:22">
+      <c r="Y30">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="31" spans="1:25">
       <c r="A31" s="1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B31">
         <v>100</v>
@@ -6303,45 +7042,54 @@
         <v>100</v>
       </c>
       <c r="K31">
+        <v>100</v>
+      </c>
+      <c r="L31">
         <v>90.90000000000001</v>
       </c>
-      <c r="L31">
+      <c r="M31">
         <v>96.90000000000001</v>
       </c>
-      <c r="M31">
-        <v>100</v>
-      </c>
       <c r="N31">
         <v>100</v>
       </c>
       <c r="O31">
+        <v>100</v>
+      </c>
+      <c r="P31">
         <v>92.3</v>
       </c>
-      <c r="P31">
-        <v>100</v>
-      </c>
       <c r="Q31">
         <v>100</v>
       </c>
       <c r="R31">
+        <v>100</v>
+      </c>
+      <c r="S31">
+        <v>100</v>
+      </c>
+      <c r="T31">
         <v>87.5</v>
       </c>
-      <c r="S31">
+      <c r="U31">
         <v>97.90000000000001</v>
       </c>
-      <c r="T31">
-        <v>100</v>
-      </c>
-      <c r="U31">
-        <v>100</v>
-      </c>
       <c r="V31">
+        <v>100</v>
+      </c>
+      <c r="W31">
+        <v>100</v>
+      </c>
+      <c r="X31">
         <v>95.2</v>
       </c>
-    </row>
-    <row r="32" spans="1:22">
+      <c r="Y31">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="32" spans="1:25">
       <c r="A32" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B32">
         <v>0</v>
@@ -6368,48 +7116,57 @@
         <v>0</v>
       </c>
       <c r="J32">
+        <v>0</v>
+      </c>
+      <c r="K32">
         <v>80</v>
       </c>
-      <c r="K32">
+      <c r="L32">
         <v>0</v>
       </c>
-      <c r="L32">
+      <c r="M32">
         <v>50</v>
       </c>
-      <c r="M32">
+      <c r="N32">
         <v>0</v>
       </c>
-      <c r="N32">
-        <v>100</v>
-      </c>
       <c r="O32">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P32">
         <v>0</v>
       </c>
       <c r="Q32">
-        <v>86.7</v>
+        <v>0</v>
       </c>
       <c r="R32">
         <v>0</v>
       </c>
       <c r="S32">
-        <v>33.3</v>
+        <v>86.7</v>
       </c>
       <c r="T32">
         <v>0</v>
       </c>
       <c r="U32">
-        <v>100</v>
+        <v>33.3</v>
       </c>
       <c r="V32">
         <v>0</v>
       </c>
-    </row>
-    <row r="33" spans="1:22">
+      <c r="W32">
+        <v>100</v>
+      </c>
+      <c r="X32">
+        <v>0</v>
+      </c>
+      <c r="Y32">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="1:25">
       <c r="A33" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B33">
         <v>80</v>
@@ -6433,17 +7190,17 @@
         <v>90</v>
       </c>
       <c r="I33">
+        <v>100</v>
+      </c>
+      <c r="J33">
         <v>90</v>
       </c>
-      <c r="J33">
-        <v>100</v>
-      </c>
       <c r="K33">
+        <v>100</v>
+      </c>
+      <c r="L33">
         <v>97.7</v>
       </c>
-      <c r="L33">
-        <v>100</v>
-      </c>
       <c r="M33">
         <v>100</v>
       </c>
@@ -6451,33 +7208,42 @@
         <v>100</v>
       </c>
       <c r="O33">
+        <v>100</v>
+      </c>
+      <c r="P33">
         <v>97.40000000000001</v>
       </c>
-      <c r="P33">
+      <c r="Q33">
+        <v>100</v>
+      </c>
+      <c r="R33">
         <v>93.8</v>
       </c>
-      <c r="Q33">
-        <v>100</v>
-      </c>
-      <c r="R33">
+      <c r="S33">
+        <v>100</v>
+      </c>
+      <c r="T33">
         <v>96.90000000000001</v>
       </c>
-      <c r="S33">
-        <v>100</v>
-      </c>
-      <c r="T33">
-        <v>100</v>
-      </c>
       <c r="U33">
         <v>100</v>
       </c>
       <c r="V33">
+        <v>100</v>
+      </c>
+      <c r="W33">
+        <v>100</v>
+      </c>
+      <c r="X33">
         <v>98.40000000000001</v>
       </c>
-    </row>
-    <row r="34" spans="1:22">
+      <c r="Y33">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="34" spans="1:25">
       <c r="A34" s="1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B34">
         <v>80</v>
@@ -6501,51 +7267,60 @@
         <v>0</v>
       </c>
       <c r="I34">
+        <v>100</v>
+      </c>
+      <c r="J34">
         <v>70</v>
       </c>
-      <c r="J34">
-        <v>100</v>
-      </c>
       <c r="K34">
+        <v>100</v>
+      </c>
+      <c r="L34">
         <v>84.09999999999999</v>
       </c>
-      <c r="L34">
+      <c r="M34">
         <v>84.40000000000001</v>
       </c>
-      <c r="M34">
-        <v>100</v>
-      </c>
       <c r="N34">
         <v>100</v>
       </c>
       <c r="O34">
+        <v>100</v>
+      </c>
+      <c r="P34">
         <v>25.6</v>
       </c>
-      <c r="P34">
+      <c r="Q34">
+        <v>100</v>
+      </c>
+      <c r="R34">
         <v>81.3</v>
       </c>
-      <c r="Q34">
-        <v>100</v>
-      </c>
-      <c r="R34">
+      <c r="S34">
+        <v>100</v>
+      </c>
+      <c r="T34">
         <v>76.59999999999999</v>
       </c>
-      <c r="S34">
+      <c r="U34">
         <v>70.8</v>
       </c>
-      <c r="T34">
+      <c r="V34">
         <v>98.3</v>
       </c>
-      <c r="U34">
-        <v>100</v>
-      </c>
-      <c r="V34">
+      <c r="W34">
+        <v>100</v>
+      </c>
+      <c r="X34">
         <v>41.3</v>
       </c>
-    </row>
-    <row r="35" spans="1:22">
+      <c r="Y34">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="35" spans="1:25">
       <c r="A35" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B35">
         <v>90</v>
@@ -6569,51 +7344,60 @@
         <v>95</v>
       </c>
       <c r="I35">
+        <v>100</v>
+      </c>
+      <c r="J35">
         <v>95</v>
       </c>
-      <c r="J35">
-        <v>100</v>
-      </c>
       <c r="K35">
+        <v>100</v>
+      </c>
+      <c r="L35">
         <v>56.8</v>
       </c>
-      <c r="L35">
+      <c r="M35">
         <v>96.90000000000001</v>
       </c>
-      <c r="M35">
-        <v>100</v>
-      </c>
       <c r="N35">
         <v>100</v>
       </c>
       <c r="O35">
+        <v>100</v>
+      </c>
+      <c r="P35">
         <v>97.40000000000001</v>
       </c>
-      <c r="P35">
+      <c r="Q35">
+        <v>100</v>
+      </c>
+      <c r="R35">
         <v>96.90000000000001</v>
       </c>
-      <c r="Q35">
-        <v>100</v>
-      </c>
-      <c r="R35">
+      <c r="S35">
+        <v>100</v>
+      </c>
+      <c r="T35">
         <v>70.3</v>
       </c>
-      <c r="S35">
+      <c r="U35">
         <v>97.90000000000001</v>
       </c>
-      <c r="T35">
-        <v>100</v>
-      </c>
-      <c r="U35">
-        <v>100</v>
-      </c>
       <c r="V35">
+        <v>100</v>
+      </c>
+      <c r="W35">
+        <v>100</v>
+      </c>
+      <c r="X35">
         <v>95.2</v>
       </c>
-    </row>
-    <row r="36" spans="1:22">
+      <c r="Y35">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="36" spans="1:25">
       <c r="A36" s="1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B36">
         <v>80</v>
@@ -6637,51 +7421,60 @@
         <v>80</v>
       </c>
       <c r="I36">
+        <v>100</v>
+      </c>
+      <c r="J36">
         <v>70</v>
       </c>
-      <c r="J36">
+      <c r="K36">
         <v>76.7</v>
       </c>
-      <c r="K36">
+      <c r="L36">
         <v>84.09999999999999</v>
       </c>
-      <c r="L36">
+      <c r="M36">
         <v>81.3</v>
       </c>
-      <c r="M36">
+      <c r="N36">
         <v>90</v>
       </c>
-      <c r="N36">
-        <v>100</v>
-      </c>
       <c r="O36">
+        <v>100</v>
+      </c>
+      <c r="P36">
         <v>74.40000000000001</v>
       </c>
-      <c r="P36">
+      <c r="Q36">
+        <v>100</v>
+      </c>
+      <c r="R36">
         <v>81.3</v>
       </c>
-      <c r="Q36">
+      <c r="S36">
         <v>84.40000000000001</v>
       </c>
-      <c r="R36">
+      <c r="T36">
         <v>78.09999999999999</v>
       </c>
-      <c r="S36">
+      <c r="U36">
         <v>58.3</v>
       </c>
-      <c r="T36">
+      <c r="V36">
         <v>91.7</v>
       </c>
-      <c r="U36">
-        <v>100</v>
-      </c>
-      <c r="V36">
+      <c r="W36">
+        <v>100</v>
+      </c>
+      <c r="X36">
         <v>73</v>
       </c>
-    </row>
-    <row r="37" spans="1:22">
+      <c r="Y36">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="37" spans="1:25">
       <c r="A37" s="1" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B37">
         <v>100</v>
@@ -6711,45 +7504,54 @@
         <v>100</v>
       </c>
       <c r="K37">
+        <v>100</v>
+      </c>
+      <c r="L37">
         <v>97.7</v>
       </c>
-      <c r="L37">
+      <c r="M37">
         <v>93.8</v>
       </c>
-      <c r="M37">
-        <v>100</v>
-      </c>
       <c r="N37">
         <v>100</v>
       </c>
       <c r="O37">
+        <v>100</v>
+      </c>
+      <c r="P37">
         <v>92.3</v>
       </c>
-      <c r="P37">
-        <v>100</v>
-      </c>
       <c r="Q37">
         <v>100</v>
       </c>
       <c r="R37">
+        <v>100</v>
+      </c>
+      <c r="S37">
+        <v>100</v>
+      </c>
+      <c r="T37">
         <v>92.2</v>
       </c>
-      <c r="S37">
+      <c r="U37">
         <v>91.7</v>
       </c>
-      <c r="T37">
+      <c r="V37">
         <v>98.3</v>
       </c>
-      <c r="U37">
-        <v>100</v>
-      </c>
-      <c r="V37">
+      <c r="W37">
+        <v>100</v>
+      </c>
+      <c r="X37">
         <v>92.09999999999999</v>
       </c>
-    </row>
-    <row r="38" spans="1:22">
+      <c r="Y37">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="38" spans="1:25">
       <c r="A38" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B38">
         <v>80</v>
@@ -6773,17 +7575,17 @@
         <v>80</v>
       </c>
       <c r="I38">
+        <v>100</v>
+      </c>
+      <c r="J38">
         <v>90</v>
       </c>
-      <c r="J38">
-        <v>100</v>
-      </c>
       <c r="K38">
+        <v>100</v>
+      </c>
+      <c r="L38">
         <v>97.7</v>
       </c>
-      <c r="L38">
-        <v>100</v>
-      </c>
       <c r="M38">
         <v>100</v>
       </c>
@@ -6791,33 +7593,42 @@
         <v>100</v>
       </c>
       <c r="O38">
+        <v>100</v>
+      </c>
+      <c r="P38">
         <v>89.7</v>
       </c>
-      <c r="P38">
+      <c r="Q38">
+        <v>100</v>
+      </c>
+      <c r="R38">
         <v>93.8</v>
       </c>
-      <c r="Q38">
-        <v>100</v>
-      </c>
-      <c r="R38">
+      <c r="S38">
+        <v>100</v>
+      </c>
+      <c r="T38">
         <v>92.2</v>
       </c>
-      <c r="S38">
+      <c r="U38">
         <v>93.8</v>
       </c>
-      <c r="T38">
+      <c r="V38">
         <v>98.3</v>
       </c>
-      <c r="U38">
-        <v>100</v>
-      </c>
-      <c r="V38">
+      <c r="W38">
+        <v>100</v>
+      </c>
+      <c r="X38">
         <v>90.5</v>
       </c>
-    </row>
-    <row r="39" spans="1:22">
+      <c r="Y38">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="39" spans="1:25">
       <c r="A39" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B39">
         <v>100</v>
@@ -6847,14 +7658,14 @@
         <v>100</v>
       </c>
       <c r="K39">
+        <v>100</v>
+      </c>
+      <c r="L39">
         <v>95.5</v>
       </c>
-      <c r="L39">
+      <c r="M39">
         <v>96.90000000000001</v>
       </c>
-      <c r="M39">
-        <v>100</v>
-      </c>
       <c r="N39">
         <v>100</v>
       </c>
@@ -6868,24 +7679,33 @@
         <v>100</v>
       </c>
       <c r="R39">
+        <v>100</v>
+      </c>
+      <c r="S39">
+        <v>100</v>
+      </c>
+      <c r="T39">
         <v>90.59999999999999</v>
       </c>
-      <c r="S39">
+      <c r="U39">
         <v>93.8</v>
       </c>
-      <c r="T39">
-        <v>100</v>
-      </c>
-      <c r="U39">
-        <v>100</v>
-      </c>
       <c r="V39">
+        <v>100</v>
+      </c>
+      <c r="W39">
+        <v>100</v>
+      </c>
+      <c r="X39">
         <v>96.8</v>
       </c>
-    </row>
-    <row r="40" spans="1:22">
+      <c r="Y39">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="40" spans="1:25">
       <c r="A40" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B40">
         <v>100</v>
@@ -6915,45 +7735,54 @@
         <v>100</v>
       </c>
       <c r="K40">
+        <v>100</v>
+      </c>
+      <c r="L40">
         <v>97.7</v>
       </c>
-      <c r="L40">
+      <c r="M40">
         <v>93.8</v>
       </c>
-      <c r="M40">
-        <v>100</v>
-      </c>
       <c r="N40">
         <v>100</v>
       </c>
       <c r="O40">
+        <v>100</v>
+      </c>
+      <c r="P40">
         <v>94.90000000000001</v>
       </c>
-      <c r="P40">
-        <v>100</v>
-      </c>
       <c r="Q40">
         <v>100</v>
       </c>
       <c r="R40">
+        <v>100</v>
+      </c>
+      <c r="S40">
+        <v>100</v>
+      </c>
+      <c r="T40">
         <v>90.59999999999999</v>
       </c>
-      <c r="S40">
+      <c r="U40">
         <v>95.8</v>
       </c>
-      <c r="T40">
-        <v>100</v>
-      </c>
-      <c r="U40">
-        <v>100</v>
-      </c>
       <c r="V40">
+        <v>100</v>
+      </c>
+      <c r="W40">
+        <v>100</v>
+      </c>
+      <c r="X40">
         <v>96.8</v>
       </c>
-    </row>
-    <row r="41" spans="1:22">
+      <c r="Y40">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="41" spans="1:25">
       <c r="A41" s="1" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B41">
         <v>100</v>
@@ -7018,10 +7847,19 @@
       <c r="V41">
         <v>100</v>
       </c>
-    </row>
-    <row r="42" spans="1:22">
+      <c r="W41">
+        <v>100</v>
+      </c>
+      <c r="X41">
+        <v>100</v>
+      </c>
+      <c r="Y41">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="42" spans="1:25">
       <c r="A42" s="1" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B42">
         <v>80</v>
@@ -7045,53 +7883,62 @@
         <v>85</v>
       </c>
       <c r="I42">
+        <v>0</v>
+      </c>
+      <c r="J42">
         <v>80</v>
       </c>
-      <c r="J42">
-        <v>100</v>
-      </c>
       <c r="K42">
+        <v>100</v>
+      </c>
+      <c r="L42">
         <v>81.8</v>
       </c>
-      <c r="L42">
+      <c r="M42">
         <v>84.40000000000001</v>
       </c>
-      <c r="M42">
+      <c r="N42">
         <v>90</v>
       </c>
-      <c r="N42">
-        <v>100</v>
-      </c>
       <c r="O42">
+        <v>100</v>
+      </c>
+      <c r="P42">
         <v>74.40000000000001</v>
       </c>
-      <c r="P42">
+      <c r="Q42">
+        <v>0</v>
+      </c>
+      <c r="R42">
         <v>50</v>
       </c>
-      <c r="Q42">
+      <c r="S42">
         <v>77.8</v>
       </c>
-      <c r="R42">
+      <c r="T42">
         <v>56.3</v>
       </c>
-      <c r="S42">
+      <c r="U42">
         <v>56.3</v>
       </c>
-      <c r="T42">
+      <c r="V42">
         <v>90</v>
       </c>
-      <c r="U42">
-        <v>100</v>
-      </c>
-      <c r="V42">
+      <c r="W42">
+        <v>100</v>
+      </c>
+      <c r="X42">
         <v>46</v>
+      </c>
+      <c r="Y42">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="3">
-    <mergeCell ref="B1:H1"/>
-    <mergeCell ref="I1:O1"/>
-    <mergeCell ref="P1:V1"/>
+    <mergeCell ref="B1:I1"/>
+    <mergeCell ref="J1:Q1"/>
+    <mergeCell ref="R1:Y1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -7112,31 +7959,31 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="2" spans="1:10">
@@ -7365,21 +8212,33 @@
     </row>
     <row r="9" spans="1:10">
       <c r="A9" t="s">
-        <v>64</v>
+        <v>12</v>
       </c>
       <c r="B9" t="s">
         <v>70</v>
       </c>
       <c r="C9">
+        <v>39</v>
+      </c>
+      <c r="D9">
+        <v>37</v>
+      </c>
+      <c r="E9">
+        <v>2</v>
+      </c>
+      <c r="F9" s="2">
+        <v>94.90000000000001</v>
+      </c>
+      <c r="G9" s="2">
+        <v>5.1</v>
+      </c>
+      <c r="H9">
+        <v>9.699999999999999</v>
+      </c>
+      <c r="I9">
         <v>0</v>
       </c>
-      <c r="D9">
-        <v>0</v>
-      </c>
-      <c r="E9">
-        <v>0</v>
-      </c>
-      <c r="I9">
+      <c r="J9" s="2">
         <v>0</v>
       </c>
     </row>
@@ -7414,7 +8273,7 @@
         <v>0</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
   </sheetData>
@@ -7448,7 +8307,7 @@
         <v>0</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>4</v>

--- a/grupos/1CV - Estadisticos 20231.xlsx
+++ b/grupos/1CV - Estadisticos 20231.xlsx
@@ -938,7 +938,7 @@
         <v>5</v>
       </c>
       <c r="AA4">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AB4">
         <v>5</v>
@@ -1036,25 +1036,25 @@
         <v>10</v>
       </c>
       <c r="Z5">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AA5">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AB5">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AC5">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AD5">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AE5">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AF5">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AG5">
         <v>10</v>
@@ -1137,13 +1137,13 @@
         <v>10</v>
       </c>
       <c r="Z6">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AA6">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AB6">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AC6">
         <v>5</v>
@@ -1152,7 +1152,7 @@
         <v>5</v>
       </c>
       <c r="AE6">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AF6">
         <v>5</v>
@@ -1238,22 +1238,22 @@
         <v>10</v>
       </c>
       <c r="Z7">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AA7">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AB7">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AC7">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AD7">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AE7">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AF7">
         <v>5</v>
@@ -1339,25 +1339,25 @@
         <v>10</v>
       </c>
       <c r="Z8">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AA8">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AB8">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AC8">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AD8">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AE8">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AF8">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AG8">
         <v>10</v>
@@ -1440,25 +1440,25 @@
         <v>10</v>
       </c>
       <c r="Z9">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AA9">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AB9">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AC9">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AD9">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AE9">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AF9">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AG9">
         <v>10</v>
@@ -1541,25 +1541,25 @@
         <v>10</v>
       </c>
       <c r="Z10">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AA10">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AB10">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AC10">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AD10">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AE10">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AF10">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AG10">
         <v>10</v>
@@ -1642,25 +1642,25 @@
         <v>10</v>
       </c>
       <c r="Z11">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AA11">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AB11">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AC11">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AD11">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AE11">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AF11">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AG11">
         <v>10</v>
@@ -1743,25 +1743,25 @@
         <v>10</v>
       </c>
       <c r="Z12">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AA12">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AB12">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AC12">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AD12">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AE12">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AF12">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AG12">
         <v>10</v>
@@ -1844,25 +1844,25 @@
         <v>10</v>
       </c>
       <c r="Z13">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AA13">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AB13">
         <v>5</v>
       </c>
       <c r="AC13">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AD13">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AE13">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AF13">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AG13">
         <v>10</v>
@@ -1945,22 +1945,22 @@
         <v>10</v>
       </c>
       <c r="Z14">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AA14">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AB14">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AC14">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AD14">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AE14">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AF14">
         <v>5</v>
@@ -2046,25 +2046,25 @@
         <v>10</v>
       </c>
       <c r="Z15">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AA15">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AB15">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AC15">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AD15">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AE15">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AF15">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AG15">
         <v>10</v>
@@ -2147,7 +2147,7 @@
         <v>10</v>
       </c>
       <c r="Z16">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AA16">
         <v>5</v>
@@ -2156,10 +2156,10 @@
         <v>5</v>
       </c>
       <c r="AC16">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AD16">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AE16">
         <v>5</v>
@@ -2248,25 +2248,25 @@
         <v>10</v>
       </c>
       <c r="Z17">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AA17">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AB17">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AC17">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AD17">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AE17">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AF17">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AG17">
         <v>10</v>
@@ -2349,22 +2349,22 @@
         <v>10</v>
       </c>
       <c r="Z18">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AA18">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AB18">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AC18">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AD18">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AE18">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AF18">
         <v>5</v>
@@ -2450,25 +2450,25 @@
         <v>10</v>
       </c>
       <c r="Z19">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AA19">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AB19">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AC19">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AD19">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AE19">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AF19">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AG19">
         <v>10</v>
@@ -2652,25 +2652,25 @@
         <v>10</v>
       </c>
       <c r="Z21">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AA21">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AB21">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AC21">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AD21">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AE21">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AF21">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AG21">
         <v>10</v>
@@ -2753,22 +2753,22 @@
         <v>10</v>
       </c>
       <c r="Z22">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AA22">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AB22">
         <v>5</v>
       </c>
       <c r="AC22">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AD22">
         <v>5</v>
       </c>
       <c r="AE22">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AF22">
         <v>5</v>
@@ -2854,22 +2854,22 @@
         <v>10</v>
       </c>
       <c r="Z23">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AA23">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AB23">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AC23">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AD23">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AE23">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AF23">
         <v>5</v>
@@ -2955,22 +2955,22 @@
         <v>10</v>
       </c>
       <c r="Z24">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AA24">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AB24">
         <v>5</v>
       </c>
       <c r="AC24">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AD24">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AE24">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AF24">
         <v>5</v>
@@ -3056,25 +3056,25 @@
         <v>10</v>
       </c>
       <c r="Z25">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AA25">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AB25">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AC25">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AD25">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AE25">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AF25">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AG25">
         <v>10</v>
@@ -3157,25 +3157,25 @@
         <v>10</v>
       </c>
       <c r="Z26">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AA26">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AB26">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AC26">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AD26">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AE26">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AF26">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AG26">
         <v>10</v>
@@ -3258,22 +3258,22 @@
         <v>10</v>
       </c>
       <c r="Z27">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AA27">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AB27">
         <v>5</v>
       </c>
       <c r="AC27">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AD27">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AE27">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AF27">
         <v>5</v>
@@ -3359,25 +3359,25 @@
         <v>10</v>
       </c>
       <c r="Z28">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AA28">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AB28">
         <v>5</v>
       </c>
       <c r="AC28">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AD28">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AE28">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AF28">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AG28">
         <v>10</v>
@@ -3460,25 +3460,25 @@
         <v>10</v>
       </c>
       <c r="Z29">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AA29">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AB29">
         <v>5</v>
       </c>
       <c r="AC29">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AD29">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AE29">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AF29">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AG29">
         <v>10</v>
@@ -3561,25 +3561,25 @@
         <v>10</v>
       </c>
       <c r="Z30">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AA30">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AB30">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AC30">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AD30">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AE30">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AF30">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AG30">
         <v>10</v>
@@ -3662,25 +3662,25 @@
         <v>10</v>
       </c>
       <c r="Z31">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AA31">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AB31">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AC31">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AD31">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AE31">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AF31">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AG31">
         <v>10</v>
@@ -3864,25 +3864,25 @@
         <v>10</v>
       </c>
       <c r="Z33">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AA33">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AB33">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AC33">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AD33">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AE33">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AF33">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AG33">
         <v>10</v>
@@ -3965,7 +3965,7 @@
         <v>10</v>
       </c>
       <c r="Z34">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AA34">
         <v>5</v>
@@ -4069,22 +4069,22 @@
         <v>10</v>
       </c>
       <c r="AA35">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AB35">
         <v>5</v>
       </c>
       <c r="AC35">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AD35">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AE35">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AF35">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AG35">
         <v>10</v>
@@ -4268,22 +4268,22 @@
         <v>10</v>
       </c>
       <c r="Z37">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AA37">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AB37">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AC37">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AD37">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AE37">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AF37">
         <v>5</v>
@@ -4369,13 +4369,13 @@
         <v>10</v>
       </c>
       <c r="Z38">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AA38">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AB38">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AC38">
         <v>5</v>
@@ -4470,25 +4470,25 @@
         <v>10</v>
       </c>
       <c r="Z39">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AA39">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AB39">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AC39">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AD39">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AE39">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AF39">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AG39">
         <v>10</v>
@@ -4571,22 +4571,22 @@
         <v>10</v>
       </c>
       <c r="Z40">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AA40">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AB40">
         <v>5</v>
       </c>
       <c r="AC40">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AD40">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AE40">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AF40">
         <v>5</v>
@@ -4672,25 +4672,25 @@
         <v>10</v>
       </c>
       <c r="Z41">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA41">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AB41">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AC41">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AD41">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AE41">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AF41">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AG41">
         <v>10</v>
@@ -4788,7 +4788,7 @@
         <v>5</v>
       </c>
       <c r="AE42">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AF42">
         <v>5</v>
@@ -8009,7 +8009,7 @@
         <v>46.2</v>
       </c>
       <c r="H2">
-        <v>5.6</v>
+        <v>7.7</v>
       </c>
       <c r="I2">
         <v>0</v>
@@ -8041,7 +8041,7 @@
         <v>38.5</v>
       </c>
       <c r="H3">
-        <v>6.1</v>
+        <v>8.1</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -8073,7 +8073,7 @@
         <v>23.1</v>
       </c>
       <c r="H4">
-        <v>6.7</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -8105,7 +8105,7 @@
         <v>20.5</v>
       </c>
       <c r="H5">
-        <v>6.2</v>
+        <v>9</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -8137,7 +8137,7 @@
         <v>17.9</v>
       </c>
       <c r="H6">
-        <v>6.9</v>
+        <v>9.1</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -8169,7 +8169,7 @@
         <v>15.4</v>
       </c>
       <c r="H7">
-        <v>6.7</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -8201,7 +8201,7 @@
         <v>12.8</v>
       </c>
       <c r="H8">
-        <v>6.7</v>
+        <v>9.4</v>
       </c>
       <c r="I8">
         <v>0</v>

--- a/grupos/1CV - Estadisticos 20231.xlsx
+++ b/grupos/1CV - Estadisticos 20231.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="259" uniqueCount="108">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="254" uniqueCount="105">
   <si>
     <t>Materia</t>
   </si>
@@ -272,9 +272,6 @@
     <t>LUIS</t>
   </si>
   <si>
-    <t>RAMIREZ</t>
-  </si>
-  <si>
     <t>SAN JUAN</t>
   </si>
   <si>
@@ -302,9 +299,6 @@
     <t>VERA</t>
   </si>
   <si>
-    <t>MOLINA</t>
-  </si>
-  <si>
     <t>AGUILAR</t>
   </si>
   <si>
@@ -336,9 +330,6 @@
   </si>
   <si>
     <t>DIANA LAURA</t>
-  </si>
-  <si>
-    <t>AIDE SCARLET</t>
   </si>
   <si>
     <t>KARINA MONSERRATH</t>
@@ -938,7 +929,7 @@
         <v>5</v>
       </c>
       <c r="AA4">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AB4">
         <v>5</v>
@@ -1036,25 +1027,25 @@
         <v>10</v>
       </c>
       <c r="Z5">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AA5">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AB5">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AC5">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AD5">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AE5">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AF5">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AG5">
         <v>10</v>
@@ -1137,13 +1128,13 @@
         <v>10</v>
       </c>
       <c r="Z6">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AA6">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AB6">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AC6">
         <v>5</v>
@@ -1152,7 +1143,7 @@
         <v>5</v>
       </c>
       <c r="AE6">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AF6">
         <v>5</v>
@@ -1238,22 +1229,22 @@
         <v>10</v>
       </c>
       <c r="Z7">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AA7">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AB7">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AC7">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AD7">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AE7">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AF7">
         <v>5</v>
@@ -1339,25 +1330,25 @@
         <v>10</v>
       </c>
       <c r="Z8">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AA8">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AB8">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AC8">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AD8">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AE8">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AF8">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AG8">
         <v>10</v>
@@ -1440,25 +1431,25 @@
         <v>10</v>
       </c>
       <c r="Z9">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AA9">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AB9">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AC9">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AD9">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AE9">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AF9">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AG9">
         <v>10</v>
@@ -1541,25 +1532,25 @@
         <v>10</v>
       </c>
       <c r="Z10">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AA10">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AB10">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AC10">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AD10">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AE10">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AF10">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AG10">
         <v>10</v>
@@ -1642,25 +1633,25 @@
         <v>10</v>
       </c>
       <c r="Z11">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AA11">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AB11">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AC11">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AD11">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AE11">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AF11">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AG11">
         <v>10</v>
@@ -1743,25 +1734,25 @@
         <v>10</v>
       </c>
       <c r="Z12">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AA12">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AB12">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AC12">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AD12">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AE12">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AF12">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AG12">
         <v>10</v>
@@ -1844,25 +1835,25 @@
         <v>10</v>
       </c>
       <c r="Z13">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AA13">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AB13">
         <v>5</v>
       </c>
       <c r="AC13">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AD13">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AE13">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AF13">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AG13">
         <v>10</v>
@@ -1945,22 +1936,22 @@
         <v>10</v>
       </c>
       <c r="Z14">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AA14">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AB14">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AC14">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AD14">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AE14">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AF14">
         <v>5</v>
@@ -2046,25 +2037,25 @@
         <v>10</v>
       </c>
       <c r="Z15">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AA15">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AB15">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AC15">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AD15">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AE15">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AF15">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AG15">
         <v>10</v>
@@ -2147,7 +2138,7 @@
         <v>10</v>
       </c>
       <c r="Z16">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AA16">
         <v>5</v>
@@ -2156,10 +2147,10 @@
         <v>5</v>
       </c>
       <c r="AC16">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AD16">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AE16">
         <v>5</v>
@@ -2248,25 +2239,25 @@
         <v>10</v>
       </c>
       <c r="Z17">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AA17">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AB17">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AC17">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AD17">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AE17">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AF17">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AG17">
         <v>10</v>
@@ -2349,22 +2340,22 @@
         <v>10</v>
       </c>
       <c r="Z18">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AA18">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AB18">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AC18">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AD18">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AE18">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AF18">
         <v>5</v>
@@ -2450,25 +2441,25 @@
         <v>10</v>
       </c>
       <c r="Z19">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AA19">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AB19">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AC19">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AD19">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AE19">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AF19">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AG19">
         <v>10</v>
@@ -2652,25 +2643,25 @@
         <v>10</v>
       </c>
       <c r="Z21">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AA21">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AB21">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AC21">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AD21">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AE21">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AF21">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AG21">
         <v>10</v>
@@ -2753,22 +2744,22 @@
         <v>10</v>
       </c>
       <c r="Z22">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AA22">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AB22">
         <v>5</v>
       </c>
       <c r="AC22">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AD22">
         <v>5</v>
       </c>
       <c r="AE22">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AF22">
         <v>5</v>
@@ -2854,22 +2845,22 @@
         <v>10</v>
       </c>
       <c r="Z23">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AA23">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AB23">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AC23">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AD23">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AE23">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AF23">
         <v>5</v>
@@ -2955,22 +2946,22 @@
         <v>10</v>
       </c>
       <c r="Z24">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AA24">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AB24">
         <v>5</v>
       </c>
       <c r="AC24">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AD24">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AE24">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AF24">
         <v>5</v>
@@ -3056,25 +3047,25 @@
         <v>10</v>
       </c>
       <c r="Z25">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AA25">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AB25">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AC25">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AD25">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AE25">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AF25">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AG25">
         <v>10</v>
@@ -3157,25 +3148,25 @@
         <v>10</v>
       </c>
       <c r="Z26">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AA26">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AB26">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AC26">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AD26">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AE26">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AF26">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AG26">
         <v>10</v>
@@ -3258,22 +3249,22 @@
         <v>10</v>
       </c>
       <c r="Z27">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AA27">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AB27">
         <v>5</v>
       </c>
       <c r="AC27">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AD27">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AE27">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AF27">
         <v>5</v>
@@ -3359,25 +3350,25 @@
         <v>10</v>
       </c>
       <c r="Z28">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AA28">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AB28">
         <v>5</v>
       </c>
       <c r="AC28">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AD28">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AE28">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AF28">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AG28">
         <v>10</v>
@@ -3460,25 +3451,25 @@
         <v>10</v>
       </c>
       <c r="Z29">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AA29">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AB29">
         <v>5</v>
       </c>
       <c r="AC29">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AD29">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AE29">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AF29">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AG29">
         <v>10</v>
@@ -3561,25 +3552,25 @@
         <v>10</v>
       </c>
       <c r="Z30">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AA30">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AB30">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AC30">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AD30">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AE30">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AF30">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AG30">
         <v>10</v>
@@ -3662,25 +3653,25 @@
         <v>10</v>
       </c>
       <c r="Z31">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AA31">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AB31">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AC31">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AD31">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AE31">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AF31">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AG31">
         <v>10</v>
@@ -3864,25 +3855,25 @@
         <v>10</v>
       </c>
       <c r="Z33">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AA33">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AB33">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AC33">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AD33">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AE33">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AF33">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AG33">
         <v>10</v>
@@ -3965,7 +3956,7 @@
         <v>10</v>
       </c>
       <c r="Z34">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AA34">
         <v>5</v>
@@ -4069,22 +4060,22 @@
         <v>10</v>
       </c>
       <c r="AA35">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AB35">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="AC35">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AD35">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AE35">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AF35">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AG35">
         <v>10</v>
@@ -4268,22 +4259,22 @@
         <v>10</v>
       </c>
       <c r="Z37">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AA37">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AB37">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AC37">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AD37">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AE37">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AF37">
         <v>5</v>
@@ -4369,13 +4360,13 @@
         <v>10</v>
       </c>
       <c r="Z38">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AA38">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AB38">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AC38">
         <v>5</v>
@@ -4470,25 +4461,25 @@
         <v>10</v>
       </c>
       <c r="Z39">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AA39">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AB39">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AC39">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AD39">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AE39">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AF39">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AG39">
         <v>10</v>
@@ -4571,22 +4562,22 @@
         <v>10</v>
       </c>
       <c r="Z40">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AA40">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AB40">
         <v>5</v>
       </c>
       <c r="AC40">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AD40">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AE40">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AF40">
         <v>5</v>
@@ -4672,25 +4663,25 @@
         <v>10</v>
       </c>
       <c r="Z41">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AA41">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AB41">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AC41">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AD41">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AE41">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AF41">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AG41">
         <v>10</v>
@@ -4788,7 +4779,7 @@
         <v>5</v>
       </c>
       <c r="AE42">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AF42">
         <v>5</v>
@@ -7353,7 +7344,7 @@
         <v>100</v>
       </c>
       <c r="L35">
-        <v>56.8</v>
+        <v>97.7</v>
       </c>
       <c r="M35">
         <v>96.90000000000001</v>
@@ -7377,7 +7368,7 @@
         <v>100</v>
       </c>
       <c r="T35">
-        <v>70.3</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="U35">
         <v>97.90000000000001</v>
@@ -8009,7 +8000,7 @@
         <v>46.2</v>
       </c>
       <c r="H2">
-        <v>7.7</v>
+        <v>5.6</v>
       </c>
       <c r="I2">
         <v>0</v>
@@ -8029,19 +8020,19 @@
         <v>39</v>
       </c>
       <c r="D3">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E3">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F3" s="2">
-        <v>61.5</v>
+        <v>64.09999999999999</v>
       </c>
       <c r="G3" s="2">
-        <v>38.5</v>
+        <v>35.9</v>
       </c>
       <c r="H3">
-        <v>8.1</v>
+        <v>6.2</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -8073,7 +8064,7 @@
         <v>23.1</v>
       </c>
       <c r="H4">
-        <v>8.800000000000001</v>
+        <v>6.7</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -8105,7 +8096,7 @@
         <v>20.5</v>
       </c>
       <c r="H5">
-        <v>9</v>
+        <v>6.2</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -8137,7 +8128,7 @@
         <v>17.9</v>
       </c>
       <c r="H6">
-        <v>9.1</v>
+        <v>6.9</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -8169,7 +8160,7 @@
         <v>15.4</v>
       </c>
       <c r="H7">
-        <v>9.199999999999999</v>
+        <v>6.7</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -8201,7 +8192,7 @@
         <v>12.8</v>
       </c>
       <c r="H8">
-        <v>9.4</v>
+        <v>6.7</v>
       </c>
       <c r="I8">
         <v>0</v>
@@ -8283,7 +8274,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G16"/>
+  <dimension ref="A1:G15"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -8321,10 +8312,10 @@
         <v>76</v>
       </c>
       <c r="C2" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D2" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="E2" t="s">
         <v>7</v>
@@ -8344,10 +8335,10 @@
         <v>76</v>
       </c>
       <c r="C3" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D3" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="E3" t="s">
         <v>11</v>
@@ -8367,10 +8358,10 @@
         <v>77</v>
       </c>
       <c r="C4" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="D4" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="E4" t="s">
         <v>7</v>
@@ -8390,10 +8381,10 @@
         <v>77</v>
       </c>
       <c r="C5" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="D5" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="E5" t="s">
         <v>11</v>
@@ -8413,10 +8404,10 @@
         <v>78</v>
       </c>
       <c r="C6" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D6" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="E6" t="s">
         <v>7</v>
@@ -8436,10 +8427,10 @@
         <v>78</v>
       </c>
       <c r="C7" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D7" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="E7" t="s">
         <v>11</v>
@@ -8459,10 +8450,10 @@
         <v>79</v>
       </c>
       <c r="C8" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D8" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="E8" t="s">
         <v>11</v>
@@ -8482,10 +8473,10 @@
         <v>80</v>
       </c>
       <c r="C9" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="D9" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="E9" t="s">
         <v>7</v>
@@ -8505,10 +8496,10 @@
         <v>80</v>
       </c>
       <c r="C10" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="D10" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="E10" t="s">
         <v>11</v>
@@ -8528,10 +8519,10 @@
         <v>81</v>
       </c>
       <c r="C11" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D11" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="E11" t="s">
         <v>11</v>
@@ -8551,10 +8542,10 @@
         <v>82</v>
       </c>
       <c r="C12" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D12" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="E12" t="s">
         <v>11</v>
@@ -8574,10 +8565,10 @@
         <v>77</v>
       </c>
       <c r="C13" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="D13" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="E13" t="s">
         <v>7</v>
@@ -8597,10 +8588,10 @@
         <v>83</v>
       </c>
       <c r="C14" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D14" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="E14" t="s">
         <v>7</v>
@@ -8614,47 +8605,24 @@
     </row>
     <row r="15" spans="1:7">
       <c r="A15">
-        <v>23330051920258</v>
+        <v>23330051920264</v>
       </c>
       <c r="B15" t="s">
         <v>84</v>
       </c>
       <c r="C15" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D15" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="E15" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="F15" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="G15">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7">
-      <c r="A16">
-        <v>23330051920264</v>
-      </c>
-      <c r="B16" t="s">
-        <v>85</v>
-      </c>
-      <c r="C16" t="s">
-        <v>95</v>
-      </c>
-      <c r="D16" t="s">
-        <v>107</v>
-      </c>
-      <c r="E16" t="s">
-        <v>11</v>
-      </c>
-      <c r="F16" t="s">
-        <v>65</v>
-      </c>
-      <c r="G16">
         <v>5</v>
       </c>
     </row>
